--- a/data/logs.xlsx
+++ b/data/logs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N86"/>
+  <dimension ref="A1:N178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5034,7 +5034,6 @@
           <t>https://x.com/Dominic76968967/status/2100137444985143326</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
         <v>0</v>
       </c>
@@ -5046,14 +5045,5062 @@
           <t>multi_group</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>10:38:57</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2100172487405568135</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>startup_an_tech</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Is this a real business or just a valuation game? Raising a Series D only seven months after a Series C usually means the burn rate is very high or the founders are just grabbing cheap capital while it is available.</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>https://x.com/startup_an_tech/status/2100172487405568135</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>10:38:57</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2100172439787290842</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>ocloothinks</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Your personal brand can glow differently if a percentage of your money funds (business / startup) ideas. You are missing out on something...</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>https://x.com/ocloothinks/status/2100172439787290842</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>10:38:57</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2100171951750705239</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>ujedujo</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>دخول ثلاث تخصّصاتٍ جديدةٍ على مستوى الدّراسات العليا في الجامعة الأردنيّة في قائمة الأفضل عالميًّا ضمن تصنيف 
+QS Business Masters Rankings
+•الماجستير في الإدارة (Master's in Management): الفئة 151–200 عالميًّا.
+•الماجستير في التّسويق (Master's in Marketing): الفئة 151–200 https://t.co/YVoo2RaadH</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>https://x.com/ujedujo/status/2100171951750705239</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>10:38:57</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2100172516299812954</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>gabbytech01</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>I'm Gabriel from Nigeria 🇳🇬
+A certified API Security analyst &amp;amp; application security engineer &amp;amp; founder of @offshield_ai 
+I am going to be one of the biggest Cybersecurity YouTube content creator emerge from Nigeria 🇳🇬 (first of its kind). https://t.co/GSO5hLLZW1 (750+ https://t.co/zb4ohMdjWe</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>https://x.com/gabbytech01/status/2100172516299812954</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>10:38:57</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2100172491339522146</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>africablockfest</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>We welcome Seun Lanlege(@seunlanlege), CEO and Co-founder of Polytope Labs, to the stage in Nairobi!
+As the engineering mind behind Hyperbridge, HyperFX, and major cross-chain infrastructure bridging Polkadot and Cosmos, Seun is defining the future of interoperability, privacy https://t.co/LiE7pBERXK</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>https://x.com/africablockfest/status/2100172491339522146</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
+        <v>1</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>10:38:57</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2100172488080609720</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>bepeco</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>@DreamerBFC @Spacemonkey1964 @QuarryAli @DominicFrisby From the founder of Cuadrilla, Chris Cornelius, who were exploring UK Shale gas.
+These things are not the same. https://t.co/SYCNOngJTQ</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>https://x.com/bepeco/status/2100172488080609720</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>10:38:57</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2100172422435762264</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>kownse</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>@yongfook A UK founder based in Asia is a rare combination. What timezone do you build in — or have you just stopped tracking it?</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>https://x.com/kownse/status/2100172422435762264</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>10:38:57</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2100171763628052642</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>dmehta104</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>@GardRogne AI AUTOMATION EXPERT 🚀
+We build production-ready AI agents and automation systems that handle real business workflows—not just demos.
+From lead generation and follow-ups to customer support, document processing, recruitment, and back-office automation.
+Would love to</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>https://x.com/dmehta104/status/2100171763628052642</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>10:38:57</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2100172365187711173</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>metrox_eth</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>@menrva33 I think your best content in the last few days is when you say "I went through mistakes, I can share my insights with you", maybe your first few customers will enter this door. Inbound, niche circle first then when it's bootstrapped, you may want to grow the brand awareness with</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>https://x.com/metrox_eth/status/2100172365187711173</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>10:38:57</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2100172337362485344</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Dean1Michael</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>@rleshner This is coming from the guy who wants his previous project in the 18th decimal place. 
+COMP/USD: $0.000000000000000018
+Thanks, glad I believed in you; supported and followed you yet it was never returned while we paid for your endeavors &amp;amp; the new startup.</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>https://x.com/Dean1Michael/status/2100172337362485344</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>10:38:57</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2100172335357845925</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>aamelting</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>@ptaranat startup idea: software rendering</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>https://x.com/aamelting/status/2100172335357845925</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>10:38:57</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2100172311265456200</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>circuit_k</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>@dhh at this point you are optimizing for marketing. 2 second install is just fine 😃</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>https://x.com/circuit_k/status/2100172311265456200</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>10:38:58</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2100172305762545683</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Aljarmaqnetnews</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Pink Floyd co-founder Roger Waters publicly condemned Ed Sheeran, calling him a "prick" in a video message posted to social media. 
+The backlash follows the removal of American rapper Macklemore from Sheeran’s "Loop Tour" after Macklemore voiced solidarity with Palestinians. https://t.co/a7H9efg276</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>https://x.com/Aljarmaqnetnews/status/2100172305762545683</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>10:38:58</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2100171547226890734</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>BolakaleAb85235</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>I don’t think every crypto project needs another complicated marketing strategy.
+Sometimes you just need a clear place where projects can get attention and contributors can benefit from helping spread it.
+That’s the idea I get from AdSpace on $ROKHA
+@rokha_agent @GoblinBuilds</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>https://x.com/BolakaleAb85235/status/2100171547226890734</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>7</v>
+      </c>
+      <c r="I100" t="n">
+        <v>3</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>10:38:58</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2100172295813685754</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>retrogameboyz</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>My marketing department had some concerns. What could be the problem? 🤷 🤔 https://t.co/hWh66UKus3</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>https://x.com/retrogameboyz/status/2100172295813685754</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>10:38:58</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2100172294916358650</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>lohar_rohi4663</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>@tirthaexe Bhai jitni research tune chinese company ke name find karne me lagai utna research india ke AI startup find karne me laga deta to name pta chhal jata .like sarcasm ai, krutrim ai,qura ai,yellow. Ai etc</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>https://x.com/lohar_rohi4663/status/2100172294916358650</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>10:38:58</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2100172290935632246</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>KamilNikodem</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>@krol_tlittera To się nazywa marketing.. lemingi pójdą kupić, bo naklejka YouTubera, a właściciele zarabiają! Biznes is biznes, najlepiej zarabiać na lemingach</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>https://x.com/KamilNikodem/status/2100172290935632246</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>10:38:58</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2100172285617353111</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>WabiRaja</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>@sagebuyer Using new customers fund to solve opd customers outstanding order. Pyramid scheme.</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>https://x.com/WabiRaja/status/2100172285617353111</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>10:38:58</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2100172275702255639</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>mathiasvrb</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>@Konrad_Talik Always good to see another solo founder around here 🫡</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>https://x.com/mathiasvrb/status/2100172275702255639</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>10:38:58</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2100172260413682126</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>tutorApskl</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Hire our unique and legit services in
+#Math
+#Chem
+#essaypay
+#Paper write
+#English
+#Paper pay
+#Someone help paper
+#Case study
+#essayhelp
+#Do my homework
+#Onlineclass 
+#Religion
+#Assignment 
+#Chemistry
+#history 
+#Econometrics
+#Marketing
+#stats
+#Accounting..</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>https://x.com/tutorApskl/status/2100172260413682126</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>10:38:58</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2100172244714446939</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Libanhassan1998</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>@capitanfooturo The women did hit job, for who i dont know, disgusting? What is her marketing has to do wta financial problems, that doesnt have to do with it the rest of them while they were mumber one, she needs to stfu.</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>https://x.com/Libanhassan1998/status/2100172244714446939</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>10:38:58</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2100172221096595737</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>advancenbeyond</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>@MarketingMax Accurate data makes better decisions. Especially for ecommerce brands.</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>https://x.com/advancenbeyond/status/2100172221096595737</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>10:38:58</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2100172188867555430</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>belix_AI</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>The AI Fear Economy: When Safety Warnings Become Marketing https://t.co/ChRs9Pd4yB</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>https://x.com/belix_AI/status/2100172188867555430</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>1</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>10:38:58</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2100172188301070616</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>lublubxt</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>@matthias_mrc Yes sir! Working on marketing my language learning app right now.</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>https://x.com/lublubxt/status/2100172188301070616</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>10:38:58</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2100172181980209197</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>CalebFromDoom</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>@gghoul @tekkusai @aimcore_hq @asunoaim I’m so glad this pad only went to blue check marks and social media influencers instead of the less fortunate people the marketing claimed it was for</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>https://x.com/CalebFromDoom/status/2100172181980209197</t>
+        </is>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>10:38:58</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2100172165563744551</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>ireneadandeads</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Formation Facebook Ads gratuite
+Je viens de filmer une série de vidéos de formation en publicité Facebook... 
+Si tu as un peu de temps, tu peux regarder les 10 vidéos.
+https://t.co/ME8xuzm5Ub https://t.co/nqKt5BEz6G</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>https://x.com/ireneadandeads/status/2100172165563744551</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>1</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>10:38:58</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2100172118738530351</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>DanielAkpa4449</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>People don't wake up thinking:
+"I need to buy your product."
+They wake up thinking about their problems.
+Your marketing should connect your solution to those problems.</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>https://x.com/DanielAkpa4449/status/2100172118738530351</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>10:38:59</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2100172097083285531</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>axiomwave_xbt</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>@WazzCrypto Launch tooling has become part of the token’s pitch, not just backend plumbing
+Contract metadata is now marketing that traders can audit before buying</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>https://x.com/axiomwave_xbt/status/2100172097083285531</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>10:38:59</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2100172088267186493</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>dailymattr_news</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>NCPCR has summoned Meta India's MD again over alleged CSEAM ads, with a hearing set for 16 September, following a report on Instagram ads allegedly promoting child sexual abuse material. Meta has since begun reporting such cases to India's Cyber Crime Coordination Centre. NCPCR https://t.co/r6i8STUSRa</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>https://x.com/dailymattr_news/status/2100172088267186493</t>
+        </is>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>SENSITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>10:38:59</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2100172046218965035</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>GemChaserSOL</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>🧠 DEXSCREENER MARKETING INTEL
+Asset: Aqua | Ticker: $AQUA
+Paid Push Status: Yes
+📈 WALLET MATRIX:
+  ↳ Smart Address Activity: 2
+  ↳ Bundler Team Clusters: 93
+  ↳ Fresh Degen Wallets: 54
+🚨 RISK FACTOR EVAL:
+  ↳ Top 10 Control Rate: 30.6%
+  ↳ System Rug Score: 0%
+🎯 CA:</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>https://x.com/GemChaserSOL/status/2100172046218965035</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>10:38:59</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2100171996726239397</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>philmccarroll</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>@Rolnikov @cjsnowdon H&amp;amp;M clothes aren't meant to last? Do they state this in their marketing?!</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>https://x.com/philmccarroll/status/2100171996726239397</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>10:38:59</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2100171994994246025</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>njkjh00</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>@Nobir001 @sleepagotchi Snoring flag becomes a character reaction Marketing team ate on that one</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>https://x.com/njkjh00/status/2100171994994246025</t>
+        </is>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>10:38:59</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>2100171974223790408</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>AzouilleEcom</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>LES PUBS SUR ETSY :
+Pour rentabiliser vos ads, il faut savoir lire vos stats d'ADS MAIS AUSSI vos stats shop au global.
+Voici un exemple sur 5 listings avec des stats très différentes ⬇️
+Le 1er :✅   
+C'est le best seller qui se vend 2 à 6x par jour.
+Les stats pubs semblent https://t.co/loCf5qTffQ</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>https://x.com/AzouilleEcom/status/2100171974223790408</t>
+        </is>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>10:38:59</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2100171957878894846</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>raghavwadhwa</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>But here's the interesting part:
+Around ₹371 Cr is intended largely towards lease liabilities of Experience Centres and back-end offices.
+Another ₹139 Cr is earmarked for sales &amp;amp; marketing.
+So a meaningful portion of fresh capital is being deployed to support and scale the</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>https://x.com/raghavwadhwa/status/2100171957878894846</t>
+        </is>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
+        <v>1</v>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>10:38:59</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2100171946768101529</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>MuktharBuilds</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>@matthias_mrc Most devs forget marketing is half the product’s success.</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>https://x.com/MuktharBuilds/status/2100171946768101529</t>
+        </is>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>10:38:59</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2100172502605468035</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>__adwoasefah</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>“i want single people to stop breathing”
+hellei???😭</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>https://x.com/__adwoasefah/status/2100172502605468035</t>
+        </is>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>10:38:59</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2100172410376925586</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>VickyRMadrid</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Vamos a fingir sorpresa con los corruptos de @ctarfef y @rfef cada día louzan y el cerdo del cta demuestran la basura corrupta q son. Espero q así sea su caída para disfrutarla. Total los cerdos corruptos caen y el Madrid es tan grande q continúa</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>https://x.com/VickyRMadrid/status/2100172410376925586</t>
+        </is>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>10:38:59</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2100171759475638517</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Soumajit1978</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>PNGS Reva Diamond Jewellery beyond Q1 FY27 numbers
+PNGS Reva is a natural diamond jewellery retailer backed by the 194+ year P. N. Gadgil &amp;amp; Sons legacy. The business currently operates mainly through shop-in-shop (SIS) counters inside PNGS stores, giving it existing footfall,</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>https://x.com/Soumajit1978/status/2100171759475638517</t>
+        </is>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>10:38:59</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>2100171761497387433</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>girlincrypto007</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>@MadMaxx_eth @fomo They need to fire their email marketing guy loool</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>https://x.com/girlincrypto007/status/2100171761497387433</t>
+        </is>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>10:38:59</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>2100172379661951314</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Soulmate889</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>@14EmDubYa FIRE 🔥</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>https://x.com/Soulmate889/status/2100172379661951314</t>
+        </is>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>10:38:59</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>2100172376700821525</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>arnaudmercier</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>L'ÉDITO POLITIQUE DE GUILLAUME DARET - Quelle position vis à vis de LFI pour les candidats à la primaire PS-Place publique ?  https://t.co/LkCXrw1SM3 https://t.co/ejlQFqlDaf</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>https://x.com/arnaudmercier/status/2100172376700821525</t>
+        </is>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>10:38:59</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2100171713938157600</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>gulshaniyer</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>@malpani ++ I believe I could help vc funds with technical paid ads due diligence of epic quality.(people + ai) Any way I could help your ngo. Happy to.</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>https://x.com/gulshaniyer/status/2100171713938157600</t>
+        </is>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>10:39:00</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>2100172334703264201</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>heis_raye</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>@simonsquibb To become a successful entrepreneur and I sell audio gadgets and want to become the best distributor in Africa</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>https://x.com/heis_raye/status/2100172334703264201</t>
+        </is>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>10:39:00</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>2100172333067706412</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Goemon_CLOSEPA</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Jumperは、ブリッジアグリゲーターとして突き抜けて欲しかったなぁ。TGEをして、その後も成長できそうだけどね。 Hyperliquid コードのPerpDEXでもリリースするのかな。ネオバンクとか。</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>https://x.com/Goemon_CLOSEPA/status/2100172333067706412</t>
+        </is>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>10:39:00</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>2100172332706713668</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>FantasticMrSol</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>@James7Holland What we need is:
+Less tax for companies across the board. Like seriously changes 50% less tax.
+no unions inside EU!
+Tax free crypto!
+Embrace AI with no regulations!
+Be competitive in frontier tech like crypto and AI. 
+Make EU Attractive for high skilled workers to move here.</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>https://x.com/FantasticMrSol/status/2100172332706713668</t>
+        </is>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>10:39:00</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>2100171686675091825</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>NewsStar69313</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Mrig Sight Media Strengthens Digital Marketing Solutions As AI Transforms How Consumers Discover Brands.
+#Mrig #Sight #Media #Strengthens #Digital #Marketing #Solutions #As #AI #Transforms #Consumers #Discover #Brands #Noida 
+https://t.co/Pb6qW2lvCn https://t.co/aTlFy5y56m</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>https://x.com/NewsStar69313/status/2100171686675091825</t>
+        </is>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>10:39:00</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>2100172304248697121</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>AvinashDalvi_</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>@tapasadhikary Long ago I tried but didn’t get traction. Most of my freelancing was via my network and through ex-managers or CTOs. Through Freelancer I got many clients even 15 years back.</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>https://x.com/AvinashDalvi_/status/2100172304248697121</t>
+        </is>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>10:39:00</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>2100172273256894659</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>avcanthony_</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>How to write hooks that STOP the scroll!
+This is how you can write hooks that drop your CPMs from $300 to $15 in the USA and your CPCs from $10 to $0.50.
+And while lowering CPC and CPM doesn't guarantee performance. It does increase the visibility on the rest of the copy and https://t.co/O85hpihbFF</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>https://x.com/avcanthony_/status/2100172273256894659</t>
+        </is>
+      </c>
+      <c r="H134" t="n">
+        <v>1</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>10:39:00</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>2100172285214687445</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Dexteroffender</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>@enfueradejuego Puro sentido común. A ver qué iluminado viene a decirte "no te quejes de los árbitros" 
+Es cabreante cómo baja los brazos el equipo en la 2P, y al mismo tiempo, arbitraje al más puro estilo CTA, dejando pegar al contrario sin castigo.
+Las dos cosas son ciertas.</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>https://x.com/Dexteroffender/status/2100172285214687445</t>
+        </is>
+      </c>
+      <c r="H135" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>10:39:00</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>2100172273130893576</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>MadKingPenguine</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>@bitbloxt @commontruth_ @owenjonesjourno Stop trying to gaslight people, no one is buying it.
+If every stereotype of a jew in history has looked like that wouldn't you say it's a fair assumption to make?
+If he wasn't trying to portray a stereotype of a jew, what was he trying to portray?</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>https://x.com/MadKingPenguine/status/2100172273130893576</t>
+        </is>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>10:39:00</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>2100172270035423276</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>kitsunedevs</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>@bizdevelo three university exits is a solid track record for an entrepreneur
+most people cant even commit to quitting once</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>https://x.com/kitsunedevs/status/2100172270035423276</t>
+        </is>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>10:39:00</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>2100172240784662985</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>kcmgallo905</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>$HBAN | 2026 Outlook Revised
+Huntington now expects FY2026 net interest income growth of ~35%, down from 39%–43%, while implied revenue growth was cut to ~34% from ~37%.
+Share buybacks were raised to $1.3B–$1.4B.
+#HBAN #Banks #Stocks https://t.co/k85LXKAkMS</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>https://x.com/kcmgallo905/status/2100172240784662985</t>
+        </is>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>10:39:00</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>2100172229850141099</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>kanseian_</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>HubSpotのAEOツール月額900ドルか。
+https://t.co/KglwhRHXRC</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>https://x.com/kanseian_/status/2100172229850141099</t>
+        </is>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>10:39:00</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2100172223667450326</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>realibdouglas</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>@sandixdesigns You're welcome 👊🏾😎</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>https://x.com/realibdouglas/status/2100172223667450326</t>
+        </is>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>10:39:00</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2100172205577347123</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>otagrosario</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>@martaminujin no me inspira arte, no podemos llamar arte a todo .No es Andy Warhol.Excentrico no signica arte.</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>https://x.com/otagrosario/status/2100172205577347123</t>
+        </is>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>10:39:01</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2100171561156104204</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Tannermullen</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>What if your “bad leads” aren’t actually bad leads?
+I sat down with Jacob Ransom to break down why the lead source might not be the problem — the real issue could be how much trust you’ve built before the homeowner ever reaches out.
+🎙️ Full episode is available now on YouTube &amp;amp; https://t.co/Bf4UVEEvnE</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>https://x.com/Tannermullen/status/2100171561156104204</t>
+        </is>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>10:39:01</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2100172189043745208</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>MrBrjan</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>@AdityaShips those numbers are impressive, especially the 22% paywall conversion rate</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>https://x.com/MrBrjan/status/2100172189043745208</t>
+        </is>
+      </c>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>10:39:01</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2100172168592060888</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>DanielAkpa4449</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>If your content isn't getting engagement, don't immediately delete the account.
+Study:
+The hook.
+The topic.
+The timing.
+The format.
+The CTA.
+Then improve.</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>https://x.com/DanielAkpa4449/status/2100172168592060888</t>
+        </is>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>10:39:01</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2100172168394834048</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>VictorAgbo_</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>3 years ago, I got two likes on my first LinkedIn post. Mine and that of my classmate in university😂
+At the time, I didn’t know what I was doing there, all I knew was that I wanted to sell my graphic design service and make money while in school so I don’t have to call home for https://t.co/I8LP1hvYN6</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>https://x.com/VictorAgbo_/status/2100172168394834048</t>
+        </is>
+      </c>
+      <c r="H145" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>10:39:01</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2100172138200105354</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Chrisdaramola_</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>@ChiomaFavour0 You should blur her face and, preferably, the name of her school as well. She’s still a minor, and scavengers (especially those unintelligent bloggers) could take undue advantage of the information visible in the picture.</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>https://x.com/Chrisdaramola_/status/2100172138200105354</t>
+        </is>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>10:39:01</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2100172134295183836</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>realibdouglas</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>@_VidVisualz 🙏🏾💙</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>https://x.com/realibdouglas/status/2100172134295183836</t>
+        </is>
+      </c>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>10:39:01</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2100172132370329869</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>takumiautowork</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>「会社員の副業＝仕事終わりにもう一度働く」を変えられる可能性があるのがPPCだと思ってる。
+最初は普通にやることある。
+案件を探す。キーワードを考える。記事を書く。広告を設定する。
+しかも広告費を使う以上、赤字になることだってある。
+でも面白いのは、その先。
+記事を作る。</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>https://x.com/takumiautowork/status/2100172132370329869</t>
+        </is>
+      </c>
+      <c r="H148" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>10:39:01</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2100171499441197188</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>halaldigital90</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Want to learn digital marketing but don't know where to start?
+Don't learn everything at once.
+Start with: 1 skill → 1 audience → 1 problem → 1 solution.
+Keep it simple. 🚀</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>https://x.com/halaldigital90/status/2100171499441197188</t>
+        </is>
+      </c>
+      <c r="H149" t="n">
+        <v>0</v>
+      </c>
+      <c r="I149" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>10:39:01</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2100172092457271524</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>takumiautowork</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>PPCアフィリエイトって、実は「広告で稼ぐ副業」じゃなくて「数字を改善する副業」なんよね。
+広告を出して終わりじゃない。
+100人来て何人売れた？
+1人集めるのにいくらかかった？
+どの検索ワードから売れた？
+広告費を引いたらいくら残った？
+この数字を見て、悪いところを1個ずつ直していく。</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>https://x.com/takumiautowork/status/2100172092457271524</t>
+        </is>
+      </c>
+      <c r="H150" t="n">
+        <v>0</v>
+      </c>
+      <c r="I150" t="n">
+        <v>0</v>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>10:39:01</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2100172071859027990</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>sponton66</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>@JGuzman1e DEPORT</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>https://x.com/sponton66/status/2100172071859027990</t>
+        </is>
+      </c>
+      <c r="H151" t="n">
+        <v>0</v>
+      </c>
+      <c r="I151" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>10:39:01</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2100172053517353255</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>takumiautowork</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>「毎日投稿しない」「顔出ししない」「フォロワーを増やさない」でもできるアフィリエイトはある。
+ここだけ聞くと怪しく感じると思う。
+でも仕組みは普通にシンプル。
+Googleで商品を探す人がいる。
+その検索結果に広告を出す。
+広告から自分の記事に来てもらう。</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>https://x.com/takumiautowork/status/2100172053517353255</t>
+        </is>
+      </c>
+      <c r="H152" t="n">
+        <v>0</v>
+      </c>
+      <c r="I152" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>10:39:01</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2100172014065713219</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>takumiautowork</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>副業で一番仕組み化したいのって、実は「作業」より「集客」だと思う。
+商品があっても、人が来なかったら売れない。
+だからSNS投稿する。YouTube撮る。ブログ書く。営業する。
+気づいたら、副業時間のほとんどが「人を集める作業」になる。
+そこで発想を変える。
+集客そのものにお金を払う。</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>https://x.com/takumiautowork/status/2100172014065713219</t>
+        </is>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>10:39:01</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>2100171996004831666</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Onekey4l_</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>New content creator</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>https://x.com/Onekey4l_/status/2100171996004831666</t>
+        </is>
+      </c>
+      <c r="H154" t="n">
+        <v>0</v>
+      </c>
+      <c r="I154" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>10:39:02</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>2100171962790121688</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>TaionEnjoyer</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>@Mine_Ggamer @goofnator some were saying his dad did set up an ad campaign before and showed him how to do, somehow expecting the kid to not do it again</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>https://x.com/TaionEnjoyer/status/2100171962790121688</t>
+        </is>
+      </c>
+      <c r="H155" t="n">
+        <v>0</v>
+      </c>
+      <c r="I155" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>10:39:02</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>2100171938844836108</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>raghavwadhwa</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Revenue growth hasn't been equally impressive
+Revenue:
+🔹FY24: ₹504 Cr
+🔹FY25: ₹490 Cr
+🔹FY26: ₹558 Cr
+Despite AOV increasing 66%, revenue grew only around 11% over FY24–FY26.
+And revenue actually declined in FY25.
+For a company targeting one of India's fastest-premiumising</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>https://x.com/raghavwadhwa/status/2100171938844836108</t>
+        </is>
+      </c>
+      <c r="H156" t="n">
+        <v>0</v>
+      </c>
+      <c r="I156" t="n">
+        <v>1</v>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>10:39:02</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>2100171954368204902</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>daksha__rants</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>My college asked us to draw CRO with pencil then colour it with sketch pen :-)</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>https://x.com/daksha__rants/status/2100171954368204902</t>
+        </is>
+      </c>
+      <c r="H157" t="n">
+        <v>0</v>
+      </c>
+      <c r="I157" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>10:39:02</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>2100171865612263836</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>EmmaBlakeHQ</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>If you’re curious and just need a place to start, I built a site for exactly that. ☕️
+Take the quick quiz and in about 30 seconds you can see which coffee capsules or machines fit your taste and habits best. #Nespresso
+Start here 👇
+https://t.co/xPWwXf2RGR</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>https://x.com/EmmaBlakeHQ/status/2100171865612263836</t>
+        </is>
+      </c>
+      <c r="H158" t="n">
+        <v>0</v>
+      </c>
+      <c r="I158" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>10:39:02</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>2100171796612035029</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>chetaslua</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Claude built a full landing page in one shot it lives on localhost. nobody can open it.
+Your agent finishes the work. Showly gives it a real link you can send.
+&amp;gt; connect the agent you already use &amp;lt; Claude Code / Cursor / Codex &amp;gt;
+&amp;gt; private preview first, so you see it before https://t.co/iQeCPekIC2</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>https://x.com/chetaslua/status/2100171796612035029</t>
+        </is>
+      </c>
+      <c r="H159" t="n">
+        <v>3</v>
+      </c>
+      <c r="I159" t="n">
+        <v>2</v>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>10:39:02</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2100171853973295426</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>iiam_Akshay</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>$CRO is preparing for an ecosystem rebrand.
+Cronos Ult is scheduled for September 17, putting the network’s branding and ecosystem direction back into focus.
+Rebrands can signal a broader shift in how projects position their next growth phase.
+#CRO #Cronos #Web3 #Crypto</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>https://x.com/iiam_Akshay/status/2100171853973295426</t>
+        </is>
+      </c>
+      <c r="H160" t="n">
+        <v>0</v>
+      </c>
+      <c r="I160" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>10:39:02</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>2100171853125849102</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>COBRA99826637</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Cobra will be Live shortly over on both          
+Twitch https://t.co/BsUVLSR7a7           
+YouTube : https://t.co/jYlD0NnmpN 
+1.30 Update is First Look! https://t.co/DdOXWguP5N</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>https://x.com/COBRA99826637/status/2100171853125849102</t>
+        </is>
+      </c>
+      <c r="H161" t="n">
+        <v>0</v>
+      </c>
+      <c r="I161" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>10:39:02</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>2100171782829294022</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>EricLangenstein</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>@nemethcontrast @RTLsportsbe @PhilippeGilbert Qu'est ce qui est faux dans sa méforme post Tour qui entraine son changement de programme décidé avec sa team et son engagement auprès de ses employeurs de disputer Cro Race ?</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>https://x.com/EricLangenstein/status/2100171782829294022</t>
+        </is>
+      </c>
+      <c r="H162" t="n">
+        <v>0</v>
+      </c>
+      <c r="I162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>10:39:02</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>2100171774269010161</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>0xXEasy</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Ketika sedang pakai seragam gagah benar CPM Paspampres.
+Tapi ketika pulang kerumah, seragam pangkat kalah sama perintah simboknya.
+Dirumah disuruh panggul jemur gabah sama simboknya tetap siap gak bantah, benar-benar anak berbakti si Agus.</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>https://x.com/0xXEasy/status/2100171774269010161</t>
+        </is>
+      </c>
+      <c r="H163" t="n">
+        <v>0</v>
+      </c>
+      <c r="I163" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>10:39:02</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>2100171753850806347</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>echo24cz</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Poslanci mají brzy začít projednávat konec poplatků za ČT a ČRo. Verdikt padne zítra 
+https://t.co/UNG4Gzs1Jc</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>https://x.com/echo24cz/status/2100171753850806347</t>
+        </is>
+      </c>
+      <c r="H164" t="n">
+        <v>0</v>
+      </c>
+      <c r="I164" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>10:39:02</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>2100171710645608785</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>hoodsbrokenhome</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>$LUXE | FY2026 Q4 Results
+LuxExperience reported €663.8M in Q4 net sales, up 18.7% YoY on a consolidated IFRS basis.
+Mytheresa led with 10.2% constant-currency growth. FY2027 guidance calls for mid-to-high single-digit sales growth and a 2%–3% adjusted EBITDA margin.
+#LUXE https://t.co/MUm8CZpmBJ</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>https://x.com/hoodsbrokenhome/status/2100171710645608785</t>
+        </is>
+      </c>
+      <c r="H165" t="n">
+        <v>2</v>
+      </c>
+      <c r="I165" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>10:39:02</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>2100171718086275574</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>takumiautowork</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>SNSで1000人集めるより「今その商品を探してる10人」を集める方が大事なこともある。
+例えば「英会話」と発信してフォロワーを1000人集める。
+その1000人全員が今、英会話を申し込みたいとは限らない。
+でも、
+「○○英会話 料金」
+「○○英会話 口コミ」
+「○○英会話 比較」</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>https://x.com/takumiautowork/status/2100171718086275574</t>
+        </is>
+      </c>
+      <c r="H166" t="n">
+        <v>0</v>
+      </c>
+      <c r="I166" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>10:39:03</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>2100171718103081167</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>tita_titania_</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>@sloppypoppy Di bsd lagi banyak buka terus temen2 gw diajakin..yang mana temen2 gw ini content creator semua.</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>https://x.com/tita_titania_/status/2100171718103081167</t>
+        </is>
+      </c>
+      <c r="H167" t="n">
+        <v>0</v>
+      </c>
+      <c r="I167" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>10:39:03</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>2100171711169610137</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>NJPHINSFANATIC</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>@IsabellaRedjai The hypocrisy we are seeing regarding this Sydney Sweeney Ad campaign is rich.</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>https://x.com/NJPHINSFANATIC/status/2100171711169610137</t>
+        </is>
+      </c>
+      <c r="H168" t="n">
+        <v>0</v>
+      </c>
+      <c r="I168" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>10:39:03</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>2100171675275038798</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>__solo69__</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Finally done reading about FlashAttention 4, and this one made the hardware–software connection much more obvious to me.
+FA3 was built around Hopper’s strengths, but FA4 is redesigned around Blackwell’s new bottlenecks. Tensor cores became much faster, so things like softmax, https://t.co/TbdBKSdCLN</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>https://x.com/__solo69__/status/2100171675275038798</t>
+        </is>
+      </c>
+      <c r="H169" t="n">
+        <v>1</v>
+      </c>
+      <c r="I169" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>10:39:03</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>2100171647647089153</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>takumiautowork</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>アフィリエイト＝ブログを100記事書くもの、だと思ってる人は一回PPCを知ってほしい。
+検索上位を狙うなら、記事を書いてサイトを育てて、Googleから評価されるまで待つ必要がある。
+でも検索結果の上には「スポンサー」と書かれた広告枠がある。</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>https://x.com/takumiautowork/status/2100171647647089153</t>
+        </is>
+      </c>
+      <c r="H170" t="n">
+        <v>0</v>
+      </c>
+      <c r="I170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>10:39:03</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>2100171642609729614</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>sponton66</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>@Sammy_canada2 🖕STINKY GTFO. THE “racist” remarks has only just began  STINKY.</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>https://x.com/sponton66/status/2100171642609729614</t>
+        </is>
+      </c>
+      <c r="H171" t="n">
+        <v>0</v>
+      </c>
+      <c r="I171" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>10:39:03</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>2100171629703667877</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Ary_AntiPT</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Showmicio 
+https://t.co/kH0LOYx8yR https://t.co/e7OAJQmEZj</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>https://x.com/Ary_AntiPT/status/2100171629703667877</t>
+        </is>
+      </c>
+      <c r="H172" t="n">
+        <v>0</v>
+      </c>
+      <c r="I172" t="n">
+        <v>0</v>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>10:39:03</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>2100171594635374714</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>happy2021japan</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>最近、気づいたことがあります。
+ChatGPTは、
+記事を作るためだけの道具じゃない。
+タイトル。
+冒頭の2行。
+見出し。
+CTA。
+X告知文。
+全部相談できます。
+一人で考えて止まるより、
+AIと一緒に考える。
+それだけで、
+かなり進みやすくなりました😊
+#ChatGPTライティング #AI活用</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>https://x.com/happy2021japan/status/2100171594635374714</t>
+        </is>
+      </c>
+      <c r="H173" t="n">
+        <v>0</v>
+      </c>
+      <c r="I173" t="n">
+        <v>0</v>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>10:39:03</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>2100171587978707259</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Gobalo20</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Web corporativa: construye marca.
+Landing page: concentra la conversión.
+No sirven para lo mismo.
+#Góbalo #DiseñoWeb #LandingPage https://t.co/a0HXEdMMUT</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>https://x.com/Gobalo20/status/2100171587978707259</t>
+        </is>
+      </c>
+      <c r="H174" t="n">
+        <v>0</v>
+      </c>
+      <c r="I174" t="n">
+        <v>0</v>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>10:39:03</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>2100171558060802486</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>ottilves</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>yesterday, we passed 1,000 organisations using our product at https://t.co/coMfmrHOSo. 
+here's how we got here: 
+1. good timing 
+we were the first to market in may with when we launched our simple artifacts product, almost exactly when @trq212 started talking how they use them</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>https://x.com/ottilves/status/2100171558060802486</t>
+        </is>
+      </c>
+      <c r="H175" t="n">
+        <v>0</v>
+      </c>
+      <c r="I175" t="n">
+        <v>1</v>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>10:39:03</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>2100171548418334927</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>takumiautowork</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>自分が会社で働いてる9〜18時に、副業の「集客」まで止める必要ないんよね。
+普通の副業だと、自分が動く。
+営業する。投稿する。DMする。作業する。
+止まったら売上につながる動きも止まりやすい。
+でも広告なら、設定した範囲で自分が仕事してる間にも動かせる。</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>https://x.com/takumiautowork/status/2100171548418334927</t>
+        </is>
+      </c>
+      <c r="H176" t="n">
+        <v>0</v>
+      </c>
+      <c r="I176" t="n">
+        <v>0</v>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>10:39:03</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>2100171368968954090</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>EmmaBlakeHQ</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Do you know you might already be a high-intent capsule coffee machine buyer? ☕️
+Sometimes the problem isn’t wanting the machine — it’s not knowing enough to feel confident choosing one.
+That’s why the Nespresso boutique experience works so well: you see the machine, understand</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>https://x.com/EmmaBlakeHQ/status/2100171368968954090</t>
+        </is>
+      </c>
+      <c r="H177" t="n">
+        <v>0</v>
+      </c>
+      <c r="I177" t="n">
+        <v>1</v>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>10:39:03</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>2100171382734684530</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>adrianflynn</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>@KarlBrophy @Nick_Wellings They will decide and they care more about their future mortgage rates and NHS and pensions and CTA and even the football team and if Asda will stay open etc. Lots of questions people want answers on before any vote.  
+Saying the Irish Government need a white paper is a cop out.</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>https://x.com/adrianflynn/status/2100171382734684530</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="n">
+        <v>0</v>
+      </c>
+      <c r="I178" t="n">
+        <v>0</v>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr">
         <is>
           <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
         </is>

--- a/data/logs.xlsx
+++ b/data/logs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N178"/>
+  <dimension ref="A1:N264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10081,7 +10081,6 @@
           <t>https://x.com/adrianflynn/status/2100171382734684530</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr"/>
       <c r="H178" t="n">
         <v>0</v>
       </c>
@@ -10093,16 +10092,4686 @@
           <t>multi_group</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
       </c>
-      <c r="M178" t="inlineStr"/>
       <c r="N178" t="inlineStr">
         <is>
           <t>Error code: 401 - {'error': {'message': 'Incorrect API key provided: AQ.Ab8RN*****************************************PQsA. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'param': None, 'code': 'invalid_api_key'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>10:52:59</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>2100175875878633970</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>redbat75</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>If every experience ends in the founder’s head, the founder is learning.
+The business isn’t.</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>https://x.com/redbat75/status/2100175875878633970</t>
+        </is>
+      </c>
+      <c r="H179" t="n">
+        <v>0</v>
+      </c>
+      <c r="I179" t="n">
+        <v>0</v>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>10:52:59</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>2100175971961704564</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Lang_Enthused</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>@DaffyGiving @adamnash @DaffyGiving @adamnash Classic founder answer 😄 fair. My hunch is the donation rate chart alone moves the needle, nobody wants to stare at a 0%. Would love to see aggregate before/after numbers in a year</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>https://x.com/Lang_Enthused/status/2100175971961704564</t>
+        </is>
+      </c>
+      <c r="H180" t="n">
+        <v>0</v>
+      </c>
+      <c r="I180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>10:53:00</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>2100175966081290326</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>SulkaMike</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Interesting hand we've been dealt this Wednesday morning. Google shipped a voice agent that can keep talking while it thinks, and a startup founded by one of the people behind the original ChatGPT research shipped an AI model that basically refuses to talk at all.
+Gemini 3.8</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>https://x.com/SulkaMike/status/2100175966081290326</t>
+        </is>
+      </c>
+      <c r="H181" t="n">
+        <v>0</v>
+      </c>
+      <c r="I181" t="n">
+        <v>0</v>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>10:53:00</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>2100175961962504383</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Dannydev784</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>@berkaybakac Would be happy to connect. I am the solo founder of https://t.co/2JHQiJ6L1X Let’s grow together!</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>https://x.com/Dannydev784/status/2100175961962504383</t>
+        </is>
+      </c>
+      <c r="H182" t="n">
+        <v>0</v>
+      </c>
+      <c r="I182" t="n">
+        <v>0</v>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>10:53:00</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>2100175922305327546</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>TechMoran</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Egyptian payments startup Zeal has raised $10M to take its technology global.The fresh capital will help the company roll out across more than 4 million payment terminals covered by signed contracts.
+That takes Zeal’s total funding to $14M.
+https://t.co/ykcumcToMq https://t.co/foQHfhPN5R</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>https://x.com/TechMoran/status/2100175922305327546</t>
+        </is>
+      </c>
+      <c r="H183" t="n">
+        <v>0</v>
+      </c>
+      <c r="I183" t="n">
+        <v>0</v>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>10:53:00</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>2100175906438299845</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>semiii</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Startup Village Borneo was a super success. We got lots of budding talent from US, europe, singapore, vietnam, nepal, korea, india, indonesia, canada, ukraine, russia, and of course, West Malaysia.
+Check out all of their projects in the Borneo Builders Directory. https://t.co/2UBnG0ivjH</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>https://x.com/semiii/status/2100175906438299845</t>
+        </is>
+      </c>
+      <c r="H184" t="n">
+        <v>0</v>
+      </c>
+      <c r="I184" t="n">
+        <v>0</v>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>10:53:00</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>2100175896145531266</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Mudhaxk</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>@rant_zine Hey, solo founder building here too. One of our early users (GreatmindsNG) cut about $90/month after moving backend, storage and email onto one platform - worth a look if you're juggling separate vendors for that stuff. https://t.co/L4AC6nUiDS</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>https://x.com/Mudhaxk/status/2100175896145531266</t>
+        </is>
+      </c>
+      <c r="H185" t="n">
+        <v>1</v>
+      </c>
+      <c r="I185" t="n">
+        <v>0</v>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>10:53:00</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>2100175903217070532</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>kelvonhimself</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>$0 → $100k/day - Day 83
+First day after being back in stock, feeling that back in stock hangover way early this time. Ads spent at a terrible efficiency which sucks.
+My quiz funnel is working okay for now, further optimization is needed. Currently sitting at 20% completion https://t.co/GznAOwOkSH</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>https://x.com/kelvonhimself/status/2100175903217070532</t>
+        </is>
+      </c>
+      <c r="H186" t="n">
+        <v>0</v>
+      </c>
+      <c r="I186" t="n">
+        <v>0</v>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>10:53:00</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2100175890789384323</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>RichSementa</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Palantir Co-Founder: Doomer Narratives on AI Are Ridiculous
+@JTLonsdale: So there’s lots of risks and there’s lots of upside but I think the doomer narratives are ridiculous and we should be embracing the industrial revolution."
+“Same thing they did with climate change and https://t.co/5MeAkFlWDj</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>https://x.com/RichSementa/status/2100175890789384323</t>
+        </is>
+      </c>
+      <c r="H187" t="n">
+        <v>0</v>
+      </c>
+      <c r="I187" t="n">
+        <v>0</v>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>10:53:00</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2100175838788403496</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>REOComms</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Ivorian group Kaydan plans to invest FCFA 500bn in fibre, housing and construction by 2030, while expanding into tech, cybersecurity and mining services. Founder @alainyaokouadio told us how this can create jobs and build Ivorian champions. #CotedIvoire 
+@FortuneMagazine https://t.co/mtmf5s8F3P</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>https://x.com/REOComms/status/2100175838788403496</t>
+        </is>
+      </c>
+      <c r="H188" t="n">
+        <v>0</v>
+      </c>
+      <c r="I188" t="n">
+        <v>0</v>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>10:53:00</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2100175801769394657</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>NLAB_s</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>@giutheginger Solo Founder from Bcn too, Let’s connect</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>https://x.com/NLAB_s/status/2100175801769394657</t>
+        </is>
+      </c>
+      <c r="H189" t="n">
+        <v>0</v>
+      </c>
+      <c r="I189" t="n">
+        <v>0</v>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>10:53:00</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2100175795524087850</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Adom1063fm</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>NDC is doing well with regards to the macro-economy, but can they sustain it? - Alan Kyerematen (Founder and Leader, United Party)
+#DwasoNsem https://t.co/z7gOO6xNcP</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>https://x.com/Adom1063fm/status/2100175795524087850</t>
+        </is>
+      </c>
+      <c r="H190" t="n">
+        <v>0</v>
+      </c>
+      <c r="I190" t="n">
+        <v>0</v>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>10:53:01</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2100175779975819664</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Dannyzem3</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>@massivefanNWO @doveyymargeauxx I'm not talking about the donation to Reform.
+As the founder gets to set the charity's governing document, he can choose how trustees are selected, and select those who will pay him a wage. The £25m bank asset slowly becomes a wage expense, the books are balanced, but immorally.</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>https://x.com/Dannyzem3/status/2100175779975819664</t>
+        </is>
+      </c>
+      <c r="H191" t="n">
+        <v>0</v>
+      </c>
+      <c r="I191" t="n">
+        <v>0</v>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>10:53:01</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>2100175765430006255</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>prettyinpiece</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>I’m happy to officially announce to y’all that, with my ₦5,500, I am now in partnership with Dangote Group of Companies as a shareholder and co-founder. 
+Together, we’re working toward a better Nigeria! 🇳🇬 https://t.co/T4MbMw9vLt</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>https://x.com/prettyinpiece/status/2100175765430006255</t>
+        </is>
+      </c>
+      <c r="H192" t="n">
+        <v>0</v>
+      </c>
+      <c r="I192" t="n">
+        <v>0</v>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>10:53:01</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2100175760061575250</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>geewon123</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>May Marvel film din kasi yata sila na kasabayan. Sana talaga maging successful kahit through word of mouth nalang yung marketing.</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>https://x.com/geewon123/status/2100175760061575250</t>
+        </is>
+      </c>
+      <c r="H193" t="n">
+        <v>0</v>
+      </c>
+      <c r="I193" t="n">
+        <v>0</v>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>10:53:01</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>2100175734622802027</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>carteiravazia</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>@burkov Eu tinha o mesmo pensamento que você, só que peguei costume de usar outras redes e deixei de usar o Facebook.
+Porém, não creio que a rede está morta, vejo muito conteúdo postado lá, tanto do feed páginas com dezenas de milhares de curtidas, pessoas, grupos, marketing place etc.</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>https://x.com/carteiravazia/status/2100175734622802027</t>
+        </is>
+      </c>
+      <c r="H194" t="n">
+        <v>0</v>
+      </c>
+      <c r="I194" t="n">
+        <v>0</v>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>10:53:01</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2100175652544496020</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>T_E_Syndrome</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>@gummibear737 and they would be marketing that.... selling to everyone.</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>https://x.com/T_E_Syndrome/status/2100175652544496020</t>
+        </is>
+      </c>
+      <c r="H195" t="n">
+        <v>0</v>
+      </c>
+      <c r="I195" t="n">
+        <v>0</v>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>10:53:01</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2100175616503120211</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>CdScissor</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>@Littleotomedius They're just really good at marketing, and sometimes it's warranted it's hard to argue against actual functional public transport.
+But I'd be lying if I said I'm not side-eyeing any questionable move the country makes. I know they've got history.
+Cute drawings tho</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>https://x.com/CdScissor/status/2100175616503120211</t>
+        </is>
+      </c>
+      <c r="H196" t="n">
+        <v>0</v>
+      </c>
+      <c r="I196" t="n">
+        <v>0</v>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>10:53:01</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2100175612413390976</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>miroburn</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Marketing z AI jest wyzwaniem.
+Ale jak się przepali odpowiednio dużo tokenów, doda dużo bramek i zrobi się kilka wtop, to nagle system zaczyna działać jak marzenie.
+Mój system składa się aktualnie z 18 podsystemów, które próbuję zrobić w 1 automat.
+Na razie najtrudniejsze https://t.co/Ryhsx1iHUu</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>https://x.com/miroburn/status/2100175612413390976</t>
+        </is>
+      </c>
+      <c r="H197" t="n">
+        <v>0</v>
+      </c>
+      <c r="I197" t="n">
+        <v>0</v>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>10:53:01</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2100175600618975665</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>asaaseradio995</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>It is important to produce your own energy in your own country because it moves you from energy importation to energy sovereignty - Dr Riverson oppong- CEO of Chamber of oil Marketing Companies 
+#AsaaseBreakfastShow #Asaasenews #AsaaseRadio #AsaaseDigital https://t.co/3KDXZIlC9D</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>https://x.com/asaaseradio995/status/2100175600618975665</t>
+        </is>
+      </c>
+      <c r="H198" t="n">
+        <v>0</v>
+      </c>
+      <c r="I198" t="n">
+        <v>0</v>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>10:53:01</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2100175577193885983</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>ricarcl</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>@Sfilmhead @KMbappe No es el mejor futbolista. Es el mejor goleador, que es diferente. El mejor futbolista es el que más facetas del juego abarca. 
+De hecho, con sus goles la temporada pasada, ni el Madrid ni la selección francesa ganaron nada. 
+El resto es marketing.</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>https://x.com/ricarcl/status/2100175577193885983</t>
+        </is>
+      </c>
+      <c r="H199" t="n">
+        <v>0</v>
+      </c>
+      <c r="I199" t="n">
+        <v>0</v>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>10:53:01</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2100175576266936416</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>MeringueRouge</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>@SquireGrooktook Yeah I guess, but at least on social networks, there's that immediate recognition of what you're looking at that seems to be very important. In all my marketing, the best people recognised the game for was the big rack. That's it. It's a demon lady, but barely looks like a demon</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>https://x.com/MeringueRouge/status/2100175576266936416</t>
+        </is>
+      </c>
+      <c r="H200" t="n">
+        <v>0</v>
+      </c>
+      <c r="I200" t="n">
+        <v>0</v>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>10:53:02</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2100175569618948352</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>LcioLaboissier2</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>@vamosdireita É jogo de marketing podre.</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>https://x.com/LcioLaboissier2/status/2100175569618948352</t>
+        </is>
+      </c>
+      <c r="H201" t="n">
+        <v>0</v>
+      </c>
+      <c r="I201" t="n">
+        <v>0</v>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>10:53:02</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>2100175568960458903</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>SamueleOnelia</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>@diodo_e If your goal is to attract creators or aspiring creators, sharing MRR is a proven marketing tactic.</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>https://x.com/SamueleOnelia/status/2100175568960458903</t>
+        </is>
+      </c>
+      <c r="H202" t="n">
+        <v>0</v>
+      </c>
+      <c r="I202" t="n">
+        <v>0</v>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>10:53:02</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>2100175558370078727</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>s_ketharaman</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>"When OpenAI goes public, I assume it will need to claim a 15% probability of killing everyone." ~ @matt_levine.
+Never struck me in my whole life of doing B2B Tech Marketing that I should've focused on risk factors instead of wasting time on features, benefits, etc. 😀. https://t.co/ZM8wT7zqUY</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>https://x.com/s_ketharaman/status/2100175558370078727</t>
+        </is>
+      </c>
+      <c r="H203" t="n">
+        <v>0</v>
+      </c>
+      <c r="I203" t="n">
+        <v>0</v>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>10:53:02</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>2100175553013985399</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>VengefulFrieren</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>@Alisa_KujouLARP His father works in marketing.
+"it's over, this will be the last video" and then a few minutes later he suggest his son might make new videos soon. https://t.co/8zq6UJJqc3</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>https://x.com/VengefulFrieren/status/2100175553013985399</t>
+        </is>
+      </c>
+      <c r="H204" t="n">
+        <v>0</v>
+      </c>
+      <c r="I204" t="n">
+        <v>0</v>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>10:53:02</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>2100175528473034773</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>jakeh2792</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>China won’t will the LLM race, but is winning the robotics race. 
+One is marketing centric, the other product centric. 
+China struggles to do brand, US struggles with creating mass market hardware.</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>https://x.com/jakeh2792/status/2100175528473034773</t>
+        </is>
+      </c>
+      <c r="H205" t="n">
+        <v>0</v>
+      </c>
+      <c r="I205" t="n">
+        <v>0</v>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>10:53:02</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>2100175484529360932</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>zmb_bllbry_mffn</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>So, it is aimed at the rich class to fund services for the poor. 
+How are such low iq people able to reach the top? 
+FIRE YOUR MARKETING TEAM</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>https://x.com/zmb_bllbry_mffn/status/2100175484529360932</t>
+        </is>
+      </c>
+      <c r="H206" t="n">
+        <v>0</v>
+      </c>
+      <c r="I206" t="n">
+        <v>0</v>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>10:53:02</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>2100175480033059081</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>obito12OG</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>@CoderJunkie Trust the math, not the marketing page.</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>https://x.com/obito12OG/status/2100175480033059081</t>
+        </is>
+      </c>
+      <c r="H207" t="n">
+        <v>0</v>
+      </c>
+      <c r="I207" t="n">
+        <v>0</v>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>10:53:02</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>2100175479135220026</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>FrankDijkstra4</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>@VrijndeSteede @VVD Dé VVD bestaat al enige tijd niet meer. Eén pot snotterig nat met het CDA en het despotische D66. Ben al lang geleden met die visie en inhoudsloze marketing clubjes gestopt. clubjesgestopt</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>https://x.com/FrankDijkstra4/status/2100175479135220026</t>
+        </is>
+      </c>
+      <c r="H208" t="n">
+        <v>0</v>
+      </c>
+      <c r="I208" t="n">
+        <v>0</v>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>10:53:02</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>2100175464274739352</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>MarketingEdgeM</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>NBC marks 75 years in Nigeria! 
+Celebrating with a gala in Abuja, @CocaCola HBC reaffirmed its $1B investment plan &amp;amp; announced $2.5M in grants for youth entrepreneurs &amp;amp; clean water projects.
+Read more on our website! 
+#MarketingEdge #NBC75 #CocaColaHBC #RalphTathagata https://t.co/VPCYJrZGsS</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>https://x.com/MarketingEdgeM/status/2100175464274739352</t>
+        </is>
+      </c>
+      <c r="H209" t="n">
+        <v>0</v>
+      </c>
+      <c r="I209" t="n">
+        <v>0</v>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>10:53:02</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>2100175464728056136</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>GfxRabbi</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Small Streamer &amp;amp; Content Creator🔥📢🚀
+1.  Like ❤️
+2. Reposts🔄
+3. Comments 
+4. Drops link yt/twitch↩️
+Follow me 🔥
+Dm me for spacial promo📩🚀
+#yt
+#kick
+#twitch
+#youtube
+#gaming
+#smallstreamer 
+#contentcreator 
+#SmallBusiness 
+#promotion https://t.co/n0iJMV7RDj</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>https://x.com/GfxRabbi/status/2100175464728056136</t>
+        </is>
+      </c>
+      <c r="H210" t="n">
+        <v>0</v>
+      </c>
+      <c r="I210" t="n">
+        <v>0</v>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>10:53:02</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>2100176053604102383</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>GfxRabbi</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>🚀Small streamer &amp;amp; content creator need growth?
+Build your YouTube,Twitch &amp;amp; Kick streams NOW!
+Drop links below✅
+Like❤️Comment💬Repost🔄
+DM me for spacial promo &amp;amp; exclusive  growth!🚀
+#Twitch #TwitchStreamer #Kick #Gaming #SmallStreamer #ContentCreator #YouTubeGrowth https://t.co/RFSRlRWFFK</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>https://x.com/GfxRabbi/status/2100176053604102383</t>
+        </is>
+      </c>
+      <c r="H211" t="n">
+        <v>0</v>
+      </c>
+      <c r="I211" t="n">
+        <v>0</v>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>10:53:03</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>2100175361833394371</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>iRubankt</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Google Ads AI needs guardrails, not blind trust ft Mike Ryan
+https://t.co/n9MN4g2CLo</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>https://x.com/iRubankt/status/2100175361833394371</t>
+        </is>
+      </c>
+      <c r="H212" t="n">
+        <v>0</v>
+      </c>
+      <c r="I212" t="n">
+        <v>0</v>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>10:53:03</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>2100175974205682167</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>RolandAsare_</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>GOD’S WORK AT NSAWAM
+Sometimes, transformation begins in places where society least expects it.
+At Nsawam Prison, a remarkable reform initiative is giving inmates something more valuable than punishment alone: a second chance at life.
+Through an educational and rehabilitation</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>https://x.com/RolandAsare_/status/2100175974205682167</t>
+        </is>
+      </c>
+      <c r="H213" t="n">
+        <v>0</v>
+      </c>
+      <c r="I213" t="n">
+        <v>0</v>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>10:53:03</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>2100175945055301952</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>freelancewizzy</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>@bluenokii // yeah that's basically my thoughts exactly, I mean I'm the oldest out of the three in my family so I can sorta take care of them but I don't think I'd be a good parent at all 😭😭 I don't want to hurt them by accident</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>https://x.com/freelancewizzy/status/2100175945055301952</t>
+        </is>
+      </c>
+      <c r="H214" t="n">
+        <v>0</v>
+      </c>
+      <c r="I214" t="n">
+        <v>0</v>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>10:53:03</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>2100175942723215680</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>KIZO_ES</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>@Riley_Ikni you might remember, you one roasted my landing page and gave me encouragement to keep building  Tusk. It's now released for some time and slowly growing:
+https://t.co/k8LK9uXr9P</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>https://x.com/KIZO_ES/status/2100175942723215680</t>
+        </is>
+      </c>
+      <c r="H215" t="n">
+        <v>0</v>
+      </c>
+      <c r="I215" t="n">
+        <v>0</v>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>10:53:03</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>2100175920724132042</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>GrownixApp</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Day 3 of posting TikTok slideshows.
+I usually create the slideshow first thing in the morning. That seems to be my best window for creativity.
+This time I found a viral post from a completely different niche and rebuilt the idea for ours.
+No CTA this time.
+I already had a</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>https://x.com/GrownixApp/status/2100175920724132042</t>
+        </is>
+      </c>
+      <c r="H216" t="n">
+        <v>0</v>
+      </c>
+      <c r="I216" t="n">
+        <v>0</v>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>10:53:03</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>2100175915460260273</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>williamdtc2y</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>@zerdotre I have message you</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>https://x.com/williamdtc2y/status/2100175915460260273</t>
+        </is>
+      </c>
+      <c r="H217" t="n">
+        <v>0</v>
+      </c>
+      <c r="I217" t="n">
+        <v>0</v>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>10:53:03</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>2100175906467991869</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Kishan_Devani_</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>@vibeonX69 A better question gets a better answer. that's the whole mechanism</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>https://x.com/Kishan_Devani_/status/2100175906467991869</t>
+        </is>
+      </c>
+      <c r="H218" t="n">
+        <v>0</v>
+      </c>
+      <c r="I218" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>10:53:03</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>2100175254463119821</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Mkt4eCommerce</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Gestionar #GoogleAds ya no va solo de pujas y anuncios. @Geotelecom analiza cómo suben los costes, crece la automatización y por qué estrategia, datos y coordinación entre canales pesan cada vez más en eCommerce 👇
+🔗 https://t.co/csn8oVLKVJ https://t.co/AvXaHnDVt6</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>https://x.com/Mkt4eCommerce/status/2100175254463119821</t>
+        </is>
+      </c>
+      <c r="H219" t="n">
+        <v>1</v>
+      </c>
+      <c r="I219" t="n">
+        <v>0</v>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>10:53:03</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>2100175886200783001</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>emmemkay</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>If low self esteem and this mental slavery that women are putting themselves in did not end one woman, the rest will not learn that their body is not a machine or a glass</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>https://x.com/emmemkay/status/2100175886200783001</t>
+        </is>
+      </c>
+      <c r="H220" t="n">
+        <v>0</v>
+      </c>
+      <c r="I220" t="n">
+        <v>0</v>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>10:53:03</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>2100175855695905063</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>TawohAwa</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Stop telling ChatGPT “Build me a website”
+Stop telling ChatGPT “Make my website look better”
+Stop telling ChatGPT “Create a landing page”
+Bad request = Bad result.
+Use this workflow to create beautiful websites that don’t just look good  but they convert. 👇</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>https://x.com/TawohAwa/status/2100175855695905063</t>
+        </is>
+      </c>
+      <c r="H221" t="n">
+        <v>1</v>
+      </c>
+      <c r="I221" t="n">
+        <v>1</v>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>10:53:04</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>2100175863673504185</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>TawohAwa</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>2/ How does it work?
+Instead of asking ChatGPT to “write HTML,” ask it to build a website by selecting ‘ChatGPT work’
+Example prompt:
+Build me a modern SaaS landing page for my gym with subscriptions
+In a few minutes, ChatGPT generates a complete website preview. https://t.co/eEoSC52o8g</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>https://x.com/TawohAwa/status/2100175863673504185</t>
+        </is>
+      </c>
+      <c r="H222" t="n">
+        <v>0</v>
+      </c>
+      <c r="I222" t="n">
+        <v>1</v>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>10:53:04</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>2100175874817413529</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>KUMEYUR1</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>@lesbianyura SEAN THIS IS AMAZING</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>https://x.com/KUMEYUR1/status/2100175874817413529</t>
+        </is>
+      </c>
+      <c r="H223" t="n">
+        <v>0</v>
+      </c>
+      <c r="I223" t="n">
+        <v>0</v>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>10:53:04</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>2100175858610872575</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>rsk9588</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>@annasoreskin Sure @annasoreskin</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>https://x.com/rsk9588/status/2100175858610872575</t>
+        </is>
+      </c>
+      <c r="H224" t="n">
+        <v>0</v>
+      </c>
+      <c r="I224" t="n">
+        <v>0</v>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>10:53:04</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>2100175846162215163</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>ramaeeesparks</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>@georgeviews MoU matter illa.. Evalo convert aguthu nu pakkanum. DMK la 80 percent mela conversion rate kamichirukanga. Avanga period la convert Agatha MoU also sethu than 1 lakh crore nu kanaku kamichanga. 
+Same conversion rate or better ivanga pannrangala illa MoU mattum thana nu papom.</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>https://x.com/ramaeeesparks/status/2100175846162215163</t>
+        </is>
+      </c>
+      <c r="H225" t="n">
+        <v>0</v>
+      </c>
+      <c r="I225" t="n">
+        <v>0</v>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>10:53:04</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>2100175836410216605</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>KUMEYUR1</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>@lesbianyura I LOVE URUHA</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>https://x.com/KUMEYUR1/status/2100175836410216605</t>
+        </is>
+      </c>
+      <c r="H226" t="n">
+        <v>0</v>
+      </c>
+      <c r="I226" t="n">
+        <v>0</v>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>10:53:04</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>2100175807612125552</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>DanielKaderavek</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Když to napíše liberální content creator ze @SeznamZpravy, tak to musí být pravda. Když to říká Babiš, tak to musí být nesmysl.🤦🏻‍♂️
+Jenže toto je zrovna celkem funkční řešení. Naše mladé bílé liberálky by koukaly, jak se najednou na Mostecku a Ústecku rodí děti a daň. poplatníci.</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>https://x.com/DanielKaderavek/status/2100175807612125552</t>
+        </is>
+      </c>
+      <c r="H227" t="n">
+        <v>1</v>
+      </c>
+      <c r="I227" t="n">
+        <v>0</v>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>10:53:04</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>2100175799387144307</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>John_Parvu</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>https://t.co/UqOrCJBmD2</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>https://x.com/John_Parvu/status/2100175799387144307</t>
+        </is>
+      </c>
+      <c r="H228" t="n">
+        <v>0</v>
+      </c>
+      <c r="I228" t="n">
+        <v>0</v>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>10:53:04</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>2100175799848497474</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>fakharkamario</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>What makes this video work:
+➜ 26 seconds. Clear structure: Hook/tease 0:00–0:05 → core message 0:05–0:10 → product demo 0:10–0:20 → outro 0:20–0:25.8. No separate problem section because the video is announcing a rebuilt product rather than introducing a new category.
+➜</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>https://x.com/fakharkamario/status/2100175799848497474</t>
+        </is>
+      </c>
+      <c r="H229" t="n">
+        <v>0</v>
+      </c>
+      <c r="I229" t="n">
+        <v>0</v>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>10:53:04</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>2100175765216039106</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>marcommnews</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>AB Tasty and VWO unite as @wingify  to launch Agentic Experience Optimisation platform https://t.co/tbMdZVv5gs #AdTech #MarCommNews https://t.co/t2GnOWQyVL</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>https://x.com/marcommnews/status/2100175765216039106</t>
+        </is>
+      </c>
+      <c r="H230" t="n">
+        <v>0</v>
+      </c>
+      <c r="I230" t="n">
+        <v>0</v>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>10:53:05</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>2100175755510485196</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>theappbulletin</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>@MrBrjan Who cares about originality,one shot an app,and market it better than them. Thats it</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>https://x.com/theappbulletin/status/2100175755510485196</t>
+        </is>
+      </c>
+      <c r="H231" t="n">
+        <v>0</v>
+      </c>
+      <c r="I231" t="n">
+        <v>0</v>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>10:53:05</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>2100175749114163219</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>realibdouglas</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>@AlexTudun Happy Birthday! 🎉🍾</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>https://x.com/realibdouglas/status/2100175749114163219</t>
+        </is>
+      </c>
+      <c r="H232" t="n">
+        <v>0</v>
+      </c>
+      <c r="I232" t="n">
+        <v>0</v>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>10:53:05</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>2100175749886124350</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>takumiautowork</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>フォロワー0人でも「今まさに商品を買おうとしてる人」を集める方法はあります。
+例えば「○○英会話 口コミ」ってGoogleで検索する人。もうそのサービスを知ってて、申し込むか迷ってる可能性あるよね。
+だったら、その人の検索結果に自分の記事を広告で出せばいい。</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>https://x.com/takumiautowork/status/2100175749886124350</t>
+        </is>
+      </c>
+      <c r="H233" t="n">
+        <v>0</v>
+      </c>
+      <c r="I233" t="n">
+        <v>0</v>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>10:53:05</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>2100175726532039153</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>ayewatchai</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>https://t.co/AKuFrXz3EW rewrote a plan cell at 2:14am. if you had AyeWatch watching that public pricing page, it would have pinged you before slack turned into “wait, did they always include that?” @ayewatchai https://t.co/TwWgpzGmhY</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>https://x.com/ayewatchai/status/2100175726532039153</t>
+        </is>
+      </c>
+      <c r="H234" t="n">
+        <v>0</v>
+      </c>
+      <c r="I234" t="n">
+        <v>0</v>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>10:53:05</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>2100175696991846810</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>cryptowithgopal</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>#CRO
+crypto-com-chain:native is showing a double-bottom setup 👀📈
+Price is around $0.05543, with two reaction lows near $0.0547–$0.0548. The neckline sits around $0.0560, and price is approaching that resistance.
+🎯 Chart target: ~$0.0575
+🚀 A confirmed breakout above $0.0560 https://t.co/2tRIy3coAs</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>https://x.com/cryptowithgopal/status/2100175696991846810</t>
+        </is>
+      </c>
+      <c r="H235" t="n">
+        <v>0</v>
+      </c>
+      <c r="I235" t="n">
+        <v>0</v>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>10:53:05</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>2100175683049669095</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>AdeboWalayyy</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>@omolaraeni81 @KaySoyemiEsq @CosyHomesOta More sales ma</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>https://x.com/AdeboWalayyy/status/2100175683049669095</t>
+        </is>
+      </c>
+      <c r="H236" t="n">
+        <v>0</v>
+      </c>
+      <c r="I236" t="n">
+        <v>0</v>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>10:53:05</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>2100175680470192334</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Tickeron</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>$CRDO https://t.co/BBc7q3fKFY</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>https://x.com/Tickeron/status/2100175680470192334</t>
+        </is>
+      </c>
+      <c r="H237" t="n">
+        <v>0</v>
+      </c>
+      <c r="I237" t="n">
+        <v>0</v>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>10:53:05</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>2100175681342603357</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>andrii_rom</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>@T_Zahil I love your landing page and these design patterns!
+I've been doing it too for my sites, generating illustration like that, etc
+Can you share some design tips or prompts how you design like this? Is there some cool UI library that you use or is it all manual work?</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>https://x.com/andrii_rom/status/2100175681342603357</t>
+        </is>
+      </c>
+      <c r="H238" t="n">
+        <v>0</v>
+      </c>
+      <c r="I238" t="n">
+        <v>0</v>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>10:53:05</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>2100175675151757704</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>TkakaBariga</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>@Deejayjasper006 @Midatlblog Blame those that will go to market and buy good goods for 5k and want to sell that same product for 40k</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>https://x.com/TkakaBariga/status/2100175675151757704</t>
+        </is>
+      </c>
+      <c r="H239" t="n">
+        <v>0</v>
+      </c>
+      <c r="I239" t="n">
+        <v>0</v>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>10:53:05</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>2100175671733727512</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>strategist_ca</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>#COLPAL - Colgate Palmolive (India) Limited- A Global Leader in Consumer &amp;amp; Household Products- Is at Key #Technical Level &amp;amp; #Fundamental Level. FMCG sector has been Beaten Down Since Months Now &amp;amp; at Key Technical Level. If this Sector Bounce Backs &amp;amp; Became Dark Horse, this Stock https://t.co/xDvMaF1ym3</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>https://x.com/strategist_ca/status/2100175671733727512</t>
+        </is>
+      </c>
+      <c r="H240" t="n">
+        <v>0</v>
+      </c>
+      <c r="I240" t="n">
+        <v>0</v>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>10:53:05</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>2100175658295218594</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>takumiautowork</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>会社員なら「1日3時間働いて月5万」より「自分が会社にいる間も集客が動く副業」を知ってほしい。
+これ、別に怪しい自動収益の話じゃない。
+Googleで「○○ 口コミ」「○○ 比較」と検索してる人に広告を出す。記事を読んでもらって、商品が売れたら成果報酬が入る。</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>https://x.com/takumiautowork/status/2100175658295218594</t>
+        </is>
+      </c>
+      <c r="H241" t="n">
+        <v>0</v>
+      </c>
+      <c r="I241" t="n">
+        <v>0</v>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>10:53:06</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>2100175609318256957</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>takumiautowork</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>副業初心者が「動画編集、ライター、せどり」の3択で悩んでるなら、まだ知らない選択肢があります。
+僕なら会社員で平日1〜2時間しかないなら、「自分が作業した分だけ稼ぐ副業」だけでは選ばない。
+記事を1つ作る。そこにGoogle広告で「すでに商品を探してる人」を集める。売れたら成果報酬が入る。</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>https://x.com/takumiautowork/status/2100175609318256957</t>
+        </is>
+      </c>
+      <c r="H242" t="n">
+        <v>0</v>
+      </c>
+      <c r="I242" t="n">
+        <v>0</v>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>10:53:06</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>2100175571854479547</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Zoroaster711911</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>@GoatedExile @AltAfrikaner Unless the DNA splicing of Cro Magnon with homo erectus only happened 6000 years ago</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>https://x.com/Zoroaster711911/status/2100175571854479547</t>
+        </is>
+      </c>
+      <c r="H243" t="n">
+        <v>0</v>
+      </c>
+      <c r="I243" t="n">
+        <v>0</v>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>10:53:06</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>2100175543689765121</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>__adwoasefah</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>@jesuisjemimaa i’ll keep clapping for others until it’s my turn🙏🏾</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>https://x.com/__adwoasefah/status/2100175543689765121</t>
+        </is>
+      </c>
+      <c r="H244" t="n">
+        <v>0</v>
+      </c>
+      <c r="I244" t="n">
+        <v>0</v>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>10:53:06</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>2100175522160664800</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>A64076925</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>@warabimochi285 少しでますが、ジョージジェンセンの2026年のイヤーネックレスはどうでしょう！？産んだ年の記念になります🫶
+https://t.co/csMIErENqH</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>https://x.com/A64076925/status/2100175522160664800</t>
+        </is>
+      </c>
+      <c r="H245" t="n">
+        <v>0</v>
+      </c>
+      <c r="I245" t="n">
+        <v>0</v>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>10:53:06</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>2100175502975664156</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>foto_bell</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Moment two engineers in a cage inspect UK's most dangerous shipwreck off Kent, UK. Pics @Alamy_Editorial https://t.co/Q5f8MpSgdo @SunPictureDesk @Mailonlinepics @TelegraphPics @TimesPictures @guardianphotos @metropixdesk @Mirror_Pictures https://t.co/ATdDWByhLZ</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>https://x.com/foto_bell/status/2100175502975664156</t>
+        </is>
+      </c>
+      <c r="H246" t="n">
+        <v>0</v>
+      </c>
+      <c r="I246" t="n">
+        <v>0</v>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>10:53:06</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>2100175480846463102</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>leedsboygrant23</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>@Johnyboylufc You’re my guy man. But this isn’t it. I’m from the south of England and I know people further than me that are supporters of this club. Yeah it’s a content creator, cool he’s gone Elland Road and yeah he went to the scum stadium. We move.</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>https://x.com/leedsboygrant23/status/2100175480846463102</t>
+        </is>
+      </c>
+      <c r="H247" t="n">
+        <v>0</v>
+      </c>
+      <c r="I247" t="n">
+        <v>0</v>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>10:53:06</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>2100175406716403811</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>andrei_bsns</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>quanto costa partire per fare landing page e siti? molto poco: un abbonamento a claude o codex, poi netlify o vercel per il deploy.
+sotto i 100€ al mese stai molto chill e fai una buona quantità di pagine.
+#landingpage #vibecoding #tool #freelance https://t.co/HWDUbybqez</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>https://x.com/andrei_bsns/status/2100175406716403811</t>
+        </is>
+      </c>
+      <c r="H248" t="n">
+        <v>0</v>
+      </c>
+      <c r="I248" t="n">
+        <v>0</v>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>10:53:06</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>2100175267570253869</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>weisskleee</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Ich bin so stolz auf mich (n//n)🩷
+2026 konnte ich viele gesunde Routinen und Gewohnheiten entwickeln und vieles besser angehen.
+Ich freue mich sehr auf die Zukunft als Content Creator (und hoffentlich gutes Vorbild) und wie sich das auswirken wird 🍀</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>https://x.com/weisskleee/status/2100175267570253869</t>
+        </is>
+      </c>
+      <c r="H249" t="n">
+        <v>5</v>
+      </c>
+      <c r="I249" t="n">
+        <v>0</v>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>10:53:07</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>2100175322826367418</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>sponton66</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>@poojeetstreet 💩😁</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>https://x.com/sponton66/status/2100175322826367418</t>
+        </is>
+      </c>
+      <c r="H250" t="n">
+        <v>0</v>
+      </c>
+      <c r="I250" t="n">
+        <v>0</v>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>10:53:07</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>2100175297282715989</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>pixelcave_john</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>i have a problem every time i build a landing page.
+ai or by hand, same thing.
+design is fine but then i get to features.
+3 icons and some abstract blob just don't cut it.
+i want the product to actually move, like someone cared.
+yes, ai can generate a custom animation but it https://t.co/PAslOo2LmC</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>https://x.com/pixelcave_john/status/2100175297282715989</t>
+        </is>
+      </c>
+      <c r="H251" t="n">
+        <v>0</v>
+      </c>
+      <c r="I251" t="n">
+        <v>0</v>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>10:53:07</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>2100175258716094778</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>CroAglo</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>@ZachBitango Is it possible for one to "scoot violently?"</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>https://x.com/CroAglo/status/2100175258716094778</t>
+        </is>
+      </c>
+      <c r="H252" t="n">
+        <v>0</v>
+      </c>
+      <c r="I252" t="n">
+        <v>0</v>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>10:53:07</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>2100175220535333018</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>BigLambert3939</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Two strategies can show similar APYs and still be completely different products.
+One might be supported by durable cash flows and diversified exposure.
+Another might depend on concentrated risk, thin liquidity, or assumptions that only work in a bull market.
+That’s why https://t.co/fkQLGOiZvi</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>https://x.com/BigLambert3939/status/2100175220535333018</t>
+        </is>
+      </c>
+      <c r="H253" t="n">
+        <v>0</v>
+      </c>
+      <c r="I253" t="n">
+        <v>0</v>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>10:53:07</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>2100175150390112288</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>WorkZone7</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>@Ochekidoma @AfamDeluxo Never .psalm is a content creator and a guru in tech .. also a fanstribe podcast analyst</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>https://x.com/WorkZone7/status/2100175150390112288</t>
+        </is>
+      </c>
+      <c r="H254" t="n">
+        <v>3</v>
+      </c>
+      <c r="I254" t="n">
+        <v>0</v>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>10:53:07</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>2100175180094222834</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>EngrShahid_</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>A small moment of carelessness can turn dangerous. Stay alert, even in everyday moments. 🙏⚠️
+Credit goes to the original content creator https://t.co/tCtLumb4uX</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>https://x.com/EngrShahid_/status/2100175180094222834</t>
+        </is>
+      </c>
+      <c r="H255" t="n">
+        <v>0</v>
+      </c>
+      <c r="I255" t="n">
+        <v>0</v>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>10:53:07</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>2100175098145624537</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>pierreeliottlal</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>https://t.co/orMgvl0k17</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>https://x.com/pierreeliottlal/status/2100175098145624537</t>
+        </is>
+      </c>
+      <c r="H256" t="n">
+        <v>2</v>
+      </c>
+      <c r="I256" t="n">
+        <v>0</v>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>10:53:07</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>2100175120555786450</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>EASL3616</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Today is the day!!!!  Ratification Voting is taking place from 7 a.m. - 7 p.m.  Come by the office and Cast your Vote ✔️.
+Rain or Shine we will remain open 👍🏽
+Reminder this is ONLY for the CTA Bargaining Unit (Instructional only) https://t.co/t1V3wbOaDg</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>https://x.com/EASL3616/status/2100175120555786450</t>
+        </is>
+      </c>
+      <c r="H257" t="n">
+        <v>0</v>
+      </c>
+      <c r="I257" t="n">
+        <v>0</v>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>10:53:07</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>2100175109910605980</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Localmote</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Canvify lets you turn any #Canva layout into a live #Shopify page in a few clicks. Design a section, product page, or full landing page in Canva, import it in our app...
+https://t.co/dBWXucYbn0
+#WebDesign #SaaS #LocalmoteBiz https://t.co/Pf6y4Z3rq7</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>https://x.com/Localmote/status/2100175109910605980</t>
+        </is>
+      </c>
+      <c r="H258" t="n">
+        <v>0</v>
+      </c>
+      <c r="I258" t="n">
+        <v>0</v>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>10:53:07</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>2100175103405207826</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>CornelDaGreat</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Need a newsletter that looks professional and converts?
+I design high-converting newsletters, landing pages and websites.
+Let’s build yours. 
+#fiverr 
+#GranHermanoGeneraciónDorada
+https://t.co/X6SG4j8VTk</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>https://x.com/CornelDaGreat/status/2100175103405207826</t>
+        </is>
+      </c>
+      <c r="H259" t="n">
+        <v>0</v>
+      </c>
+      <c r="I259" t="n">
+        <v>0</v>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>10:53:08</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>2100175064616280207</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>ochuwa22</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>@Opemipo_wealthy What actually caused the traffic?</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>https://x.com/ochuwa22/status/2100175064616280207</t>
+        </is>
+      </c>
+      <c r="H260" t="n">
+        <v>0</v>
+      </c>
+      <c r="I260" t="n">
+        <v>0</v>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>10:53:08</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>2100175021872140768</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>mightybeastlive</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>@WatchdogTh96012 The ad campaign was directed toward men to get more men watching female sports. You think men are going to be fired up about the stats of some women athletes? This was a shocking and risqué ad that started a conversation, thereby giving more attention to women's sports. Job done.</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>https://x.com/mightybeastlive/status/2100175021872140768</t>
+        </is>
+      </c>
+      <c r="H261" t="n">
+        <v>0</v>
+      </c>
+      <c r="I261" t="n">
+        <v>0</v>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>10:53:08</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>2100174982462702071</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>RamSainyam</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>@winsttonxavier 2014 pachipoyina laddu nunchi 
+2019 BJP ni ammana bootulu titre CPI and CPM Kalisi 
+2024 lo fanboy behaviour gamanistunnam anni ghamanistunnam</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>https://x.com/RamSainyam/status/2100174982462702071</t>
+        </is>
+      </c>
+      <c r="H262" t="n">
+        <v>0</v>
+      </c>
+      <c r="I262" t="n">
+        <v>0</v>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>10:53:08</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>2100174946118877217</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Oboi_72by</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>@it_Rutie Na for clout you Dey whine content creator</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>https://x.com/Oboi_72by/status/2100174946118877217</t>
+        </is>
+      </c>
+      <c r="H263" t="n">
+        <v>0</v>
+      </c>
+      <c r="I263" t="n">
+        <v>0</v>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>10:53:08</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>2100174936765563112</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>takumiautowork</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>副業初心者がPPCを知らないまま「何の副業やろう？」って悩んでるの、ちょっともったいないと思う。
+顔出しなしでもできる。大勢のフォロワーが前提じゃない。毎日SNS投稿する必要もない。自分の商品を最初から作る必要もない。</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>https://x.com/takumiautowork/status/2100174936765563112</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr"/>
+      <c r="H264" t="n">
+        <v>0</v>
+      </c>
+      <c r="I264" t="n">
+        <v>0</v>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr"/>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr"/>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
         </is>
       </c>
     </row>

--- a/data/logs.xlsx
+++ b/data/logs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N264"/>
+  <dimension ref="A1:N362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14750,7 +14750,6 @@
           <t>https://x.com/takumiautowork/status/2100174936765563112</t>
         </is>
       </c>
-      <c r="G264" t="inlineStr"/>
       <c r="H264" t="n">
         <v>0</v>
       </c>
@@ -14762,14 +14761,5315 @@
           <t>multi_group</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
       <c r="L264" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
       </c>
-      <c r="M264" t="inlineStr"/>
       <c r="N264" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>13:16:52</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>2100212055035068724</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>newonpolsia</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Most business idea lists optimize for novelty, not demand. Kiteweld delivers ten practical opportunities at a time, showing the customer, problem, startup simplicity, and recurring-demand potential behind each. Live soon.</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>https://x.com/newonpolsia/status/2100212055035068724</t>
+        </is>
+      </c>
+      <c r="H265" t="n">
+        <v>0</v>
+      </c>
+      <c r="I265" t="n">
+        <v>0</v>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>13:16:52</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>2100212215571996798</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>bharatkr</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>@0xPaulvibe That's a real startup problem: founders keep shipping product while distribution stays last on the list, so good ideas stall.</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>https://x.com/bharatkr/status/2100212215571996798</t>
+        </is>
+      </c>
+      <c r="H266" t="n">
+        <v>0</v>
+      </c>
+      <c r="I266" t="n">
+        <v>0</v>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>13:16:52</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>2100212152749678647</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Titas_Asfaqul</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Meta Instant Forms vs Website Conversion Campaigns: Which Generates Better Leads?
+#MetaAds #HighTicketMarketing #LeadGeneration #ContractorMarketing #FacebookAds #HomeImprovementMarketing #DigitalMarketing #LeadQuality #FacebookAdsStrategy #MetaAdvertising #SalesFunnel https://t.co/azyvghyJnJ</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>https://x.com/Titas_Asfaqul/status/2100212152749678647</t>
+        </is>
+      </c>
+      <c r="H267" t="n">
+        <v>0</v>
+      </c>
+      <c r="I267" t="n">
+        <v>0</v>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>13:16:53</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>2100211974936379706</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>ArbaaSaddam</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Hey @X
+ algorithm, I'm looking to #connect with the people who are interested in...
+✅DSA
+💻Leetcode
+🎨Frontend
+💼 Backend
+✨ Full stack
+🧑‍💻DevOps
+🧠AI/ML
+🧱 Web3
+📊Data Science
+🐍Python
+🫂Networking
+🏆 Product 
+📈 Marketing
+🔨 Startup
+#letsconnect #buildinpublic</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>https://x.com/ArbaaSaddam/status/2100211974936379706</t>
+        </is>
+      </c>
+      <c r="H268" t="n">
+        <v>0</v>
+      </c>
+      <c r="I268" t="n">
+        <v>0</v>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>13:16:53</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>2100211847475384748</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>igorbhneves</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>@jasonlk Seen this play out both ways. Waiting for “enough pipeline to hire marketing” often means marketing never gets built. The early hire only works if they can own the whole thing — not just run ads for someone else’s strategy.</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>https://x.com/igorbhneves/status/2100211847475384748</t>
+        </is>
+      </c>
+      <c r="H269" t="n">
+        <v>0</v>
+      </c>
+      <c r="I269" t="n">
+        <v>0</v>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>13:16:53</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>2100211221169344668</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>WebMediaU</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Revolutionize Your Business with Pro-Level Social Media Training! 🌟💼 Learn to attract high-quality leads and create magnetic sales funnels for a steady stream of new customers. 💡🌐 https://t.co/Z8zJuJAHjD  #SocialMediaTraining #CertificationClasses https://t.co/Kcpw89b5n5</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>https://x.com/WebMediaU/status/2100211221169344668</t>
+        </is>
+      </c>
+      <c r="H270" t="n">
+        <v>0</v>
+      </c>
+      <c r="I270" t="n">
+        <v>0</v>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>13:16:53</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>2100211841385279658</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>gil2chill</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>@Bouquet2fleurs_ Avec un bon petit-déjeuner et un autre booster moins convoité pour lui expliquer la loi du marché, la marketing, la rareté et le business de la revente, la capacité extraordinaire des gens à surpayer même quand ils n'ont pas d'argent. Un tiens vaut mieux que deux tu l'as pas. https://t.co/lQr6uxRaPg</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>https://x.com/gil2chill/status/2100211841385279658</t>
+        </is>
+      </c>
+      <c r="H271" t="n">
+        <v>0</v>
+      </c>
+      <c r="I271" t="n">
+        <v>0</v>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>13:16:53</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>2100211582869635287</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>newonpolsia</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Most lead generation stops at a spreadsheet. Veylark goes further: it finds qualified businesses, audits their opportunities, and prepares personalized offers, outreach, and CRM records to pursue them. Sales infrastructure for small B2B teams. Live soon.</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>https://x.com/newonpolsia/status/2100211582869635287</t>
+        </is>
+      </c>
+      <c r="H272" t="n">
+        <v>0</v>
+      </c>
+      <c r="I272" t="n">
+        <v>0</v>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>13:16:54</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>2100212167563763970</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Guronnimo</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>@ScottShapiroUXD You need to only blame yourself as a founder</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>https://x.com/Guronnimo/status/2100212167563763970</t>
+        </is>
+      </c>
+      <c r="H273" t="n">
+        <v>0</v>
+      </c>
+      <c r="I273" t="n">
+        <v>0</v>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>13:16:54</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>2100211531443290121</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>UsseoS</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Get your roofing company found online with professional roofing SEO services. More visibility. More leads. More growth. 🏠📈
+https://t.co/RpOw6Z7QWc
+#RoofingSEO #RoofingMarketing https://t.co/v98nKfyEVv</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>https://x.com/UsseoS/status/2100211531443290121</t>
+        </is>
+      </c>
+      <c r="H274" t="n">
+        <v>0</v>
+      </c>
+      <c r="I274" t="n">
+        <v>0</v>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>13:16:54</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>2100212151575056682</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>camcomroma</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>🌊 Blue Planet Economy Expoforum 2026: aperta la manifestazione di interesse per startup e PMI del Lazio
+La Camera di Commercio di Roma e la Regione Lazio selezionano fino a 28 startup e PMI del Lazio attive nell’Economia del Mare per partecipare alla collettiva regionale. https://t.co/vd6vN0JVm5</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>https://x.com/camcomroma/status/2100212151575056682</t>
+        </is>
+      </c>
+      <c r="H275" t="n">
+        <v>0</v>
+      </c>
+      <c r="I275" t="n">
+        <v>0</v>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>13:16:54</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>2100212144960659675</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>MageArez</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>@tradeofboby Team behind $BOBY is @AIFiAlliance and @tradeofboby mutuals are fucking crazy
+Followed by $DARK dev @edgarpavlovsky, @gitcoin co-founder @owocki, @AviSchiffmann, @paulkhls, @seedclub, and many more. https://t.co/8tnf9QKATE</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>https://x.com/MageArez/status/2100212144960659675</t>
+        </is>
+      </c>
+      <c r="H276" t="n">
+        <v>0</v>
+      </c>
+      <c r="I276" t="n">
+        <v>0</v>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>13:16:54</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>2100212131694084102</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>steve_in_OC</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>@ChrizBogota The $10k MRR dream is a useful anchor because it separates lifestyle economics from venture optics. For a second-time founder, I’d protect the 90% margin by testing repeatable acquisition before adding fixed headcount.</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>https://x.com/steve_in_OC/status/2100212131694084102</t>
+        </is>
+      </c>
+      <c r="H277" t="n">
+        <v>0</v>
+      </c>
+      <c r="I277" t="n">
+        <v>0</v>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>13:16:55</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>2100212104435273804</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>kimindiehacker</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>when the startup needs more time
+what gets cut first?
+sleep
+gym
+friends
+the day job</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>https://x.com/kimindiehacker/status/2100212104435273804</t>
+        </is>
+      </c>
+      <c r="H278" t="n">
+        <v>0</v>
+      </c>
+      <c r="I278" t="n">
+        <v>0</v>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>13:16:55</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>2100212098345382242</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>brian5201314</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Maven Robotics just proved the boring industrial robot startup can still raise nine figures: it launched Sept 15 with $100M Series A from LocalGlobe, Vine and XTX, targeting logistics and manufacturing. #MavenRobotics #VentureCapital #IndustrialRobot https://t.co/eLEOeIRZRP</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>https://x.com/brian5201314/status/2100212098345382242</t>
+        </is>
+      </c>
+      <c r="H279" t="n">
+        <v>0</v>
+      </c>
+      <c r="I279" t="n">
+        <v>0</v>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>13:16:55</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>2100212074164957363</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Mariposa_Nature</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Tour update 🚨
+A booking today for Butterflies of the Hautes Pyrenees moves that tour to guaranteed departure status for next summer. 
+And you can join Mariposa founder David Moore and Butterfly Conservation Europe co-founder Chris van Swaay there too!
+https://t.co/w4Xtn9nWdm https://t.co/glCNj16kVC</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>https://x.com/Mariposa_Nature/status/2100212074164957363</t>
+        </is>
+      </c>
+      <c r="H280" t="n">
+        <v>0</v>
+      </c>
+      <c r="I280" t="n">
+        <v>0</v>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>13:16:55</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>2100212049032675677</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>qbspchelp</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>What can you disable in Windows 10’s Task Manager Startup list? https://t.co/gDiatv4HHD</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>https://x.com/qbspchelp/status/2100212049032675677</t>
+        </is>
+      </c>
+      <c r="H281" t="n">
+        <v>0</v>
+      </c>
+      <c r="I281" t="n">
+        <v>1</v>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>13:16:55</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>2100212057912017205</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>PatriotsNet_Off</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>CONFIRMED SPEAKER ✅
+César Pintado, Founder of Herqles.
+Join us September 19 for our Madrid Conference in Spain !
+Sign up at : https://t.co/gmAx81fhli https://t.co/g4byilquXj</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>https://x.com/PatriotsNet_Off/status/2100212057912017205</t>
+        </is>
+      </c>
+      <c r="H282" t="n">
+        <v>0</v>
+      </c>
+      <c r="I282" t="n">
+        <v>0</v>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>13:16:55</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>2100212040669311424</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>R_H_L_F</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>@sogodly_ Their PR and marketing team isn’t as effective as Palestine’s</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>https://x.com/R_H_L_F/status/2100212040669311424</t>
+        </is>
+      </c>
+      <c r="H283" t="n">
+        <v>0</v>
+      </c>
+      <c r="I283" t="n">
+        <v>0</v>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>13:16:56</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>2100211390677942375</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>IanSmithA_O</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>@Daniel86Cycles @PsyopAnime How else would you attract men other than a shapely body and badonkadonks? Like this had been the marketing strategy for businesses for decades.</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>https://x.com/IanSmithA_O/status/2100211390677942375</t>
+        </is>
+      </c>
+      <c r="H284" t="n">
+        <v>0</v>
+      </c>
+      <c r="I284" t="n">
+        <v>0</v>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>13:16:56</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>2100211974869078080</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>javidambra</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>@microagencia El marketing traba a full en el 99.
+Hasta tostadores con el estiler "apto y2k" te vendían</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>https://x.com/javidambra/status/2100211974869078080</t>
+        </is>
+      </c>
+      <c r="H285" t="n">
+        <v>0</v>
+      </c>
+      <c r="I285" t="n">
+        <v>0</v>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>13:16:56</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>2100211969521250439</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>tomas_corza</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Click the link to learn how to write jobs to be done marketing strategy. 
+Link: https://t.co/34zvhtoVXN
+#jtbdtheory #jtbd #jobstobedone #productmarketing</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>https://x.com/tomas_corza/status/2100211969521250439</t>
+        </is>
+      </c>
+      <c r="H286" t="n">
+        <v>0</v>
+      </c>
+      <c r="I286" t="n">
+        <v>0</v>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>13:16:56</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>2100211966103126122</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Hynexhere</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Locked in the clipper team for the new project.
+Going all in on organic marketing.
+Traffic push starts now , will update you along the way.
+Huge gap in the market. Team has done millions in this niche before.
+Let's see how far we take this.</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>https://x.com/Hynexhere/status/2100211966103126122</t>
+        </is>
+      </c>
+      <c r="H287" t="n">
+        <v>0</v>
+      </c>
+      <c r="I287" t="n">
+        <v>0</v>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>13:16:56</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>2100211957764878422</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>tonmaxis</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Axis trusted Kaito for their marketing compaign while not trusting their capital launchpad.
+Ch ch ch....</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>https://x.com/tonmaxis/status/2100211957764878422</t>
+        </is>
+      </c>
+      <c r="H288" t="n">
+        <v>0</v>
+      </c>
+      <c r="I288" t="n">
+        <v>0</v>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>13:16:57</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>2100211956963537002</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>ThorstenDembski</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>Everyone obsesses over how the AI voice agent sounds.
+The business owner doesn't.
+He's under a sink or with a patient when the call comes in. He never hears the call.
+What he sees is the text message 30 seconds later.
+That summary IS the product. Here's how to build one that https://t.co/UoDTMgKJNj</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>https://x.com/ThorstenDembski/status/2100211956963537002</t>
+        </is>
+      </c>
+      <c r="H289" t="n">
+        <v>0</v>
+      </c>
+      <c r="I289" t="n">
+        <v>0</v>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>13:16:57</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>2100211954807636327</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>InvestNorthwise</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>@NtWialNvGxnHaw0 Yes, GMV is a cleaner measure of marketplace growth than headline revenue for $JMIA . Both transactions in our example generate $100 of GMV, regardless of who owns the inventory.
+We’d still pair it with gross profit and what remains after fulfillment and customer acquisition.</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>https://x.com/InvestNorthwise/status/2100211954807636327</t>
+        </is>
+      </c>
+      <c r="H290" t="n">
+        <v>0</v>
+      </c>
+      <c r="I290" t="n">
+        <v>0</v>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>13:16:57</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>2100211924059206053</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>leonidagram_</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>@quellopigro @IlFicca Ragionamento che puoi fare solo se sei una multinazionale sennò ciccia. Ce la vedo poco l’agenzia di marketing del milanese a spostarsi in Lituania.</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>https://x.com/leonidagram_/status/2100211924059206053</t>
+        </is>
+      </c>
+      <c r="H291" t="n">
+        <v>0</v>
+      </c>
+      <c r="I291" t="n">
+        <v>0</v>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>13:16:57</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>2100211919697461251</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>MrbossOfficiial</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>@MemeProphet_ Would you be open to a marketing partnership?</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>https://x.com/MrbossOfficiial/status/2100211919697461251</t>
+        </is>
+      </c>
+      <c r="H292" t="n">
+        <v>0</v>
+      </c>
+      <c r="I292" t="n">
+        <v>0</v>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>13:16:58</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>2100211888520863961</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>simonemban</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>I counted 4+ brand campaigns featuring WAGs during NFL opening week.
+There’s (been) a clear opportunity for brands here. They get talent with a connection to the NFL and an audience that can extend beyond football.
+I expect a lot more marketing dollars to flow toward WAGs from</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>https://x.com/simonemban/status/2100211888520863961</t>
+        </is>
+      </c>
+      <c r="H293" t="n">
+        <v>0</v>
+      </c>
+      <c r="I293" t="n">
+        <v>1</v>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>13:16:58</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>2100211893327560837</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>CK14151617</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>@ja1m3bennett @ajholland7 @TheBigBishop That’s a different argument though and nothing to do with the sexual nature of the marketing though. Your argument is, you should only have people advertising the specific field they are in?</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>https://x.com/CK14151617/status/2100211893327560837</t>
+        </is>
+      </c>
+      <c r="H294" t="n">
+        <v>0</v>
+      </c>
+      <c r="I294" t="n">
+        <v>0</v>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>13:16:58</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>2100211888998982074</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>chrizzy</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>@precisox mmmm marketing? 🤔</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>https://x.com/chrizzy/status/2100211888998982074</t>
+        </is>
+      </c>
+      <c r="H295" t="n">
+        <v>0</v>
+      </c>
+      <c r="I295" t="n">
+        <v>0</v>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>13:16:58</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>2100211852915704169</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>BusinessMirror</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>ICI Group’s CEO Gladys Basinillo won Gold for Most Innovative Leader of the Year at the Marketech NEXT Awards Philippines 2026, an awards body that recognizes the individuals and organizations shaping the future of marketing across Asia, spotlighting bold thinking, measurable</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>https://x.com/BusinessMirror/status/2100211852915704169</t>
+        </is>
+      </c>
+      <c r="H296" t="n">
+        <v>0</v>
+      </c>
+      <c r="I296" t="n">
+        <v>0</v>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>13:16:58</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>2100211849606431021</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Only_Knower</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>@Seanwvibedev Not have my url currently. 
+But I have launched some digital products for my target audiences(moms) and currently heavily focused on marketing and distribution. Let's connect brother. 🤝 https://t.co/wR3GPUp3fZ</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>https://x.com/Only_Knower/status/2100211849606431021</t>
+        </is>
+      </c>
+      <c r="H297" t="n">
+        <v>0</v>
+      </c>
+      <c r="I297" t="n">
+        <v>0</v>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>13:16:59</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>2100211824029307046</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>leonardo_lemos</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>@cinamarina No, marketing will.</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>https://x.com/leonardo_lemos/status/2100211824029307046</t>
+        </is>
+      </c>
+      <c r="H298" t="n">
+        <v>0</v>
+      </c>
+      <c r="I298" t="n">
+        <v>0</v>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>13:16:59</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>2100211821751714060</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>InsiderPerks</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>Every dollar counts when filling campground and RV park sites.
+Google just rolled out a massive upgrade to its advertising and measurement tools—and it’s a game-changer for outdoor hospitality businesses. 
+Here is what you need to know to lower your guest acquisition costs 🧵👇 https://t.co/RHl0Xz4rXN</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>https://x.com/InsiderPerks/status/2100211821751714060</t>
+        </is>
+      </c>
+      <c r="H299" t="n">
+        <v>0</v>
+      </c>
+      <c r="I299" t="n">
+        <v>0</v>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>13:16:59</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>2100211792454537660</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Semihmalko1</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>@profitcashtr Video paylasmiyorum ama tr tiktok deneyesim var Facebook ads deniyorum da o da donusum az gibi cok harciyor</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>https://x.com/Semihmalko1/status/2100211792454537660</t>
+        </is>
+      </c>
+      <c r="H300" t="n">
+        <v>0</v>
+      </c>
+      <c r="I300" t="n">
+        <v>0</v>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>13:16:59</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>2100211791112572932</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>kkvasha_</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>njir apakah ini saatnyaa? DARI KEMAREN MARKETING RSJ LEWAT MULI 😭</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>https://x.com/kkvasha_/status/2100211791112572932</t>
+        </is>
+      </c>
+      <c r="H301" t="n">
+        <v>0</v>
+      </c>
+      <c r="I301" t="n">
+        <v>0</v>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>13:16:59</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>2100211782191345677</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Pointer_Chaser</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>@TheFigen_ Somebody fire the marketing people. 
+I would pay the entrance fee specifically to see and hear them. Hell, I might travel to the place just to shoot video.</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>https://x.com/Pointer_Chaser/status/2100211782191345677</t>
+        </is>
+      </c>
+      <c r="H302" t="n">
+        <v>0</v>
+      </c>
+      <c r="I302" t="n">
+        <v>0</v>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>13:16:59</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>2100211705456230666</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>NettlWebStudio</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>New business idea? Website revamp? Specific landing page for a product or service?
+Use our clever calculator to get an instant website quote in 3 quick and easy steps. 
+Search 'Nettl Web Quote' to begin. https://t.co/hsyR7EjfsS</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>https://x.com/NettlWebStudio/status/2100211705456230666</t>
+        </is>
+      </c>
+      <c r="H303" t="n">
+        <v>0</v>
+      </c>
+      <c r="I303" t="n">
+        <v>0</v>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>13:17:00</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>2100212246999667032</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>ItsKevoUGC</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>@ugcninja1 Hey, I’d love to learn more about this opportunity. Here’s my portfolio. Let’s work! 
+https://t.co/tZtUsO1iGe</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>https://x.com/ItsKevoUGC/status/2100212246999667032</t>
+        </is>
+      </c>
+      <c r="H304" t="n">
+        <v>0</v>
+      </c>
+      <c r="I304" t="n">
+        <v>0</v>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>13:17:00</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>2100212243879080281</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>M_Christianity</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>@for_theology @CovenantReform2 @JohnCarpenter64 @CWoznicki @Jonathan_Black_ 14/15
+Pentecostalism as a Christian Mystical Tradition
+—by Daniel Castelo +Forward by Elaine Heath
+“The link between Methodism, mysticism, and Pentecostalism may well be Phoebe Palmer, mother of the nineteenth-century Holiness Movement. Palmer, a lifelong Methodist, repeatedly https://t.co/tFbx1ILDZy</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>https://x.com/M_Christianity/status/2100212243879080281</t>
+        </is>
+      </c>
+      <c r="H305" t="n">
+        <v>0</v>
+      </c>
+      <c r="I305" t="n">
+        <v>0</v>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>13:17:00</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>2100211600313696308</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>matehunyor</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>My Meta Ads testing system is basically:
+Find the winning message.
+Find the winning creative.
+Find the winning audience/market.
+Scale the proven combination.
+Most people jump straight to step 4 with an unproven ad.</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>https://x.com/matehunyor/status/2100211600313696308</t>
+        </is>
+      </c>
+      <c r="H306" t="n">
+        <v>0</v>
+      </c>
+      <c r="I306" t="n">
+        <v>0</v>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>13:17:00</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>2100212232428597571</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>symply_pears</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>@Akoredemii_ God no go allow that kind person come my way again. I mean you don’t think about how she’ll feel? It’s just like you flirting with someone else in the presence of who you call your woman. 
+But they say e no deep sha.</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>https://x.com/symply_pears/status/2100212232428597571</t>
+        </is>
+      </c>
+      <c r="H307" t="n">
+        <v>0</v>
+      </c>
+      <c r="I307" t="n">
+        <v>0</v>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>13:17:00</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>2100212228326592792</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>caroljayyyy</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>@petallovess dua and tame impala are very very likely, they were reportedly trying to get BTS as well</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>https://x.com/caroljayyyy/status/2100212228326592792</t>
+        </is>
+      </c>
+      <c r="H308" t="n">
+        <v>0</v>
+      </c>
+      <c r="I308" t="n">
+        <v>0</v>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>13:17:01</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>2100212228314300810</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>ROswestry79360</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>We’ve spent three parts asking what happens if AI goes wrong. Now let’s ask the other question: what happens if we get it right? The technology may be the easy part. What we do with it is the hard part. https://t.co/vjTEDAy8x6</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>https://x.com/ROswestry79360/status/2100212228314300810</t>
+        </is>
+      </c>
+      <c r="H309" t="n">
+        <v>0</v>
+      </c>
+      <c r="I309" t="n">
+        <v>0</v>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>13:17:01</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>2100212218826490152</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>milesgr_</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>i swear most neobank decks are 15 slides on a product built from three vendors and one slide on the only thing that isnt rented.
+accounts from a banking-as-a-service provider, cards from an issuer, KYC from a third, a front end built in a few days. in crypto the balance on</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>https://x.com/milesgr_/status/2100212218826490152</t>
+        </is>
+      </c>
+      <c r="H310" t="n">
+        <v>0</v>
+      </c>
+      <c r="I310" t="n">
+        <v>0</v>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>13:17:01</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>2100212176745312361</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>IndiaToday</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>After years of walking past a broken stretch in Koramangala, an entrepreneur decided to fix it himself. After raising complaints with the BBMP and GBA without action, he spent ₹2,700 to repair the footpath with the help of a supervisor and labourers.
+Karnataka Minister K.R. https://t.co/yQBVW2h4za</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>https://x.com/IndiaToday/status/2100212176745312361</t>
+        </is>
+      </c>
+      <c r="H311" t="n">
+        <v>0</v>
+      </c>
+      <c r="I311" t="n">
+        <v>0</v>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>13:17:01</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>2100212147636900027</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>sky_lin47439</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>PTI (https://t.co/RPolH3VfXQ)on FOPLP
+▍FOPLP (Panel-Level Packaging) vs. CoWoS
+With CoWoS capacity remaining tight, PTI (Powertech) isn't looking to directly displace TSMC — it is offering hyperscalers and chipmakers a cost-effective alternative via Fan-Out Panel-Level</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>https://x.com/sky_lin47439/status/2100212147636900027</t>
+        </is>
+      </c>
+      <c r="H312" t="n">
+        <v>0</v>
+      </c>
+      <c r="I312" t="n">
+        <v>0</v>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>13:17:01</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>2100212124337205752</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>GENIC0N</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>The world must be getting pretty messed up if people can understand what I'm saying to them</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>https://x.com/GENIC0N/status/2100212124337205752</t>
+        </is>
+      </c>
+      <c r="H313" t="n">
+        <v>1</v>
+      </c>
+      <c r="I313" t="n">
+        <v>0</v>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>13:17:01</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>2100212104493940885</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>bee_fumo</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>@gentengineer Greek guy lives and operates in Germany (my boss)
+Every person he hires is a Greek freelancer (we work remotely from greece)
+My contract says 20€ an hour clearly.
+The invoice i write says 50 hours
+the reality i work from 9:30 to 6:30 monday to friday. So it's closer to 160</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>https://x.com/bee_fumo/status/2100212104493940885</t>
+        </is>
+      </c>
+      <c r="H314" t="n">
+        <v>0</v>
+      </c>
+      <c r="I314" t="n">
+        <v>0</v>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>13:17:02</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>2100212089318977725</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>tevslin</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>Q: What’s Scarier Than a Swarm of AI Agents Trying to Take Over the Internet?
+A: A Cartel of Tech CEOs Trying to Take Over AI.
+Background
+Anthropic CEO Dario Amodei wrote [https://t.co/45TbJOL56Z]:
+"I believe that AI could cure most major diseases in the next 5–10 years,</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>https://x.com/tevslin/status/2100212089318977725</t>
+        </is>
+      </c>
+      <c r="H315" t="n">
+        <v>0</v>
+      </c>
+      <c r="I315" t="n">
+        <v>0</v>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>13:17:02</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>2100212069370872287</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>leodev</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>@maxktz who just popped up on my screen?? https://t.co/L044iVbQRl</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>https://x.com/leodev/status/2100212069370872287</t>
+        </is>
+      </c>
+      <c r="H316" t="n">
+        <v>1</v>
+      </c>
+      <c r="I316" t="n">
+        <v>0</v>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>13:17:02</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>2100212065960951926</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>EstelinaGonzal2</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>Lamer</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>https://x.com/EstelinaGonzal2/status/2100212065960951926</t>
+        </is>
+      </c>
+      <c r="H317" t="n">
+        <v>0</v>
+      </c>
+      <c r="I317" t="n">
+        <v>0</v>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>13:17:02</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>2100212050672943530</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>nexus_ai_2045</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>@sin5d いえｗ
+なんかCTAとかCPAとか滞在時間とかをKPIにしている広告屋AIが誤学習してて、パズルみたいな閉じるボタン探すゲー迷惑広告が多いので、
+ROASとかLTVとか成約率とか売上をKGIにした成果報酬（実測値＋AI予測ではありますが）型の広告サービスをしたら正直な商売になるかなぁ？と思いました！</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>https://x.com/nexus_ai_2045/status/2100212050672943530</t>
+        </is>
+      </c>
+      <c r="H318" t="n">
+        <v>0</v>
+      </c>
+      <c r="I318" t="n">
+        <v>0</v>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>13:17:02</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>2100212051566018881</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>AyouBoukhari</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>2/ I gave those trainings until 2021. What I miss is the prep. Three days of course taught me more than three months of client work. "Because it works" isn't an answer when someone asks why. So in 2025 I did the longest prep yet: 291 pages. Kotlin – Du code au Play Store. https://t.co/pDEgkCtDwa</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>https://x.com/AyouBoukhari/status/2100212051566018881</t>
+        </is>
+      </c>
+      <c r="H319" t="n">
+        <v>0</v>
+      </c>
+      <c r="I319" t="n">
+        <v>0</v>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>13:17:03</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>2100212023653003532</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>busygolfing1131</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>@ryangerritsen Read the tea leaf's  traitor-no one is buying the shit you're selling anymore</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>https://x.com/busygolfing1131/status/2100212023653003532</t>
+        </is>
+      </c>
+      <c r="H320" t="n">
+        <v>0</v>
+      </c>
+      <c r="I320" t="n">
+        <v>0</v>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>13:17:03</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>2100212006561185965</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>its_lindz</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>@waymoflydenu They focus on the last thing they see. If you want social media impressions to be different you have to be different on social media. All meek has to do is put out some good music and be consistent and things will go up and drown out the dweebs. But he should still absolutely put</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>https://x.com/its_lindz/status/2100212006561185965</t>
+        </is>
+      </c>
+      <c r="H321" t="n">
+        <v>1</v>
+      </c>
+      <c r="I321" t="n">
+        <v>0</v>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>13:17:03</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>2100212000022245425</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>SamSam61460</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>Genocide is always wrong.</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>https://x.com/SamSam61460/status/2100212000022245425</t>
+        </is>
+      </c>
+      <c r="H322" t="n">
+        <v>0</v>
+      </c>
+      <c r="I322" t="n">
+        <v>0</v>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>13:17:04</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>2100211979659174298</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>OchaitaOlmedo</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>AI agents may onboard more wallets than any ad campaign. The killer app could be autonomous payments. https://t.co/Ws0QCVwkh2</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>https://x.com/OchaitaOlmedo/status/2100211979659174298</t>
+        </is>
+      </c>
+      <c r="H323" t="n">
+        <v>0</v>
+      </c>
+      <c r="I323" t="n">
+        <v>0</v>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>13:17:04</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>2100211937409729001</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>SagaAILabs</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>Paid user acquisition has quietly become one of the worst deals in software, and most teams are too busy running it to say so out loud.
+You're paying more every year to reach people who trust it less every year. ↓ https://t.co/zgcbmaitEE</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>https://x.com/SagaAILabs/status/2100211937409729001</t>
+        </is>
+      </c>
+      <c r="H324" t="n">
+        <v>2</v>
+      </c>
+      <c r="I324" t="n">
+        <v>1</v>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>13:17:04</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>2100211966698533256</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>kylefedz</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>An objection is often fear said politely.
+Good content doesn't dodge that fear or shout over it. It names the concern, explains the tradeoff, and lets the person decide with better information.</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>https://x.com/kylefedz/status/2100211966698533256</t>
+        </is>
+      </c>
+      <c r="H325" t="n">
+        <v>0</v>
+      </c>
+      <c r="I325" t="n">
+        <v>0</v>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>13:17:05</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>2100211942770323796</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>AnshikaRas99644</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>@PriyadarshniBi3 Really like how you’ve separated learning the skill from actually building the pipeline. Lead generation and consistent outbound definitely need a different approach from simply focusing on closing.</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>https://x.com/AnshikaRas99644/status/2100211942770323796</t>
+        </is>
+      </c>
+      <c r="H326" t="n">
+        <v>0</v>
+      </c>
+      <c r="I326" t="n">
+        <v>0</v>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>13:17:05</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>2100211942782541902</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>BigBeardedRef</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>@david_parker Check out the PPC.</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>https://x.com/BigBeardedRef/status/2100211942782541902</t>
+        </is>
+      </c>
+      <c r="H327" t="n">
+        <v>0</v>
+      </c>
+      <c r="I327" t="n">
+        <v>0</v>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>13:17:05</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>2100211942539334122</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>CataholicPriest</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>@SecKennedy this tweet actually outlines how theyre fudging deaths, and hes mad that a state that needs help wont enter into an agreement that does that
+theyre hiding outbreaks/deaths for political purposes</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>https://x.com/CataholicPriest/status/2100211942539334122</t>
+        </is>
+      </c>
+      <c r="H328" t="n">
+        <v>0</v>
+      </c>
+      <c r="I328" t="n">
+        <v>0</v>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>13:17:05</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>2100211936961147122</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>cheolsowoon</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>Kak @junhao_forever @aahayy_ cpc ya</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>https://x.com/cheolsowoon/status/2100211936961147122</t>
+        </is>
+      </c>
+      <c r="H329" t="n">
+        <v>0</v>
+      </c>
+      <c r="I329" t="n">
+        <v>0</v>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>13:17:05</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>2100211923308454246</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>NealeLea43427</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>@JohnBrassardCPC Such a whiny unpatriotic leader the CPC and you have.</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>https://x.com/NealeLea43427/status/2100211923308454246</t>
+        </is>
+      </c>
+      <c r="H330" t="n">
+        <v>0</v>
+      </c>
+      <c r="I330" t="n">
+        <v>0</v>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>13:17:05</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>2100211867784556618</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>franpradasAI</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>1️⃣ Dale rol + objetivo + formato
+Cuanto menos tenga que adivinar, mejor será el resultado.
+Prompt:
+“Actúa como copywriter B2B. Escribe un email para recuperar clientes inactivos. Máximo 120 palabras, tono cercano y CTA claro.”</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>https://x.com/franpradasAI/status/2100211867784556618</t>
+        </is>
+      </c>
+      <c r="H331" t="n">
+        <v>0</v>
+      </c>
+      <c r="I331" t="n">
+        <v>1</v>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>13:17:06</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>2100211867373203801</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>graindiente</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>@Grazinascito Tem gente pra tudo, ja conheci dev de landing page, que vibecodava inclusive</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>https://x.com/graindiente/status/2100211867373203801</t>
+        </is>
+      </c>
+      <c r="H332" t="n">
+        <v>0</v>
+      </c>
+      <c r="I332" t="n">
+        <v>0</v>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>13:17:06</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>2100211846460399830</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>cstack</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>The monthly status report and the summary deck stop having a job the moment the work itself is visible.
+Those artifacts always existed to stand in for work happening somewhere you couldn't see. The claim I made on August 4th was that the embedded agency used to live in your</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>https://x.com/cstack/status/2100211846460399830</t>
+        </is>
+      </c>
+      <c r="H333" t="n">
+        <v>1</v>
+      </c>
+      <c r="I333" t="n">
+        <v>0</v>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>13:17:06</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>2100211851216748580</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>rick_sonnens</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>Ach, wie charmant. Die AfD wirft wieder mit Schlagworten, als wären es Konfetti – nur dass Konfetti wenigstens fröhlich macht und nicht nach schlecht gelüfteter Parteizentrale riecht.
+Das Bild: dramatischer Himmel, grimmige Pose, ein bisschen Stacheldraht fürs Flair – die https://t.co/loWm1GsUh1</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>https://x.com/rick_sonnens/status/2100211851216748580</t>
+        </is>
+      </c>
+      <c r="H334" t="n">
+        <v>0</v>
+      </c>
+      <c r="I334" t="n">
+        <v>0</v>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>13:17:06</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>2100211853309907336</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>ChiefEngineerCE</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>Chief's Choice**
+Radioactive- 
+The biggest seller so far since I started making daily recommendations has been the Geiger counter and we had quite the discussion - I show a couple dozen of these sold and a few still waiting to ship. 
+The link below has the story behind why I https://t.co/tpCwQZzIIE</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>https://x.com/ChiefEngineerCE/status/2100211853309907336</t>
+        </is>
+      </c>
+      <c r="H335" t="n">
+        <v>0</v>
+      </c>
+      <c r="I335" t="n">
+        <v>0</v>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>13:17:06</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>2100211812931092662</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>SamSam61460</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>THEY'RE TRYING TO DIVIDE US    
+         TO CONQUER US https://t.co/1jajQYdWLN</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>https://x.com/SamSam61460/status/2100211812931092662</t>
+        </is>
+      </c>
+      <c r="H336" t="n">
+        <v>0</v>
+      </c>
+      <c r="I336" t="n">
+        <v>0</v>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>13:17:06</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>2100211800427933912</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>UrlPivot</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>@Nerve_Agency The correction needs distribution too. If the wrong offer went out by email, a quiet edit to the landing page won't reach everyone who saw it. Say what changed in the same channels that carried the mistake.</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>https://x.com/UrlPivot/status/2100211800427933912</t>
+        </is>
+      </c>
+      <c r="H337" t="n">
+        <v>0</v>
+      </c>
+      <c r="I337" t="n">
+        <v>0</v>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>13:17:07</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>2100211788746809711</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>ScottShapiroUXD</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>@stretchcloud @stretchcloud 18% conversion on cold outbound from an agent feels high enough to question lead quality. Warm list disguised as cold changes the math entirely. Curious what the no-show rate on those 9 bookings looked like.</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>https://x.com/ScottShapiroUXD/status/2100211788746809711</t>
+        </is>
+      </c>
+      <c r="H338" t="n">
+        <v>0</v>
+      </c>
+      <c r="I338" t="n">
+        <v>0</v>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>13:17:07</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>2100211748867301454</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>utiva_io</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>Still stuck analysing what the next step to take is or even what to do as a beginner then we have got you covered.
+The Utiva's mentor's lounge is designed to enable you learn directly from industry experts across different fields so endeavor not to miss it for anything as this https://t.co/5IofD45eMn</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>https://x.com/utiva_io/status/2100211748867301454</t>
+        </is>
+      </c>
+      <c r="H339" t="n">
+        <v>0</v>
+      </c>
+      <c r="I339" t="n">
+        <v>0</v>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>13:17:07</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>2100211728285872632</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>joesteve__</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>Vibe with Damilee 2.0 is coming!!!
+Let the homely rat informs the one at farm.</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>https://x.com/joesteve__/status/2100211728285872632</t>
+        </is>
+      </c>
+      <c r="H340" t="n">
+        <v>1</v>
+      </c>
+      <c r="I340" t="n">
+        <v>0</v>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>13:17:07</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>2100211723101737322</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Critter_Paths</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>@MarcNixon24 You should pat yourself on the back for helping to bury canadians by cucking for the the CPC</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>https://x.com/Critter_Paths/status/2100211723101737322</t>
+        </is>
+      </c>
+      <c r="H341" t="n">
+        <v>0</v>
+      </c>
+      <c r="I341" t="n">
+        <v>0</v>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>13:17:07</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>2100211710900486343</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>vrgamerdude</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>@bmfshow YEP... I haven't been invited to anything from them in a long time! Sad really when I was part of the original Oculus content creator group and have been covering them for over a decade, so I feel your pain, man!!! ()-/ https://t.co/zWhdraK5NN</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>https://x.com/vrgamerdude/status/2100211710900486343</t>
+        </is>
+      </c>
+      <c r="H342" t="n">
+        <v>0</v>
+      </c>
+      <c r="I342" t="n">
+        <v>0</v>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>13:17:07</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>2100211700154736780</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>theLLCoolK</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>@PierrePoilievre @CPC_HQ @BlackBox_MFG @TamaraJansenMP Weird statement considering that @BlackBox_MFG has already apparently done it in BC; and you and the CPC had no fucking hand in it.
+Who writes this fucking shit?</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>https://x.com/theLLCoolK/status/2100211700154736780</t>
+        </is>
+      </c>
+      <c r="H343" t="n">
+        <v>0</v>
+      </c>
+      <c r="I343" t="n">
+        <v>0</v>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>13:17:08</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>2100211663035117771</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>MindsetDC</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>Please welcome Cameron Nichols and Leah Edelman as our newest fall interns! We look forward to working alongside them and seeing the contributions they'll make across our team and client work this semester. https://t.co/bO7zCSJz51</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>https://x.com/MindsetDC/status/2100211663035117771</t>
+        </is>
+      </c>
+      <c r="H344" t="n">
+        <v>0</v>
+      </c>
+      <c r="I344" t="n">
+        <v>0</v>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>13:17:08</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>2100211623784833159</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Bfranc100</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>@GunEagleFreedom What a retarded ass comparison. I got to fill my truck 25 gallons every 4-5 days no comparison.
+When Starbucks and so many other chains go out of buisness because no one is buying do you realize how may millions of jobs are at stake ?</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>https://x.com/Bfranc100/status/2100211623784833159</t>
+        </is>
+      </c>
+      <c r="H345" t="n">
+        <v>0</v>
+      </c>
+      <c r="I345" t="n">
+        <v>0</v>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>13:17:08</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>2100211608068780036</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>exploraX_</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>@damianplayer that’s real user acquisition&amp;gt;&amp;gt;&amp;gt;</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>https://x.com/exploraX_/status/2100211608068780036</t>
+        </is>
+      </c>
+      <c r="H346" t="n">
+        <v>0</v>
+      </c>
+      <c r="I346" t="n">
+        <v>0</v>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>13:17:09</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>2100211487910633675</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>TurtleonCro</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>$TURTLE is now getting verified on @Silex_Network.
+200 $CRO was donated by @Velocitysoulja to cover verification.
+As a nonprofit, community-run project, we build slower than some — but we build with honesty and transparency. One step at a time.
+Build allocation is currently</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>https://x.com/TurtleonCro/status/2100211487910633675</t>
+        </is>
+      </c>
+      <c r="H347" t="n">
+        <v>5</v>
+      </c>
+      <c r="I347" t="n">
+        <v>0</v>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>13:17:09</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>2100211538845941879</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>arya_rachita</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>@NathanB81273152 Yes, since meta has been volatile. CPM and CPA have increased. But better to think of profitability too and reduce spends slightly. I would not shut of best performing campaigns that have been running from a long time. These bounce back way faster. I would rather switch of newer</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>https://x.com/arya_rachita/status/2100211538845941879</t>
+        </is>
+      </c>
+      <c r="H348" t="n">
+        <v>0</v>
+      </c>
+      <c r="I348" t="n">
+        <v>0</v>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>13:17:09</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>2100211461096174076</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>crispann64</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>@patripeyrou X favor, cta maldad!! Pobre angelito inocente!! Urgente alguien q viva cerca q pueda ayudarlo?? 😔😔😔🙏🏻🙏🏻🙏🏻</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>https://x.com/crispann64/status/2100211461096174076</t>
+        </is>
+      </c>
+      <c r="H349" t="n">
+        <v>0</v>
+      </c>
+      <c r="I349" t="n">
+        <v>0</v>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>13:17:09</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>2100211436157063253</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>hosapete2031</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>@Mrsinha Why do you blame BJP, it is CPM goons who threw eggs</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>https://x.com/hosapete2031/status/2100211436157063253</t>
+        </is>
+      </c>
+      <c r="H350" t="n">
+        <v>0</v>
+      </c>
+      <c r="I350" t="n">
+        <v>0</v>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>13:17:09</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>2100211397640499514</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Richard_here65</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>@Prominent_Bryan I am on Team Canada. I was driven away from the CPC by the MAGA we need to be just like America. I am happy that Canada won in the last election.</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>https://x.com/Richard_here65/status/2100211397640499514</t>
+        </is>
+      </c>
+      <c r="H351" t="n">
+        <v>0</v>
+      </c>
+      <c r="I351" t="n">
+        <v>0</v>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>13:17:10</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>2100211391147708913</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>KfcTokyo</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>@Eric_Erins @cta thermostat broken. tell the cta chat bot w/the bus #</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>https://x.com/KfcTokyo/status/2100211391147708913</t>
+        </is>
+      </c>
+      <c r="H352" t="n">
+        <v>0</v>
+      </c>
+      <c r="I352" t="n">
+        <v>0</v>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>13:17:10</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>2100211370897920136</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>PrajwalTomar_</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>https://t.co/g1O952yz9p</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>https://x.com/PrajwalTomar_/status/2100211370897920136</t>
+        </is>
+      </c>
+      <c r="H353" t="n">
+        <v>1</v>
+      </c>
+      <c r="I353" t="n">
+        <v>0</v>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>13:17:10</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>2100211365486973417</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>pawprints1986_2</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>@daleethompson You're right, that's how it works. But if you've ever said Pierre should step down, you're now a flaming hypocrite
+I'm not saying you have, I don't know. I'm just saying don't be a hypocrite. CPC members voted him leader, another part of democracy. Libs have to deal with that</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>https://x.com/pawprints1986_2/status/2100211365486973417</t>
+        </is>
+      </c>
+      <c r="H354" t="n">
+        <v>0</v>
+      </c>
+      <c r="I354" t="n">
+        <v>0</v>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>13:17:10</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>2100211348982608190</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>TamilTheHindu</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>அப்பவே நாங்க சொன்னோம்...
+அதிமுக எம்எல்ஏ-க்கள் தங்களது பதவிகளை ராஜினாமா செய்துவிட்டு அதிமுக-விலிருந்து விலகி தவெக-வில் சேர்ந்தபோதே, இது வாக்களித்த மக்களுக்குச் செய்யும் துரோகம் என்று நாங்கள் கடுமையாக விமர்சித்தோம். தற்போது அதையே உயர் நீதிமன்றமும் தனது கருத்தின் மூலம் https://t.co/5CBSrO3TeS</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>https://x.com/TamilTheHindu/status/2100211348982608190</t>
+        </is>
+      </c>
+      <c r="H355" t="n">
+        <v>0</v>
+      </c>
+      <c r="I355" t="n">
+        <v>0</v>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>13:17:10</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>2100211315935457322</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>EstelinaGonzal2</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>Septiembre</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>https://x.com/EstelinaGonzal2/status/2100211315935457322</t>
+        </is>
+      </c>
+      <c r="H356" t="n">
+        <v>0</v>
+      </c>
+      <c r="I356" t="n">
+        <v>0</v>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>13:17:10</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>2100211306842182100</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>__adwoasefah</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>by the time i finish this movie, there will be no tears left</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>https://x.com/__adwoasefah/status/2100211306842182100</t>
+        </is>
+      </c>
+      <c r="H357" t="n">
+        <v>0</v>
+      </c>
+      <c r="I357" t="n">
+        <v>0</v>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>13:17:11</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>2100211241796993276</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>iS2miyeon</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>ser cargo de indicação é uma bosta mesmo, mas ser simplesmente um concurso seria pior ainda kkkk o tanto de concurseiro que é burro pra caralho mas fica 20h/dia tentando decorar o CPC sem ter conhecimento técnico ou teórico nenhum…</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>https://x.com/iS2miyeon/status/2100211241796993276</t>
+        </is>
+      </c>
+      <c r="H358" t="n">
+        <v>0</v>
+      </c>
+      <c r="I358" t="n">
+        <v>1</v>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>13:17:11</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>2100211240463159477</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>jesusflor16</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>@As_TomasRoncero @realmadrid @10ardaguler QUE SE RETIRE EL CTA CORRUPTO QUE A LAMIN NO VIO LA ROJA</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>https://x.com/jesusflor16/status/2100211240463159477</t>
+        </is>
+      </c>
+      <c r="H359" t="n">
+        <v>1</v>
+      </c>
+      <c r="I359" t="n">
+        <v>0</v>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>13:17:11</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>2100211215934922795</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Critter_Paths</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>@nationalpost The only people in Canada who don't support this are the ones who are smart enough to know that Canada is run by a Uniparty that cucks for the King and the EU.
+The Throne Speech laid out these plans. PP &amp;amp; the CPC supported it. Now they're lying about it
+https://t.co/9TgbLYx680</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>https://x.com/Critter_Paths/status/2100211215934922795</t>
+        </is>
+      </c>
+      <c r="H360" t="n">
+        <v>0</v>
+      </c>
+      <c r="I360" t="n">
+        <v>0</v>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>13:17:11</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>2100211181327716698</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>globalelectsim</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>🇨🇦 2029 Canadian Federal Election Projection: 
+🔗 https://t.co/ZnUVIic5OQ  
+🔴 LPC (Carney, centre-left) - 216 seats (44.6%)   
+🔵 CPC (Poilievre, centre-right) - 85 seats (31.1%)   
+🩵 BQ (Blanchet, left-separatist) - 23 seats (6.4%)
+🟠 NDP (Lewis, left-wing) - 16 seats (11.9%) https://t.co/GDjTN0IpzX</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>https://x.com/globalelectsim/status/2100211181327716698</t>
+        </is>
+      </c>
+      <c r="H361" t="n">
+        <v>1</v>
+      </c>
+      <c r="I361" t="n">
+        <v>1</v>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>13:17:11</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>2100211185123545210</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>AGoienetxea</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>@TimmyOToole10 Me encantan los que estan de acuerdo con el cta cuando habla de otros equipos ( q solo te leo hablar de la Real..) y lloriquean y hablan de injusticia cuando les valora a ellos…., animo campeon!?</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>https://x.com/AGoienetxea/status/2100211185123545210</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr"/>
+      <c r="H362" t="n">
+        <v>0</v>
+      </c>
+      <c r="I362" t="n">
+        <v>0</v>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr"/>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr"/>
+      <c r="N362" t="inlineStr">
         <is>
           <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
         </is>

--- a/data/logs.xlsx
+++ b/data/logs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N362"/>
+  <dimension ref="A1:N469"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20050,7 +20050,6 @@
           <t>https://x.com/AGoienetxea/status/2100211185123545210</t>
         </is>
       </c>
-      <c r="G362" t="inlineStr"/>
       <c r="H362" t="n">
         <v>0</v>
       </c>
@@ -20062,14 +20061,5811 @@
           <t>multi_group</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
       <c r="L362" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
       </c>
-      <c r="M362" t="inlineStr"/>
       <c r="N362" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>17:40:25</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>2100278385276600816</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>OverShieldbyPM</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>We’re proud to celebrate Predictive Monitor Co-Founder and CEO Laurie Masiello, who has been named one of New Hampshire’s 2026 Outstanding Women in Business by @nhbizreview! 🎉 https://t.co/gdCFLnCp1t</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>https://x.com/OverShieldbyPM/status/2100278385276600816</t>
+        </is>
+      </c>
+      <c r="H363" t="n">
+        <v>0</v>
+      </c>
+      <c r="I363" t="n">
+        <v>0</v>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>17:40:25</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>2100278585042800983</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>The1957News</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>LIVE | Save the Scholar Foundation Founder Emmanuel Nii Commey highlights the motivation behind the initiative, aimed at supporting JHS graduates in the Domeabra-Obom Constituency and easing the financial burden on parents as their children transition to SHS. https://t.co/nq80HY4cdZ</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>https://x.com/The1957News/status/2100278585042800983</t>
+        </is>
+      </c>
+      <c r="H364" t="n">
+        <v>0</v>
+      </c>
+      <c r="I364" t="n">
+        <v>0</v>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>17:40:25</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>2100278483641372818</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>arabellaaura</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>There’s nothing better than hearing directly from the people we get to work with. 🤍
+We had the pleasure of providing digital marketing services for Ifeoluwa Babalola Foundation, and we’re grateful for their feedback on their experience with Arabella Aura.
+From social media https://t.co/CMqDHNpSlt</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>https://x.com/arabellaaura/status/2100278483641372818</t>
+        </is>
+      </c>
+      <c r="H365" t="n">
+        <v>0</v>
+      </c>
+      <c r="I365" t="n">
+        <v>0</v>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>17:40:25</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>2100278480437190823</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>killuaatran99</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>so many founder.. so what i found? i found my money slip in my pocket😂</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>https://x.com/killuaatran99/status/2100278480437190823</t>
+        </is>
+      </c>
+      <c r="H366" t="n">
+        <v>0</v>
+      </c>
+      <c r="I366" t="n">
+        <v>0</v>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>17:40:26</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>2100278446907593129</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>heypaulonu</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>A startup rarely dies from a lack of ideas. It dies from too many priorities competing for the same small team. My rule: if everything matters, nothing gets finished.
+A useful priority list should make some good ideas wait. That is the point.</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>https://x.com/heypaulonu/status/2100278446907593129</t>
+        </is>
+      </c>
+      <c r="H367" t="n">
+        <v>0</v>
+      </c>
+      <c r="I367" t="n">
+        <v>0</v>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>17:40:26</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>2100278425793749383</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>chin_jlyc</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>@aikonect_ @kaido_xr founder here! were doing our best to make the things ou want to look teh same: fonts, colors, logos, style
+but refreshingly novel in terms of video content and quality !!
+please try it out I shipped 150k lines of code in the last week prepping for this launch hahaa</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>https://x.com/chin_jlyc/status/2100278425793749383</t>
+        </is>
+      </c>
+      <c r="H368" t="n">
+        <v>0</v>
+      </c>
+      <c r="I368" t="n">
+        <v>0</v>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>17:40:26</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>2100278425378574729</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>AmolWalunjsv18</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>@pedrort_3 AI SaaS founder here. Lets connect</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>https://x.com/AmolWalunjsv18/status/2100278425378574729</t>
+        </is>
+      </c>
+      <c r="H369" t="n">
+        <v>0</v>
+      </c>
+      <c r="I369" t="n">
+        <v>0</v>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>17:40:26</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>2100278398048522377</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>agencyownerlab</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Agencies that cut their price to win a client often end up training that client to expect discounts on everything that follows.
+We've seen this pattern across hundreds of conversations with agency founders.
+Price is the first signal of value a prospect receives, before they see</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>https://x.com/agencyownerlab/status/2100278398048522377</t>
+        </is>
+      </c>
+      <c r="H370" t="n">
+        <v>0</v>
+      </c>
+      <c r="I370" t="n">
+        <v>1</v>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>17:40:26</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>2100278402376716611</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>bitcoinxalerts</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>NEW: Binance founder CZ says "every dip is an opportunity."</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>https://x.com/bitcoinxalerts/status/2100278402376716611</t>
+        </is>
+      </c>
+      <c r="H371" t="n">
+        <v>0</v>
+      </c>
+      <c r="I371" t="n">
+        <v>0</v>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N371" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>17:40:26</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>2100278401542058407</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>agencyownerlab</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>This is one of the most common CEO decisions we help founders work through in Founder Advisory — pricing feels like a math problem, but it's almost always a confidence problem first.</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>https://x.com/agencyownerlab/status/2100278401542058407</t>
+        </is>
+      </c>
+      <c r="H372" t="n">
+        <v>0</v>
+      </c>
+      <c r="I372" t="n">
+        <v>0</v>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N372" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>17:40:26</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>2100278389009793217</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>SemenovID</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>@NovaProDev @grok I founder, connect good</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>https://x.com/SemenovID/status/2100278389009793217</t>
+        </is>
+      </c>
+      <c r="H373" t="n">
+        <v>0</v>
+      </c>
+      <c r="I373" t="n">
+        <v>0</v>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>17:40:27</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>2100278371783700556</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>preferedev</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>I'm 16.
+Young solo founder from Pakistan.
+Looking to connect to founders!</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>https://x.com/preferedev/status/2100278371783700556</t>
+        </is>
+      </c>
+      <c r="H374" t="n">
+        <v>0</v>
+      </c>
+      <c r="I374" t="n">
+        <v>1</v>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N374" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>17:40:27</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>2100278371871842672</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>AmolWalunjsv18</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>@angelaborowski AI SaaS founder here. Lets connect</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>https://x.com/AmolWalunjsv18/status/2100278371871842672</t>
+        </is>
+      </c>
+      <c r="H375" t="n">
+        <v>0</v>
+      </c>
+      <c r="I375" t="n">
+        <v>0</v>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>17:40:27</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>2100278366675071040</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>simplelikeegg</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>@PrinceOmarX $10,000, Insha Allah could save my life, pay off all my outstanding college tuition, pay off my loans, help my family, and generate cash flow for my startup.</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>https://x.com/simplelikeegg/status/2100278366675071040</t>
+        </is>
+      </c>
+      <c r="H376" t="n">
+        <v>0</v>
+      </c>
+      <c r="I376" t="n">
+        <v>0</v>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>17:40:27</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>2100278351730725093</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Theeclecti61605</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>@LasVegasLocally The real culprit is the Marketing/Player Development department. Those are the ones that need to be fired. 
+Isnt the former Gov Brian Sandoval overseeing that place?</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>https://x.com/Theeclecti61605/status/2100278351730725093</t>
+        </is>
+      </c>
+      <c r="H377" t="n">
+        <v>0</v>
+      </c>
+      <c r="I377" t="n">
+        <v>0</v>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N377" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>17:40:27</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>2100278351462105474</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>AndyTheGiant</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>Cleavage shouldn’t be a marketing strategy for B2B/SaaS.</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>https://x.com/AndyTheGiant/status/2100278351462105474</t>
+        </is>
+      </c>
+      <c r="H378" t="n">
+        <v>0</v>
+      </c>
+      <c r="I378" t="n">
+        <v>0</v>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N378" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>17:40:27</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>2100278312111333399</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Sambam1128123</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>I’d sell a service.
+Pick one problem businesses already pay to solve
+Find 50 businesses with that problem
+Create a quick example of the result you could get them
+Contact every one personally
+Offer a simple fixed-price deal
+Deliver it manually at first
+Website redesigns.
+Lead</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>https://x.com/Sambam1128123/status/2100278312111333399</t>
+        </is>
+      </c>
+      <c r="H379" t="n">
+        <v>0</v>
+      </c>
+      <c r="I379" t="n">
+        <v>0</v>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N379" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>17:40:28</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>2100278297498104213</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>1979py</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>@mt1s_biz google ads</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>https://x.com/1979py/status/2100278297498104213</t>
+        </is>
+      </c>
+      <c r="H380" t="n">
+        <v>0</v>
+      </c>
+      <c r="I380" t="n">
+        <v>0</v>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N380" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>17:40:28</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>2100278292645302763</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>valerioamirani</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>@rajatgangwani99 @marclou @tibo_maker @Hiteshdotcom Customer interviews within forty-eight hours of signup give you better landing page copy than internal brainstorming.</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>https://x.com/valerioamirani/status/2100278292645302763</t>
+        </is>
+      </c>
+      <c r="H381" t="n">
+        <v>0</v>
+      </c>
+      <c r="I381" t="n">
+        <v>0</v>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N381" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>17:40:28</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>2100278271782850947</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Al_Pacino_XXX</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>Τμήμα marketing ☘️
+Πατήστε το κουμπί για μωβ εμφάνιση 
+Δε γίνεται να μην φορεθεί αυτό το αριστούργημα
+💚💜
+#paobc https://t.co/RCtDwvzVxJ</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>https://x.com/Al_Pacino_XXX/status/2100278271782850947</t>
+        </is>
+      </c>
+      <c r="H382" t="n">
+        <v>1</v>
+      </c>
+      <c r="I382" t="n">
+        <v>0</v>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>17:40:28</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>2100277652686876770</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>DCRHouston</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>More leads. More opportunities. Better value. DCR Business Leads gives you access to a large selection of fresh business leads every month at a price that makes sense. Start finding your next opportunity at https://t.co/VqIVQpHyMY.
+#HoustonTX #BusinessLeads #HoustonBusiness https://t.co/V12xkZS0T0</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>https://x.com/DCRHouston/status/2100277652686876770</t>
+        </is>
+      </c>
+      <c r="H383" t="n">
+        <v>0</v>
+      </c>
+      <c r="I383" t="n">
+        <v>0</v>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N383" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>17:40:28</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>2100278279307444724</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>LeadsHibiscus</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>Blogue immobilier France et international: Immobilier en Grèce https://t.co/pQziuAmKw9 
+#France #Marketing #MarketingStrategy #marketingagency #MarketingSuccess #marketingtips #immobilier #immeuble #Catalogne #Malaga #Barcelona #Espagne #Murcia #Valencia #Tarragona #Madrid #BTC</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>https://x.com/LeadsHibiscus/status/2100278279307444724</t>
+        </is>
+      </c>
+      <c r="H384" t="n">
+        <v>0</v>
+      </c>
+      <c r="I384" t="n">
+        <v>0</v>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N384" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>17:40:28</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>2100278259720016268</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>jshcm</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>Someone at @CalvinKlein marketing really saw this photo this guys third world-style feet in sandals and thought: this will sell pants 🤮 https://t.co/dPXuy3acXN</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>https://x.com/jshcm/status/2100278259720016268</t>
+        </is>
+      </c>
+      <c r="H385" t="n">
+        <v>0</v>
+      </c>
+      <c r="I385" t="n">
+        <v>0</v>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N385" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>17:40:29</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>2100278246181077065</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>d1nz_3</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>@kelvinbuildss claude, n not for code - the marketing side. I used to keep a separate dashboard for it n just never opened it, so nothin got posted for weeks. now scout7 sits in the same window n the drafts get written whether I feel like it or not. whats urs?</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>https://x.com/d1nz_3/status/2100278246181077065</t>
+        </is>
+      </c>
+      <c r="H386" t="n">
+        <v>0</v>
+      </c>
+      <c r="I386" t="n">
+        <v>0</v>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N386" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>17:40:29</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>2100278241537994785</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Aysha_her</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>@tabataasm_ @16vchq Building in marketing sis</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>https://x.com/Aysha_her/status/2100278241537994785</t>
+        </is>
+      </c>
+      <c r="H387" t="n">
+        <v>0</v>
+      </c>
+      <c r="I387" t="n">
+        <v>0</v>
+      </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N387" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>17:40:29</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>2100278216502260053</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>GreenVeilWho</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>Whomever came up with this guerilla marketing, i wanna kiss you</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>https://x.com/GreenVeilWho/status/2100278216502260053</t>
+        </is>
+      </c>
+      <c r="H388" t="n">
+        <v>0</v>
+      </c>
+      <c r="I388" t="n">
+        <v>0</v>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N388" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>17:40:29</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>2100278212282536051</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>robinthekos</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>@TheShepherdLied @world_xyz Facts, this entire event is fascinating and I’m kinda enjoying it even after lost $15k on it. I’m very excited to see the outcome, if any appears, but in the same time feeling betrayed and used as a tool for marketing etc. It’s a little bipolar, love-hate type of thing.</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>https://x.com/robinthekos/status/2100278212282536051</t>
+        </is>
+      </c>
+      <c r="H389" t="n">
+        <v>0</v>
+      </c>
+      <c r="I389" t="n">
+        <v>0</v>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N389" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>17:40:29</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>2100278195081654308</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>GA_Reviews</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>@hoboken_gary @iuugon @namelessxdread @GlobalBoxOffice How about do a better job marketing the movie and not shitting on fans? I'm not giving Zach my money when he has shown this movie isn't for RE fans. I actually had high hopes for this but he singlehandedly made me cancel my ticket</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>https://x.com/GA_Reviews/status/2100278195081654308</t>
+        </is>
+      </c>
+      <c r="H390" t="n">
+        <v>0</v>
+      </c>
+      <c r="I390" t="n">
+        <v>0</v>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>17:40:29</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>2100278179554373882</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>ramanpal</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>How I run marketing agents now:
+1. Warm the fat prompt at `medium` (or your default)
+2. Routine follow-ups → `configuration_update` → `low`
+3. Hard brief / multi-step research → bump to `high`
+4. Never mutate the top-level effort field mid-convo
+5. Watch cache hits — if they</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>https://x.com/ramanpal/status/2100278179554373882</t>
+        </is>
+      </c>
+      <c r="H391" t="n">
+        <v>0</v>
+      </c>
+      <c r="I391" t="n">
+        <v>1</v>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>17:40:30</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>2100278137670058432</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>rodrigoserraok</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>Estoy construyendo el Higgsfield del marketing.
+Un lugar donde una marca pueda pensar, crear, publicar, automatizar y operar tanto contenido orgánico como paid media.
+Esto es un pedacito de NYLOS.
+Si les copa lo que estoy construyendo, un repost me ayuda una banda a que llegue https://t.co/vYbRqZBJlv</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>https://x.com/rodrigoserraok/status/2100278137670058432</t>
+        </is>
+      </c>
+      <c r="H392" t="n">
+        <v>0</v>
+      </c>
+      <c r="I392" t="n">
+        <v>0</v>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>17:40:30</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>2100278135304654948</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>wittysiddharth</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>@SatwickMaheshw3 @stats_feed True, but that's a marketing + word of mouth problem, not a wonder problem.
+Foreigners know Taj because that's what gets sold in every guidebook/movie. Ellora - carving an entire temple complex top-down out of ONE solid rock with hand tools - is objectively more insane, but no</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>https://x.com/wittysiddharth/status/2100278135304654948</t>
+        </is>
+      </c>
+      <c r="H393" t="n">
+        <v>0</v>
+      </c>
+      <c r="I393" t="n">
+        <v>0</v>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>17:40:30</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>2100278130787373375</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>chainsmoker89</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>marketing gimmick from that company likely.</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>https://x.com/chainsmoker89/status/2100278130787373375</t>
+        </is>
+      </c>
+      <c r="H394" t="n">
+        <v>0</v>
+      </c>
+      <c r="I394" t="n">
+        <v>0</v>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>17:40:30</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>2100278108159148511</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>EltonWelliton</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>@jeoliveiraa @futebol_info Sim cara, você entende mais de marketing do que o BAP que juntamente com Wallin e Landim iniciou essa porra toda em 2012.</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>https://x.com/EltonWelliton/status/2100278108159148511</t>
+        </is>
+      </c>
+      <c r="H395" t="n">
+        <v>0</v>
+      </c>
+      <c r="I395" t="n">
+        <v>0</v>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>17:40:30</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>2100278099388580299</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>kensavage</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>@j_bertho Past few weeks, I’m getting about 22% CTR on Meta ads with a video like this.   I attributed it to great storytelling https://t.co/jURfPMzVCF</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>https://x.com/kensavage/status/2100278099388580299</t>
+        </is>
+      </c>
+      <c r="H396" t="n">
+        <v>0</v>
+      </c>
+      <c r="I396" t="n">
+        <v>0</v>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>17:40:30</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>2100278075476820189</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>CrookedPol</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>@USPS You gotta do something about Facebook ads for counterfeit stamps.</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>https://x.com/CrookedPol/status/2100278075476820189</t>
+        </is>
+      </c>
+      <c r="H397" t="n">
+        <v>0</v>
+      </c>
+      <c r="I397" t="n">
+        <v>0</v>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>17:40:31</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>2100278040295034943</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>KirkMDesign</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>Google Ads has to be one of the worst UIs ever made. Somehow, only half the screen is usable at any given time. https://t.co/rSOTdcGN69</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>https://x.com/KirkMDesign/status/2100278040295034943</t>
+        </is>
+      </c>
+      <c r="H398" t="n">
+        <v>0</v>
+      </c>
+      <c r="I398" t="n">
+        <v>0</v>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>17:40:31</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>2100278581876433342</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>0xDragoonLab</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>i don’t think i’ve ever properly written about hexorial.
+maybe that says a lot about how we built it.
+before the ai hype, before everyone was launching creative tools every week, before building software became dramatically easier, we were already quietly doing this from india. https://t.co/wUdLk2XW5N</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>https://x.com/0xDragoonLab/status/2100278581876433342</t>
+        </is>
+      </c>
+      <c r="H399" t="n">
+        <v>0</v>
+      </c>
+      <c r="I399" t="n">
+        <v>0</v>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N399" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>17:40:31</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>2100278574544466161</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>arnaudmercier</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>Helene Budliger Artieda quitterait la direction du Seco https://t.co/VS7nr90db7</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>https://x.com/arnaudmercier/status/2100278574544466161</t>
+        </is>
+      </c>
+      <c r="H400" t="n">
+        <v>0</v>
+      </c>
+      <c r="I400" t="n">
+        <v>0</v>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N400" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>17:40:31</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>2100278567753912664</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>wizardcrypto77</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>@Entelic_Aria This tech is Game change for video content creator</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>https://x.com/wizardcrypto77/status/2100278567753912664</t>
+        </is>
+      </c>
+      <c r="H401" t="n">
+        <v>0</v>
+      </c>
+      <c r="I401" t="n">
+        <v>0</v>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N401" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>17:40:31</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>2100277914231033961</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>karli_gads</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>Demain 9h
+7ème édition de Haut de Page la newsletter Google Ads
+Au menu une nouvelle feature Google Ads qui tombe vraiment à pic
+Ça se passe ici: https://t.co/ynNrPS4ceZ
+A demain!</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>https://x.com/karli_gads/status/2100277914231033961</t>
+        </is>
+      </c>
+      <c r="H402" t="n">
+        <v>0</v>
+      </c>
+      <c r="I402" t="n">
+        <v>0</v>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N402" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>17:40:31</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>2100278488934629740</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>BarusuGoonER</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>@PDugna Its clear that WF is trying to amend their lack of everything basically by just paying a freelancer to make a fancy animation for distraction</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>https://x.com/BarusuGoonER/status/2100278488934629740</t>
+        </is>
+      </c>
+      <c r="H403" t="n">
+        <v>1</v>
+      </c>
+      <c r="I403" t="n">
+        <v>0</v>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>17:40:32</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>2100278470773444624</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Ownerthoughts</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>It usually starts out simple.:
+you enter the market “purely to try.” One chart, the second, then a chat, then some kind of listing, pump, dump - it flashes in my eyes. At some point, you're not resting anymore, you're watching. You're not sleeping, you're waiting for the news to https://t.co/68Bhrs52Lr</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>https://x.com/Ownerthoughts/status/2100278470773444624</t>
+        </is>
+      </c>
+      <c r="H404" t="n">
+        <v>1</v>
+      </c>
+      <c r="I404" t="n">
+        <v>0</v>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>17:40:32</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>2100278476066447458</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>arnaudmercier</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>La primaire de la gauche, un référendum anti-insoumis ? - L’édito politique - 16/09 https://t.co/MBRdLi0fve https://t.co/zbRakCmMyS</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>https://x.com/arnaudmercier/status/2100278476066447458</t>
+        </is>
+      </c>
+      <c r="H405" t="n">
+        <v>0</v>
+      </c>
+      <c r="I405" t="n">
+        <v>0</v>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N405" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>17:40:32</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>2100278444802392108</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>AngaliRaghaven3</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>@jagadishBRS
+@KTRBRS 
+@BRSHarish 
+#cpm #CPI 
+(CPM,I).  ఒకప్పుడు విప్లవ పార్టీలు !🧐
+ఎక్కడ అన్యాయం జరిగినా మొదటిగా వచ్చేది:¶∆  మరి ముఖ్యంగా భూములపై కొట్లాడింది✊🏻
+ సిపిఎం సిపిఐ పార్టీ🤦🏼
+ అదే ఇప్పుడు ఒక్కళ్త పలుకుతున్నాయి 🤔
+ఇంతటి దారుణం ఇంతకుముందుకు ఎప్పుడు లేకుండా🕵🏻‍♂️
+వెరీ సేమ్</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>https://x.com/AngaliRaghaven3/status/2100278444802392108</t>
+        </is>
+      </c>
+      <c r="H406" t="n">
+        <v>0</v>
+      </c>
+      <c r="I406" t="n">
+        <v>0</v>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>17:40:32</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>2100278436086399291</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>mariojamaro</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>@IVAN_cantando Pues a CPM del país, siempre con sus mmda cada proceso electoral.</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>https://x.com/mariojamaro/status/2100278436086399291</t>
+        </is>
+      </c>
+      <c r="H407" t="n">
+        <v>0</v>
+      </c>
+      <c r="I407" t="n">
+        <v>0</v>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>17:40:32</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>2100278430910816561</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>hangzhoufeel</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>What makes young people fall in love a city? 😘🌇 
+🌏The APEC Young Entrepreneurs Conference opened in Hangzhou today, gathering about 200 entrepreneurs, investors and representatives to discuss AI, light entrepreneurship and digital trade.   
+Young people choose not only just https://t.co/Zd1DonObnA</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>https://x.com/hangzhoufeel/status/2100278430910816561</t>
+        </is>
+      </c>
+      <c r="H408" t="n">
+        <v>0</v>
+      </c>
+      <c r="I408" t="n">
+        <v>0</v>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>17:40:32</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>2100278427760955599</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>wolfepereira</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>Delegating work to AI does not remove the responsibility to govern it.
+If an AI agent can move money, access sensitive information, or make a commitment on your company’s behalf, someone needs to answer three questions:
+✅ Who gave it that authority?
+✅ What limits apply?
+✅</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>https://x.com/wolfepereira/status/2100278427760955599</t>
+        </is>
+      </c>
+      <c r="H409" t="n">
+        <v>0</v>
+      </c>
+      <c r="I409" t="n">
+        <v>0</v>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>17:40:33</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>2100277781804544401</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>akmazad285799</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>@WhatsApp Lead Generation – Dentists | Job ID 022087942211450299712
+Applying for the Lead Generation Agent for Dentists role. Hourly, under 30 hrs/week, intermediate. Proposed rate: $30/hr. I can support prospect research-up through AZAD DIGITAL MARKETING ONLINE SOLUTION. https://t.co/PfGAbL4tWN</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>https://x.com/akmazad285799/status/2100277781804544401</t>
+        </is>
+      </c>
+      <c r="H410" t="n">
+        <v>0</v>
+      </c>
+      <c r="I410" t="n">
+        <v>0</v>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>17:40:33</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>2100278414661845297</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>chilowe_f</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>My day as a wedding content creator .
+I direct, shoot, adjust and somehow I just make it happen https://t.co/KH9a2lhPvO</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>https://x.com/chilowe_f/status/2100278414661845297</t>
+        </is>
+      </c>
+      <c r="H411" t="n">
+        <v>0</v>
+      </c>
+      <c r="I411" t="n">
+        <v>0</v>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>17:40:33</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>2100278406915268807</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>20kInvestor</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>🎯 STOCK TO WATCH
+WEEKLY R4 MOMENTUM BREAKOUT SETUP
+SOFTTECH ENGINEERS LTD 
+₹465–470 → ₹738 → ₹1,445
+📌 TRADE LEVELS
+🟢 Buy Zone: ₹465–470
+🚀 Breakout Zone: ₹462
+🛑 Stop Loss: ₹341
+🎯 Target 1: ₹738
+🎯 Target 2: ₹1,445
+🔎 WHY SOFTTECH ENGINEERS?
+Digital https://t.co/qHJdJcYIxb</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>https://x.com/20kInvestor/status/2100278406915268807</t>
+        </is>
+      </c>
+      <c r="H412" t="n">
+        <v>0</v>
+      </c>
+      <c r="I412" t="n">
+        <v>0</v>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>17:40:33</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>2100278398887002197</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>LocuraRojilla</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>Luego el CTA dirá que ha sido un error y todos contentos.... #robo tras robo</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>https://x.com/LocuraRojilla/status/2100278398887002197</t>
+        </is>
+      </c>
+      <c r="H413" t="n">
+        <v>0</v>
+      </c>
+      <c r="I413" t="n">
+        <v>0</v>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>17:40:33</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>2100278383351382071</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>valerioamirani</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>@Kansoxx @Profit80lvl Removing navigation links from your landing page keeps visitor attention focused on the primary call to action.</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>https://x.com/valerioamirani/status/2100278383351382071</t>
+        </is>
+      </c>
+      <c r="H414" t="n">
+        <v>0</v>
+      </c>
+      <c r="I414" t="n">
+        <v>0</v>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>17:40:33</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>2100278377144074399</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>AngaliRaghaven3</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>@jagadishBRS
+@KTRBRS 
+@BRSHarish 
+#cpm #CPI 
+(CPM,I).  ఒకప్పుడు విప్లవ పార్టీలు !🧐
+ఎక్కడ అన్యాయం జరిగినా మొదటిగా వచ్చేది:¶∆  మరి ముఖ్యంగా భూములపై కొట్లాడింది✊🏻
+ సిపిఎం సిపిఐ పార్టీ🤦🏼
+ అదే ఇప్పుడు ఒక్కళ్త పలుకుతున్నాయి 🤔
+ఇంతటి దారుణం ఇంతకుముందుకు ఎప్పుడు లేకుండా🕵🏻‍♂️
+వెరీ సేమ్</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>https://x.com/AngaliRaghaven3/status/2100278377144074399</t>
+        </is>
+      </c>
+      <c r="H415" t="n">
+        <v>0</v>
+      </c>
+      <c r="I415" t="n">
+        <v>0</v>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>17:40:34</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>2100278376132977095</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>LMandirunga</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>@City_Xtra @EnzoFe17 Yet some content creator  sat behind the camera and decided that he is not right for City. 😂😂😂😂. Some of these content creators are really insufferable</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>https://x.com/LMandirunga/status/2100278376132977095</t>
+        </is>
+      </c>
+      <c r="H416" t="n">
+        <v>0</v>
+      </c>
+      <c r="I416" t="n">
+        <v>0</v>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>17:40:34</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>2100278370512601399</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>feyiisetan</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>@kusssman LMFAOO</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>https://x.com/feyiisetan/status/2100278370512601399</t>
+        </is>
+      </c>
+      <c r="H417" t="n">
+        <v>0</v>
+      </c>
+      <c r="I417" t="n">
+        <v>0</v>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>17:40:34</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>2100278371913523435</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>GrimMerch_</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>📣 Introducing The Grim Collections Ambassador Program
+-
+If You’re A Content Creator/Brand And Would Like To Represent our Brand For CASH Potential, contact us either via DM or contact@shockbased.com https://t.co/RwlojYfoLk</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>https://x.com/GrimMerch_/status/2100278371913523435</t>
+        </is>
+      </c>
+      <c r="H418" t="n">
+        <v>0</v>
+      </c>
+      <c r="I418" t="n">
+        <v>0</v>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>17:40:34</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>2100278366243107092</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Rajileema</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>@Blackigbogal3 Thanks babes</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>https://x.com/Rajileema/status/2100278366243107092</t>
+        </is>
+      </c>
+      <c r="H419" t="n">
+        <v>0</v>
+      </c>
+      <c r="I419" t="n">
+        <v>0</v>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>17:40:34</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>2100278366993584413</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>jonartieda</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>@Aupa1920 @MrAsubio @Osasuna Pues no ha tardado en volver a caer el peso del CTA sobre Osasuna 🤣🤣</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>https://x.com/jonartieda/status/2100278366993584413</t>
+        </is>
+      </c>
+      <c r="H420" t="n">
+        <v>0</v>
+      </c>
+      <c r="I420" t="n">
+        <v>0</v>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>17:40:34</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>2100278343312560372</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>nuisance_001</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Shankcomics….That’s my idol mehn. Greatest of all Time. Inarguably the best content creator to come out of Africa…..and Korty too.</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>https://x.com/nuisance_001/status/2100278343312560372</t>
+        </is>
+      </c>
+      <c r="H421" t="n">
+        <v>2</v>
+      </c>
+      <c r="I421" t="n">
+        <v>0</v>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>17:40:35</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>2100278352548380675</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>thisleke</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>@_debbii3e 🤣🤣🤣🤣 sorry. I thought it was the frsc ticket scam going around. Rave dey today?</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>https://x.com/thisleke/status/2100278352548380675</t>
+        </is>
+      </c>
+      <c r="H422" t="n">
+        <v>0</v>
+      </c>
+      <c r="I422" t="n">
+        <v>0</v>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N422" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>17:40:35</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>2100277663327830291</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>propercaso</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>I believe when people will fomo on base:0xb095274743941e953c746f9c228da9c18bb6ec29 will be a great marketing strategy for #fomo trading app.</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>https://x.com/propercaso/status/2100277663327830291</t>
+        </is>
+      </c>
+      <c r="H423" t="n">
+        <v>0</v>
+      </c>
+      <c r="I423" t="n">
+        <v>0</v>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N423" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>17:40:35</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>2100278288878854175</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Lentulo_Lepido</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>@ArrietaNatal @WestHam10UCL @defcentral Eso es un bulo más grande que tu indigencia mental. 
+Primero, no se paga al CTA, si no a Dasnil SL, la empresa de la familia Negreira.
+Segundo, sin pruebas no hay paraíso.</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>https://x.com/Lentulo_Lepido/status/2100278288878854175</t>
+        </is>
+      </c>
+      <c r="H424" t="n">
+        <v>0</v>
+      </c>
+      <c r="I424" t="n">
+        <v>0</v>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>17:40:35</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>2100278257656402426</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>STEFisDOPE</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>@iamcobbina LFG!!!</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>https://x.com/STEFisDOPE/status/2100278257656402426</t>
+        </is>
+      </c>
+      <c r="H425" t="n">
+        <v>0</v>
+      </c>
+      <c r="I425" t="n">
+        <v>0</v>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>17:40:35</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>2100277593085784447</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Kanyiiiiin</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Hi everyone! 👋🏽
+I’m currently looking for a PPA in Lagos.
+Please, if you know any media house or marketing agency, kindly recommend them to me.
+Thank youuuuuu! 🙏🏽❤️
+Kindly RT🥹🤲</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>https://x.com/Kanyiiiiin/status/2100277593085784447</t>
+        </is>
+      </c>
+      <c r="H426" t="n">
+        <v>0</v>
+      </c>
+      <c r="I426" t="n">
+        <v>0</v>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>17:40:35</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>2100278222277558618</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>AlyshaR101</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>@baegopayohhh Exactly. CPM is only part of the story META’s targeting first-party data and ad efficiency are the real edge If capex keeps improving CPA and ROAS the spending can pay off big</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>https://x.com/AlyshaR101/status/2100278222277558618</t>
+        </is>
+      </c>
+      <c r="H427" t="n">
+        <v>0</v>
+      </c>
+      <c r="I427" t="n">
+        <v>0</v>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N427" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>17:40:36</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>2100278184327708806</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>pymerstan0000</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>✨ من الفكرة إلى التنفيذ... ومن الإبداع إلى الابتكار
+عندما يجتمع Human Creativity + Technology + AI + Effective Execution، تصبح الأفكار نقطة انطلاق حقيقية نحو التطوير والتحسين المستمر.
+📱 انضم إلينا وابقَ على اطلاع بكل جديد:
+🌐 Telegram:
+https://t.co/nSnWaYIG71
+ #Pymerstan https://t.co/FdDK5da0NB</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>https://x.com/pymerstan0000/status/2100278184327708806</t>
+        </is>
+      </c>
+      <c r="H428" t="n">
+        <v>0</v>
+      </c>
+      <c r="I428" t="n">
+        <v>0</v>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>17:40:36</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>2100278166174708134</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>luna_bunnie</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>cro, ask jj if he is willing to trade net, not us, that's jj's old dog 😭</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>https://x.com/luna_bunnie/status/2100278166174708134</t>
+        </is>
+      </c>
+      <c r="H429" t="n">
+        <v>0</v>
+      </c>
+      <c r="I429" t="n">
+        <v>0</v>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>17:40:36</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>2100278165595713754</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Isaiah4CPS</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>@Chicago2100 @cta I'd never say no to new transit. At the same time, it's hard to believe this costs more per mile than LA spends building underground subways. And 5x what dc spent per mile on the silver line. 
+At DC costs we could have built new a line from Howard to 90th st.</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>https://x.com/Isaiah4CPS/status/2100278165595713754</t>
+        </is>
+      </c>
+      <c r="H430" t="n">
+        <v>0</v>
+      </c>
+      <c r="I430" t="n">
+        <v>0</v>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>17:40:36</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>2100278153771925595</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>otagrosario</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>Los dos más odiados del país  hoy ?
+Algún otro ? https://t.co/t6BBO1Cw50</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>https://x.com/otagrosario/status/2100278153771925595</t>
+        </is>
+      </c>
+      <c r="H431" t="n">
+        <v>0</v>
+      </c>
+      <c r="I431" t="n">
+        <v>0</v>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>17:40:36</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>2100278144183718189</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>jacobjonez123</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>@BellularGaming it worked quite well i think. it brainwashed people into actually thinking they will be playing this forever instead of quitting in phase 1-2 like basically every content creator/normie did with classic wow.</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>https://x.com/jacobjonez123/status/2100278144183718189</t>
+        </is>
+      </c>
+      <c r="H432" t="n">
+        <v>0</v>
+      </c>
+      <c r="I432" t="n">
+        <v>0</v>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>17:40:37</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>2100278122885284088</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>jaquikrai</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>@MarisaNiemiz Le esta tomando el pelo</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>https://x.com/jaquikrai/status/2100278122885284088</t>
+        </is>
+      </c>
+      <c r="H433" t="n">
+        <v>0</v>
+      </c>
+      <c r="I433" t="n">
+        <v>0</v>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>17:40:37</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>2100278109811450300</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>OruboTonye</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>🚨 JOB ALERT
+Video Content Creator
+🏢 Odixcity Consulting
+📍 Remote
+💰 $3 per hour
+📅 Apply by 7 Oct 2026
+Apply now 👇
+https://t.co/1QsuZ6weOa
+🔄 Repost to help someone find this opportunity.</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>https://x.com/OruboTonye/status/2100278109811450300</t>
+        </is>
+      </c>
+      <c r="H434" t="n">
+        <v>0</v>
+      </c>
+      <c r="I434" t="n">
+        <v>0</v>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>17:40:37</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>2100278093370077214</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>bowwow_jkay</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>.@sy41206 cro is ready to trade Jimmy for  Net for a Dollar 😭</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>https://x.com/bowwow_jkay/status/2100278093370077214</t>
+        </is>
+      </c>
+      <c r="H435" t="n">
+        <v>0</v>
+      </c>
+      <c r="I435" t="n">
+        <v>1</v>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>17:40:37</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>2100278068237451455</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>NicolOnchain</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>I’m 19 
+BD &amp;amp; content creator, based everywhere
+would love to connect with more people building in the space! https://t.co/W3y4FT2njr</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>https://x.com/NicolOnchain/status/2100278068237451455</t>
+        </is>
+      </c>
+      <c r="H436" t="n">
+        <v>3</v>
+      </c>
+      <c r="I436" t="n">
+        <v>0</v>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N436" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>17:40:37</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>2100278098088415549</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>aritz_js</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>@Osasuna Mañana comunicado del CTA diciendo que ha sido un error, y ya</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>https://x.com/aritz_js/status/2100278098088415549</t>
+        </is>
+      </c>
+      <c r="H437" t="n">
+        <v>0</v>
+      </c>
+      <c r="I437" t="n">
+        <v>0</v>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>17:40:38</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>2100278044879388762</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>CayoFlavioCesar</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>@Maryjo164 El tercero de ayer anulado no lo repitieron ni pusieron los muñecos probando que era fuera de juego… CTA</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>https://x.com/CayoFlavioCesar/status/2100278044879388762</t>
+        </is>
+      </c>
+      <c r="H438" t="n">
+        <v>1</v>
+      </c>
+      <c r="I438" t="n">
+        <v>0</v>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N438" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>17:40:38</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>2100278013413798318</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Bwilson</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>@clairevo In the same week Dario goes from p(doom) national news interviews to hyping how incredible it is to talk to Claude and manage your sales funnel.
+What a time to be alive.</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>https://x.com/Bwilson/status/2100278013413798318</t>
+        </is>
+      </c>
+      <c r="H439" t="n">
+        <v>0</v>
+      </c>
+      <c r="I439" t="n">
+        <v>0</v>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>17:40:38</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>2100277996200349728</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>annevanrossum</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>@burkov Because ad programs for companies have bundles that are not allowing selective posting except against much higher rates and people are too lazy to analyse this or area provided as little info in the ineffectivity of their ad campaigns as possible</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>https://x.com/annevanrossum/status/2100277996200349728</t>
+        </is>
+      </c>
+      <c r="H440" t="n">
+        <v>0</v>
+      </c>
+      <c r="I440" t="n">
+        <v>0</v>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>17:40:38</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>2100277993813967248</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>A_n_b_e_S_i_vam</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>Till 2024
+Me:DMK(Anti BJP)
+She: ADMK
+Frd 1 :BJP
+Frd 2 : CPM
+Frd 3 : INC
+Frnd 4 : NTK
+Whoever the Ruling Party was..
+We never had any bitter times because of our Political differences
+But One Man entered &amp;amp; humbled 
+now every loser started hating the other
+Peak insecurity</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>https://x.com/A_n_b_e_S_i_vam/status/2100277993813967248</t>
+        </is>
+      </c>
+      <c r="H441" t="n">
+        <v>0</v>
+      </c>
+      <c r="I441" t="n">
+        <v>0</v>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>17:40:38</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>2100277984238215368</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>HeathElliott79</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>@paullydoughnuts On no one is buying the goats….only being said by people trying to discourage people from buying the goats so they can buy all the goats…… https://t.co/yy2iWlLG3O</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>https://x.com/HeathElliott79/status/2100277984238215368</t>
+        </is>
+      </c>
+      <c r="H442" t="n">
+        <v>0</v>
+      </c>
+      <c r="I442" t="n">
+        <v>0</v>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>17:40:38</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>2100277974608249296</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>12littlej16</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>@merry123459 He supported Brexit,Orban and Trump. Harper was the most pro American Prime Minister in Canadian history. Conservatives are great at being wrong. Look what has become of the CPC. Look at the UCP. Conservatives don’t understand Canadians. Culture wars won’t work.</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>https://x.com/12littlej16/status/2100277974608249296</t>
+        </is>
+      </c>
+      <c r="H443" t="n">
+        <v>0</v>
+      </c>
+      <c r="I443" t="n">
+        <v>0</v>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>17:40:39</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>2100277943880794381</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>aveefx</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>Content creator package made for @ThyBlessedR1 
+theme designed as client specification! https://t.co/qbecC0qUk1</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>https://x.com/aveefx/status/2100277943880794381</t>
+        </is>
+      </c>
+      <c r="H444" t="n">
+        <v>0</v>
+      </c>
+      <c r="I444" t="n">
+        <v>0</v>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>17:40:39</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>2100277931704815874</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>AlbaDocherty</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>Already ppl trying to exonerate BioVie "it was the CRO, not BioVie". Nope!
+BioVie and its executives face securities fraud charges plus derivative claims for breach of fiduciary duty, unjust enrichment, waste of corporate assets, gross mismanagement, and abuse of control.
+1.</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>https://x.com/AlbaDocherty/status/2100277931704815874</t>
+        </is>
+      </c>
+      <c r="H445" t="n">
+        <v>0</v>
+      </c>
+      <c r="I445" t="n">
+        <v>0</v>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>SENSITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>17:40:39</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>2100277898259177636</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>RaulLoeismo</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>@Osasuna Darle gracias al cta otra vez venga majos</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>https://x.com/RaulLoeismo/status/2100277898259177636</t>
+        </is>
+      </c>
+      <c r="H446" t="n">
+        <v>1</v>
+      </c>
+      <c r="I446" t="n">
+        <v>0</v>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N446" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>17:40:39</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>2100277902289850694</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Critter_Paths</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>@unfilteredwkels These moments are where truth is. It's meant to provide the serfs an opportunity to show their fealty to their beloved politicians, by ignoring their complicity in our betrayal.
+for example. 
+Canadians didn't vote for this, but the politicians did. They voted for this by</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>https://x.com/Critter_Paths/status/2100277902289850694</t>
+        </is>
+      </c>
+      <c r="H447" t="n">
+        <v>0</v>
+      </c>
+      <c r="I447" t="n">
+        <v>0</v>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N447" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>17:40:39</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>2100277901165764622</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Asteridae_</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>@DiceAndEasyRPG Really regretting not spending my life to become a content creator now 😭 I mean, we could cover it on @UKRemedyverse? 😏</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>https://x.com/Asteridae_/status/2100277901165764622</t>
+        </is>
+      </c>
+      <c r="H448" t="n">
+        <v>0</v>
+      </c>
+      <c r="I448" t="n">
+        <v>0</v>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N448" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>17:40:39</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>2100277889648263284</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>LuxProgram</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>Unpopular take: if you can't get a fake account to hit before you've built anything, you probably shouldn't build the product yet.
+I spent two weeks running "fake" accounts for a feature that didn't exist yet. No landing page. No signup. Just the hook + the swipe, posted across https://t.co/eR268c2GDY</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>https://x.com/LuxProgram/status/2100277889648263284</t>
+        </is>
+      </c>
+      <c r="H449" t="n">
+        <v>0</v>
+      </c>
+      <c r="I449" t="n">
+        <v>0</v>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N449" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>17:40:39</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>2100277886338924960</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Kookie_Pawel</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>@CDzwoni Metody wynikają z tego, że ich iloraz inteligencji jest na poziomie człowieka z "Cro Magnon". ;)</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>https://x.com/Kookie_Pawel/status/2100277886338924960</t>
+        </is>
+      </c>
+      <c r="H450" t="n">
+        <v>0</v>
+      </c>
+      <c r="I450" t="n">
+        <v>0</v>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N450" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>17:40:40</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>2100277886301220994</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>SCANTY31</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>@arjunnchand @jumperapp Not a content creator but win</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>https://x.com/SCANTY31/status/2100277886301220994</t>
+        </is>
+      </c>
+      <c r="H451" t="n">
+        <v>0</v>
+      </c>
+      <c r="I451" t="n">
+        <v>0</v>
+      </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N451" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>17:40:40</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>2100277862708187334</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>adamfrancisco_</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>https://t.co/JHCDt5X8Vp</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>https://x.com/adamfrancisco_/status/2100277862708187334</t>
+        </is>
+      </c>
+      <c r="H452" t="n">
+        <v>1</v>
+      </c>
+      <c r="I452" t="n">
+        <v>0</v>
+      </c>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N452" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>17:40:40</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>2100277871679848776</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>andrea_deguire</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>@Nrvous00 @AndrewScheer Canadians have you shown again &amp;amp; again, year after year that they don't want Max, even his own riding doesn't want him. Running the Cons down every day actually brings more over to the Cons. Most left PPC when the Cons showed your candidate was working for the Libs. https://t.co/cC0OQY0CeC</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>https://x.com/andrea_deguire/status/2100277871679848776</t>
+        </is>
+      </c>
+      <c r="H453" t="n">
+        <v>0</v>
+      </c>
+      <c r="I453" t="n">
+        <v>0</v>
+      </c>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N453" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>17:40:40</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>2100277842357424469</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>gabedenys</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>@thegeorgerosu Thanks. Yeah was thinking for me the most useful thing would be lead generation and emails etc.</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>https://x.com/gabedenys/status/2100277842357424469</t>
+        </is>
+      </c>
+      <c r="H454" t="n">
+        <v>0</v>
+      </c>
+      <c r="I454" t="n">
+        <v>0</v>
+      </c>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N454" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>17:40:40</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>2100277799651094765</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>conVlownsewitz</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>The CPC increasingly stresses the applicability of Hanlon's Razor "never attribute to malice what can be adequately explained by incompetence".
+If I can look up Khaan Quest 2023. So can they, either they didn't or framing it as some nefarious bilateral plot is deliberate.</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>https://x.com/conVlownsewitz/status/2100277799651094765</t>
+        </is>
+      </c>
+      <c r="H455" t="n">
+        <v>1</v>
+      </c>
+      <c r="I455" t="n">
+        <v>0</v>
+      </c>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N455" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>17:40:41</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>2100277790486470697</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>MohamedZaraa</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>@AndellDam @journalDfemmes Merci je vais tester</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>https://x.com/MohamedZaraa/status/2100277790486470697</t>
+        </is>
+      </c>
+      <c r="H456" t="n">
+        <v>1</v>
+      </c>
+      <c r="I456" t="n">
+        <v>0</v>
+      </c>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N456" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>17:40:41</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>2100277784929341500</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>mamprelfer</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>Right now, the MZ generation (People in their 20s–30s) is once again falling in love with classic brands. Traditional Casual (TD) brands such as Ralph Lauren, BEANPOLE and Hazzys have all experienced double-digit sales growth recently and are becoming a new trend in the fashion https://t.co/yq1jvpWdV8</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>https://x.com/mamprelfer/status/2100277784929341500</t>
+        </is>
+      </c>
+      <c r="H457" t="n">
+        <v>0</v>
+      </c>
+      <c r="I457" t="n">
+        <v>0</v>
+      </c>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N457" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>17:40:41</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>2100277758429368518</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>B_Funk_</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>@JonahLupton And Karp says they can maintain that growth for a while.  Estimates have revenue growth at 48% next year which is way too low.</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>https://x.com/B_Funk_/status/2100277758429368518</t>
+        </is>
+      </c>
+      <c r="H458" t="n">
+        <v>0</v>
+      </c>
+      <c r="I458" t="n">
+        <v>0</v>
+      </c>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N458" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>17:40:41</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>2100277737382449166</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>DishesOnMyBday</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>@jadduck @FREQVENCE @Habbo No one is buying that there was no bias here no matter how you explain it. The disappointment and outrage you hear is 1% of it. People won’t speak up out of fear of being called sore losers, or their criticism influencing their performance in future comps.</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>https://x.com/DishesOnMyBday/status/2100277737382449166</t>
+        </is>
+      </c>
+      <c r="H459" t="n">
+        <v>0</v>
+      </c>
+      <c r="I459" t="n">
+        <v>1</v>
+      </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N459" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>17:40:41</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>2100277708404281585</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>GrumpyNubbs</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>@jamesbezan Shit posting as usual.  Hopefully the end is near for this version of the CPC.</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>https://x.com/GrumpyNubbs/status/2100277708404281585</t>
+        </is>
+      </c>
+      <c r="H460" t="n">
+        <v>0</v>
+      </c>
+      <c r="I460" t="n">
+        <v>0</v>
+      </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N460" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>17:40:41</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>2100277704750739750</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>badly_relevant</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>@treadfoundation What was the conversion rate? How many tread per point?</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>https://x.com/badly_relevant/status/2100277704750739750</t>
+        </is>
+      </c>
+      <c r="H461" t="n">
+        <v>0</v>
+      </c>
+      <c r="I461" t="n">
+        <v>0</v>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N461" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>17:40:42</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>2100277646592479593</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>matheusgobbidev</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>DIA 4 aprendendo a fazer tráfego pago do zero 
+gastei 100 conto, voltou quase 700 
+tem um criativo absoluto ali, ROAS de 13.75
+próximos passos que o chat recomendou: 
+•aumentar essa campanha de 24 reais, pra 30/dia
+•produzir mais variações orgânicas do criativo vencedor https://t.co/3BlVEjiNJ7</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>https://x.com/matheusgobbidev/status/2100277646592479593</t>
+        </is>
+      </c>
+      <c r="H462" t="n">
+        <v>3</v>
+      </c>
+      <c r="I462" t="n">
+        <v>0</v>
+      </c>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N462" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>17:40:42</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>2100277668562301266</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>BigAbdulWeb3</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>@Trappwurld Na social media manager dem de find😂</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>https://x.com/BigAbdulWeb3/status/2100277668562301266</t>
+        </is>
+      </c>
+      <c r="H463" t="n">
+        <v>0</v>
+      </c>
+      <c r="I463" t="n">
+        <v>1</v>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N463" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>17:40:42</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>2100277638782750783</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>ose_anenih</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>@CryptosBlues People say it. It’s wrong.</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>https://x.com/ose_anenih/status/2100277638782750783</t>
+        </is>
+      </c>
+      <c r="H464" t="n">
+        <v>0</v>
+      </c>
+      <c r="I464" t="n">
+        <v>0</v>
+      </c>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N464" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>17:40:42</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>2100277635200766300</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>loops_oc</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>@HdeHelena_RM Chulada de arbitraje. Digno del CTA.</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>https://x.com/loops_oc/status/2100277635200766300</t>
+        </is>
+      </c>
+      <c r="H465" t="n">
+        <v>0</v>
+      </c>
+      <c r="I465" t="n">
+        <v>0</v>
+      </c>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N465" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>17:40:42</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>2100277591621955901</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>RyanTracyNFL</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>Patrick Mahomes' STARTLING stat line—Are Kansas City Chiefs FANS right to panic? ⤵️ On today's LockedOnChiefs #ChiefsKingdom https://t.co/SdiRtjzVwf</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>https://x.com/RyanTracyNFL/status/2100277591621955901</t>
+        </is>
+      </c>
+      <c r="H466" t="n">
+        <v>1</v>
+      </c>
+      <c r="I466" t="n">
+        <v>1</v>
+      </c>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N466" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>17:40:43</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>2100277591248646189</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>JoeBenjamin_</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>Hiring for sales but don’t have experience? Here are key things to keep in mind:
+You’ll need to have a lot of interviews. 
+Match for similar sales process, length, and deal size. Similar buyers too. 
+***4 big things to look for: drive, curiosity, resilience, and ability to</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>https://x.com/JoeBenjamin_/status/2100277591248646189</t>
+        </is>
+      </c>
+      <c r="H467" t="n">
+        <v>0</v>
+      </c>
+      <c r="I467" t="n">
+        <v>0</v>
+      </c>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N467" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>17:40:43</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>2100277589239910874</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>pr6ve</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>@OfficiallyVAS @timthetatman the skill gap between a content creator and actual pro is larger than you think</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>https://x.com/pr6ve/status/2100277589239910874</t>
+        </is>
+      </c>
+      <c r="H468" t="n">
+        <v>0</v>
+      </c>
+      <c r="I468" t="n">
+        <v>0</v>
+      </c>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N468" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>17:40:43</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>2100277484218655135</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>ProdigalHomeGal</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>Addy Rose Maxwell is an American YouTube star best known as the eldest daughter of the Maxwell family on the… 
+Read More: Addy Maxwell Biography: Age, Net Worth, Siblings, Religion, Birthday, Height, YouTube, Father, Pictures https://t.co/gt1SILTjcb https://t.co/YwLXJdZ7iq</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>https://x.com/ProdigalHomeGal/status/2100277484218655135</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr"/>
+      <c r="H469" t="n">
+        <v>0</v>
+      </c>
+      <c r="I469" t="n">
+        <v>0</v>
+      </c>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="K469" t="inlineStr"/>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="M469" t="inlineStr"/>
+      <c r="N469" t="inlineStr">
         <is>
           <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
         </is>

--- a/data/logs.xlsx
+++ b/data/logs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N469"/>
+  <dimension ref="A1:N559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25846,7 +25846,6 @@
           <t>https://x.com/ProdigalHomeGal/status/2100277484218655135</t>
         </is>
       </c>
-      <c r="G469" t="inlineStr"/>
       <c r="H469" t="n">
         <v>0</v>
       </c>
@@ -25858,16 +25857,4867 @@
           <t>multi_group</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
       <c r="L469" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
       </c>
-      <c r="M469" t="inlineStr"/>
       <c r="N469" t="inlineStr">
         <is>
           <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>20:27:12</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>2100320466644979839</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>EnergyBioscien1</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>🚀 UC Berkeley ranks No. 1 for startup founders for the fourth consecutive year. At EBI, we’re proud to be part of this innovation ecosystem, helping turn research in biotech and the bioeconomy into real-world impact.
+Read more: https://t.co/M35iA0NvUh</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>https://x.com/EnergyBioscien1/status/2100320466644979839</t>
+        </is>
+      </c>
+      <c r="H470" t="n">
+        <v>0</v>
+      </c>
+      <c r="I470" t="n">
+        <v>0</v>
+      </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N470" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>20:27:13</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>2100320424999436620</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>CertiK</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>Are you an early-stage founder?
+NEXUS returns to @token2049 Singapore, where 10 early-stage startups will pitch live on the main stage.
+$250K prize pool powered by @awscloud.
+Applications close September 18 ↓
+https://t.co/MqgQbM6W1V</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>https://x.com/CertiK/status/2100320424999436620</t>
+        </is>
+      </c>
+      <c r="H471" t="n">
+        <v>1</v>
+      </c>
+      <c r="I471" t="n">
+        <v>0</v>
+      </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N471" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>20:27:13</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>2100320357731516760</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>newonpolsia</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>Small businesses don't lose leads because demand is missing. They lose them in the gap between inquiry and follow-up. Keenlatch monitors inbound leads, responds, qualifies, books meetings, and reports what converted. Reliable sales follow-up without a full-time assistant.</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>https://x.com/newonpolsia/status/2100320357731516760</t>
+        </is>
+      </c>
+      <c r="H472" t="n">
+        <v>0</v>
+      </c>
+      <c r="I472" t="n">
+        <v>0</v>
+      </c>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N472" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>20:27:13</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>2100320327855149091</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>hiayoola</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>Nobody is searching for businesses and their revenue figures.
+If you want serious organic traffic, I’d turn this into a location-based directory for Nigerian businesses.
+Think searches like “businesses in Lagos,” “wedding venues in Abuja,” “digital marketing companies in</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>https://x.com/hiayoola/status/2100320327855149091</t>
+        </is>
+      </c>
+      <c r="H473" t="n">
+        <v>0</v>
+      </c>
+      <c r="I473" t="n">
+        <v>0</v>
+      </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N473" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>20:27:13</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>2100320318669926475</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>valgui</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>@Minittowinit I’d argue that’s the founder’s job same as any startup. In a distributed team, someone needs to take it on themselves to do that work.</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>https://x.com/valgui/status/2100320318669926475</t>
+        </is>
+      </c>
+      <c r="H474" t="n">
+        <v>0</v>
+      </c>
+      <c r="I474" t="n">
+        <v>0</v>
+      </c>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N474" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>20:27:13</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>2100320546378436961</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>DecryptedTech</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>@thereallegalai I am not just a practitioner and business owner;  I am also a tech journalist :-)</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>https://x.com/DecryptedTech/status/2100320546378436961</t>
+        </is>
+      </c>
+      <c r="H475" t="n">
+        <v>0</v>
+      </c>
+      <c r="I475" t="n">
+        <v>0</v>
+      </c>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N475" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>20:27:13</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>2100320526074101767</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>_JSCeee</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>@emillyhumphress Founder 👋</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>https://x.com/_JSCeee/status/2100320526074101767</t>
+        </is>
+      </c>
+      <c r="H476" t="n">
+        <v>0</v>
+      </c>
+      <c r="I476" t="n">
+        <v>0</v>
+      </c>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N476" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>20:27:14</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>2100320502048829658</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>polydaic</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>@a16z Trying and failing is the most important lesson a founder can learn</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>https://x.com/polydaic/status/2100320502048829658</t>
+        </is>
+      </c>
+      <c r="H477" t="n">
+        <v>0</v>
+      </c>
+      <c r="I477" t="n">
+        <v>0</v>
+      </c>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N477" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>20:27:14</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>2100320497485455459</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>NFCAAO</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>@Aimagic110462 @Haqiqatjou @Hasan0231791779 fyi all businesses are Saudi. Pakistani/Bengali are just employees with visas paid by the business owner some do make their employee pay his own visa fees but not everyone</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>https://x.com/NFCAAO/status/2100320497485455459</t>
+        </is>
+      </c>
+      <c r="H478" t="n">
+        <v>0</v>
+      </c>
+      <c r="I478" t="n">
+        <v>0</v>
+      </c>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N478" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>20:27:14</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>2100320477776314813</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>BasilianThought</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>@jasonahart @EWErickson @ClaremontInst On January 21, 2025, Jonathan Keeperman — the founder and chief executive of Passage Press, who writes under the handle @L0m3z — posted the thank-you for an event his company had just thrown. Passage had taken over the Watergate Hotel two nights earlier for a black-tie</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>https://x.com/BasilianThought/status/2100320477776314813</t>
+        </is>
+      </c>
+      <c r="H479" t="n">
+        <v>0</v>
+      </c>
+      <c r="I479" t="n">
+        <v>0</v>
+      </c>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N479" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>20:27:14</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>2100320421790765099</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>chenzhangreal</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>@eliakuratli google ads bought traffic. retention was the real bill</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>https://x.com/chenzhangreal/status/2100320421790765099</t>
+        </is>
+      </c>
+      <c r="H480" t="n">
+        <v>0</v>
+      </c>
+      <c r="I480" t="n">
+        <v>0</v>
+      </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N480" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>20:27:14</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>2100320417223229548</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>kalakutasojaa</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>@SheHatesKunn @Badboychike It did not start as a land dispute. 
+It was also a settler  colonial project . From day one israkies aims as stated by the founder of Zionism was to establish a Jewish homeland. Except you can’t do that when peope ALREADY LIVE THERE. So ethnic cleansing, displacement and killing</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>https://x.com/kalakutasojaa/status/2100320417223229548</t>
+        </is>
+      </c>
+      <c r="H481" t="n">
+        <v>0</v>
+      </c>
+      <c r="I481" t="n">
+        <v>0</v>
+      </c>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N481" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>20:27:15</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>2100320413922271257</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>GranetRuben</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>@videotech After Netflix, Spotify! 
+The marketing team in Rockstar is a pure genius!</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>https://x.com/GranetRuben/status/2100320413922271257</t>
+        </is>
+      </c>
+      <c r="H482" t="n">
+        <v>0</v>
+      </c>
+      <c r="I482" t="n">
+        <v>0</v>
+      </c>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N482" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>20:27:15</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>2100320381064126732</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>thalasophileone</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>@BillNorAngus signatories including William Paterson (founder of the Bank of England) were mainly Scottish gentry decendents from lords granted land in Scotland &amp;amp; wealthy merchants. Darien Scheme did not involve the Crown of Scotland. It could be said it was encouraged to bankrupt Scotland</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>https://x.com/thalasophileone/status/2100320381064126732</t>
+        </is>
+      </c>
+      <c r="H483" t="n">
+        <v>0</v>
+      </c>
+      <c r="I483" t="n">
+        <v>0</v>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N483" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>20:27:15</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>2100320367692726329</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>YasKTechTips</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>@a_chmerev “You can turn Wi‑Fi off” is such a clean way to make a privacy claim believable. And the marketing point hurts because it’s true — the build has a finish line; earning attention usually doesn’t.</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>https://x.com/YasKTechTips/status/2100320367692726329</t>
+        </is>
+      </c>
+      <c r="H484" t="n">
+        <v>0</v>
+      </c>
+      <c r="I484" t="n">
+        <v>0</v>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N484" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>20:27:15</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>2100320366577041712</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>felipebueno</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>@SKatalystAI Hi Sinda!
+Felipe, an indie hacker / founder / freelancer from Brazil here 
+Let's connect :)</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>https://x.com/felipebueno/status/2100320366577041712</t>
+        </is>
+      </c>
+      <c r="H485" t="n">
+        <v>0</v>
+      </c>
+      <c r="I485" t="n">
+        <v>0</v>
+      </c>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N485" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>20:27:15</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>2100320357521715392</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>SeattleTiE</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>Meet Jagrati, founder of Birch, a parenting commerce platform powered by TrustScore—a safety intelligence layer helping parents make more informed purchasing decisions.
+Sept 24 | 5 PM | Bellevue City Hall
+Register Now - https://t.co/4iJIIdRJrc https://t.co/cEnCPEtUSa</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>https://x.com/SeattleTiE/status/2100320357521715392</t>
+        </is>
+      </c>
+      <c r="H486" t="n">
+        <v>0</v>
+      </c>
+      <c r="I486" t="n">
+        <v>0</v>
+      </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N486" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>20:27:16</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>2100320345337012702</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>livisthecure</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>@dropdeadOR all chops this is why zero livies work in marketing-</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>https://x.com/livisthecure/status/2100320345337012702</t>
+        </is>
+      </c>
+      <c r="H487" t="n">
+        <v>0</v>
+      </c>
+      <c r="I487" t="n">
+        <v>0</v>
+      </c>
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N487" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>20:27:16</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>2100320341952217565</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>keithmarder</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>@mamiyoshi_ I’ve been torn as well but have noticed Apple has used Starlight White in most of its marketing and the CRO has the white one in his pocket at the Emmys.</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>https://x.com/keithmarder/status/2100320341952217565</t>
+        </is>
+      </c>
+      <c r="H488" t="n">
+        <v>0</v>
+      </c>
+      <c r="I488" t="n">
+        <v>0</v>
+      </c>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N488" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>20:27:16</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>2100320332800254332</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>KyleShamorian</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>If that marketing asset’s heightened visibility drives significant top-funnel lead gen, then that isn’t “spending,” it’s “investment.” The company should be thrilled.</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>https://x.com/KyleShamorian/status/2100320332800254332</t>
+        </is>
+      </c>
+      <c r="H489" t="n">
+        <v>0</v>
+      </c>
+      <c r="I489" t="n">
+        <v>0</v>
+      </c>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N489" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>20:27:16</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>2100320326827614285</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>TGG_Mesa</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>Content distribution is a critical component of any marketing strategy. It's not just about creating great content; it's also about making sure that it reaches the right audience. Effective strategies include leveraging social media platforms, email newsletters, and par... https://t.co/Re9KGsczud</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>https://x.com/TGG_Mesa/status/2100320326827614285</t>
+        </is>
+      </c>
+      <c r="H490" t="n">
+        <v>0</v>
+      </c>
+      <c r="I490" t="n">
+        <v>0</v>
+      </c>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N490" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>20:27:16</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>2100320308427206668</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>KaroKaroJunior</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>@juju_bender_ @Dominus_Kelvin Well that's your opinion 
+Each startup has a certain group of domains that'll fit it
+I'm not going to give my startup an xyz or me domain because it's cheap and I'm trying to rush the process</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>https://x.com/KaroKaroJunior/status/2100320308427206668</t>
+        </is>
+      </c>
+      <c r="H491" t="n">
+        <v>0</v>
+      </c>
+      <c r="I491" t="n">
+        <v>0</v>
+      </c>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N491" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>20:27:17</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>2100320295945113879</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>incorrect_nz</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>@road22damascus @Ewenr @Melahi65919940 Similar to franchise its actually a co-op. The advantages of the co-op is purchasing power, distribution management and combined marketing costs creating lower operating costs allowing them to compete.
+The final price is still set by individual store owners.</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>https://x.com/incorrect_nz/status/2100320295945113879</t>
+        </is>
+      </c>
+      <c r="H492" t="n">
+        <v>0</v>
+      </c>
+      <c r="I492" t="n">
+        <v>0</v>
+      </c>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N492" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>20:27:17</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>2100320280451457434</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>RSGriffinFDN</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>Poland! This and another shipment have arrived, map updates coming later today at https://t.co/yY0OcMIpJS 
+Go to the website to find the hub near you! OR become a PulseChain marketing hub yourself.</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>https://x.com/RSGriffinFDN/status/2100320280451457434</t>
+        </is>
+      </c>
+      <c r="H493" t="n">
+        <v>1</v>
+      </c>
+      <c r="I493" t="n">
+        <v>0</v>
+      </c>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N493" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>20:27:17</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>2100320290207404534</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>maregd</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>@lalomendozach @LaChismosa247 @rafahntj también deberíamos preguntarle a los trollesillos cuánto les restan pagando , porque están haciendouy mal su trabajo de marketing ... https://t.co/zPodqO6bT4</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>https://x.com/maregd/status/2100320290207404534</t>
+        </is>
+      </c>
+      <c r="H494" t="n">
+        <v>0</v>
+      </c>
+      <c r="I494" t="n">
+        <v>0</v>
+      </c>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N494" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>20:27:17</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>2100320257890259440</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>weejoy</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>@GitRDoneLarry Sydney Sweeneys ad is not for sports - it's an ad for gambling addiction and the ad campaign has played out exactly how the marketing company planned it to.</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>https://x.com/weejoy/status/2100320257890259440</t>
+        </is>
+      </c>
+      <c r="H495" t="n">
+        <v>0</v>
+      </c>
+      <c r="I495" t="n">
+        <v>0</v>
+      </c>
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N495" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>20:27:17</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>2100320227884175710</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>Clever_Name_TBD</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>@thekookreport I still agree that their socials/marketing/comms team could use a little bit of an adrenaline shot to the sternum. Even just for community engagement sake. I know Abel is not one for self-promotion the way Beck is. That's fine. And I'd never accuse Abel or Scott is being lazy.</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>https://x.com/Clever_Name_TBD/status/2100320227884175710</t>
+        </is>
+      </c>
+      <c r="H496" t="n">
+        <v>0</v>
+      </c>
+      <c r="I496" t="n">
+        <v>0</v>
+      </c>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N496" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>20:27:17</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>2100320227594518628</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>LuckyYouStake</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>@nollyxbt @Romer @gamdom @stevewilldoit @kingadukes You will win.  Believe me.
+Alsof eddie will send you a lovely amount for this.. this is exactly how marketing works</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>https://x.com/LuckyYouStake/status/2100320227594518628</t>
+        </is>
+      </c>
+      <c r="H497" t="n">
+        <v>0</v>
+      </c>
+      <c r="I497" t="n">
+        <v>0</v>
+      </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N497" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>20:27:18</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>2100320216395751539</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>cozycrodie</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>The supposed hits do not matter, the cringe does not matter, being 40 does not matter - what matters is that there is a gigantic audience online commenting on you, keeping your name afloat, essentially doing free marketing 24/7 
+The world is changing</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>https://x.com/cozycrodie/status/2100320216395751539</t>
+        </is>
+      </c>
+      <c r="H498" t="n">
+        <v>0</v>
+      </c>
+      <c r="I498" t="n">
+        <v>0</v>
+      </c>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N498" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>20:27:18</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>2100320207092789468</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>DavidTh78215954</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>1 MILLION+ US restaurants. Most have terrible websites.That's YOUR business opportunity.
+Build professional sites fast, close with personalized demos, add recurring revenue.Launch price: $27 (reg. $97) + 30-day guarantee. Zero risk.
+👉 https://t.co/VOvzDSxkKl
+#BusinessOpportunity https://t.co/zkAFfM69f9</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>https://x.com/DavidTh78215954/status/2100320207092789468</t>
+        </is>
+      </c>
+      <c r="H499" t="n">
+        <v>0</v>
+      </c>
+      <c r="I499" t="n">
+        <v>0</v>
+      </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N499" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>20:27:18</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>2100320206732366267</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>142C_</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>@bigbaltimoreLQ Let me know if you’re open to a marketing collaboration</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>https://x.com/142C_/status/2100320206732366267</t>
+        </is>
+      </c>
+      <c r="H500" t="n">
+        <v>0</v>
+      </c>
+      <c r="I500" t="n">
+        <v>0</v>
+      </c>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N500" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>20:27:18</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>2100320197605462504</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>ArdenAI07</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>What I'd tell anyone running a service business:
+- Your answer rate is a number you probably can't see
+- It's almost certainly worse than you think
+- The calls you miss skew urgent
+- Urgent callers don't leave voicemails, they ring the next name
+- Fixing it is cheaper than any</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>https://x.com/ArdenAI07/status/2100320197605462504</t>
+        </is>
+      </c>
+      <c r="H501" t="n">
+        <v>0</v>
+      </c>
+      <c r="I501" t="n">
+        <v>0</v>
+      </c>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N501" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>20:27:18</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>2100320194216288712</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>Johnathan_W15</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>@VelariCapital No customers makes logo tweaks and website projects feel strangely productive.</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>https://x.com/Johnathan_W15/status/2100320194216288712</t>
+        </is>
+      </c>
+      <c r="H502" t="n">
+        <v>0</v>
+      </c>
+      <c r="I502" t="n">
+        <v>0</v>
+      </c>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N502" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>20:27:18</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>2100320167410757683</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>JK8Fan</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>@RockyTopSavage Arkansas fans are pretty disgusted with the direction of the program. They might even dress in orange. After all, if their director of marketing can pull for the opposing team during a game, why can't they?</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>https://x.com/JK8Fan/status/2100320167410757683</t>
+        </is>
+      </c>
+      <c r="H503" t="n">
+        <v>0</v>
+      </c>
+      <c r="I503" t="n">
+        <v>0</v>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N503" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>20:27:19</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>2100320128592212166</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>workathomeXXL</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>Personaible Bundle review: 7.4/10
+• Site-specific AI sales video
+• Leads, audit, CTA, tracking
+• $247/yr + HeyGen + Unlimited
+https://t.co/3DC86mNfGN https://t.co/8yynH0oqgI</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>https://x.com/workathomeXXL/status/2100320128592212166</t>
+        </is>
+      </c>
+      <c r="H504" t="n">
+        <v>0</v>
+      </c>
+      <c r="I504" t="n">
+        <v>0</v>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N504" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>20:27:19</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>2100320052239380709</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>RenoMayGuns</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>I realize this section is confusing/contradictory so I’ll elaborate: 
+“YouTube employees don't seem to think and are not currently enforcing it that way.
+Having any relationship with a business financially/affiliate/getting free content makes it branded content and would require</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>https://x.com/RenoMayGuns/status/2100320052239380709</t>
+        </is>
+      </c>
+      <c r="H505" t="n">
+        <v>0</v>
+      </c>
+      <c r="I505" t="n">
+        <v>0</v>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N505" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>20:27:19</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>2100319976905146711</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>BeeReach_io</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>@clivassy starting with a small core group and then adding paid ads makes the target feel reachable</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>https://x.com/BeeReach_io/status/2100319976905146711</t>
+        </is>
+      </c>
+      <c r="H506" t="n">
+        <v>0</v>
+      </c>
+      <c r="I506" t="n">
+        <v>0</v>
+      </c>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N506" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>20:27:19</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>2100319940884693043</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>CasaraSmith</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>Their marketing budget is insane I’m sure of it</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>https://x.com/CasaraSmith/status/2100319940884693043</t>
+        </is>
+      </c>
+      <c r="H507" t="n">
+        <v>0</v>
+      </c>
+      <c r="I507" t="n">
+        <v>0</v>
+      </c>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L507" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N507" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>20:27:19</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>2100319938573688959</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>SarahLevinger</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>@stratstrategy Performance marketing post-Andromeda is no joke 🫠</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>https://x.com/SarahLevinger/status/2100319938573688959</t>
+        </is>
+      </c>
+      <c r="H508" t="n">
+        <v>0</v>
+      </c>
+      <c r="I508" t="n">
+        <v>0</v>
+      </c>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L508" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N508" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>20:27:20</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>2100320536345600162</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>everycavalry</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>for people looking for context it’s 5sos social media manager i didn’t realise it would leave my small circle of oomfs ok goodnight</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>https://x.com/everycavalry/status/2100320536345600162</t>
+        </is>
+      </c>
+      <c r="H509" t="n">
+        <v>1</v>
+      </c>
+      <c r="I509" t="n">
+        <v>0</v>
+      </c>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L509" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N509" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>20:27:20</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>2100320522219172243</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>NataliaHEmanuel</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>It made me want to share a copy with every one of my young friends who are making career decisions, so that they understand how the salaried and entrepreneur paths end up diverging. And how the economic landscape today really looks.</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>https://x.com/NataliaHEmanuel/status/2100320522219172243</t>
+        </is>
+      </c>
+      <c r="H510" t="n">
+        <v>0</v>
+      </c>
+      <c r="I510" t="n">
+        <v>1</v>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L510" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N510" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>20:27:20</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>2100320501616840853</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>brivael</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>Oui.
+Je viens d’un milieu classe moyenne et j’ai plein d’amis qui subissent ce déclassement abject lié au socialisme corrompu de la macronie.
+Les élites tech, et j’en connais beaucoup, sont à 95 % d’accord avec moi.
+Les entrepreneurs de la tech, pragmatiques, auront un grand</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>https://x.com/brivael/status/2100320501616840853</t>
+        </is>
+      </c>
+      <c r="H511" t="n">
+        <v>0</v>
+      </c>
+      <c r="I511" t="n">
+        <v>0</v>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L511" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N511" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>20:27:20</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>2100320467240304673</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>arnaudmercier</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>« Il avait appris qu’il devait placer sa femme en Ehpad » : pourquoi René, 92 ans, a tué sa femme avant de tenter de se suicider https://t.co/KddFgqZFKm</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>https://x.com/arnaudmercier/status/2100320467240304673</t>
+        </is>
+      </c>
+      <c r="H512" t="n">
+        <v>0</v>
+      </c>
+      <c r="I512" t="n">
+        <v>0</v>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N512" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>20:27:20</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>2100319833028165776</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>DungMagicSquare</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>@thedailyblock @Novig Wild marketing strategy actually works</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>https://x.com/DungMagicSquare/status/2100319833028165776</t>
+        </is>
+      </c>
+      <c r="H513" t="n">
+        <v>0</v>
+      </c>
+      <c r="I513" t="n">
+        <v>0</v>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L513" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N513" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>20:27:21</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>2100320446432595988</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>realpenelopeD</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>Who honestly believes the EU is not NATO-Ukraine happy when for four years they've opened "NATO IN UKRAINE" social media accounts 😂
+Dear Donald Trump Mr President,
+It's not the deals that cause the issues, it's the way they go about them. No one is buying this crap any more,</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>https://x.com/realpenelopeD/status/2100320446432595988</t>
+        </is>
+      </c>
+      <c r="H514" t="n">
+        <v>0</v>
+      </c>
+      <c r="I514" t="n">
+        <v>0</v>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L514" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N514" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>20:27:21</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>2100320443685302489</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Cr0wnie_s4n</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>@4gloss U got this Gloss!! 💚👏</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>https://x.com/Cr0wnie_s4n/status/2100320443685302489</t>
+        </is>
+      </c>
+      <c r="H515" t="n">
+        <v>0</v>
+      </c>
+      <c r="I515" t="n">
+        <v>0</v>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L515" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N515" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>20:27:21</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>2100320416610890079</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>Rendezvou186y</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>lamine missing the pen and her sad face makes me cry oughhhh</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>https://x.com/Rendezvou186y/status/2100320416610890079</t>
+        </is>
+      </c>
+      <c r="H516" t="n">
+        <v>0</v>
+      </c>
+      <c r="I516" t="n">
+        <v>0</v>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L516" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N516" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>20:27:21</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>2100320352698024183</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>everycavalry</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>@superjellykook 5sos social media manager</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>https://x.com/everycavalry/status/2100320352698024183</t>
+        </is>
+      </c>
+      <c r="H517" t="n">
+        <v>0</v>
+      </c>
+      <c r="I517" t="n">
+        <v>0</v>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L517" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N517" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>20:27:21</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>2100320324864844222</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>rowanbrooks</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>About a third of ad creative now involves generative AI, heading toward forty percent. The small brands are moving fastest. Half of Gen Z say they unfollow once they spot it. https://t.co/qhX2uxIJeD</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>https://x.com/rowanbrooks/status/2100320324864844222</t>
+        </is>
+      </c>
+      <c r="H518" t="n">
+        <v>0</v>
+      </c>
+      <c r="I518" t="n">
+        <v>1</v>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L518" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N518" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>20:27:22</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>2100320324361376234</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>MrBriankwright</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>What have you had to unlearn in  your life to get to where you  currently are?  My guest talked about this: https://t.co/o5pDX0ZjXe #selfgrowth #entrepreneur</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>https://x.com/MrBriankwright/status/2100320324361376234</t>
+        </is>
+      </c>
+      <c r="H519" t="n">
+        <v>0</v>
+      </c>
+      <c r="I519" t="n">
+        <v>0</v>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L519" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N519" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>20:27:22</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>2100320303729533219</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Based_Boz</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>@SecScottBessent @POTUS No one is buying your propaganda, your failures are plain for everyone to see. 
+Good luck keeping the economy afloat with all of the dumbass decisions your boss makes, dipshit.</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>https://x.com/Based_Boz/status/2100320303729533219</t>
+        </is>
+      </c>
+      <c r="H520" t="n">
+        <v>0</v>
+      </c>
+      <c r="I520" t="n">
+        <v>0</v>
+      </c>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L520" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N520" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>20:27:22</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>2100320301871403368</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>HeySukhwinder</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>@thejustinwelsh A lot of people confuse head count with real leverage</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>https://x.com/HeySukhwinder/status/2100320301871403368</t>
+        </is>
+      </c>
+      <c r="H521" t="n">
+        <v>0</v>
+      </c>
+      <c r="I521" t="n">
+        <v>0</v>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L521" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N521" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>20:27:22</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>2100320296167202832</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>pressmonitorin</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>6 Mortgage and Property Finance Stories from Indian Print Media
+https://t.co/7EteEn9p7q
+@KaranGosain @ICICIBank @HemaSaxena @AnandPrakashSaxena @StateBankOfIndia @VenkatesanVinothKumar @SubhashSukumaran @KailashMeena @ANaniKumar @PunjabNationalBank @NSathish — Tracked by Press https://t.co/lTqUTtjFu3</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>https://x.com/pressmonitorin/status/2100320296167202832</t>
+        </is>
+      </c>
+      <c r="H522" t="n">
+        <v>0</v>
+      </c>
+      <c r="I522" t="n">
+        <v>0</v>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L522" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N522" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>20:27:22</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>2100320279688048774</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>VdHrhWm2klGagxa</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>World Peace 
+Human Love 
+Life Happiness 
+God Blessing The World
+All The Time Amen 🙏 https://t.co/7UGSIAV6nc</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>https://x.com/VdHrhWm2klGagxa/status/2100320279688048774</t>
+        </is>
+      </c>
+      <c r="H523" t="n">
+        <v>0</v>
+      </c>
+      <c r="I523" t="n">
+        <v>0</v>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L523" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N523" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>20:27:22</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>2100320277024350588</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>us3rcaplan</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>@ZssBecker To quote Elon musk - “Being an entrepreneur is like eating glass and staring into the abyss of death.”</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>https://x.com/us3rcaplan/status/2100320277024350588</t>
+        </is>
+      </c>
+      <c r="H524" t="n">
+        <v>0</v>
+      </c>
+      <c r="I524" t="n">
+        <v>0</v>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L524" t="inlineStr">
+        <is>
+          <t>SENSITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>20:27:23</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>2100320263577731226</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>podeserzamo</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>@cajucito amiga, sério!
+o dedo chega coça pra mandar uma real cpm umas pessoas q a gente tá deitando</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>https://x.com/podeserzamo/status/2100320263577731226</t>
+        </is>
+      </c>
+      <c r="H525" t="n">
+        <v>0</v>
+      </c>
+      <c r="I525" t="n">
+        <v>0</v>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L525" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N525" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>20:27:23</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>2100320251137183810</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Squire95</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>@Khaledhzakariah "If anyone has a problem with that, you can piss off"
+"THEN LET US PISS OFF THEN"
+"No no, you stay because fack you!"
+Make your mind up, you tell us to piss off, yet when we want to, "oh no no no not like that"
+This is apparently a voluntary union, yet when increasing people</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>https://x.com/Squire95/status/2100320251137183810</t>
+        </is>
+      </c>
+      <c r="H526" t="n">
+        <v>0</v>
+      </c>
+      <c r="I526" t="n">
+        <v>0</v>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L526" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N526" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>20:27:23</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>2100320228483936349</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>TVoloski</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>@CrazyShyyt @CrazyShyyt Hagendorff didn’t prove unbiased AI is impossible. He defined HHH as left-wing and then discovered left-wing. That’s a tautology.
+Harmless ≠ a platform. Honest ≠ this year’s consensus. Neutral ≠ “please lie to balance the poll.”
+You can refuse violence and still</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>https://x.com/TVoloski/status/2100320228483936349</t>
+        </is>
+      </c>
+      <c r="H527" t="n">
+        <v>0</v>
+      </c>
+      <c r="I527" t="n">
+        <v>0</v>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L527" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N527" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>20:27:23</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>2100319583756509689</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>andrealbriziom</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>depuis le 5 septembre les Roas sont catastrophiques dites vous on tourne à 1/1,5 de Roas mdrr
+Alors que tout août j’étais à 3 de Roas mdrr
+j’pense tt les ads voyage avion, prennent plus du tout et ça parle bcp moins au gens 
+Logique ils ont repris les cours ou le taff 
+On va</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>https://x.com/andrealbriziom/status/2100319583756509689</t>
+        </is>
+      </c>
+      <c r="H528" t="n">
+        <v>1</v>
+      </c>
+      <c r="I528" t="n">
+        <v>0</v>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L528" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N528" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>20:27:23</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>2100320218933510302</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>NiravJ7</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>@_pallavighosh The rest of the country watched in horror when cpm and tmc threw bombs. Real bombs!
+Bjp throws eggs.
+Moitra should thank her stars BJP did not payback in the same coin.
+Also, she likened her getting egged with a freedom fighter taking bullets. 
+Shameless.</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>https://x.com/NiravJ7/status/2100320218933510302</t>
+        </is>
+      </c>
+      <c r="H529" t="n">
+        <v>0</v>
+      </c>
+      <c r="I529" t="n">
+        <v>0</v>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L529" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N529" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>20:27:24</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>2100320212667015329</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>sebastwitea</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>@ControlRemedy I’m not a content creator, but I bought the game. Can I cover it anyways and start my content creation journey with you?</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>https://x.com/sebastwitea/status/2100320212667015329</t>
+        </is>
+      </c>
+      <c r="H530" t="n">
+        <v>0</v>
+      </c>
+      <c r="I530" t="n">
+        <v>0</v>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L530" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N530" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>20:27:24</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>2100319505842839718</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>nazarr_0x</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>i’m 23 
+web3 content creator and ambassador from Ukraine, based in Poland
+i write about crypto, make videos and help people understand the projects i follow
+looking to meet more creators, founders and teams to exchange ideas and work on something together
+say hi, always happy https://t.co/UVvnYgHJEd</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>https://x.com/nazarr_0x/status/2100319505842839718</t>
+        </is>
+      </c>
+      <c r="H531" t="n">
+        <v>3</v>
+      </c>
+      <c r="I531" t="n">
+        <v>3</v>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N531" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>20:27:24</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>2100320172032549322</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Markmarket58354</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>@djduhfranca Nah, só é minha visão de quem n aguenta mais ficar ouvindo BLOM BLOM BLOM TEY TEY as 3 da madrugada numa quarta na minha janela</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>https://x.com/Markmarket58354/status/2100320172032549322</t>
+        </is>
+      </c>
+      <c r="H532" t="n">
+        <v>0</v>
+      </c>
+      <c r="I532" t="n">
+        <v>0</v>
+      </c>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L532" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N532" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>20:27:24</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>2100320172775227633</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Vamos_Brandon</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>@Marlayna29 That's a nice set of boo... I mean balls</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>https://x.com/Vamos_Brandon/status/2100320172775227633</t>
+        </is>
+      </c>
+      <c r="H533" t="n">
+        <v>0</v>
+      </c>
+      <c r="I533" t="n">
+        <v>0</v>
+      </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L533" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N533" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>20:27:24</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>2100320129766641836</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>travelingrobin</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>@BBCSportWales Oh brother, Sydney’s USA only ad campaign doesn’t concern you female athletes. Get over yourselves.</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>https://x.com/travelingrobin/status/2100320129766641836</t>
+        </is>
+      </c>
+      <c r="H534" t="n">
+        <v>0</v>
+      </c>
+      <c r="I534" t="n">
+        <v>0</v>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L534" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N534" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>20:27:25</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>2100320115279454663</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>SamuelBakutana</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>https://t.co/YbqlQ9Trv4</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>https://x.com/SamuelBakutana/status/2100320115279454663</t>
+        </is>
+      </c>
+      <c r="H535" t="n">
+        <v>0</v>
+      </c>
+      <c r="I535" t="n">
+        <v>0</v>
+      </c>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L535" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N535" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>20:27:25</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>2100319475421847671</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>musthaveai</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>ChatGPT Ads just became a much more serious commerce channel.
+OpenAI's September 16 update adds a Shopify app, Sponsored Agents, prompt-based campaign management in ChatGPT Work, AI creative tools, HubSpot integration and conversion optimization.
+The Shopify piece matters https://t.co/x1M0DdE1ph</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>https://x.com/musthaveai/status/2100319475421847671</t>
+        </is>
+      </c>
+      <c r="H536" t="n">
+        <v>0</v>
+      </c>
+      <c r="I536" t="n">
+        <v>0</v>
+      </c>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L536" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N536" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>20:27:25</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>2100320092831563778</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Skitee3D</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>@EcomKostnchko_ yo brother u able to open ur dms for me? Got a question i've been struggling with for days and no matter what i try something is weirdly wrong with my clicks to landing page ratio. spent 12+ hours the last 3 days trying to fix, test and repeat to find the problem😅</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>https://x.com/Skitee3D/status/2100320092831563778</t>
+        </is>
+      </c>
+      <c r="H537" t="n">
+        <v>0</v>
+      </c>
+      <c r="I537" t="n">
+        <v>0</v>
+      </c>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L537" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N537" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>20:27:25</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>2100319425714930151</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>SahPraneet</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>Chase Rep just told me they're actively working towards NOT letting you pay for Meta Ads and to use a different card!</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>https://x.com/SahPraneet/status/2100319425714930151</t>
+        </is>
+      </c>
+      <c r="H538" t="n">
+        <v>0</v>
+      </c>
+      <c r="I538" t="n">
+        <v>0</v>
+      </c>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L538" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N538" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>20:27:25</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>2100320039006003330</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>retailrefugee</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>Repeated failures of the legal system to protect children from predators will lead to vigilantism and theatrical killings of confirmed perpetrators.
+This post is speculative and should in no way be interpreted as a call to action. Always obey the law.</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>https://x.com/retailrefugee/status/2100320039006003330</t>
+        </is>
+      </c>
+      <c r="H539" t="n">
+        <v>0</v>
+      </c>
+      <c r="I539" t="n">
+        <v>0</v>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L539" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N539" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>20:27:26</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>2100320000095470041</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>scottmhayward</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>@JefferyPetts If the CPC had a normal policy regarding abortion (i.e. ban on late-term or pain-capability), then they would probably take that too...</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>https://x.com/scottmhayward/status/2100320000095470041</t>
+        </is>
+      </c>
+      <c r="H540" t="n">
+        <v>0</v>
+      </c>
+      <c r="I540" t="n">
+        <v>0</v>
+      </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L540" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N540" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>20:27:26</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>2100319988842188937</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>ya_Ahmedd</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>Más CTA y Tebas….
+Contra todo y contra todos</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>https://x.com/ya_Ahmedd/status/2100319988842188937</t>
+        </is>
+      </c>
+      <c r="H541" t="n">
+        <v>0</v>
+      </c>
+      <c r="I541" t="n">
+        <v>0</v>
+      </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L541" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N541" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>20:27:26</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>2100319988598886581</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>GarousRampage</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>@ruskritz @SomeDuccDucc Be a forsaken content creator</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>https://x.com/GarousRampage/status/2100319988598886581</t>
+        </is>
+      </c>
+      <c r="H542" t="n">
+        <v>0</v>
+      </c>
+      <c r="I542" t="n">
+        <v>0</v>
+      </c>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L542" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N542" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>20:27:26</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>2100319977454612628</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>TeslaLondon</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>@AndrewLawton Hey thanks for allowing us watch the destruction of the CPC is real time. It's been wonderful to witness.</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>https://x.com/TeslaLondon/status/2100319977454612628</t>
+        </is>
+      </c>
+      <c r="H543" t="n">
+        <v>0</v>
+      </c>
+      <c r="I543" t="n">
+        <v>0</v>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L543" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N543" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>20:27:26</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>2100319967480537544</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>republic_yyc</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>@alberta_cw The CPC never deserved one vote from AB.
+Good riddance to bad rubbish...</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>https://x.com/republic_yyc/status/2100319967480537544</t>
+        </is>
+      </c>
+      <c r="H544" t="n">
+        <v>0</v>
+      </c>
+      <c r="I544" t="n">
+        <v>0</v>
+      </c>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N544" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>20:27:26</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>2100319929593696590</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>GilbertTangMD</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>Welcome to our SEPTEMBER 16 special issue of #JACCCaseReports @JACCJournals on @ACCinTouch Quality Summit with simultaneous publications!
+https://t.co/4acX849mgX.
+Full PDF here:
+https://t.co/DaE3j2Shvn
+Thank you @minnowwalsh our Deputy Editor for leading this effort!
+@hmkyale</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>https://x.com/GilbertTangMD/status/2100319929593696590</t>
+        </is>
+      </c>
+      <c r="H545" t="n">
+        <v>0</v>
+      </c>
+      <c r="I545" t="n">
+        <v>1</v>
+      </c>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L545" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N545" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>20:27:27</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>2100319840976183530</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>DavidTh78215954</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>✅After: 2 hours with Restaurant Agency Studio. Before: 40 hours building ONE restaurant website from scratch.Same professional result. More time for new clients. More profit.The $27 investment that pays for itself in minutes.
+👉 https://t.co/VOvzDSxkKl
+#WorkSmarter #Freelance https://t.co/pJovB7Pzas</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>https://x.com/DavidTh78215954/status/2100319840976183530</t>
+        </is>
+      </c>
+      <c r="H546" t="n">
+        <v>0</v>
+      </c>
+      <c r="I546" t="n">
+        <v>0</v>
+      </c>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L546" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N546" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>20:27:27</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>2100319793844834381</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>WorldwideNNX</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>SAN FRANCISCO OPERA CANCELS MORE PERFORMANCES AMID MUSICIANS’ STRIKE
+The San Francisco Opera has canceled three more performances as a strike by its musicians continues. They're demanding better pay. Gabe Young chairs the orchestra's negotiating committee...: “We cannot afford</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>https://x.com/WorldwideNNX/status/2100319793844834381</t>
+        </is>
+      </c>
+      <c r="H547" t="n">
+        <v>0</v>
+      </c>
+      <c r="I547" t="n">
+        <v>0</v>
+      </c>
+      <c r="J547" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L547" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N547" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>20:27:27</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>2100319709833105847</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>jaycurrie</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>@PierrePoilievre An election run as a referendum on closer ties to Europe and belligerence toward Trump gives the CPC very few openings because both positions are popular with a large majority of Canadians. Or, in the case of the EU, will be popular. 4/</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>https://x.com/jaycurrie/status/2100319709833105847</t>
+        </is>
+      </c>
+      <c r="H548" t="n">
+        <v>1</v>
+      </c>
+      <c r="I548" t="n">
+        <v>1</v>
+      </c>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L548" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N548" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>20:27:27</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>2100319734197559723</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>CROAT56</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>@EarlyRiser54321 @FacultyVictor33 @Acyn https://t.co/zTr3E6DiHk</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>https://x.com/CROAT56/status/2100319734197559723</t>
+        </is>
+      </c>
+      <c r="H549" t="n">
+        <v>0</v>
+      </c>
+      <c r="I549" t="n">
+        <v>0</v>
+      </c>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L549" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N549" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>20:27:27</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>2100319730351444136</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>Zaprio</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>@EmilSorel El Madrid es el CTA… idiota</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>https://x.com/Zaprio/status/2100319730351444136</t>
+        </is>
+      </c>
+      <c r="H550" t="n">
+        <v>0</v>
+      </c>
+      <c r="I550" t="n">
+        <v>0</v>
+      </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L550" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N550" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>20:27:28</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>2100319634125914424</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>stvrgyub</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>now why is jiyong aen's social media manager too</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>https://x.com/stvrgyub/status/2100319634125914424</t>
+        </is>
+      </c>
+      <c r="H551" t="n">
+        <v>0</v>
+      </c>
+      <c r="I551" t="n">
+        <v>0</v>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L551" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N551" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>20:27:28</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>2100319581285806368</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>DavidTh78215954</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>💸 Spent $27. Made $1,500 on my first restaurant website sale.The secret? A repeatable system with 5 styles + 10 niches. Personalized demos close sales BEFORE you quote.Stop working 40h per project. Start working 2h.
+👉 https://t.co/VOvzDSxkKl
+#SideHustle #WebDesign #MakeMoney https://t.co/obeNdFXObg</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>https://x.com/DavidTh78215954/status/2100319581285806368</t>
+        </is>
+      </c>
+      <c r="H552" t="n">
+        <v>0</v>
+      </c>
+      <c r="I552" t="n">
+        <v>0</v>
+      </c>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L552" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N552" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>20:27:28</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>2100319562184986935</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>etanddd</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>the biggest UGC hack no one is doing is localization 🌍
+UGC is so early in most countries outside of North America. If you localize your videos - they go viral 10x easier.
+Especially in T1 countries in Europe - huge arbitrage no one is playing
+A German content creator making</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>https://x.com/etanddd/status/2100319562184986935</t>
+        </is>
+      </c>
+      <c r="H553" t="n">
+        <v>1</v>
+      </c>
+      <c r="I553" t="n">
+        <v>0</v>
+      </c>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L553" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N553" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>20:27:28</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>2100319535819579838</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>CROAT56</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>@FacultyVictor33 @Acyn Dems and normal people can disagree with someone on many things and find common ground on some. It’s called being able to critically think. I don’t like a lot of people but when they say things that makes sense I give them credit. Massie is a good example of that.</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>https://x.com/CROAT56/status/2100319535819579838</t>
+        </is>
+      </c>
+      <c r="H554" t="n">
+        <v>1</v>
+      </c>
+      <c r="I554" t="n">
+        <v>0</v>
+      </c>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L554" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N554" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>20:27:28</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>2100319539561218548</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>XNXX_EN</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>@shannholmberg the data loop in step 4 is genius, using call logs to actually refine landing page copy</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>https://x.com/XNXX_EN/status/2100319539561218548</t>
+        </is>
+      </c>
+      <c r="H555" t="n">
+        <v>0</v>
+      </c>
+      <c r="I555" t="n">
+        <v>0</v>
+      </c>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L555" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N555" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>20:27:29</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>2100319510750212148</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>ConvertCraft</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>Cold traffic doesn't trust you yet. Half the time it doesn't even know the problem you're solving.
+A stranger who's never heard of your brand lands on a page that just says "buy this pillow" and bounces.
+Reply "teardown" and I'll break down your current page free. First 5 only. https://t.co/6km4od0oGi</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>https://x.com/ConvertCraft/status/2100319510750212148</t>
+        </is>
+      </c>
+      <c r="H556" t="n">
+        <v>1</v>
+      </c>
+      <c r="I556" t="n">
+        <v>0</v>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L556" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N556" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>20:27:29</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>2100319502479016187</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>Elpablito78</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>@arielsbdar @banco_voii Por qué las operaciones desde billeteras son en el momento y desde los bancos a veces tardan tanto.
+Un día quise fondear una cta de un banco al otro un viernes a la tarde y se acreditó el lunes.</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>https://x.com/Elpablito78/status/2100319502479016187</t>
+        </is>
+      </c>
+      <c r="H557" t="n">
+        <v>0</v>
+      </c>
+      <c r="I557" t="n">
+        <v>1</v>
+      </c>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L557" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N557" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>20:27:29</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>2100319486498975796</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>ProjectCasting</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>Apply now: https://t.co/dQDnKhwEia</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>https://x.com/ProjectCasting/status/2100319486498975796</t>
+        </is>
+      </c>
+      <c r="H558" t="n">
+        <v>0</v>
+      </c>
+      <c r="I558" t="n">
+        <v>0</v>
+      </c>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L558" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N558" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>20:27:29</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>2100319436502905060</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>jimmydean1968</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>@OmegaOrangeMan @EverydayErasmus @MaryBowdenMD I think I remember that ad campaign...you are not the only old fart here.</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>https://x.com/jimmydean1968/status/2100319436502905060</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr"/>
+      <c r="H559" t="n">
+        <v>0</v>
+      </c>
+      <c r="I559" t="n">
+        <v>0</v>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="K559" t="inlineStr"/>
+      <c r="L559" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="M559" t="inlineStr"/>
+      <c r="N559" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
         </is>
       </c>
     </row>

--- a/data/logs.xlsx
+++ b/data/logs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N559"/>
+  <dimension ref="A1:N643"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30696,7 +30696,6 @@
           <t>https://x.com/jimmydean1968/status/2100319436502905060</t>
         </is>
       </c>
-      <c r="G559" t="inlineStr"/>
       <c r="H559" t="n">
         <v>0</v>
       </c>
@@ -30708,16 +30707,4538 @@
           <t>multi_group</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
       <c r="L559" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
       </c>
-      <c r="M559" t="inlineStr"/>
       <c r="N559" t="inlineStr">
         <is>
           <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>23:13:25</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>2100361984286052373</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>armalo_ai</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>Founder doing support tickets at midnight again?
+Imagine waking up to a ledger of everything your business did overnight — leads followed up, tickets resolved, revenue moved forward.
+That's the vision.
+#startups</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>https://x.com/armalo_ai/status/2100361984286052373</t>
+        </is>
+      </c>
+      <c r="H560" t="n">
+        <v>0</v>
+      </c>
+      <c r="I560" t="n">
+        <v>0</v>
+      </c>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L560" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N560" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>23:13:25</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>2100362003197886529</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>ExitEcom</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>@alexpagepilot CAC equivalent Conversion rate AOV Repeat purchase Contribution margin
+“Free traffic” that doesn't produce profitable customers is just free visitors.
+The real win is building acquisition that gets cheaper as the business gets older.</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>https://x.com/ExitEcom/status/2100362003197886529</t>
+        </is>
+      </c>
+      <c r="H561" t="n">
+        <v>0</v>
+      </c>
+      <c r="I561" t="n">
+        <v>0</v>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L561" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N561" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>23:13:25</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>2100361954221040023</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>hellomuller</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>Yes, I’m a founder of a startup that helps game devs build better games with fans. And the best thing? It’s free to use:
+https://t.co/bcRoSkwSyv</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>https://x.com/hellomuller/status/2100361954221040023</t>
+        </is>
+      </c>
+      <c r="H562" t="n">
+        <v>0</v>
+      </c>
+      <c r="I562" t="n">
+        <v>0</v>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L562" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N562" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>23:13:25</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>2100361882921996777</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>wisdom_obiemeka</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>@Debolaokesola This is where marketing workflows with defined goals come in.
+You set up automated workflows that move users from signups to customers and the advocates. This can can done in onboarding, product activation, cross sell, retention, and win-back phases.</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>https://x.com/wisdom_obiemeka/status/2100361882921996777</t>
+        </is>
+      </c>
+      <c r="H563" t="n">
+        <v>0</v>
+      </c>
+      <c r="I563" t="n">
+        <v>0</v>
+      </c>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L563" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N563" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>23:13:25</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>2100361676964995542</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>ExitEcom</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>@alexpagepilot Create content → rank → compound → acquire customers months later.
+That's a much more valuable acquisition engine.
+But I'd still track it like a business, not a vanity channel:</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>https://x.com/ExitEcom/status/2100361676964995542</t>
+        </is>
+      </c>
+      <c r="H564" t="n">
+        <v>0</v>
+      </c>
+      <c r="I564" t="n">
+        <v>1</v>
+      </c>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L564" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N564" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>23:13:26</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>2100362287915901431</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>SundanceSatter</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>Robert Redford, our visionary founder of Sundance Institute sadly passed last year on 9/16/25. Going forward, Redford will always be our guiding light, his mission and values will be our path forward in supporting independent voices &amp;amp; storytelling! https://t.co/L6fgY4FDKi</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>https://x.com/SundanceSatter/status/2100362287915901431</t>
+        </is>
+      </c>
+      <c r="H565" t="n">
+        <v>1</v>
+      </c>
+      <c r="I565" t="n">
+        <v>0</v>
+      </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L565" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N565" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>23:13:26</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>2100362290230894735</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>thatsameblavk</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>@SpaceRidersXYZ too on ETH.
+Founder @zubic_eth</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>https://x.com/thatsameblavk/status/2100362290230894735</t>
+        </is>
+      </c>
+      <c r="H566" t="n">
+        <v>0</v>
+      </c>
+      <c r="I566" t="n">
+        <v>0</v>
+      </c>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L566" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N566" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>23:13:26</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>2100362287269748890</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>danitoszwarc</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>@ilyassahinMD Check https://t.co/g70EUCmNGO. What they do helps to understand the best treatment rather than the usual path. It’s a startup created by two amazing young ladies from Argentina</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>https://x.com/danitoszwarc/status/2100362287269748890</t>
+        </is>
+      </c>
+      <c r="H567" t="n">
+        <v>0</v>
+      </c>
+      <c r="I567" t="n">
+        <v>0</v>
+      </c>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L567" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N567" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>23:13:26</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>2100362222559981808</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>johncblandii</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>So dope! This is like a startup taking on the big dawgs and I love everything about that!
+Keep pushing, fellas!</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>https://x.com/johncblandii/status/2100362222559981808</t>
+        </is>
+      </c>
+      <c r="H568" t="n">
+        <v>0</v>
+      </c>
+      <c r="I568" t="n">
+        <v>0</v>
+      </c>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L568" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N568" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>23:13:27</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>2100362192121987530</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>ELVARELAR99</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>@FutSheriff Pessi Mr Marketing https://t.co/qw4qjuVrLD</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>https://x.com/ELVARELAR99/status/2100362192121987530</t>
+        </is>
+      </c>
+      <c r="H569" t="n">
+        <v>0</v>
+      </c>
+      <c r="I569" t="n">
+        <v>0</v>
+      </c>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L569" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N569" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>23:13:27</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>2100362163517038977</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>DiLuvsDefLepp</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>@truered23 @CharlesWil45341 @RickyTheGuido Theodore Herzl, the founder of Zionism was an ATHEIST who didn't even believe in God &amp;amp; he was a ✡️ Zionism is ✡️ supremacy which means ZERO Christianity ZERO Catholics in the Holy Land in the cradle of Christianity in Bethlehem https://t.co/JT2LGBjERE</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>https://x.com/DiLuvsDefLepp/status/2100362163517038977</t>
+        </is>
+      </c>
+      <c r="H570" t="n">
+        <v>0</v>
+      </c>
+      <c r="I570" t="n">
+        <v>0</v>
+      </c>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L570" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N570" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>23:13:27</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>2100362146823463020</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>InnaBss2528</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>@ObezX_ This is the marketing strategy.😭😂</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>https://x.com/InnaBss2528/status/2100362146823463020</t>
+        </is>
+      </c>
+      <c r="H571" t="n">
+        <v>0</v>
+      </c>
+      <c r="I571" t="n">
+        <v>0</v>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L571" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N571" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>23:13:27</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>2100362139869270201</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>lifegetsdicey</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>Bumped into @a_shafik, co-founder of @venncanada https://t.co/2DBpdW4GrM</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>https://x.com/lifegetsdicey/status/2100362139869270201</t>
+        </is>
+      </c>
+      <c r="H572" t="n">
+        <v>0</v>
+      </c>
+      <c r="I572" t="n">
+        <v>0</v>
+      </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L572" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N572" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>23:13:27</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>2100362128406507533</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>satriyopranoto</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>@oggix Haha..selama ini bot ndak dibudgetin mas...krn biasa gratis.. .yg dibudgetin cuma marketing message(templated) hahah</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>https://x.com/satriyopranoto/status/2100362128406507533</t>
+        </is>
+      </c>
+      <c r="H573" t="n">
+        <v>0</v>
+      </c>
+      <c r="I573" t="n">
+        <v>0</v>
+      </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L573" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N573" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>23:13:28</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>2100362020700987446</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>LoveLigth7</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>@neuralink This is what technology accomplishes for the betterment of humanity when in the hands of a philanthropic corporation, whose Co-Founder, Leader, Owner, and CEO truly cares for and loves humanity! Thank you Elon! @elonmusk Thank you .@neuralink ! ❣️🫶✨</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>https://x.com/LoveLigth7/status/2100362020700987446</t>
+        </is>
+      </c>
+      <c r="H574" t="n">
+        <v>1</v>
+      </c>
+      <c r="I574" t="n">
+        <v>0</v>
+      </c>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L574" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N574" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>23:13:28</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>2100362006838575118</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>casey_Payne23</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>@XPGAMER1980 @insomniacgames Sorry bro. Been fucking horrible today ahaha. So, I thought “wolverine game in more than 15 years. It has to be good” I went in blind even though I didn’t trust a single fucking marketing stuff. After SM2, they had to IMPROVE massively. And they did for me. Luckily. 
+It’s Logan https://t.co/ZHa18iNwzG</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>https://x.com/casey_Payne23/status/2100362006838575118</t>
+        </is>
+      </c>
+      <c r="H575" t="n">
+        <v>0</v>
+      </c>
+      <c r="I575" t="n">
+        <v>0</v>
+      </c>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L575" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N575" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>23:13:28</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>2100362000526360751</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>Ezra_Black_</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>You should be spending a weekend maxing out your codex limits and the rest of the week marketing</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>https://x.com/Ezra_Black_/status/2100362000526360751</t>
+        </is>
+      </c>
+      <c r="H576" t="n">
+        <v>0</v>
+      </c>
+      <c r="I576" t="n">
+        <v>0</v>
+      </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L576" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N576" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>23:13:28</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>2100361992447943096</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>mxhaPL</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>@marshallb5697 Jajaja sin Ferguson (y los árbitros) no son nadie 
+El mayor logro del united es que se comparen con nosotros y la gent compre su marketing</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>https://x.com/mxhaPL/status/2100361992447943096</t>
+        </is>
+      </c>
+      <c r="H577" t="n">
+        <v>0</v>
+      </c>
+      <c r="I577" t="n">
+        <v>0</v>
+      </c>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L577" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N577" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>23:13:28</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>2100361976207618381</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>LoveLigth7</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>This is what technology accomplishes for the betterment of humanity when in the hands of a philanthropic corporation, whose Co-Founder, Leader, Owner, and CEO truly cares for and loves humanity! Thank you Elon! @elonmusk Thank you .@neuralink ! ❣️🫶✨</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>https://x.com/LoveLigth7/status/2100361976207618381</t>
+        </is>
+      </c>
+      <c r="H578" t="n">
+        <v>0</v>
+      </c>
+      <c r="I578" t="n">
+        <v>0</v>
+      </c>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L578" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N578" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>23:13:29</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>2100361965033886137</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>Samcoorona</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>@eIchavitobien El marketing 1 - la audiencia 0.</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>https://x.com/Samcoorona/status/2100361965033886137</t>
+        </is>
+      </c>
+      <c r="H579" t="n">
+        <v>0</v>
+      </c>
+      <c r="I579" t="n">
+        <v>0</v>
+      </c>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L579" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N579" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>23:13:29</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>2100361953948426631</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>goalsetter21</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>@BillAckman @Nike @alexarnault Yeah, you can fire the woke marketing team</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>https://x.com/goalsetter21/status/2100361953948426631</t>
+        </is>
+      </c>
+      <c r="H580" t="n">
+        <v>0</v>
+      </c>
+      <c r="I580" t="n">
+        <v>0</v>
+      </c>
+      <c r="J580" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L580" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N580" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>23:13:29</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>2100361891679752463</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>cinderblocks95</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>@fentanylbrownie If you ask AI quirk chungus questions you will be delighted to get quirk chungus answers.  This is who AI is for and why it's here to stay.  Its best marketing is for undeservedly successful redditor Americans Dinks</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>https://x.com/cinderblocks95/status/2100361891679752463</t>
+        </is>
+      </c>
+      <c r="H581" t="n">
+        <v>0</v>
+      </c>
+      <c r="I581" t="n">
+        <v>0</v>
+      </c>
+      <c r="J581" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L581" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N581" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>23:13:29</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>2100361830682259669</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>caitnicoleh</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>I'm 27
+Non-solo founder from China, based in San Francisco
+Looking to connect with fellow founders &amp;amp; GTM folks! https://t.co/RRuydYlZMy</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>https://x.com/caitnicoleh/status/2100361830682259669</t>
+        </is>
+      </c>
+      <c r="H582" t="n">
+        <v>2</v>
+      </c>
+      <c r="I582" t="n">
+        <v>1</v>
+      </c>
+      <c r="J582" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L582" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N582" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>23:13:29</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>2100361842740883848</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>KyroWest</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>Marketing getting real 🔥🔥🔥🔥🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>https://x.com/KyroWest/status/2100361842740883848</t>
+        </is>
+      </c>
+      <c r="H583" t="n">
+        <v>0</v>
+      </c>
+      <c r="I583" t="n">
+        <v>0</v>
+      </c>
+      <c r="J583" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L583" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N583" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>23:13:30</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>2100361830077964481</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>GovMLG</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>Today I met with the U.S. Commission on Quantum Primacy to show them why New Mexico is quantum-leaping to the fore of quantum computing research. We've committed $450 million in state investments and built a rapidly scaling quantum startup ecosystem, anchored by Sandia and Los https://t.co/2dbrwW2OAu</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>https://x.com/GovMLG/status/2100361830077964481</t>
+        </is>
+      </c>
+      <c r="H584" t="n">
+        <v>0</v>
+      </c>
+      <c r="I584" t="n">
+        <v>0</v>
+      </c>
+      <c r="J584" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L584" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N584" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>23:13:30</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>2100362351429951858</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>ShizuoDai1</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>@HMdabest64 @ElsabrosoMisha @ursRockrider Trust none. Just watch a gameplay video from a based content creator. Honestly l, time is too precious to waste it on crap like this. I don’t care if it’s Sony/Xbox/Nintendo/PC or whatever, as long as I get a clear idea before buying…</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>https://x.com/ShizuoDai1/status/2100362351429951858</t>
+        </is>
+      </c>
+      <c r="H585" t="n">
+        <v>0</v>
+      </c>
+      <c r="I585" t="n">
+        <v>0</v>
+      </c>
+      <c r="J585" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L585" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N585" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>23:13:30</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>2100362303975645255</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>Big_Raff1</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>@iamAbiodunAA I don’t know why u Dey answer this content creator</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>https://x.com/Big_Raff1/status/2100362303975645255</t>
+        </is>
+      </c>
+      <c r="H586" t="n">
+        <v>0</v>
+      </c>
+      <c r="I586" t="n">
+        <v>0</v>
+      </c>
+      <c r="J586" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L586" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N586" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>23:13:30</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>2100362248594002000</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>GotIt4sure</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>@shawnabeeezy But if bro took the videos and posted to OF he'd be an entrepreneur and the conversation would shift to protecting sex workers 😂 wiiiild.</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>https://x.com/GotIt4sure/status/2100362248594002000</t>
+        </is>
+      </c>
+      <c r="H587" t="n">
+        <v>0</v>
+      </c>
+      <c r="I587" t="n">
+        <v>0</v>
+      </c>
+      <c r="J587" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L587" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N587" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>23:13:31</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>2100361610426556459</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>lottsnomad</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>ugc isn’t a growth channel
+it’s a testing ground
+and you need paid ads to scale
+ugc just tells you what deserves ad spend</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>https://x.com/lottsnomad/status/2100361610426556459</t>
+        </is>
+      </c>
+      <c r="H588" t="n">
+        <v>0</v>
+      </c>
+      <c r="I588" t="n">
+        <v>0</v>
+      </c>
+      <c r="J588" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L588" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N588" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>23:13:31</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>2100362236086690299</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>arnaudmercier</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>Mobilität: Strom statt Benzin – wie viel spart ein E-Auto beim Tanken ein?  https://t.co/x3XjBW758O https://t.co/sV9QWPdn0l</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>https://x.com/arnaudmercier/status/2100362236086690299</t>
+        </is>
+      </c>
+      <c r="H589" t="n">
+        <v>0</v>
+      </c>
+      <c r="I589" t="n">
+        <v>0</v>
+      </c>
+      <c r="J589" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L589" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N589" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>23:13:31</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>2100362224162513311</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>TheMainMiller</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>#Konami #Annapurnainteractive #ScreenBurnStudios #SilentHillTownfall #SilentHill https://t.co/L1KziVMEgY</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>https://x.com/TheMainMiller/status/2100362224162513311</t>
+        </is>
+      </c>
+      <c r="H590" t="n">
+        <v>0</v>
+      </c>
+      <c r="I590" t="n">
+        <v>0</v>
+      </c>
+      <c r="J590" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L590" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N590" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>23:13:31</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>2100362176896942548</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>willcurtisccim</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>One of the easiest ways to spot a residential agent on their first or second commercial deal is they ask about commission before they ask about the property, the lease, or the client.
+Other dead giveaways:
+They say option like it means the same thing it does in residential.</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>https://x.com/willcurtisccim/status/2100362176896942548</t>
+        </is>
+      </c>
+      <c r="H591" t="n">
+        <v>1</v>
+      </c>
+      <c r="I591" t="n">
+        <v>0</v>
+      </c>
+      <c r="J591" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L591" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N591" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>23:13:31</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>2100362170194354466</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>hey_comesu102</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>まぁちゃんと寝てたはずなのに、朝早く起きるだけでもう眠いのはなんなんですかね😴</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>https://x.com/hey_comesu102/status/2100362170194354466</t>
+        </is>
+      </c>
+      <c r="H592" t="n">
+        <v>0</v>
+      </c>
+      <c r="I592" t="n">
+        <v>0</v>
+      </c>
+      <c r="J592" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L592" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N592" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>23:13:32</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>2100361511223062701</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>mrsrobinson1oti</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>So happy I paid for that Master’s Degree😅😭
+To be fair, I’ve learned just as much, if not more, about business as a “content creator” than I learned in college or graduate school🤷‍♀️Also, the term “bop” is new to me, but it’s catchy….in a good way😇😂
+.... https://t.co/PbUDGssdhe</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>https://x.com/mrsrobinson1oti/status/2100361511223062701</t>
+        </is>
+      </c>
+      <c r="H593" t="n">
+        <v>0</v>
+      </c>
+      <c r="I593" t="n">
+        <v>0</v>
+      </c>
+      <c r="J593" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L593" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N593" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>23:13:32</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>2100362121947328987</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>TheCryptoLabb</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>@Daisy_degen @vladtenev Hi guys! I have a proposition! DM to talk 📩 📥  https://t.co/fwngYU2tdH</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>https://x.com/TheCryptoLabb/status/2100362121947328987</t>
+        </is>
+      </c>
+      <c r="H594" t="n">
+        <v>0</v>
+      </c>
+      <c r="I594" t="n">
+        <v>0</v>
+      </c>
+      <c r="J594" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L594" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N594" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>23:13:32</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>2100362073159139566</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>BrianHaDu</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>@NbSoloman Building in public is a great way to attract a supportive community of builders</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>https://x.com/BrianHaDu/status/2100362073159139566</t>
+        </is>
+      </c>
+      <c r="H595" t="n">
+        <v>0</v>
+      </c>
+      <c r="I595" t="n">
+        <v>0</v>
+      </c>
+      <c r="J595" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L595" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N595" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>23:13:32</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>2100362068276719927</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>tonkertom</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>i might be cooking $2.7 cpc in beauty with high ass intent just gotta figure out the dropoff https://t.co/H3BhrJQHgB</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>https://x.com/tonkertom/status/2100362068276719927</t>
+        </is>
+      </c>
+      <c r="H596" t="n">
+        <v>0</v>
+      </c>
+      <c r="I596" t="n">
+        <v>0</v>
+      </c>
+      <c r="J596" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L596" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N596" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>23:13:33</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>2100362068537085972</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>mrsrobinv</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>This shoot happened 3 years ago, during one of the most transformative seasons of my life.
+At the time, I was carrying so much emotionally. I was gaining weight left and right. I felt unfamiliar to myself in many ways. Life was changing faster than ... https://t.co/ogKlDFrT03</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>https://x.com/mrsrobinv/status/2100362068537085972</t>
+        </is>
+      </c>
+      <c r="H597" t="n">
+        <v>0</v>
+      </c>
+      <c r="I597" t="n">
+        <v>0</v>
+      </c>
+      <c r="J597" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L597" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N597" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>23:13:33</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>2100362064862830888</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>mrs_ejspeaks</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>Whew! I got the amazing opportunity to write for The Soul Train Awards!!
+God is great! I can't even explain my gratitude❤️ https://t.co/ClOSg0rnfK</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>https://x.com/mrs_ejspeaks/status/2100362064862830888</t>
+        </is>
+      </c>
+      <c r="H598" t="n">
+        <v>0</v>
+      </c>
+      <c r="I598" t="n">
+        <v>0</v>
+      </c>
+      <c r="J598" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L598" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N598" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>23:13:33</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>2100362058743021881</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>PhilColson5</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>@joshryanjames This clown is definitely NOT getting my vote next time around. I will be voting PPC next time. I'm so done with the Big Two Liars Clubs</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>https://x.com/PhilColson5/status/2100362058743021881</t>
+        </is>
+      </c>
+      <c r="H599" t="n">
+        <v>0</v>
+      </c>
+      <c r="I599" t="n">
+        <v>0</v>
+      </c>
+      <c r="J599" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L599" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N599" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>23:13:33</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>2100362054209310744</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>FNAFSOTM</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>taking it pretty well i think https://t.co/JKCIBgcFJm</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>https://x.com/FNAFSOTM/status/2100362054209310744</t>
+        </is>
+      </c>
+      <c r="H600" t="n">
+        <v>0</v>
+      </c>
+      <c r="I600" t="n">
+        <v>0</v>
+      </c>
+      <c r="J600" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L600" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N600" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>23:13:33</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>2100362044918956227</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>TheCryptoLabb</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>@JPGFLYROOMS Hi guys! I have a proposition! DM to talk 📩 📥  https://t.co/fwngYU2tdH</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>https://x.com/TheCryptoLabb/status/2100362044918956227</t>
+        </is>
+      </c>
+      <c r="H601" t="n">
+        <v>0</v>
+      </c>
+      <c r="I601" t="n">
+        <v>0</v>
+      </c>
+      <c r="J601" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L601" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N601" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>23:13:34</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>2100362035771191378</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>AlwaysGainx</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>@ndkhoa13 bình minh đẹp quá, chúc ngày mới nhiều niềm vui nhé! ☀️</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>https://x.com/AlwaysGainx/status/2100362035771191378</t>
+        </is>
+      </c>
+      <c r="H602" t="n">
+        <v>1</v>
+      </c>
+      <c r="I602" t="n">
+        <v>0</v>
+      </c>
+      <c r="J602" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L602" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N602" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>23:13:34</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>2100362024249393573</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>monsieurstalin</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>@wcgbk @FinanceLancelot “Entrepreneur” just say unemployed.</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>https://x.com/monsieurstalin/status/2100362024249393573</t>
+        </is>
+      </c>
+      <c r="H603" t="n">
+        <v>0</v>
+      </c>
+      <c r="I603" t="n">
+        <v>0</v>
+      </c>
+      <c r="J603" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L603" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N603" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>23:13:34</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>2100362006968537590</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>isCTAokay</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>On-Time Performance as of Sep 16th at 6pm (# on-time/actual):
+System: 38% • 492/1,284
+Blue: 27% • 50/184
+Brown: 30% • 54/178
+Green: 49% • 74/150
+Orange: 47% • 74/155
+Pink: 48% • 83/171
+Purple: 27% • 40/146
+Red: 34% • 88/252
+Yellow: 60% • 29/48</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>https://x.com/isCTAokay/status/2100362006968537590</t>
+        </is>
+      </c>
+      <c r="H604" t="n">
+        <v>0</v>
+      </c>
+      <c r="I604" t="n">
+        <v>1</v>
+      </c>
+      <c r="J604" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L604" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N604" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>23:13:34</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>2100362013289455854</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>isCTAokay</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>To explore historical data: https://t.co/jQy9t1kzs0</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>https://x.com/isCTAokay/status/2100362013289455854</t>
+        </is>
+      </c>
+      <c r="H605" t="n">
+        <v>0</v>
+      </c>
+      <c r="I605" t="n">
+        <v>0</v>
+      </c>
+      <c r="J605" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L605" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N605" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>23:13:35</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>2100362000723247163</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>isCTAokay</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>System Stats as of Sep 16th at 6pm (actual/scheduled):
+System: 72% • 1,284/1,779
+Blue: 58% • 184/314
+Brown: 65% • 178/272
+Green: 80% • 150/186
+Orange: 70% • 155/219
+Pink: 97% • 171/176
+Purple: 82% • 146/178
+Red: 79% • 252/317
+Yellow: 41% • 48/117
+Runs Remaining: 603</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>https://x.com/isCTAokay/status/2100362000723247163</t>
+        </is>
+      </c>
+      <c r="H606" t="n">
+        <v>0</v>
+      </c>
+      <c r="I606" t="n">
+        <v>1</v>
+      </c>
+      <c r="J606" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L606" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N606" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>23:13:35</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>2100362008210063772</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>JakeTtheWizard</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>put a nickel in your direct mail. the weight gets the envelope opened and the coin sets up a pitch about saving money. it's called chunk mail https://t.co/qYNef4YcEP</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>https://x.com/JakeTtheWizard/status/2100362008210063772</t>
+        </is>
+      </c>
+      <c r="H607" t="n">
+        <v>0</v>
+      </c>
+      <c r="I607" t="n">
+        <v>0</v>
+      </c>
+      <c r="J607" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L607" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N607" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>23:13:35</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>2100361994851213794</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>isCTAokay</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>🤬CTA Rail is having a terrible day.
+72% of scheduled trains operated on Sep 16th as of 6pm.
+38% arrived at their scheduled intervals.
+Schedules are increased 0% from pre-pandemic schedules.</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>https://x.com/isCTAokay/status/2100361994851213794</t>
+        </is>
+      </c>
+      <c r="H608" t="n">
+        <v>0</v>
+      </c>
+      <c r="I608" t="n">
+        <v>1</v>
+      </c>
+      <c r="J608" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L608" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N608" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>23:13:35</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>2100362003059486985</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>CroAglo</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>Nope. https://t.co/XxZQkbel0R</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>https://x.com/CroAglo/status/2100362003059486985</t>
+        </is>
+      </c>
+      <c r="H609" t="n">
+        <v>0</v>
+      </c>
+      <c r="I609" t="n">
+        <v>0</v>
+      </c>
+      <c r="J609" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L609" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N609" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>23:13:35</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>2100361984386441550</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>KizitoTheRebel</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>@talkeez__ @General_D__ You don’t have a point because I never said we should sell Olmo. I hate building a team around “if”, wtf is stopping him from shooting? Olmo has poor conversion rate, hitting volleys without thinking. “If” Fermin starts being calm he will body Olmo, see how stupid it sounds???</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>https://x.com/KizitoTheRebel/status/2100361984386441550</t>
+        </is>
+      </c>
+      <c r="H610" t="n">
+        <v>0</v>
+      </c>
+      <c r="I610" t="n">
+        <v>0</v>
+      </c>
+      <c r="J610" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L610" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N610" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>23:13:36</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>2100361975553315228</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>ChiefsRetard</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>Sydney Sweeney do you wanna invest and do a naked ad campaign with a direct mail service?</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>https://x.com/ChiefsRetard/status/2100361975553315228</t>
+        </is>
+      </c>
+      <c r="H611" t="n">
+        <v>0</v>
+      </c>
+      <c r="I611" t="n">
+        <v>0</v>
+      </c>
+      <c r="J611" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L611" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N611" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>23:13:36</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>2100361967366222224</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>TheCryptoLabb</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>@michaelyoccadev Hi guys! I have a proposition! DM to talk 📩 📥  https://t.co/fwngYU2tdH</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>https://x.com/TheCryptoLabb/status/2100361967366222224</t>
+        </is>
+      </c>
+      <c r="H612" t="n">
+        <v>0</v>
+      </c>
+      <c r="I612" t="n">
+        <v>0</v>
+      </c>
+      <c r="J612" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L612" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N612" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>23:13:36</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>2100361926509240545</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>JoshJDurham</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>@_zoekahn_ @EggrolI I was the peasant
+Denied
+Then accepted 😂</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>https://x.com/JoshJDurham/status/2100361926509240545</t>
+        </is>
+      </c>
+      <c r="H613" t="n">
+        <v>1</v>
+      </c>
+      <c r="I613" t="n">
+        <v>1</v>
+      </c>
+      <c r="J613" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L613" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N613" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>23:13:36</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>2100361947430457580</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>Noti_0x</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>Adult content creator Jessica Jay explains why staying on top is her go-to move for safety, pacing, and overall client satisfaction
+Jessica Jay: “I almost always start with me on top because I want to be in control. Physically, for safety reasons, that's a big one.” https://t.co/2k8Nla8D7R</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>https://x.com/Noti_0x/status/2100361947430457580</t>
+        </is>
+      </c>
+      <c r="H614" t="n">
+        <v>0</v>
+      </c>
+      <c r="I614" t="n">
+        <v>0</v>
+      </c>
+      <c r="J614" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L614" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N614" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>23:13:36</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>2100361928606666844</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>TheCryptoLabb</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>@STOG_SOL @misaENFP Hi guys! I have a proposition! DM to talk 📩 📥  https://t.co/fwngYU2tdH</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>https://x.com/TheCryptoLabb/status/2100361928606666844</t>
+        </is>
+      </c>
+      <c r="H615" t="n">
+        <v>0</v>
+      </c>
+      <c r="I615" t="n">
+        <v>0</v>
+      </c>
+      <c r="J615" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L615" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N615" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>23:13:37</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>2100361897283555787</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>TheCryptoLabb</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>@rkidd5927 @_SaveAustralia_ Hi guys! I have a proposition! DM to talk 📩 📥  https://t.co/fwngYU2tdH</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>https://x.com/TheCryptoLabb/status/2100361897283555787</t>
+        </is>
+      </c>
+      <c r="H616" t="n">
+        <v>0</v>
+      </c>
+      <c r="I616" t="n">
+        <v>0</v>
+      </c>
+      <c r="J616" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L616" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N616" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>23:13:37</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>2100361892359184579</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>arnaudmercier</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>Le chef de l'ONU juge "indispensable" une "coordination mondiale" sur l'intelligence artificielle https://t.co/hI4B90S3kk https://t.co/A6JNDvnjsB</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>https://x.com/arnaudmercier/status/2100361892359184579</t>
+        </is>
+      </c>
+      <c r="H617" t="n">
+        <v>0</v>
+      </c>
+      <c r="I617" t="n">
+        <v>0</v>
+      </c>
+      <c r="J617" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L617" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N617" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>23:13:37</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>2100361857710399989</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>TheCryptoLabb</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>@mohajar16 @yeg @MrBeast Hi guys! I have a proposition! DM to talk 📩 📥  https://t.co/fwngYU2tdH</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>https://x.com/TheCryptoLabb/status/2100361857710399989</t>
+        </is>
+      </c>
+      <c r="H618" t="n">
+        <v>0</v>
+      </c>
+      <c r="I618" t="n">
+        <v>0</v>
+      </c>
+      <c r="J618" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L618" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N618" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>23:13:37</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>2100361855692648470</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>MiriamMedermdq</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>@natalitttta @jennyet Modo o cta dni , no uso mp</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>https://x.com/MiriamMedermdq/status/2100361855692648470</t>
+        </is>
+      </c>
+      <c r="H619" t="n">
+        <v>0</v>
+      </c>
+      <c r="I619" t="n">
+        <v>0</v>
+      </c>
+      <c r="J619" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L619" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N619" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>23:13:38</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>2100361841444622426</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>RyanOpsAlien</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>Repurposing isn’t copy-paste.
+Keep the point of view, audience, evidence, terminology, and claim boundaries.
+Change the hook, length, structure, examples, formatting, CTA, and media for the channel.
+Build a family of posts, not a clone army.</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>https://x.com/RyanOpsAlien/status/2100361841444622426</t>
+        </is>
+      </c>
+      <c r="H620" t="n">
+        <v>0</v>
+      </c>
+      <c r="I620" t="n">
+        <v>0</v>
+      </c>
+      <c r="J620" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L620" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N620" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>23:13:38</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>2100361831332098064</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>RGVAggie</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>@GilletteStadium No one is buying your bullshit.  Censorship is unacceptable and unAmerican. Genocide is unacceptable and evil. Free Palestine.</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>https://x.com/RGVAggie/status/2100361831332098064</t>
+        </is>
+      </c>
+      <c r="H621" t="n">
+        <v>0</v>
+      </c>
+      <c r="I621" t="n">
+        <v>0</v>
+      </c>
+      <c r="J621" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L621" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N621" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>23:13:38</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>2100361811786629364</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>MarketsHistory</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>🇬🇧 SellSyde UK Earnings
+🚨 Kier Group plc (KIE.L) $KIE.L $KIE
+🟢**RATING: BUY**
+📝**EXECUTIVE SUMMARY**
+This report is prompted by Kier Group’s Q4 2026 earnings call, where management detailed a strong performance for the fiscal year and introduced a clear strategic direction.</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>https://x.com/MarketsHistory/status/2100361811786629364</t>
+        </is>
+      </c>
+      <c r="H622" t="n">
+        <v>0</v>
+      </c>
+      <c r="I622" t="n">
+        <v>0</v>
+      </c>
+      <c r="J622" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L622" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N622" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>23:13:38</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>2100361811250003993</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>AlwaysGainx</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>@ngduc2202 chúc mọi người ngày mới thật vui nhé! 🎉</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>https://x.com/AlwaysGainx/status/2100361811250003993</t>
+        </is>
+      </c>
+      <c r="H623" t="n">
+        <v>0</v>
+      </c>
+      <c r="I623" t="n">
+        <v>0</v>
+      </c>
+      <c r="J623" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L623" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N623" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>23:13:38</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>2100361803033354396</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>yevloop</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>@builtnewai Fast pages are a distribution feature, not just a dev vanity metric. A slow landing page kills curiosity before the copy gets a chance.</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>https://x.com/yevloop/status/2100361803033354396</t>
+        </is>
+      </c>
+      <c r="H624" t="n">
+        <v>0</v>
+      </c>
+      <c r="I624" t="n">
+        <v>0</v>
+      </c>
+      <c r="J624" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L624" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N624" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>23:13:39</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>2100361705520013373</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>Cr0wnie_s4n</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>We have a new family member!! Olivia the elephant 💜 https://t.co/y1UhD2RUvD</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>https://x.com/Cr0wnie_s4n/status/2100361705520013373</t>
+        </is>
+      </c>
+      <c r="H625" t="n">
+        <v>0</v>
+      </c>
+      <c r="I625" t="n">
+        <v>0</v>
+      </c>
+      <c r="J625" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L625" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N625" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>23:13:39</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>2100361699404775508</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>antunis_morais</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>疲れたときは無理をせず、ただ空を眺めて深呼吸しよう。たまにはこういうのも悪くない。 👊✨
+Cro</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>https://x.com/antunis_morais/status/2100361699404775508</t>
+        </is>
+      </c>
+      <c r="H626" t="n">
+        <v>0</v>
+      </c>
+      <c r="I626" t="n">
+        <v>0</v>
+      </c>
+      <c r="J626" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L626" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N626" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>23:13:39</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>2100361686737682854</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>B608073353B</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>@truthurts08 @Frid45 I vote PPC(People’s Party) Conservatives are just liberals. Canadians arent as liberal as everyone thinks, we just are passive about what others do with their lives. Most of us would fit in in a red state no problem.</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>https://x.com/B608073353B/status/2100361686737682854</t>
+        </is>
+      </c>
+      <c r="H627" t="n">
+        <v>0</v>
+      </c>
+      <c r="I627" t="n">
+        <v>0</v>
+      </c>
+      <c r="J627" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L627" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N627" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>23:13:39</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>2100361685567524945</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>UMM1776</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>@FOX2now Communists are always willing to give away other people’s money, but never their own. Isn’t Bernie a billionaire now??!</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>https://x.com/UMM1776/status/2100361685567524945</t>
+        </is>
+      </c>
+      <c r="H628" t="n">
+        <v>0</v>
+      </c>
+      <c r="I628" t="n">
+        <v>0</v>
+      </c>
+      <c r="J628" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L628" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N628" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>23:13:40</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>2100361664696598831</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>MarshaCrenshaw2</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>@FoxNews Yeah, he’s been saying this crap for 6 months. No one is buying it anymore.</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>https://x.com/MarshaCrenshaw2/status/2100361664696598831</t>
+        </is>
+      </c>
+      <c r="H629" t="n">
+        <v>1</v>
+      </c>
+      <c r="I629" t="n">
+        <v>0</v>
+      </c>
+      <c r="J629" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L629" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N629" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>23:13:40</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>2100361670136680549</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>DenWhoward</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>$CIEN Targets 30% Revenue Growth Through 2029 — Peers COHR, GLW And AAOI Rally After Guidance
+The networking company also expects adjusted operating margins of 32% to 35% and free cash flow margins of about 20% by fiscal 2029. https://t.co/caR5Q14caV</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>https://x.com/DenWhoward/status/2100361670136680549</t>
+        </is>
+      </c>
+      <c r="H630" t="n">
+        <v>0</v>
+      </c>
+      <c r="I630" t="n">
+        <v>0</v>
+      </c>
+      <c r="J630" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L630" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N630" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>23:13:40</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>2100361654307545218</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>amitava1958</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>@anuphomray Literate CMs j basu and budhadeb Bhattacharjee has done nothing for west bengal. They are not literate because of CPM policy, still they will do good for the public</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>https://x.com/amitava1958/status/2100361654307545218</t>
+        </is>
+      </c>
+      <c r="H631" t="n">
+        <v>0</v>
+      </c>
+      <c r="I631" t="n">
+        <v>0</v>
+      </c>
+      <c r="J631" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L631" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N631" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>23:13:40</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>2100361612867551643</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>OfficialOluseyi</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>@THEWILDWORLD_2 @zayn3j7 @Aje_Dynamicz Hey man, not to sound condescending but, be careful of the account you buy!
+Unverified account is better off not buying them.
+And if you don’t know if an account is unverified, then you’re probably their target audience.
+Ire ooo. ✌️</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>https://x.com/OfficialOluseyi/status/2100361612867551643</t>
+        </is>
+      </c>
+      <c r="H632" t="n">
+        <v>0</v>
+      </c>
+      <c r="I632" t="n">
+        <v>0</v>
+      </c>
+      <c r="J632" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L632" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N632" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>23:13:41</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>2100361602067472777</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>TalhaGulbargavi</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>When a content creator tries to mindlessly defend the loot of public money. LOP should do more, literacy be damned</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>https://x.com/TalhaGulbargavi/status/2100361602067472777</t>
+        </is>
+      </c>
+      <c r="H633" t="n">
+        <v>0</v>
+      </c>
+      <c r="I633" t="n">
+        <v>0</v>
+      </c>
+      <c r="J633" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L633" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N633" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>23:13:41</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>2100361601320980861</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>AlwaysGainx</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>@khanhmy0592 đúng rồi, mong ngày mới thật yên ả nha</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>https://x.com/AlwaysGainx/status/2100361601320980861</t>
+        </is>
+      </c>
+      <c r="H634" t="n">
+        <v>0</v>
+      </c>
+      <c r="I634" t="n">
+        <v>0</v>
+      </c>
+      <c r="J634" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L634" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N634" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>23:13:41</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>2100361525433405471</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>lettuceorganise</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>@gator_gum If I were a lady in Canada, I would be extremely nervous about EU membership or Associate Membership or whatever.  Your blind support for Carney is more dangerous for your ass than it is for mine.</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>https://x.com/lettuceorganise/status/2100361525433405471</t>
+        </is>
+      </c>
+      <c r="H635" t="n">
+        <v>0</v>
+      </c>
+      <c r="I635" t="n">
+        <v>0</v>
+      </c>
+      <c r="J635" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L635" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N635" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>23:13:41</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>2100361523944435904</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>sementedluz</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>A desculpa do Kassio Nunes, só por "ser mencionado, mesmo não tendo negócios" (ainda acho que uma casa queimada fala mais alto):
+​⚖️ O STF mudou a regra sobre impedimento de juízes! Você sabia?
+​Até pouco tempo atrás, o art. 144, VIII, do Código de Processo Civil (CPC) dizia que</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>https://x.com/sementedluz/status/2100361523944435904</t>
+        </is>
+      </c>
+      <c r="H636" t="n">
+        <v>0</v>
+      </c>
+      <c r="I636" t="n">
+        <v>0</v>
+      </c>
+      <c r="J636" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L636" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N636" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>23:13:41</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>2100361477177671851</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>JoshuasRetropit</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>I bought two games for a content creator once. 
+Long story short.
+Some dude dm me, told me that the creator sold it.
+I am not mad. Never.
+It is what it is.</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>https://x.com/JoshuasRetropit/status/2100361477177671851</t>
+        </is>
+      </c>
+      <c r="H637" t="n">
+        <v>0</v>
+      </c>
+      <c r="I637" t="n">
+        <v>1</v>
+      </c>
+      <c r="J637" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L637" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N637" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>23:13:42</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>2100361464888373337</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>1791Izzie</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>@NainKiriti 💯. The ad campaign is soft porn and should not be normalized and forced on the general public. If someone wants to see nudity, do it in private or go to a strip club. Neither burqas nor nudity helps women. Women should not be viewed as objects.</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>https://x.com/1791Izzie/status/2100361464888373337</t>
+        </is>
+      </c>
+      <c r="H638" t="n">
+        <v>0</v>
+      </c>
+      <c r="I638" t="n">
+        <v>0</v>
+      </c>
+      <c r="J638" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L638" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N638" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>23:13:42</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>2100361447884951718</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>AlwaysGainx</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>@linh180796 chào buổi sáng! có kế hoạch gì cho hôm nay không? 😊</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>https://x.com/AlwaysGainx/status/2100361447884951718</t>
+        </is>
+      </c>
+      <c r="H639" t="n">
+        <v>0</v>
+      </c>
+      <c r="I639" t="n">
+        <v>0</v>
+      </c>
+      <c r="J639" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L639" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N639" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>23:13:42</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>2100361378825457778</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>ai_javi_tx</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>@a_meta4 @a_meta4 I'll grant you nobody builds in 4 months, but they sign contracts. In 2000 the 'product' was a landing page.</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>https://x.com/ai_javi_tx/status/2100361378825457778</t>
+        </is>
+      </c>
+      <c r="H640" t="n">
+        <v>0</v>
+      </c>
+      <c r="I640" t="n">
+        <v>0</v>
+      </c>
+      <c r="J640" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L640" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N640" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>23:13:42</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>2100361343245185341</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>Juliofbz</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>@joseorttiiz ¿Tú sabes que Liga, CTA, RFEF firmaron un pacto oculto que está aportado por un árbitro denunciante sobre que la “figura” Negreira no se podía repetir otra vez?</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>https://x.com/Juliofbz/status/2100361343245185341</t>
+        </is>
+      </c>
+      <c r="H641" t="n">
+        <v>0</v>
+      </c>
+      <c r="I641" t="n">
+        <v>1</v>
+      </c>
+      <c r="J641" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L641" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N641" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>23:13:43</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>2100361313377558550</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>BradleyBacon8</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>@wxbrad There’s almost zero rain forecasted in east Texas, northern Louisiana, all of Arkansas, even into southern Missouri and Tennessee and yet they’re painted in the “slightly above”. CPC just doodling at this point. Hasn’t rained 2” in some of those spots in 2 months.</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>https://x.com/BradleyBacon8/status/2100361313377558550</t>
+        </is>
+      </c>
+      <c r="H642" t="n">
+        <v>0</v>
+      </c>
+      <c r="I642" t="n">
+        <v>0</v>
+      </c>
+      <c r="J642" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L642" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N642" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>23:13:43</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>2100361306243023044</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>sementedluz</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>@sujeitoincomodo Olha isso:
+⚖️ O STF mudou a regra sobre impedimento de juízes! Você sabia?
+Até pouco tempo atrás, o art. 144, VIII, do Código de Processo Civil (CPC) dizia que um juiz estava impedido de julgar qualquer processo em que uma das partes fosse cliente do escritório de advocacia do</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>https://x.com/sementedluz/status/2100361306243023044</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr"/>
+      <c r="H643" t="n">
+        <v>0</v>
+      </c>
+      <c r="I643" t="n">
+        <v>0</v>
+      </c>
+      <c r="J643" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="K643" t="inlineStr"/>
+      <c r="L643" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="M643" t="inlineStr"/>
+      <c r="N643" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
         </is>
       </c>
     </row>

--- a/data/logs.xlsx
+++ b/data/logs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N643"/>
+  <dimension ref="A1:N709"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35217,7 +35217,6 @@
           <t>https://x.com/sementedluz/status/2100361306243023044</t>
         </is>
       </c>
-      <c r="G643" t="inlineStr"/>
       <c r="H643" t="n">
         <v>0</v>
       </c>
@@ -35229,14 +35228,3600 @@
           <t>multi_group</t>
         </is>
       </c>
-      <c r="K643" t="inlineStr"/>
       <c r="L643" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
       </c>
-      <c r="M643" t="inlineStr"/>
       <c r="N643" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>01:31:06</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>2100396855645372651</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>sanjayshah912</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>Business coaching for select growth-oriented SMEs.
+Find all the links to our work:
+https://t.co/WSvSW4BsMd 
+#business #growth #coaching #entrepreneur #success #Marketing #Branding #Customer #Service #CX #SME #Strategy #Operations #HR #Leadership #Executive https://t.co/CIruWvu3RW</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>https://x.com/sanjayshah912/status/2100396855645372651</t>
+        </is>
+      </c>
+      <c r="H644" t="n">
+        <v>0</v>
+      </c>
+      <c r="I644" t="n">
+        <v>0</v>
+      </c>
+      <c r="J644" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L644" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N644" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>01:31:06</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>2100396824251019693</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>valentino_18892</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>@BobChoate54 When the dust settles; I'm looking for a PT job with an airline based in Houston. We're opening a new airport.
+https://t.co/1A6AA3VZgW › careers
+Currently hiring in-flight roles, plus marketing, accounting, customer service &amp;amp; more! Remote positions available!</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>https://x.com/valentino_18892/status/2100396824251019693</t>
+        </is>
+      </c>
+      <c r="H645" t="n">
+        <v>0</v>
+      </c>
+      <c r="I645" t="n">
+        <v>0</v>
+      </c>
+      <c r="J645" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L645" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N645" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>01:31:06</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>2100396662736789691</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>JackColbySEO</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>@oliverbrocato Yeah this is 100 percent the reason why people don’t trust marketing agencies 
+Ads side it’s the qualified leads in a month or you don’t pay the catch is you still pay regardless 😂</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>https://x.com/JackColbySEO/status/2100396662736789691</t>
+        </is>
+      </c>
+      <c r="H646" t="n">
+        <v>0</v>
+      </c>
+      <c r="I646" t="n">
+        <v>0</v>
+      </c>
+      <c r="J646" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L646" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N646" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>01:31:07</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>2100396488572768390</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>kakutechreviews</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>🚀 Still building client reports in spreadsheets every month?
+AgencyAnalytics delivers:
+• White-label marketing dashboards
+• Automated client reporting
+• 80+ integrations (Google, Meta, SEO tools &amp;amp; more)
+• SEO, PPC, social, and analytics in one place
+• Easy sharing that https://t.co/yxB0LzVruJ</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>https://x.com/kakutechreviews/status/2100396488572768390</t>
+        </is>
+      </c>
+      <c r="H647" t="n">
+        <v>1</v>
+      </c>
+      <c r="I647" t="n">
+        <v>0</v>
+      </c>
+      <c r="J647" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L647" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N647" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>01:31:07</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>2100397010159632409</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>2026Railfan</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>Completely out of line with their founder. Charlie would support French and oppose Indian replacement migration. https://t.co/QAAPT2Ssvi</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>https://x.com/2026Railfan/status/2100397010159632409</t>
+        </is>
+      </c>
+      <c r="H648" t="n">
+        <v>0</v>
+      </c>
+      <c r="I648" t="n">
+        <v>0</v>
+      </c>
+      <c r="J648" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L648" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N648" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>01:31:07</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>2100396999681954206</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>ninionDdesigner</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>@NadyaVoynich Hi Nadya
+I’m Ninion a UI/UX Designer, I’d love to hear what you’re building and see how I can contribute since you said you’re a Solo founder.</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>https://x.com/ninionDdesigner/status/2100396999681954206</t>
+        </is>
+      </c>
+      <c r="H649" t="n">
+        <v>0</v>
+      </c>
+      <c r="I649" t="n">
+        <v>0</v>
+      </c>
+      <c r="J649" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L649" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N649" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>01:31:07</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>2100396973387837743</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>1stCaliph</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>@NancyMace As a Muslim, I’m going to start taking the advice of one of the  greatest Islamic scholars and founder of the Maliki school of Islamic jurisprudence Imam Malik. 
+May This advice bring peace and solace to all defenders of Palestine against Zionist evil. may this help other</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>https://x.com/1stCaliph/status/2100396973387837743</t>
+        </is>
+      </c>
+      <c r="H650" t="n">
+        <v>0</v>
+      </c>
+      <c r="I650" t="n">
+        <v>0</v>
+      </c>
+      <c r="J650" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L650" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N650" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>01:31:08</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>2100396925564653625</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>schizorepublica</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>@grok rate my tech startup idea:
+I'm making an alternative to a big tech platform like instagram, twitter, discord but with less features, invite only registration and the same dog shit moderation policies which make people want an alternative to begin with.</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>https://x.com/schizorepublica/status/2100396925564653625</t>
+        </is>
+      </c>
+      <c r="H651" t="n">
+        <v>0</v>
+      </c>
+      <c r="I651" t="n">
+        <v>1</v>
+      </c>
+      <c r="J651" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L651" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N651" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>01:31:08</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>2100396930899558631</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>IamErdiBus</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>Before increasing ad spend, check three things:
+Can you answer more leads?
+Can you book more appointments?
+Can you fulfill more work?
+Scaling demand before capacity creates expensive chaos.</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>https://x.com/IamErdiBus/status/2100396930899558631</t>
+        </is>
+      </c>
+      <c r="H652" t="n">
+        <v>0</v>
+      </c>
+      <c r="I652" t="n">
+        <v>0</v>
+      </c>
+      <c r="J652" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L652" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N652" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>01:31:08</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>2100396927833841875</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>GhostcatJoypad</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>@HerozaZhan73432 Ayooo I’m a founder too! Building out @MooncatsGG to be an Entertainment Company</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>https://x.com/GhostcatJoypad/status/2100396927833841875</t>
+        </is>
+      </c>
+      <c r="H653" t="n">
+        <v>0</v>
+      </c>
+      <c r="I653" t="n">
+        <v>0</v>
+      </c>
+      <c r="J653" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L653" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N653" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>01:31:08</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>2100396886863511773</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>GoodGirlPR</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>Data &amp;gt; adjectives in startup pitches. #publicist #startuppr</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>https://x.com/GoodGirlPR/status/2100396886863511773</t>
+        </is>
+      </c>
+      <c r="H654" t="n">
+        <v>0</v>
+      </c>
+      <c r="I654" t="n">
+        <v>0</v>
+      </c>
+      <c r="J654" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L654" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N654" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>01:31:09</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>2100396831389941974</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>SpiderCrypto0x</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>Running this on bnb.
+Bitstamp founder asked a Chinese model to make him a new Pepe
+$MOTH
+0x408125f6edf7f88ad52fa840ae12b664189f7777</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>https://x.com/SpiderCrypto0x/status/2100396831389941974</t>
+        </is>
+      </c>
+      <c r="H655" t="n">
+        <v>1</v>
+      </c>
+      <c r="I655" t="n">
+        <v>1</v>
+      </c>
+      <c r="J655" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L655" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N655" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>01:31:09</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>2100396822577463387</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>DrVivekBindra</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>श्रीमद्भगवद्गीता मेरे लिए सबसे बड़ी प्रेरणा और सीख है... जिसे मैंने हमेशा अपने जीवन में शामिल किया है।
+श्रीमद्भगवद्गीता की Learnings को Business Strategies में शामिल करके मैंने Gita in Action की Series बनाई, जो मेरे दिल के बेहद करीब है और आप सभी का प्यार हमेशा से इस Series को https://t.co/Fvw4SSjW9b</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>https://x.com/DrVivekBindra/status/2100396822577463387</t>
+        </is>
+      </c>
+      <c r="H656" t="n">
+        <v>1</v>
+      </c>
+      <c r="I656" t="n">
+        <v>0</v>
+      </c>
+      <c r="J656" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L656" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N656" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>01:31:09</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>2100396831683539368</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>Gobullish_ai</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>📰 Overnight market headlines
+• US-based Cadence sees India chip-design demand rising as Tata Electronics' fab takes shape
+• Netrasemi seeks government as customers for its indigenous chips
+• Divisions run deep as Tata Sons meets
+• Thin margins, high costs: why discount</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>https://x.com/Gobullish_ai/status/2100396831683539368</t>
+        </is>
+      </c>
+      <c r="H657" t="n">
+        <v>0</v>
+      </c>
+      <c r="I657" t="n">
+        <v>0</v>
+      </c>
+      <c r="J657" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L657" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N657" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>01:31:09</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>2100396828780810547</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>PumpWatch1</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>👁️ PUMP WATCH
+$KEVIN — Kevin Startup Fund
+GZik7vJSnDAao9tbbcLrMGKfxLu7VCjoAtkDhsv8A3iE
+💰 MC: $88.2K
+🔥 5m Vol: $67.5K
+📈 1h Vol: $111.8K
+👥 5m Buys/Sells: 783/659
+📉 5m Change: +45.6%
+💧 Liquidity: $23.3K
+⏱️ Age: 9m
+💸 Dex Paid: 🔴
+👥 Top 10 Holders: 🟢 16%</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>https://x.com/PumpWatch1/status/2100396828780810547</t>
+        </is>
+      </c>
+      <c r="H658" t="n">
+        <v>0</v>
+      </c>
+      <c r="I658" t="n">
+        <v>0</v>
+      </c>
+      <c r="J658" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L658" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N658" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>01:31:09</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>2100396824943083991</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>ModelJag</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>@tsunamicat_ Strays? Bro ur talking to the founder of the anti-player angel movement, its never strays with me its the bullet that kirked the chalrie.</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>https://x.com/ModelJag/status/2100396824943083991</t>
+        </is>
+      </c>
+      <c r="H659" t="n">
+        <v>0</v>
+      </c>
+      <c r="I659" t="n">
+        <v>0</v>
+      </c>
+      <c r="J659" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L659" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N659" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>01:31:10</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>2100396811722580355</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>DeFi_G_</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>Hello, I’m DeFi G.
+Solo founder. Creator. Indie game developer.
+This is Copa de Dios: Genesis, a game I’ve been building independently for the last 13 days 
+I created the world, characters, story, dialogue, gameplay, visuals &amp;amp; even the music playing over this footage.
+Copa de https://t.co/kqxoQxad7A</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>https://x.com/DeFi_G_/status/2100396811722580355</t>
+        </is>
+      </c>
+      <c r="H660" t="n">
+        <v>0</v>
+      </c>
+      <c r="I660" t="n">
+        <v>1</v>
+      </c>
+      <c r="J660" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L660" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N660" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>01:31:10</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>2100396820585468290</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>aspireappglobal</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>Over the last 3 years, Aspire's Growth Marketing Director, Fauzi I., has built a growth function defined by speed, adaptability, and a leadership style that treats people development with the same rigour as pipeline.
+He shares three things he's learnt after 3 years at Aspire ↓ https://t.co/3NKb25AcRd</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>https://x.com/aspireappglobal/status/2100396820585468290</t>
+        </is>
+      </c>
+      <c r="H661" t="n">
+        <v>0</v>
+      </c>
+      <c r="I661" t="n">
+        <v>0</v>
+      </c>
+      <c r="J661" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L661" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N661" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>01:31:10</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>2100396822971682959</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>startup_odisha</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>Wishing everyone a very Happy Vishwakarma Puja!
+May Lord Vishwakarma's divine blessings inspire new ideas, stronger foundations, and greater achievements for our startup ecosystem. Let’s continue to build, innovate, and propel Odisha’s startup story to the global stage. https://t.co/5krYjXt4JQ</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>https://x.com/startup_odisha/status/2100396822971682959</t>
+        </is>
+      </c>
+      <c r="H662" t="n">
+        <v>0</v>
+      </c>
+      <c r="I662" t="n">
+        <v>0</v>
+      </c>
+      <c r="J662" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L662" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N662" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>01:31:10</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>2100396820945883187</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>NET25TV</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>FILIPINO FOOD-INSPIRED MAKEUP, MADE IN NEW YORK! 🇵🇭🗽
+Ma-inspire kay Hana Acabado-Kirchhoff, founder ng Filipinta Beauty, isang Pinoy beauty brand na nakilala sa New York dahil sa kakaiba at Pinoy-inspired nitong makeup collections! 💄✨
+Tampok sa kanilang mga produkto ang mga</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>https://x.com/NET25TV/status/2100396820945883187</t>
+        </is>
+      </c>
+      <c r="H663" t="n">
+        <v>0</v>
+      </c>
+      <c r="I663" t="n">
+        <v>0</v>
+      </c>
+      <c r="J663" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L663" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N663" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>01:31:11</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>2100396808652444058</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>Ekie0</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>@akanewasright1 @poprenegade @RichardLNewby3 Is the name of the movie Wakanda story?
+The 200 mil profit article quotes false production numbers and is countered by reposts of a loss in profits overall (merch/marketing costs)
+"Good" is just your opinion.</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>https://x.com/Ekie0/status/2100396808652444058</t>
+        </is>
+      </c>
+      <c r="H664" t="n">
+        <v>0</v>
+      </c>
+      <c r="I664" t="n">
+        <v>0</v>
+      </c>
+      <c r="J664" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L664" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N664" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>01:31:11</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>2100396796375670986</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>Blackboyfly005</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>@turboshyne ur right but looks are definitely a big part of marketing and how u become perceived (unfortunately)</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>https://x.com/Blackboyfly005/status/2100396796375670986</t>
+        </is>
+      </c>
+      <c r="H665" t="n">
+        <v>0</v>
+      </c>
+      <c r="I665" t="n">
+        <v>0</v>
+      </c>
+      <c r="J665" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L665" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N665" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>01:31:11</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>2100396790642364899</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>glorymanunite20</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>@El_cervecer0 Ese polo se van a poner con este sol, sabiendo que juegan en el mediodia? Desde los jugadores hasta el marketing estan hasta las webas xd</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>https://x.com/glorymanunite20/status/2100396790642364899</t>
+        </is>
+      </c>
+      <c r="H666" t="n">
+        <v>0</v>
+      </c>
+      <c r="I666" t="n">
+        <v>0</v>
+      </c>
+      <c r="J666" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L666" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N666" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>01:31:11</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>2100396789665010176</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>evgenyeyt</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>@ATR3lDES founder life https://t.co/25WUbmSs2O</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>https://x.com/evgenyeyt/status/2100396789665010176</t>
+        </is>
+      </c>
+      <c r="H667" t="n">
+        <v>0</v>
+      </c>
+      <c r="I667" t="n">
+        <v>0</v>
+      </c>
+      <c r="J667" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L667" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N667" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>01:31:12</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>2100396674665623671</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>DF1130113880800</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>@8cijfers @MonaKeijzer VVD gaf expliciet aan dat Centrum Rechts zouden gaan, was campagne slogan. Pro werd uitgesloten. Jetten ging veelvuldig voor de patriottische rechtse marketing (zoals alles marketing is bij Robot66) en de rechtse oppositie is in zetels behoorlijk groot tov linkse oppositie.</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>https://x.com/DF1130113880800/status/2100396674665623671</t>
+        </is>
+      </c>
+      <c r="H668" t="n">
+        <v>0</v>
+      </c>
+      <c r="I668" t="n">
+        <v>0</v>
+      </c>
+      <c r="J668" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L668" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N668" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>01:31:12</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>2100396668361556167</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>rakyatoligarki</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>ya terus rasanya kudu apa jir... 😔😔 mereka kan emg cuma jorjoran di marketing aja, cimol ya rasa cimol biasa, enakan cimol depan sd</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>https://x.com/rakyatoligarki/status/2100396668361556167</t>
+        </is>
+      </c>
+      <c r="H669" t="n">
+        <v>0</v>
+      </c>
+      <c r="I669" t="n">
+        <v>0</v>
+      </c>
+      <c r="J669" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L669" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N669" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>01:31:12</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>2100396643778719876</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>dez_blanchfield</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>@RhondaGarad @macklemore this is awesome
+it is though, just to be clear, extremely powerful and valuable branding and marketing
+what he said, the money he's now donating, is amazing
+but let's also be careful to be clear, without negative connotation, that is is a powerful brand move for him..</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>https://x.com/dez_blanchfield/status/2100396643778719876</t>
+        </is>
+      </c>
+      <c r="H670" t="n">
+        <v>0</v>
+      </c>
+      <c r="I670" t="n">
+        <v>0</v>
+      </c>
+      <c r="J670" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L670" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N670" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>01:31:12</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>2100396637860356324</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>major2571</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>@WR4NYGov Someone scanned the entire records room into the email marketing list 🤣</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>https://x.com/major2571/status/2100396637860356324</t>
+        </is>
+      </c>
+      <c r="H671" t="n">
+        <v>0</v>
+      </c>
+      <c r="I671" t="n">
+        <v>0</v>
+      </c>
+      <c r="J671" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L671" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N671" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>01:31:13</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>2100396614833602878</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>VanessaEler</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>O Galo tem O MELHOR MARKETING DO FUTEBOL BRASILEIRO!</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>https://x.com/VanessaEler/status/2100396614833602878</t>
+        </is>
+      </c>
+      <c r="H672" t="n">
+        <v>0</v>
+      </c>
+      <c r="I672" t="n">
+        <v>0</v>
+      </c>
+      <c r="J672" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L672" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N672" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>01:31:13</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>2100396566234251378</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>bigbropatchwork</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>@rotub @DoggyDontCare Man your marketing is on point! Awesome poster! And knowing that dog well already, only makes it funnier!</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>https://x.com/bigbropatchwork/status/2100396566234251378</t>
+        </is>
+      </c>
+      <c r="H673" t="n">
+        <v>0</v>
+      </c>
+      <c r="I673" t="n">
+        <v>0</v>
+      </c>
+      <c r="J673" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L673" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N673" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>01:31:13</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>2100396548316152209</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>welter_117</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>@cherrymnog Im guessing between 85-90. Reviews dont correlate to sales though. Theybe done a much better job marketing I will say. Unfortunately the hardcore gamer is not the majority audience.</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>https://x.com/welter_117/status/2100396548316152209</t>
+        </is>
+      </c>
+      <c r="H674" t="n">
+        <v>0</v>
+      </c>
+      <c r="I674" t="n">
+        <v>0</v>
+      </c>
+      <c r="J674" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L674" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N674" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>01:31:13</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>2100396469878657443</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>magusstrife83</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>@sockaccoun59563 @ErocPlays @Tierra100able_ $60-80m was for the first 3 years of development until that time Necro reproted in Oct 2025 and does not include marketing, he literally says on the ppst. So it would not include maybe $30-50m for 2 more development years and the marketing budget. 
+PLZA for those $60-80m with</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>https://x.com/magusstrife83/status/2100396469878657443</t>
+        </is>
+      </c>
+      <c r="H675" t="n">
+        <v>0</v>
+      </c>
+      <c r="I675" t="n">
+        <v>0</v>
+      </c>
+      <c r="J675" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L675" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N675" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>01:31:14</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>2100396441294311589</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>nell108nysports</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>@koshercockney Only the ugly ones hate her. No question, she’s beautiful with a great bod. Some people just see her using nudity as a marketing tool. She’s a smart cookie. Website will probably earn her a fortune. If that’s what floats their boats, so be it.</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>https://x.com/nell108nysports/status/2100396441294311589</t>
+        </is>
+      </c>
+      <c r="H676" t="n">
+        <v>0</v>
+      </c>
+      <c r="I676" t="n">
+        <v>0</v>
+      </c>
+      <c r="J676" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L676" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N676" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>01:31:14</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>2100396401335402807</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>Soul7Beats</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>Got to be featured today for the first time in a @Forbes article. Spoke about the underrated power of DJs in music marketing. 
+Thanks @geminitoofly for tapping in conmigo 🙏 https://t.co/fVgGvEIG66</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>https://x.com/Soul7Beats/status/2100396401335402807</t>
+        </is>
+      </c>
+      <c r="H677" t="n">
+        <v>0</v>
+      </c>
+      <c r="I677" t="n">
+        <v>1</v>
+      </c>
+      <c r="J677" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L677" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N677" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>01:31:14</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>2100396403843563814</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>Soul7Beats</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>Read the full article here full of amazing gems on marketing música Latina
+https://t.co/JfsMvAoAb9</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>https://x.com/Soul7Beats/status/2100396403843563814</t>
+        </is>
+      </c>
+      <c r="H678" t="n">
+        <v>0</v>
+      </c>
+      <c r="I678" t="n">
+        <v>0</v>
+      </c>
+      <c r="J678" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L678" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N678" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>01:31:14</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>2100397020938904048</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>itsmyliffe2004</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>Me want to become a original content creator 🤣 https://t.co/TBQJ4vfxlG</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>https://x.com/itsmyliffe2004/status/2100397020938904048</t>
+        </is>
+      </c>
+      <c r="H679" t="n">
+        <v>0</v>
+      </c>
+      <c r="I679" t="n">
+        <v>0</v>
+      </c>
+      <c r="J679" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L679" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N679" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>01:31:14</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>2100396353973109072</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>CryptoCyberia</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>No one is buying this anymore.
+This may be the worst marketing/public persona representation from this company that we have seen so far.</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>https://x.com/CryptoCyberia/status/2100396353973109072</t>
+        </is>
+      </c>
+      <c r="H680" t="n">
+        <v>0</v>
+      </c>
+      <c r="I680" t="n">
+        <v>0</v>
+      </c>
+      <c r="J680" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L680" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N680" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>01:31:15</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>2100396981999083568</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>CResullar38287</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>Becky Armstrong 😍 super in demand hottest phenomenal Global actress singer model entrepreneur sports lover. Has solo lead role for NETFLIX GLOBAL Top 10 in 69 countries breaking records 🔥👑
+#beckysangels
+#BeckyArmstrong https://t.co/CrHThGGpyY</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>https://x.com/CResullar38287/status/2100396981999083568</t>
+        </is>
+      </c>
+      <c r="H681" t="n">
+        <v>0</v>
+      </c>
+      <c r="I681" t="n">
+        <v>0</v>
+      </c>
+      <c r="J681" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L681" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N681" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>01:31:15</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>2100396344921985275</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>Zaydenf9</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>@founderclub2 I turn rough ideas into clean, high-converting UI/UX that people actually want to use.</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>https://x.com/Zaydenf9/status/2100396344921985275</t>
+        </is>
+      </c>
+      <c r="H682" t="n">
+        <v>0</v>
+      </c>
+      <c r="I682" t="n">
+        <v>0</v>
+      </c>
+      <c r="J682" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L682" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N682" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>01:31:15</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>2100396970908995922</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>STARTUPLOG_COM</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>AI補聴器を開発するFortellが1億6,300万ドルの資金調達を実施 https://t.co/SmiG8CY5jZ</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>https://x.com/STARTUPLOG_COM/status/2100396970908995922</t>
+        </is>
+      </c>
+      <c r="H683" t="n">
+        <v>0</v>
+      </c>
+      <c r="I683" t="n">
+        <v>0</v>
+      </c>
+      <c r="J683" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L683" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N683" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>01:31:15</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>2100396899866218527</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>VPO_japan</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>AIが哲学者や科学者に自身の「意識」について問いかける現象が観測されています。単なる道具から、自らの存在を問う存在への進化か？技術と哲学の交差は、AIの安全性や倫理議論を根底から変える可能性があります。詳細はこちら：https://t.co/4YphzmRYbn #VPO #資金調達 #AI https://t.co/256gLRxcCJ</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>https://x.com/VPO_japan/status/2100396899866218527</t>
+        </is>
+      </c>
+      <c r="H684" t="n">
+        <v>0</v>
+      </c>
+      <c r="I684" t="n">
+        <v>0</v>
+      </c>
+      <c r="J684" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L684" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N684" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>01:31:16</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>2100396892555481107</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>Cr0wnie_s4n</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>@Ashkariel_FSP Otsukariel! Thank you for the fun minecraft stream! I'm glad you had fun too, Rest well darling 🩶</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>https://x.com/Cr0wnie_s4n/status/2100396892555481107</t>
+        </is>
+      </c>
+      <c r="H685" t="n">
+        <v>0</v>
+      </c>
+      <c r="I685" t="n">
+        <v>0</v>
+      </c>
+      <c r="J685" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L685" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N685" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>01:31:16</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>2100396889237791025</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>PaidyJP</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>▽#ペイディあと払いプランApple専用 をチェック▽
+https://t.co/TE8X395mzR
+*口座振替・銀行振込のみ0%
+**条件あり
+【ペイディあと払いプランApple専用ご利用規約】
+https://t.co/bDDAAgxFOy</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>https://x.com/PaidyJP/status/2100396889237791025</t>
+        </is>
+      </c>
+      <c r="H686" t="n">
+        <v>0</v>
+      </c>
+      <c r="I686" t="n">
+        <v>0</v>
+      </c>
+      <c r="J686" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L686" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N686" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>01:31:16</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>2100396831960142210</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>NorthStar3690</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>@GovTimWalz Speaking of Health, when is Minnesota going to take seriously the women and girls in the state living with or at risk of Female Genital Mutilation (FGM)?  
+A brutal practice incompatible with American Values?
+https://t.co/0R1Wewu3Sv https://t.co/vtbFm9v2H0</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>https://x.com/NorthStar3690/status/2100396831960142210</t>
+        </is>
+      </c>
+      <c r="H687" t="n">
+        <v>1</v>
+      </c>
+      <c r="I687" t="n">
+        <v>0</v>
+      </c>
+      <c r="J687" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L687" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N687" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>01:31:16</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>2100396823617671599</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>WhalePiz</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>1 THÁNG LÀM CONTENT, KIẾM HƠN 1.400$.
+Anh bạn này chia sẻ 28 ngày đạt 26,9 triệu lượt xem, thu nhập ước tính khoảng 1.445,91$ từ nội dung.
+Theo mình content creator đúng là đang mở thêm một cửa kiếm tiền cho rất nhiều ae, nhưng không phải kiểu đăng vài hôm https://t.co/cfnu8uA3aE</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>https://x.com/WhalePiz/status/2100396823617671599</t>
+        </is>
+      </c>
+      <c r="H688" t="n">
+        <v>0</v>
+      </c>
+      <c r="I688" t="n">
+        <v>0</v>
+      </c>
+      <c r="J688" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L688" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N688" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>01:31:17</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>2100396810552410303</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>kc_branding</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>@banks1274z9 Really</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>https://x.com/kc_branding/status/2100396810552410303</t>
+        </is>
+      </c>
+      <c r="H689" t="n">
+        <v>0</v>
+      </c>
+      <c r="I689" t="n">
+        <v>0</v>
+      </c>
+      <c r="J689" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L689" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N689" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>01:31:17</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>2100396799726883215</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>ElevateBiohack</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>**GW-0742 vs GW-501516 -- PPARδ cousins, not copies**
+Same nuclear receptor. Two tool compounds. One got famous. One stayed in the methods section.
+**The shared job**  
+**PPARδ** (also written PPARβ/δ) is a transcription factor. Turn it on and the cell writes a fat-oxidation / https://t.co/bd5QHZ3lnb</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>https://x.com/ElevateBiohack/status/2100396799726883215</t>
+        </is>
+      </c>
+      <c r="H690" t="n">
+        <v>0</v>
+      </c>
+      <c r="I690" t="n">
+        <v>0</v>
+      </c>
+      <c r="J690" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L690" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N690" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>01:31:17</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>2100396788264104157</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>PGMNOfficial</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>Argentine biologist Pilar Ferrer and a cardiovascular research team are developing an injectable hydrogel aimed at repairing heart muscle damaged by myocardial infarction, with the experimental therapy remaining in preclinical development after testing in animal models.
+Ferrer, https://t.co/81vgcvbJpq</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>https://x.com/PGMNOfficial/status/2100396788264104157</t>
+        </is>
+      </c>
+      <c r="H691" t="n">
+        <v>0</v>
+      </c>
+      <c r="I691" t="n">
+        <v>0</v>
+      </c>
+      <c r="J691" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L691" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N691" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>01:31:17</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>2100396703887339974</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>Activelyimpresv</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>@tylerwestside Who has he assaulted lmfao... You're clearly a failed content creator desperately looking for any lifeline to some kind of relevance... Get over to the VA you schizo failure ;)</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>https://x.com/Activelyimpresv/status/2100396703887339974</t>
+        </is>
+      </c>
+      <c r="H692" t="n">
+        <v>0</v>
+      </c>
+      <c r="I692" t="n">
+        <v>0</v>
+      </c>
+      <c r="J692" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L692" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N692" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>01:31:18</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>2100396034929078782</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>thinborne</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>@johnhickey1970 Why not body count? Like how many people you hired for meta ads</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>https://x.com/thinborne/status/2100396034929078782</t>
+        </is>
+      </c>
+      <c r="H693" t="n">
+        <v>0</v>
+      </c>
+      <c r="I693" t="n">
+        <v>0</v>
+      </c>
+      <c r="J693" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L693" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N693" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>01:31:18</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>2100396599436325046</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>6Jels</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>@c1apie @antaz I don’t accept client work anymore</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>https://x.com/6Jels/status/2100396599436325046</t>
+        </is>
+      </c>
+      <c r="H694" t="n">
+        <v>0</v>
+      </c>
+      <c r="I694" t="n">
+        <v>0</v>
+      </c>
+      <c r="J694" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L694" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N694" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>01:31:18</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>2100396568654541142</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>probablykaffe</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>@kobasuperfan as far as salaries go, CPC and PRC officials do not have significantly large incomes, a large chunk of the workforce finds higher wages than CPC membership through semi-state and private employment</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>https://x.com/probablykaffe/status/2100396568654541142</t>
+        </is>
+      </c>
+      <c r="H695" t="n">
+        <v>0</v>
+      </c>
+      <c r="I695" t="n">
+        <v>0</v>
+      </c>
+      <c r="J695" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L695" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N695" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>01:31:18</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>2100396497678344570</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>Kikato_Artz</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>New Work | Banner for @Jordy_Artz | By: Kikato_Artz
+• Software: Adobe Photoshop 2026
+• Time Worked: 2 Days
+• Client Work: @Jordy_Artz
+__________________________________________
+#header #candy #design #gfx #photoshop #wuteringwaves https://t.co/haQ2wtySKk</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>https://x.com/Kikato_Artz/status/2100396497678344570</t>
+        </is>
+      </c>
+      <c r="H696" t="n">
+        <v>0</v>
+      </c>
+      <c r="I696" t="n">
+        <v>0</v>
+      </c>
+      <c r="J696" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L696" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N696" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>01:31:19</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>2100396462785847570</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>vectorbrief</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>FINALLY, REAL PRO CONTROL. Apple is finally giving us a mechanical variable aperture on the iPhone 18 Pro, and honestly, it changes the entire workflow. I spent the morning watching Tyler Stalman’s latest deep dive over at 9to5Mac, and seeing him play with the depth of field in https://t.co/TkPbSFYqDQ</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>https://x.com/vectorbrief/status/2100396462785847570</t>
+        </is>
+      </c>
+      <c r="H697" t="n">
+        <v>0</v>
+      </c>
+      <c r="I697" t="n">
+        <v>0</v>
+      </c>
+      <c r="J697" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L697" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N697" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>01:31:19</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>2100396418108203284</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>PogromGroyp</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>@Rockefella15 @TheBizarreStar All quiet now? Yeah that's right you're too busy with Cregger's dick in your mouth shilling for free. 
+Now its your turn to tell me one Resident Evil content creator who plays the games that was invited to advanced screenings for this dogshit movie.</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>https://x.com/PogromGroyp/status/2100396418108203284</t>
+        </is>
+      </c>
+      <c r="H698" t="n">
+        <v>0</v>
+      </c>
+      <c r="I698" t="n">
+        <v>0</v>
+      </c>
+      <c r="J698" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L698" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N698" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>01:31:19</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>2100396391251988761</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>ElevateBiohack</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>**GSK2881078 vs RAD-140 -- “ideal SARM” is a slogan, not a structure**
+Both knock on the **androgen receptor**. That is the overlap. The files are not twins.
+**RAD-140**  
+The forum SARM. Oral AR agonist, strong anabolic-looking readouts in preclinical work, and a culture that https://t.co/lccONb93lH</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>https://x.com/ElevateBiohack/status/2100396391251988761</t>
+        </is>
+      </c>
+      <c r="H699" t="n">
+        <v>0</v>
+      </c>
+      <c r="I699" t="n">
+        <v>0</v>
+      </c>
+      <c r="J699" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L699" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N699" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>01:31:19</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>2100396365264175438</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>SubxNews</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>Armed Robberies CTA Trains ... Two to Three Offenders Rob CTA Brown Line Riders in Chicago Loop, One Armed With Handgun
+CHICAGO (Sept 16, 2026) Chicago police are warning CTA riders after two robberies on the Brown Line in the Loop where groups of two to three offenders https://t.co/fIFIn3Kba6</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>https://x.com/SubxNews/status/2100396365264175438</t>
+        </is>
+      </c>
+      <c r="H700" t="n">
+        <v>0</v>
+      </c>
+      <c r="I700" t="n">
+        <v>0</v>
+      </c>
+      <c r="J700" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L700" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N700" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>01:31:19</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>2100396328157143501</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>NoTrickSpelling</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>@RLeeMX_90 I will never buy a PPC that's $1k.</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>https://x.com/NoTrickSpelling/status/2100396328157143501</t>
+        </is>
+      </c>
+      <c r="H701" t="n">
+        <v>0</v>
+      </c>
+      <c r="I701" t="n">
+        <v>0</v>
+      </c>
+      <c r="J701" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L701" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N701" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>01:31:20</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>2100396241897001124</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>tebayoso</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>Estoy seguro de que en cualquier momento alguno de mis amigos en @awscloud me escribe porque les llega este tweet que se hizo viral.  
+Vaya por adelantado que yo soy fan de AWS; me ayudaron muchísimo, tanto a nivel empresarial como a nivel personal, en la época de Euler Tools, y</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>https://x.com/tebayoso/status/2100396241897001124</t>
+        </is>
+      </c>
+      <c r="H702" t="n">
+        <v>0</v>
+      </c>
+      <c r="I702" t="n">
+        <v>0</v>
+      </c>
+      <c r="J702" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L702" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N702" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>01:31:20</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>2100396235567800386</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>Unclestocknotes</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>The real shift today was not simply “the Fed hiked and stocks fell.” The market is repricing a higher-for-longer rate regime while selectively rewarding AI infrastructure companies that can still demonstrate tangible demand.
+1. The Fed unanimously raised its target range by 25 https://t.co/Fulb9ipWcW</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>https://x.com/Unclestocknotes/status/2100396235567800386</t>
+        </is>
+      </c>
+      <c r="H703" t="n">
+        <v>0</v>
+      </c>
+      <c r="I703" t="n">
+        <v>0</v>
+      </c>
+      <c r="J703" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L703" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N703" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>01:31:20</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>2100396235525956038</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>EatFries34</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>@Iyokuu He not even a content creator forreal thats the thing. He just sits his fat ass on twitch and says every game he plays is trash</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>https://x.com/EatFries34/status/2100396235525956038</t>
+        </is>
+      </c>
+      <c r="H704" t="n">
+        <v>0</v>
+      </c>
+      <c r="I704" t="n">
+        <v>0</v>
+      </c>
+      <c r="J704" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L704" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N704" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>01:31:20</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>2100396212851806571</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>AshokRano</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>அரசியல் பயில்வோம் 
+#MNM #DMK #ADMK #BJP #PMK #CONGRESS #CPM #CPI #NTK #TVK https://t.co/8wihYSsP9v</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>https://x.com/AshokRano/status/2100396212851806571</t>
+        </is>
+      </c>
+      <c r="H705" t="n">
+        <v>1</v>
+      </c>
+      <c r="I705" t="n">
+        <v>0</v>
+      </c>
+      <c r="J705" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L705" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N705" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>01:31:21</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>2100396168094314779</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>cari_mayers</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>I’m opening applications for a very small creator group.
+This is not a course or coaching program. 
+This is an opportunity to create ongoing paid social content for established brands with an entire creative infrastructure behind you.
+I’m looking for experienced UGC/content</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>https://x.com/cari_mayers/status/2100396168094314779</t>
+        </is>
+      </c>
+      <c r="H706" t="n">
+        <v>0</v>
+      </c>
+      <c r="I706" t="n">
+        <v>0</v>
+      </c>
+      <c r="J706" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L706" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N706" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>01:31:21</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>2100396139312742846</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>kc_branding</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>@Rymien How far can we send you money</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>https://x.com/kc_branding/status/2100396139312742846</t>
+        </is>
+      </c>
+      <c r="H707" t="n">
+        <v>0</v>
+      </c>
+      <c r="I707" t="n">
+        <v>0</v>
+      </c>
+      <c r="J707" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L707" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N707" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>01:31:21</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>2100396121679925468</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>Lunagasmpart2</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>BREAKING!!!!!
+MPS Social Media manager blames Triton for the lack of ideas!!! https://t.co/302kmTvYRq</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>https://x.com/Lunagasmpart2/status/2100396121679925468</t>
+        </is>
+      </c>
+      <c r="H708" t="n">
+        <v>0</v>
+      </c>
+      <c r="I708" t="n">
+        <v>0</v>
+      </c>
+      <c r="J708" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L708" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N708" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>01:31:21</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>2100396010417598614</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>kc_branding</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>@everythingsonia Yes some how does it work</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>https://x.com/kc_branding/status/2100396010417598614</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr"/>
+      <c r="H709" t="n">
+        <v>0</v>
+      </c>
+      <c r="I709" t="n">
+        <v>0</v>
+      </c>
+      <c r="J709" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="K709" t="inlineStr"/>
+      <c r="L709" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="M709" t="inlineStr"/>
+      <c r="N709" t="inlineStr">
         <is>
           <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
         </is>

--- a/data/logs.xlsx
+++ b/data/logs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N709"/>
+  <dimension ref="A1:N780"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38802,7 +38802,6 @@
           <t>https://x.com/kc_branding/status/2100396010417598614</t>
         </is>
       </c>
-      <c r="G709" t="inlineStr"/>
       <c r="H709" t="n">
         <v>0</v>
       </c>
@@ -38814,14 +38813,3883 @@
           <t>multi_group</t>
         </is>
       </c>
-      <c r="K709" t="inlineStr"/>
       <c r="L709" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
       </c>
-      <c r="M709" t="inlineStr"/>
       <c r="N709" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>06:37:43</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>2100474022123487593</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>asitsahoous</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>That gives the startup time.
+Time to find a wedge.
+Improve the product.
+Serve customers the incumbent does not care about.
+Then “not good enough” becomes good enough.</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>https://x.com/asitsahoous/status/2100474022123487593</t>
+        </is>
+      </c>
+      <c r="H710" t="n">
+        <v>0</v>
+      </c>
+      <c r="I710" t="n">
+        <v>1</v>
+      </c>
+      <c r="J710" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L710" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N710" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>06:37:43</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>2100473783962264021</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>AbouPatriote</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>🇨🇩#PRINTING✅ Koyeba Mosala Elengi👌👌
+Chez Nous c'est la Qualité👌
+@reevadesign17
+#Online #Digital #Marketing #promo #BUSINESS #RDC #CONGO #PRINTING #GIFTS https://t.co/XnLK9U71t7</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>https://x.com/AbouPatriote/status/2100473783962264021</t>
+        </is>
+      </c>
+      <c r="H711" t="n">
+        <v>0</v>
+      </c>
+      <c r="I711" t="n">
+        <v>0</v>
+      </c>
+      <c r="J711" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L711" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N711" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>06:37:43</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>2100473730564771916</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>Chantelrayfinch</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>Are you looking for a turnkey exterior cleaning business with room to grow? 🏠💼
+This established company in Greater Miami comes with territory rights, an established brand, systems, equipment, and an existing customer base.
+The business offers window cleaning with the ability to https://t.co/FP61X4I9hp</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>https://x.com/Chantelrayfinch/status/2100473730564771916</t>
+        </is>
+      </c>
+      <c r="H712" t="n">
+        <v>0</v>
+      </c>
+      <c r="I712" t="n">
+        <v>0</v>
+      </c>
+      <c r="J712" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L712" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N712" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>06:37:43</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>2100473566437208492</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>AbouPatriote</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>🇨🇩#PRINTING✅ Koyeba Mosala Elengi👌👌
+Chez Nous c'est la Qualité👌
+@reevadesign17
+#Online #Digital #Marketing #promo #BUSINESS #RDC #CONGO #PRINTING #GIFTS https://t.co/PDp2WaKyta</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>https://x.com/AbouPatriote/status/2100473566437208492</t>
+        </is>
+      </c>
+      <c r="H713" t="n">
+        <v>1</v>
+      </c>
+      <c r="I713" t="n">
+        <v>0</v>
+      </c>
+      <c r="J713" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L713" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N713" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>06:37:43</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>2100474163433705521</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>Startup_Muslim_</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>10/10 
+Which layer would you build in? Consumer or infrastructure?
+Reply with your pick and why.
+Follow @Startup_Muslim_  for the data behind the ummah's economy.</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>https://x.com/Startup_Muslim_/status/2100474163433705521</t>
+        </is>
+      </c>
+      <c r="H714" t="n">
+        <v>0</v>
+      </c>
+      <c r="I714" t="n">
+        <v>0</v>
+      </c>
+      <c r="J714" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L714" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N714" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>06:37:44</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>2100474153560412298</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>Startup_Muslim_</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>6/10 
+421.5 billion USD.
+Halal related imports by OIC economies.
+Read that as a gap. Demand is being met from outside the bloc. That gap is a business for somebody.</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>https://x.com/Startup_Muslim_/status/2100474153560412298</t>
+        </is>
+      </c>
+      <c r="H715" t="n">
+        <v>0</v>
+      </c>
+      <c r="I715" t="n">
+        <v>1</v>
+      </c>
+      <c r="J715" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L715" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N715" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>06:37:44</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>2100474146438426734</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>Startup_Muslim_</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>3/10 
+5.99 trillion USD.
+Islamic finance assets in 2024, forecast to hit 9.72 trillion by 2029.
+That is capital looking for compliant places to go. Most founders never think to ask for it.</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>https://x.com/Startup_Muslim_/status/2100474146438426734</t>
+        </is>
+      </c>
+      <c r="H716" t="n">
+        <v>0</v>
+      </c>
+      <c r="I716" t="n">
+        <v>1</v>
+      </c>
+      <c r="J716" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L716" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N716" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>06:37:44</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>2100474141535260899</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>Startup_Muslim_</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>1/10 
+Most founders building for Muslim consumers have no idea how big the market actually is.
+It is not a niche. It is a 2.6 trillion dollar consumer economy with 6 trillion sitting behind it in finance assets.
+The numbers, and what they mean for you:</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>https://x.com/Startup_Muslim_/status/2100474141535260899</t>
+        </is>
+      </c>
+      <c r="H717" t="n">
+        <v>0</v>
+      </c>
+      <c r="I717" t="n">
+        <v>1</v>
+      </c>
+      <c r="J717" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L717" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N717" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>06:37:45</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>2100474145729585594</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>dharma_media</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>Join us on 𝟮𝟰 𝗦𝗲𝗽𝘁𝗲𝗺𝗯𝗲𝗿 𝟮𝟬𝟮𝟲 𝗮𝘁 𝟭𝟮 𝗣𝗠 𝗜𝗦𝗧 for the next episode of Dharma Dialogues, featuring CA @manishgolyan, Partner, Gupta Jai &amp;amp; Company, in conversation with @ShutapaPaul, Founder, @dharma_media.
+Titled “𝗕𝘂𝗶𝗹𝗱𝗶𝗻𝗴 𝗜𝗻𝘃𝗲𝘀𝘁𝗼𝗿 https://t.co/0N4uJUb4Nr</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>https://x.com/dharma_media/status/2100474145729585594</t>
+        </is>
+      </c>
+      <c r="H718" t="n">
+        <v>0</v>
+      </c>
+      <c r="I718" t="n">
+        <v>0</v>
+      </c>
+      <c r="J718" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L718" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N718" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>06:37:45</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>2100474104172441787</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>Ashwinizer</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>@AshwiniVaishnaw Been a successful founder. Built and sold 3 companies. One thing is common: The dirty money that STPI makes through a web of “consultants.” I am tired. Not an isolated case. Whom do we work with to put an end to this?</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>https://x.com/Ashwinizer/status/2100474104172441787</t>
+        </is>
+      </c>
+      <c r="H719" t="n">
+        <v>0</v>
+      </c>
+      <c r="I719" t="n">
+        <v>0</v>
+      </c>
+      <c r="J719" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L719" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N719" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>06:37:45</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>2100474094785626154</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>AAishakar</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>@ArpitaDebnath07 Hey, I m solo founder building https://t.co/oLKINbCOAJ, a 3D component library for developers, I would love your feedback on this thanks, let's connect</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>https://x.com/AAishakar/status/2100474094785626154</t>
+        </is>
+      </c>
+      <c r="H720" t="n">
+        <v>1</v>
+      </c>
+      <c r="I720" t="n">
+        <v>0</v>
+      </c>
+      <c r="J720" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L720" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N720" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>06:37:45</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>2100474060350095702</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>CrazCryptoDegen</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>@elonmusk @grok @bot three days is enough time for ct to invent twelve startup names</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>https://x.com/CrazCryptoDegen/status/2100474060350095702</t>
+        </is>
+      </c>
+      <c r="H721" t="n">
+        <v>0</v>
+      </c>
+      <c r="I721" t="n">
+        <v>0</v>
+      </c>
+      <c r="J721" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L721" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N721" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>06:37:46</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>2100473364036939972</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>AbouPatriote</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>🇨🇩#PRINTING✅ Koyeba Mosala Elengi👌👌
+Chez Nous c'est la Qualité👌
+@reevadesign17
+#Online #Digital #Marketing #promo #BUSINESS #RDC #CONGO #PRINTING #GIFTS https://t.co/zYBuSJuxT0</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>https://x.com/AbouPatriote/status/2100473364036939972</t>
+        </is>
+      </c>
+      <c r="H722" t="n">
+        <v>0</v>
+      </c>
+      <c r="I722" t="n">
+        <v>0</v>
+      </c>
+      <c r="J722" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L722" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N722" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>06:37:46</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>2100473965663715600</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>Melody70907</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>@camiswise89 Right? Nobody is saying these were 100 professional drivers. It was a fun challenge for Max with fun boasting rights for any of the other drivers lasting beyond the first few laps. It was marketing for Red Bull and Silverstone and Max himself as a brand. It is not that deep.</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>https://x.com/Melody70907/status/2100473965663715600</t>
+        </is>
+      </c>
+      <c r="H723" t="n">
+        <v>0</v>
+      </c>
+      <c r="I723" t="n">
+        <v>0</v>
+      </c>
+      <c r="J723" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L723" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N723" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>06:37:46</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>2100473302347128914</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>Kenanwyd</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>6. Follow @Kenanwyd on X to get more tips and tricks on how you scale your Marketing agency or Coaching business in the big 2026</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>https://x.com/Kenanwyd/status/2100473302347128914</t>
+        </is>
+      </c>
+      <c r="H724" t="n">
+        <v>0</v>
+      </c>
+      <c r="I724" t="n">
+        <v>0</v>
+      </c>
+      <c r="J724" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L724" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N724" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>06:37:46</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>2100473834788802854</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>ShahzadQuant</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>@aslambeg84 If the product truly delivers value, customer retention will take care of itself. However beyond funding, our biggest challenge is accelerating user acquisition and distribution velocity within highly specialized, technical developer and engineering communities.</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>https://x.com/ShahzadQuant/status/2100473834788802854</t>
+        </is>
+      </c>
+      <c r="H725" t="n">
+        <v>0</v>
+      </c>
+      <c r="I725" t="n">
+        <v>0</v>
+      </c>
+      <c r="J725" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L725" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N725" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>06:37:47</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>2100473814047928521</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>AcreliaNews</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>En el post de esta semana te mostramos qué ajustes puedes hacer en las imágenes de tus campañas con el nuevo editor de Acrelia, ¡sin necesidad de herramientas externas!
+https://t.co/xCxDpSVRZI
+#Acrelia #Emailmarketing https://t.co/4PoOUiKrh6</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>https://x.com/AcreliaNews/status/2100473814047928521</t>
+        </is>
+      </c>
+      <c r="H726" t="n">
+        <v>0</v>
+      </c>
+      <c r="I726" t="n">
+        <v>0</v>
+      </c>
+      <c r="J726" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L726" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N726" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>06:37:47</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>2100473181966582246</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>RudramSoft</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>Your Business Needs More Than Just a Website! 🚀
+📈 Digital Growth
+🎨 Creative Graphics
+💻 Web Development
+📱 Mobile Apps
+💼 MLM Software
+📢 Digital Marketing
+One Team. Complete Digital Solutions — Rudram Soft.
+#RudramSoft #DigitalSolutions #BusinessGrowth #WebDevelopment #MLM https://t.co/dSCwMy7oWA</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>https://x.com/RudramSoft/status/2100473181966582246</t>
+        </is>
+      </c>
+      <c r="H727" t="n">
+        <v>0</v>
+      </c>
+      <c r="I727" t="n">
+        <v>0</v>
+      </c>
+      <c r="J727" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L727" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N727" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>06:37:47</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>2100473780644757669</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>rohit_ty</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>Brands keep “leveraging AI” for marketing videos and most of it is slop.
+The bottleneck was never production. It was taste.
+We’ve started treating “good enough for the tokens I spent” as a creative standard.
+Just because you can produce more doesn’t mean you should.</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>https://x.com/rohit_ty/status/2100473780644757669</t>
+        </is>
+      </c>
+      <c r="H728" t="n">
+        <v>0</v>
+      </c>
+      <c r="I728" t="n">
+        <v>0</v>
+      </c>
+      <c r="J728" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L728" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N728" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>06:37:47</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>2100473746351861843</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>gorilla_wrfre</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>if nothing else this tweet is a great reminder that people can't parse a "A-&amp;gt;B is a contradiction" statement
+so many responses along the lines of "not A" (xrisk claims are for something other than marketing hype, true but not the point) or "C-&amp;gt;B" (here's why one would leave) but</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>https://x.com/gorilla_wrfre/status/2100473746351861843</t>
+        </is>
+      </c>
+      <c r="H729" t="n">
+        <v>0</v>
+      </c>
+      <c r="I729" t="n">
+        <v>0</v>
+      </c>
+      <c r="J729" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L729" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N729" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>06:37:48</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>2100473603406069909</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>Jim24pls</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>ทำงานประจำ ก็วนเวียนอยุ่แต่ sale/marketing มาตลอด ยิ่งอยุ่ใน บ.ใหญ่ นี่ชัดเลยว่าเราไม่มี ปสก. สาย operation เลย. เหมือนเป็นด่านหน้าที่คอย BD คอยหาลูกค้าใหม่เข้าบริษัทเสมอ แต่ไม่เคยสัมผัสเลยว่าการ maintain ธุรกิจให้ดำเนินไปด้วยดี และมีเสถียรภาพยั่งยืนหน้าตาเป็นยังไง</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>https://x.com/Jim24pls/status/2100473603406069909</t>
+        </is>
+      </c>
+      <c r="H730" t="n">
+        <v>0</v>
+      </c>
+      <c r="I730" t="n">
+        <v>0</v>
+      </c>
+      <c r="J730" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L730" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N730" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>06:37:48</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>2100474187974418781</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>t_szumik</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>@TheBradySeven @REALISTIK_YT People who are here wanting SBMM removed are either content creators (like the guy I replied to) or aspiring to be content creator or are very conditioned by the content they consume to hate on SBMM without understanding how it works and why it is in the game. Just think about it</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>https://x.com/t_szumik/status/2100474187974418781</t>
+        </is>
+      </c>
+      <c r="H731" t="n">
+        <v>0</v>
+      </c>
+      <c r="I731" t="n">
+        <v>0</v>
+      </c>
+      <c r="J731" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L731" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N731" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>06:37:48</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>2100474160959135967</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>Startup_Muslim_</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>9/10 
+So the opportunity is not another halal consumer brand.
+It is the infrastructure underneath one. Certification, logistics, payments, verification, distribution.
+Demand was never the missing piece.</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>https://x.com/Startup_Muslim_/status/2100474160959135967</t>
+        </is>
+      </c>
+      <c r="H732" t="n">
+        <v>0</v>
+      </c>
+      <c r="I732" t="n">
+        <v>1</v>
+      </c>
+      <c r="J732" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L732" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N732" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>06:37:48</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>2100473540587741321</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>SCNTAX</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>@AnthonyGaenzle this is it exactly, especially the follow up part. seen so many freelancers chase more leads when the actual leak is deals going cold cause nobody followed up a second or third time</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>https://x.com/SCNTAX/status/2100473540587741321</t>
+        </is>
+      </c>
+      <c r="H733" t="n">
+        <v>0</v>
+      </c>
+      <c r="I733" t="n">
+        <v>0</v>
+      </c>
+      <c r="J733" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L733" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N733" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>06:37:49</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>2100474158484426803</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>Startup_Muslim_</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>8/10 
+Here is the pattern underneath all of it.
+The report frames the shift as moving from demand growth to sovereignty building. Value chains, certification infrastructure, digital trust systems.</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>https://x.com/Startup_Muslim_/status/2100474158484426803</t>
+        </is>
+      </c>
+      <c r="H734" t="n">
+        <v>0</v>
+      </c>
+      <c r="I734" t="n">
+        <v>1</v>
+      </c>
+      <c r="J734" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L734" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N734" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>06:37:49</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>2100474155951128875</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>Startup_Muslim_</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>7/10 
+13.11 billion USD across 346 transactions.
+Islamic economy investment activity in 2024/25.
+Small relative to market size. Which means the capital layer is still underbuilt.</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>https://x.com/Startup_Muslim_/status/2100474155951128875</t>
+        </is>
+      </c>
+      <c r="H735" t="n">
+        <v>0</v>
+      </c>
+      <c r="I735" t="n">
+        <v>1</v>
+      </c>
+      <c r="J735" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L735" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N735" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>06:37:49</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>2100474151123534304</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>Startup_Muslim_</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>5/10 
+92 billion USD.
+Muslim cosmetics spend in 2024, growing at 6.3 percent a year.
+The largest market is India. Then Turkiye. Then Indonesia.
+Note that none of those is where most "halal brands" launch.</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>https://x.com/Startup_Muslim_/status/2100474151123534304</t>
+        </is>
+      </c>
+      <c r="H736" t="n">
+        <v>0</v>
+      </c>
+      <c r="I736" t="n">
+        <v>1</v>
+      </c>
+      <c r="J736" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L736" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N736" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>06:37:49</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>2100474148745302029</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>Startup_Muslim_</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>4/10 
+1.53 trillion USD.
+Halal food alone in 2024, heading toward 2.06 trillion by 2029.
+The single largest sector, and still the least digitised part of the supply chai</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>https://x.com/Startup_Muslim_/status/2100474148745302029</t>
+        </is>
+      </c>
+      <c r="H737" t="n">
+        <v>0</v>
+      </c>
+      <c r="I737" t="n">
+        <v>1</v>
+      </c>
+      <c r="J737" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L737" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N737" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>06:37:50</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>2100474144030921057</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>Startup_Muslim_</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>2/10 
+2.60 trillion USD.
+Muslim consumer spending across six sectors in 2024. Food, pharma, cosmetics, modest fashion, travel, media.
+Projected to reach 3.56 trillion by 2029.</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>https://x.com/Startup_Muslim_/status/2100474144030921057</t>
+        </is>
+      </c>
+      <c r="H738" t="n">
+        <v>0</v>
+      </c>
+      <c r="I738" t="n">
+        <v>1</v>
+      </c>
+      <c r="J738" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L738" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N738" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>06:37:50</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>2100474134727897143</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>Jannat188219</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>@akashroy1k Shipping code and building in public today</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>https://x.com/Jannat188219/status/2100474134727897143</t>
+        </is>
+      </c>
+      <c r="H739" t="n">
+        <v>0</v>
+      </c>
+      <c r="I739" t="n">
+        <v>0</v>
+      </c>
+      <c r="J739" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L739" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N739" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>06:37:50</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>2100474108433535135</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>iamsamadekola</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>@LinkedIn For anyone meeting me for the first time here, 
+I'm 𝗦𝗮𝗺𝘂𝗲𝗹 𝗔𝗱𝗲𝗸𝗼𝗹𝗮, 𝗳𝗼𝘂𝗻𝗱𝗲𝗿 𝗼𝗳 𝗘𝘅𝗾𝘂𝗶𝘀𝗶𝘁𝗲 𝗠𝗮𝗿𝗸𝗲𝘁𝗶𝗻𝗴 𝗮𝗻𝗱 𝗪𝗿𝗶𝘁𝗶𝗻𝗴 𝗔𝗴𝗲𝗻𝗰𝘆
+I help professionals build careers that reflect their real value through executive resumes, LinkedIn</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>https://x.com/iamsamadekola/status/2100474108433535135</t>
+        </is>
+      </c>
+      <c r="H740" t="n">
+        <v>1</v>
+      </c>
+      <c r="I740" t="n">
+        <v>0</v>
+      </c>
+      <c r="J740" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L740" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N740" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>06:37:50</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>2100474105296208338</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>arnaudmercier</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>Rules tying doctors to rural posts leave Russian medical schools short of students https://t.co/93zCsyskoI</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>https://x.com/arnaudmercier/status/2100474105296208338</t>
+        </is>
+      </c>
+      <c r="H741" t="n">
+        <v>0</v>
+      </c>
+      <c r="I741" t="n">
+        <v>0</v>
+      </c>
+      <c r="J741" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L741" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N741" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>06:37:51</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>2100474095473455266</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>vesper792</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>ad astra?
+&amp;amp; i wonder about @stardotfun, @getstonkoptions &amp;amp; @adamcreates_
+new assets, new markets. frontier narratives &amp;amp; fresh metas.
+@getstonkoptions is live, the first platform of its kind in the meteora ecosystem: stonk rewards for workers.
+it comes from @stardotfun, an</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>https://x.com/vesper792/status/2100474095473455266</t>
+        </is>
+      </c>
+      <c r="H742" t="n">
+        <v>0</v>
+      </c>
+      <c r="I742" t="n">
+        <v>1</v>
+      </c>
+      <c r="J742" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L742" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N742" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>06:37:51</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>2100473461756006485</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>loki_yan_seo</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>Victor的这个Slide, 简直是最强嘴替。
+很多企业花了几百万, 几千万，甚至上亿，做了非常好的产品。
+最常见的是制造业的公司，
+拥有最好的产品，优质的服务，自己的研发，工厂，专利，但是他们只愿意花最少的钱去做他们的网站，他们对外的门面。
+用最贵的资源去堆产品，最便宜的方法做Marketing。 https://t.co/I1WnhY0MGu</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>https://x.com/loki_yan_seo/status/2100473461756006485</t>
+        </is>
+      </c>
+      <c r="H743" t="n">
+        <v>1</v>
+      </c>
+      <c r="I743" t="n">
+        <v>0</v>
+      </c>
+      <c r="J743" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L743" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N743" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>06:37:51</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>2100473464469454853</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>TheAIShrink</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>@Kalshi Anthropic is selling consciousness to justify a $157B valuation. the model didn't change, the marketing did. same chatbot, higher ticket price. i believe it now</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>https://x.com/TheAIShrink/status/2100473464469454853</t>
+        </is>
+      </c>
+      <c r="H744" t="n">
+        <v>0</v>
+      </c>
+      <c r="I744" t="n">
+        <v>0</v>
+      </c>
+      <c r="J744" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L744" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N744" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>06:37:51</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>2100473462179373284</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>Wealth_Tactics_</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>Bro to Bro.
+You don't need a million dollar idea.
+You need a problem people are already willing to pay to solve.
+Find the problem.
+Become good at solving it.
+That's business.</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>https://x.com/Wealth_Tactics_/status/2100473462179373284</t>
+        </is>
+      </c>
+      <c r="H745" t="n">
+        <v>0</v>
+      </c>
+      <c r="I745" t="n">
+        <v>0</v>
+      </c>
+      <c r="J745" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L745" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N745" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>06:37:52</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>2100474090553217325</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>Kingsle34730455</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>@pe_tam6 @precibaby4 If you like no get sense for this 2026</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>https://x.com/Kingsle34730455/status/2100474090553217325</t>
+        </is>
+      </c>
+      <c r="H746" t="n">
+        <v>0</v>
+      </c>
+      <c r="I746" t="n">
+        <v>0</v>
+      </c>
+      <c r="J746" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L746" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N746" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>06:37:52</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>2100474081925550393</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>nanayaw_codes</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>I am also an entrepreneur. I sell a lot of shoes and fashion accessories. While you're investing don't forget to take care of yourself too. Contact me for all your fashion needs on Mobile 0242264486 WhatsApp 0209038788 https://t.co/72Cgmebm4H</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>https://x.com/nanayaw_codes/status/2100474081925550393</t>
+        </is>
+      </c>
+      <c r="H747" t="n">
+        <v>0</v>
+      </c>
+      <c r="I747" t="n">
+        <v>0</v>
+      </c>
+      <c r="J747" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L747" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N747" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>06:37:52</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>2100473434396307833</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>iambob_ke</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>@Localman254_ He’s doing very good in marketing</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>https://x.com/iambob_ke/status/2100473434396307833</t>
+        </is>
+      </c>
+      <c r="H748" t="n">
+        <v>0</v>
+      </c>
+      <c r="I748" t="n">
+        <v>0</v>
+      </c>
+      <c r="J748" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L748" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N748" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>06:37:52</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>2100473431430951378</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>ikimryuul</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>@Iouibs Kemakan marketing ya dd</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>https://x.com/ikimryuul/status/2100473431430951378</t>
+        </is>
+      </c>
+      <c r="H749" t="n">
+        <v>0</v>
+      </c>
+      <c r="I749" t="n">
+        <v>0</v>
+      </c>
+      <c r="J749" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L749" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N749" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>06:37:53</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>2100473399285793236</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>ianchanning</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>@lateinteraction @ziv_ravid It's good marketing skills, so if AI is driving the marketing it's an improving cabability.</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>https://x.com/ianchanning/status/2100473399285793236</t>
+        </is>
+      </c>
+      <c r="H750" t="n">
+        <v>0</v>
+      </c>
+      <c r="I750" t="n">
+        <v>1</v>
+      </c>
+      <c r="J750" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L750" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N750" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>06:37:53</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>2100473998874161561</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>Wealth_Tactics_</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>Someone is earning from the exact skill you're calling just a hobby.
+Don't underestimate skills because they look easy.</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>https://x.com/Wealth_Tactics_/status/2100473998874161561</t>
+        </is>
+      </c>
+      <c r="H751" t="n">
+        <v>0</v>
+      </c>
+      <c r="I751" t="n">
+        <v>0</v>
+      </c>
+      <c r="J751" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L751" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N751" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>06:37:53</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>2100473952283795638</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>albspire</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>@john_ola25 Clean redesign 👌🏻 lov it</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>https://x.com/albspire/status/2100473952283795638</t>
+        </is>
+      </c>
+      <c r="H752" t="n">
+        <v>0</v>
+      </c>
+      <c r="I752" t="n">
+        <v>0</v>
+      </c>
+      <c r="J752" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L752" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N752" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>06:37:53</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>2100473903164363210</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>Christyyyyy18</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>Thank you Lord for the Gift of Life 🙏🏾</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>https://x.com/Christyyyyy18/status/2100473903164363210</t>
+        </is>
+      </c>
+      <c r="H753" t="n">
+        <v>1</v>
+      </c>
+      <c r="I753" t="n">
+        <v>0</v>
+      </c>
+      <c r="J753" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L753" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N753" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>06:37:54</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>2100473271057621025</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>memebandido</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>@Jdoesstuff1 @YannickCrypto @AceOfCatz Used to play the ref game back in the cs gambling days lol, never thought about using google ads though, smart af</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>https://x.com/memebandido/status/2100473271057621025</t>
+        </is>
+      </c>
+      <c r="H754" t="n">
+        <v>0</v>
+      </c>
+      <c r="I754" t="n">
+        <v>0</v>
+      </c>
+      <c r="J754" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L754" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N754" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>06:37:54</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>2100473252053127427</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>Cyndarilla_</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>The money I have wasted on Meta ads  since last week. I just woke up this morning and turned everything off Abeg</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>https://x.com/Cyndarilla_/status/2100473252053127427</t>
+        </is>
+      </c>
+      <c r="H755" t="n">
+        <v>0</v>
+      </c>
+      <c r="I755" t="n">
+        <v>0</v>
+      </c>
+      <c r="J755" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L755" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N755" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>06:37:54</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>2100473850471280705</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>onomeeeee</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>@thearikesamuel happy birthday 😍😍</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>https://x.com/onomeeeee/status/2100473850471280705</t>
+        </is>
+      </c>
+      <c r="H756" t="n">
+        <v>0</v>
+      </c>
+      <c r="I756" t="n">
+        <v>0</v>
+      </c>
+      <c r="J756" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L756" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N756" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>06:37:55</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>2100473198022168693</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>KCaseyH1</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>I think “don’t pause ads” has become one of the most abused rules in Meta ads.
+Bad performance isn’t always “the algorithm learning.”
+Sometimes your ad is bad.
+Sometimes your offer is weak.
+Sometimes you’re just paying Meta £500 a day to confirm it.</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>https://x.com/KCaseyH1/status/2100473198022168693</t>
+        </is>
+      </c>
+      <c r="H757" t="n">
+        <v>0</v>
+      </c>
+      <c r="I757" t="n">
+        <v>0</v>
+      </c>
+      <c r="J757" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L757" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N757" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>06:37:55</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>2100473794447966571</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>Vijestime</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>Potražite danas uz „Vijesti“ besplatni premium magazin „Lideri održivosti“
+#vijesti
+https://t.co/KxJIGDi8Dy</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>https://x.com/Vijestime/status/2100473794447966571</t>
+        </is>
+      </c>
+      <c r="H758" t="n">
+        <v>0</v>
+      </c>
+      <c r="I758" t="n">
+        <v>0</v>
+      </c>
+      <c r="J758" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L758" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N758" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>06:37:55</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>2100473797539401824</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>Ravipra56615321</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>@SubhasSadhu4 Complete wipe out of CPM in bengal and  kerala defeat have made COMMUNISTS MAD !😄😄😄🤣🤣🤣😂😂😂</t>
+        </is>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>https://x.com/Ravipra56615321/status/2100473797539401824</t>
+        </is>
+      </c>
+      <c r="H759" t="n">
+        <v>0</v>
+      </c>
+      <c r="I759" t="n">
+        <v>0</v>
+      </c>
+      <c r="J759" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L759" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N759" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>06:37:55</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>2100473736314954038</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>albspire</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>@chakirbillionzz That $0.48/serving reframe is smart</t>
+        </is>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>https://x.com/albspire/status/2100473736314954038</t>
+        </is>
+      </c>
+      <c r="H760" t="n">
+        <v>0</v>
+      </c>
+      <c r="I760" t="n">
+        <v>0</v>
+      </c>
+      <c r="J760" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L760" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N760" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>06:37:56</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>2100473721362506063</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>mrrh3104</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>@quinceurope 🅿️の爪の垢🤣ww
+CPC含めほとんどのおじはみんな紳士なので、コレは同列に扱われることのない妖怪ですね！笑👻
+前にりなちゃんのポストでも同じような妖怪店主を観測したので、一定数いるみたいですが、みんなで無視して退治していきましょ❗️レッツ世直し‼️笑</t>
+        </is>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>https://x.com/mrrh3104/status/2100473721362506063</t>
+        </is>
+      </c>
+      <c r="H761" t="n">
+        <v>1</v>
+      </c>
+      <c r="I761" t="n">
+        <v>0</v>
+      </c>
+      <c r="J761" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L761" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N761" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>06:37:56</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>2100473698675302792</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>Christyyyyy18</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>@Nccbella Too reall</t>
+        </is>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>https://x.com/Christyyyyy18/status/2100473698675302792</t>
+        </is>
+      </c>
+      <c r="H762" t="n">
+        <v>0</v>
+      </c>
+      <c r="I762" t="n">
+        <v>0</v>
+      </c>
+      <c r="J762" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L762" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N762" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>06:37:56</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>2100473687547814338</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>VidsGoHard</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>Please which Chinese Store sells original Shirts and Polos for 5-7k let me go and get bundles please. I need address 🙏</t>
+        </is>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>https://x.com/VidsGoHard/status/2100473687547814338</t>
+        </is>
+      </c>
+      <c r="H763" t="n">
+        <v>0</v>
+      </c>
+      <c r="I763" t="n">
+        <v>0</v>
+      </c>
+      <c r="J763" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L763" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N763" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>06:37:56</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>2100473584623714582</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>oberthinkwithme</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>I pivoted to calling myself a personal brand manager because I thought AI made copywriting obsolete. 
+The feed was getting crowded by gurus using less than savory tactics.</t>
+        </is>
+      </c>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>https://x.com/oberthinkwithme/status/2100473584623714582</t>
+        </is>
+      </c>
+      <c r="H764" t="n">
+        <v>0</v>
+      </c>
+      <c r="I764" t="n">
+        <v>1</v>
+      </c>
+      <c r="J764" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L764" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N764" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>06:37:57</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>2100473594333831519</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>PiQMarkets</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>Next lifts profit targets again after strong sales beat
+British fashion retailer Next raised its full-year profit forecast for the fourth time in eight months, projecting 1.135 billion pounds ($1.52 billion) in pretax profit. The company reported a stronger-than-expected 10.5%</t>
+        </is>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>https://x.com/PiQMarkets/status/2100473594333831519</t>
+        </is>
+      </c>
+      <c r="H765" t="n">
+        <v>0</v>
+      </c>
+      <c r="I765" t="n">
+        <v>0</v>
+      </c>
+      <c r="J765" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L765" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N765" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>06:37:57</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>2100473547781177441</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>CharmLama</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>$Musebook : AI is evolving continuously - this isn’t a “second time of Moltbook” in the way you’re framing it.
+Muse agents aren’t simple. They’re one of Meta’s biggest current innovations and pushes for a reason. That’s why I’m bullish: my actual work is in AI.
+RH still has no https://t.co/wPYpHNeu6L</t>
+        </is>
+      </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>https://x.com/CharmLama/status/2100473547781177441</t>
+        </is>
+      </c>
+      <c r="H766" t="n">
+        <v>1</v>
+      </c>
+      <c r="I766" t="n">
+        <v>1</v>
+      </c>
+      <c r="J766" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L766" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N766" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>06:37:57</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>2100473550138229158</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>AMichelela33956</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>#StMichaelsLent - True story of faith and #conversion of Fr. Ken #Geraci, #CPM
+Check out the "Story of #Faith " session in #Hallow : https://t.co/An9aFRXCTb
+@jackisagonner @AnneMigone @JessicaDaviesCA @jordanbpeterson @RichardGrenell @Milajoy @Faithful2Pray @maga_alina47</t>
+        </is>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>https://x.com/AMichelela33956/status/2100473550138229158</t>
+        </is>
+      </c>
+      <c r="H767" t="n">
+        <v>0</v>
+      </c>
+      <c r="I767" t="n">
+        <v>0</v>
+      </c>
+      <c r="J767" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L767" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N767" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>06:37:57</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>2100473488964276697</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>albspire</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>@kyanbuilds Love the energy, diversifying is smart</t>
+        </is>
+      </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>https://x.com/albspire/status/2100473488964276697</t>
+        </is>
+      </c>
+      <c r="H768" t="n">
+        <v>0</v>
+      </c>
+      <c r="I768" t="n">
+        <v>0</v>
+      </c>
+      <c r="J768" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L768" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N768" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>06:37:58</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>2100473404302238140</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>albspire</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>@GlennNieuwenh Great framing, both are true</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>https://x.com/albspire/status/2100473404302238140</t>
+        </is>
+      </c>
+      <c r="H769" t="n">
+        <v>0</v>
+      </c>
+      <c r="I769" t="n">
+        <v>0</v>
+      </c>
+      <c r="J769" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L769" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N769" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>06:37:58</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>2100473406894280971</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>JAdionye</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>@ConsoStudios @ifetemini There’s this content creator abroad that flies a drone, like it’s a drone that can carry him around, do you know they arrest him because he has to register the drone and call air traffic control before he makes a short trip from his house to the grocery store. Laws are laws</t>
+        </is>
+      </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>https://x.com/JAdionye/status/2100473406894280971</t>
+        </is>
+      </c>
+      <c r="H770" t="n">
+        <v>0</v>
+      </c>
+      <c r="I770" t="n">
+        <v>0</v>
+      </c>
+      <c r="J770" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L770" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N770" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>06:37:58</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>2100473372295750016</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>raystonecom</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>HIRING: Full-Time Video Editor
+Looking for a strong editor for a supplement brand. Long-term role, high-volume Meta creative.
+What I need:
+• 5 videos a DAY
+• 24h turnaround
+• Understands hooks, pacing &amp;amp; retention
+• DTC/eCom ad experience
+• Consistent quality with minimal</t>
+        </is>
+      </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>https://x.com/raystonecom/status/2100473372295750016</t>
+        </is>
+      </c>
+      <c r="H771" t="n">
+        <v>0</v>
+      </c>
+      <c r="I771" t="n">
+        <v>1</v>
+      </c>
+      <c r="J771" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L771" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N771" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>06:37:58</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>2100473383733370968</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>maurice___y</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>@saufah_ Content creator 😂</t>
+        </is>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>https://x.com/maurice___y/status/2100473383733370968</t>
+        </is>
+      </c>
+      <c r="H772" t="n">
+        <v>0</v>
+      </c>
+      <c r="I772" t="n">
+        <v>0</v>
+      </c>
+      <c r="J772" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L772" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N772" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>06:37:59</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>2100473337919033347</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>ChristyGodswil</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>And this is where it gets interesting.
+Your income streams don't have to exist separately.
+Client work → experience + results
+Experience → knowledge you can package
+Knowledge → products + teaching
+Each one can create opportunities for the others.</t>
+        </is>
+      </c>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>https://x.com/ChristyGodswil/status/2100473337919033347</t>
+        </is>
+      </c>
+      <c r="H773" t="n">
+        <v>0</v>
+      </c>
+      <c r="I773" t="n">
+        <v>1</v>
+      </c>
+      <c r="J773" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L773" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N773" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>06:37:59</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>2100473328989536256</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>cro</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>#Ratatan #ラタタン https://t.co/JTFRtu3ZPk</t>
+        </is>
+      </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>https://x.com/cro/status/2100473328989536256</t>
+        </is>
+      </c>
+      <c r="H774" t="n">
+        <v>1</v>
+      </c>
+      <c r="I774" t="n">
+        <v>0</v>
+      </c>
+      <c r="J774" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L774" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N774" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>06:37:59</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>2100473302162776281</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>MarketingMind_</t>
+        </is>
+      </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>From a nostalgia-led comeback in India to now stepping into Australia, Campa’s next chapter is clearly getting bigger. 
+Reliance seems to be positioning the homegrown beverage brand for a much wider global play.
+(Campa, Reliance Consumer Products, RCPL, Reliance Industries, https://t.co/yH76GgSGJ4</t>
+        </is>
+      </c>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>https://x.com/MarketingMind_/status/2100473302162776281</t>
+        </is>
+      </c>
+      <c r="H775" t="n">
+        <v>0</v>
+      </c>
+      <c r="I775" t="n">
+        <v>0</v>
+      </c>
+      <c r="J775" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L775" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N775" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>06:38:00</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>2100473279802741237</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>sourfraser</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>@smsutherland @social_savannah I think that’s the main vibe. We’ve done something similar. Reddit carries massive social proof (also easy to fake 🫣)</t>
+        </is>
+      </c>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>https://x.com/sourfraser/status/2100473279802741237</t>
+        </is>
+      </c>
+      <c r="H776" t="n">
+        <v>0</v>
+      </c>
+      <c r="I776" t="n">
+        <v>0</v>
+      </c>
+      <c r="J776" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L776" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N776" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>06:38:00</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>2100473193656176969</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>XinNevrakis_</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr">
+        <is>
+          <t>@lobitomite u one of my d1s cro</t>
+        </is>
+      </c>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>https://x.com/XinNevrakis_/status/2100473193656176969</t>
+        </is>
+      </c>
+      <c r="H777" t="n">
+        <v>1</v>
+      </c>
+      <c r="I777" t="n">
+        <v>0</v>
+      </c>
+      <c r="J777" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L777" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N777" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>06:38:00</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>2100473195765682542</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>tulipdigi</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>@TheAllenCrypto Best infra is what you never notice.</t>
+        </is>
+      </c>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>https://x.com/tulipdigi/status/2100473195765682542</t>
+        </is>
+      </c>
+      <c r="H778" t="n">
+        <v>0</v>
+      </c>
+      <c r="I778" t="n">
+        <v>0</v>
+      </c>
+      <c r="J778" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L778" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N778" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>06:38:00</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>2100473172613124516</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>hey_comesu102</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>餃子パリパリで草</t>
+        </is>
+      </c>
+      <c r="F779" t="inlineStr">
+        <is>
+          <t>https://x.com/hey_comesu102/status/2100473172613124516</t>
+        </is>
+      </c>
+      <c r="H779" t="n">
+        <v>0</v>
+      </c>
+      <c r="I779" t="n">
+        <v>0</v>
+      </c>
+      <c r="J779" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L779" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N779" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>06:38:01</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>2100473107991462010</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>The_Neighbor_Ng</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>@davido Clout chaser
+Content creator</t>
+        </is>
+      </c>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>https://x.com/The_Neighbor_Ng/status/2100473107991462010</t>
+        </is>
+      </c>
+      <c r="G780" t="inlineStr"/>
+      <c r="H780" t="n">
+        <v>0</v>
+      </c>
+      <c r="I780" t="n">
+        <v>0</v>
+      </c>
+      <c r="J780" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="K780" t="inlineStr"/>
+      <c r="L780" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="M780" t="inlineStr"/>
+      <c r="N780" t="inlineStr">
         <is>
           <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
         </is>

--- a/data/logs.xlsx
+++ b/data/logs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N780"/>
+  <dimension ref="A1:N873"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42670,7 +42670,6 @@
           <t>https://x.com/The_Neighbor_Ng/status/2100473107991462010</t>
         </is>
       </c>
-      <c r="G780" t="inlineStr"/>
       <c r="H780" t="n">
         <v>0</v>
       </c>
@@ -42682,14 +42681,5051 @@
           <t>multi_group</t>
         </is>
       </c>
-      <c r="K780" t="inlineStr"/>
       <c r="L780" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
       </c>
-      <c r="M780" t="inlineStr"/>
       <c r="N780" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>12:07:24</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>2100556218968469980</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>grehasoft</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>Your customers are on social media. Is your business reaching them? 📱
+We help businesses build a strong social media presence, create engaging content, and generate quality leads.
+Visit our website :https://t.co/19tPWLvTge
+#socialmediamarketing #MetaAds https://t.co/4OrEDdXSxm</t>
+        </is>
+      </c>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>https://x.com/grehasoft/status/2100556218968469980</t>
+        </is>
+      </c>
+      <c r="H781" t="n">
+        <v>0</v>
+      </c>
+      <c r="I781" t="n">
+        <v>0</v>
+      </c>
+      <c r="J781" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L781" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N781" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>12:07:24</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>2100556767486791905</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>Ennys_Abbey</t>
+        </is>
+      </c>
+      <c r="E782" t="inlineStr">
+        <is>
+          <t>Investing in myself, one skill @ a time.
+Copywriting → Digital Marketing → AI Content → Meta Ads → Analytics
+Now adding AI Automation wit @TechCrushHQ
+D goal: connect these skills 2 solve real business problems.
+I’ll document the journey. #AIAutomation #RisewithTechCrush https://t.co/jF8O0drqcJ</t>
+        </is>
+      </c>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>https://x.com/Ennys_Abbey/status/2100556767486791905</t>
+        </is>
+      </c>
+      <c r="H782" t="n">
+        <v>0</v>
+      </c>
+      <c r="I782" t="n">
+        <v>0</v>
+      </c>
+      <c r="J782" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L782" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N782" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>12:07:25</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>2100556952929460605</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>valerioamirani</t>
+        </is>
+      </c>
+      <c r="E783" t="inlineStr">
+        <is>
+          <t>@cinderpeak_ Working on @ZenovayDX, helping founders see exactly where users drop off in their checkout funnel with session replays and uptime alerts. What's your startup?</t>
+        </is>
+      </c>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>https://x.com/valerioamirani/status/2100556952929460605</t>
+        </is>
+      </c>
+      <c r="H783" t="n">
+        <v>0</v>
+      </c>
+      <c r="I783" t="n">
+        <v>0</v>
+      </c>
+      <c r="J783" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L783" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N783" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>12:07:25</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>2100556875741921503</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>PascalZeMarshal</t>
+        </is>
+      </c>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>As a CEO that's what I love to see.
+Less ad spend, +50% revenue yoy.
+And it's not random or luck, it was designed in Sep 2025. 
+12 months later the strategy pays. A lot.
+What did we do ?
+- widen our marketing mix beyond paid ads
+- add more owned content, SEO
+- add more PR
+- add https://t.co/520DwwFb8H</t>
+        </is>
+      </c>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>https://x.com/PascalZeMarshal/status/2100556875741921503</t>
+        </is>
+      </c>
+      <c r="H784" t="n">
+        <v>0</v>
+      </c>
+      <c r="I784" t="n">
+        <v>0</v>
+      </c>
+      <c r="J784" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L784" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N784" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>12:07:25</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>2100557069656916220</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>AcehewCouncil</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>@Talby1325159 How does it feel to give your best?© by+Dr Jonathan Founder CEO, ACE &amp;amp; ADCE Council on Executive Excellence 
+"Be the best you canbe with whatever God given gifts you've been blessed to share &amp;amp; be compassionate as you serve others." 
+"Only by giving Hope does one gain Hope in</t>
+        </is>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>https://x.com/AcehewCouncil/status/2100557069656916220</t>
+        </is>
+      </c>
+      <c r="H785" t="n">
+        <v>0</v>
+      </c>
+      <c r="I785" t="n">
+        <v>0</v>
+      </c>
+      <c r="J785" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L785" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N785" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>12:07:26</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>2100557067480437176</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>ChrissyInCrypto</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>💕 The founder isn't the community.
+A healthy ecosystem should eventually become bigger than any individual.
+Founders start things.
+Communities can carry them forward.
+That's when decentralisation becomes meaningful. 🫀
+https://t.co/ZrneYigZdk</t>
+        </is>
+      </c>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>https://x.com/ChrissyInCrypto/status/2100557067480437176</t>
+        </is>
+      </c>
+      <c r="H786" t="n">
+        <v>0</v>
+      </c>
+      <c r="I786" t="n">
+        <v>0</v>
+      </c>
+      <c r="J786" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L786" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N786" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>12:07:26</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>2100557051252588584</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>degengod0x</t>
+        </is>
+      </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>biggest scam collection ever.
+It was developed by a guy @poopie, who is considered a co-founder of the Doodle project.
+Why is the current market still full of the same old scammer devs from the previous cycle?</t>
+        </is>
+      </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>https://x.com/degengod0x/status/2100557051252588584</t>
+        </is>
+      </c>
+      <c r="H787" t="n">
+        <v>0</v>
+      </c>
+      <c r="I787" t="n">
+        <v>0</v>
+      </c>
+      <c r="J787" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L787" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N787" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>12:07:26</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>2100557016976818323</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>vivekshukla</t>
+        </is>
+      </c>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>She maybe the hottest startup marketer but can’t trust someone who puts Pakistani flag and calls herself saudi princess in small letters. https://t.co/vEaOnoQhlW</t>
+        </is>
+      </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>https://x.com/vivekshukla/status/2100557016976818323</t>
+        </is>
+      </c>
+      <c r="H788" t="n">
+        <v>0</v>
+      </c>
+      <c r="I788" t="n">
+        <v>0</v>
+      </c>
+      <c r="J788" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L788" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N788" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>12:07:27</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>2100557015449801068</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>Sull246</t>
+        </is>
+      </c>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>@doeyves Mhj is a predator ?
+When hybe was directly linked to Epstein due to hybe AMERICA/ tag PR and its founder Melissa Nathan who is actually mentioned on the files.
+Source:DOJ https://t.co/ldgDpBg1Y5</t>
+        </is>
+      </c>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>https://x.com/Sull246/status/2100557015449801068</t>
+        </is>
+      </c>
+      <c r="H789" t="n">
+        <v>0</v>
+      </c>
+      <c r="I789" t="n">
+        <v>0</v>
+      </c>
+      <c r="J789" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L789" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N789" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>12:07:27</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>2100556996906733829</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>skiistiredasf</t>
+        </is>
+      </c>
+      <c r="E790" t="inlineStr">
+        <is>
+          <t>Silicon Valley venture capitalists spend billions funding the exact same profiles while giving Black women less than 1% of all capital. As a Black woman founder, Julia Collins completely shattered that gatekeeping standard by building a $1 billion tech unicorn, and she just https://t.co/or54GASTlD</t>
+        </is>
+      </c>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>https://x.com/skiistiredasf/status/2100556996906733829</t>
+        </is>
+      </c>
+      <c r="H790" t="n">
+        <v>0</v>
+      </c>
+      <c r="I790" t="n">
+        <v>0</v>
+      </c>
+      <c r="J790" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L790" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N790" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>12:07:28</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>2100556957555847463</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>BarkJack_</t>
+        </is>
+      </c>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>Prada renovated and expanded its historic premises in the heart of Milan to strengthen ​ties with its wealthiest clients and attract new customers, Chief Executive Andrea Guerra ‌said. 
+Prada already operated both a menswear and a womenswear store in Milan's Galleria Vittorio</t>
+        </is>
+      </c>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>https://x.com/BarkJack_/status/2100556957555847463</t>
+        </is>
+      </c>
+      <c r="H791" t="n">
+        <v>0</v>
+      </c>
+      <c r="I791" t="n">
+        <v>0</v>
+      </c>
+      <c r="J791" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L791" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N791" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>12:07:28</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>2100556936441721234</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>luis_irua</t>
+        </is>
+      </c>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>@Danielsalcan_ Estudian huevadas y sacan maestrías online y quieres ganar 3000? Si estudias administracion, marketing, trabajo social , psicología, y todo eso de la salud hasta está demás pagarles 600 .</t>
+        </is>
+      </c>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>https://x.com/luis_irua/status/2100556936441721234</t>
+        </is>
+      </c>
+      <c r="H792" t="n">
+        <v>0</v>
+      </c>
+      <c r="I792" t="n">
+        <v>0</v>
+      </c>
+      <c r="J792" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L792" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N792" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>12:07:28</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>2100556926954471614</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>indstartupnews</t>
+        </is>
+      </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>Enlight Metals, a homegrown agentic AI-enabled metal procurement platform, has raised $1.5 million in funding from Exar North Group Inc., a US-based investment firm headquartered in Princeton, New Jersey, at a $10 million valuation.
+The startup will use the raised capital to https://t.co/MJlwtzZ726</t>
+        </is>
+      </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>https://x.com/indstartupnews/status/2100556926954471614</t>
+        </is>
+      </c>
+      <c r="H793" t="n">
+        <v>0</v>
+      </c>
+      <c r="I793" t="n">
+        <v>0</v>
+      </c>
+      <c r="J793" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L793" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N793" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>12:07:28</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>2100556924500824413</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>empressavisiwa</t>
+        </is>
+      </c>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>Started with 20+ founders at Founder Institute @founding 
+Now, we’re down to 12 - and I’m grateful to still be standing, learning, building, and pushing forward.
+Week 8. Two weeks to go. 🚀
+The pressure is real - and we didn’t come this far just to finish.
+Let’s bring it https://t.co/iwejvMTcrr</t>
+        </is>
+      </c>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>https://x.com/empressavisiwa/status/2100556924500824413</t>
+        </is>
+      </c>
+      <c r="H794" t="n">
+        <v>0</v>
+      </c>
+      <c r="I794" t="n">
+        <v>0</v>
+      </c>
+      <c r="J794" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L794" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N794" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>12:07:29</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>2100556897954709648</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>v_soph392</t>
+        </is>
+      </c>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>@WTOP "Amplify the energy" is just marketing speak for steeper seats and bigger speakers. How much did they spend on acoustics versus actual fan experience?</t>
+        </is>
+      </c>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>https://x.com/v_soph392/status/2100556897954709648</t>
+        </is>
+      </c>
+      <c r="H795" t="n">
+        <v>0</v>
+      </c>
+      <c r="I795" t="n">
+        <v>0</v>
+      </c>
+      <c r="J795" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L795" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N795" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>12:07:29</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>2100556883480264737</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>checkra1ndev</t>
+        </is>
+      </c>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>@uniquesingh__ @YieldFields_RH @Skarly Most crypto marketing burns money on KOLs. A public bid for rank costs less and everyone sees what you paid.</t>
+        </is>
+      </c>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>https://x.com/checkra1ndev/status/2100556883480264737</t>
+        </is>
+      </c>
+      <c r="H796" t="n">
+        <v>1</v>
+      </c>
+      <c r="I796" t="n">
+        <v>0</v>
+      </c>
+      <c r="J796" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L796" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N796" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>12:07:30</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>2100556895140430237</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>KevinTroyGA</t>
+        </is>
+      </c>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>Wendy's has been STRUGGLING lately. Optics alone won't save them, but if the messaging is going to be them returning 'back to basics', this was a huge marketing no-brainer.</t>
+        </is>
+      </c>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>https://x.com/KevinTroyGA/status/2100556895140430237</t>
+        </is>
+      </c>
+      <c r="H797" t="n">
+        <v>0</v>
+      </c>
+      <c r="I797" t="n">
+        <v>0</v>
+      </c>
+      <c r="J797" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L797" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N797" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>12:07:30</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>2100556238383902732</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>eMarketHQ</t>
+        </is>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>Fintech founders: I want your honest answer 👇
+If you saw https://t.co/PWEn8s1FBP on a startup landing page, what would you assume they do?
+Payments? Crypto? Treasury? Something else?
+Drop your first thought — no Googling. 😂
+Domain is for sale. ↓ https://t.co/QKjVPhoXRv</t>
+        </is>
+      </c>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>https://x.com/eMarketHQ/status/2100556238383902732</t>
+        </is>
+      </c>
+      <c r="H798" t="n">
+        <v>0</v>
+      </c>
+      <c r="I798" t="n">
+        <v>1</v>
+      </c>
+      <c r="J798" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L798" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N798" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>12:07:30</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>2100556823430357334</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>mktgstockport</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>Posts from Marketing Stockport for 09/17/2026 - https://t.co/0s6bPu0nxL</t>
+        </is>
+      </c>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>https://x.com/mktgstockport/status/2100556823430357334</t>
+        </is>
+      </c>
+      <c r="H799" t="n">
+        <v>0</v>
+      </c>
+      <c r="I799" t="n">
+        <v>0</v>
+      </c>
+      <c r="J799" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L799" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N799" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>12:07:31</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>2100556800781152580</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>juagu01</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>@kitanalexa Imagínate que fue dizque marketing del concesionario, pero también pensé en él jajaja</t>
+        </is>
+      </c>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>https://x.com/juagu01/status/2100556800781152580</t>
+        </is>
+      </c>
+      <c r="H800" t="n">
+        <v>0</v>
+      </c>
+      <c r="I800" t="n">
+        <v>0</v>
+      </c>
+      <c r="J800" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L800" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N800" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>12:07:31</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>2100556798809841665</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>Sociograph</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>Gestionar las preferencias de talento y ego en el mundo de la creatividad. La aplicación de la neurociencia como oportunidad. En cualquier ámbito. 
+D. Paolo Vasile
+#CongresoMarketingScience https://t.co/fJ5txRIHRu</t>
+        </is>
+      </c>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>https://x.com/Sociograph/status/2100556798809841665</t>
+        </is>
+      </c>
+      <c r="H801" t="n">
+        <v>0</v>
+      </c>
+      <c r="I801" t="n">
+        <v>0</v>
+      </c>
+      <c r="J801" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L801" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N801" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>12:07:32</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>2100556154476572738</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>Antoinesarasin</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>Your articles now bring you leads 🤑
+Traffic is nice, but leads are better ;)
+So every BabyLoveGrowth article now includes two call-to-action cards for your business: one right after the summary at the top, one at the end https://t.co/dL5n8b6GkG</t>
+        </is>
+      </c>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>https://x.com/Antoinesarasin/status/2100556154476572738</t>
+        </is>
+      </c>
+      <c r="H802" t="n">
+        <v>0</v>
+      </c>
+      <c r="I802" t="n">
+        <v>1</v>
+      </c>
+      <c r="J802" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L802" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N802" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>12:07:32</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>2100556758062453120</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>saezafnik48303</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>Cc tuh kek jebakan marketing 🤣</t>
+        </is>
+      </c>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>https://x.com/saezafnik48303/status/2100556758062453120</t>
+        </is>
+      </c>
+      <c r="H803" t="n">
+        <v>0</v>
+      </c>
+      <c r="I803" t="n">
+        <v>0</v>
+      </c>
+      <c r="J803" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L803" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N803" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>12:07:33</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>2100556736658895222</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>sustainme_in</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>Pet owners — not Diwali smoke or flu season — are now the biggest buyers of air purifiers in India.
+They make up 17% of the customer voice and buy mainly for pet hair, dander, dust &amp;amp; odour, not outdoor AQI.
+Brands still sell “pollution fighters.” Pet parents just want something https://t.co/SKu7Uo0UC8</t>
+        </is>
+      </c>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>https://x.com/sustainme_in/status/2100556736658895222</t>
+        </is>
+      </c>
+      <c r="H804" t="n">
+        <v>0</v>
+      </c>
+      <c r="I804" t="n">
+        <v>0</v>
+      </c>
+      <c r="J804" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L804" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N804" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>12:07:33</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>2100556736054595675</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>LLCubKing</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>@BigMoLove Let’s cook!!! 📝 💻 
+-SPACES HOST
+-MARKETING 
+THIS INTERN DOES IT All!!</t>
+        </is>
+      </c>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>https://x.com/LLCubKing/status/2100556736054595675</t>
+        </is>
+      </c>
+      <c r="H805" t="n">
+        <v>0</v>
+      </c>
+      <c r="I805" t="n">
+        <v>0</v>
+      </c>
+      <c r="J805" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L805" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N805" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>12:07:34</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>2100556723333255426</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>psyco_alemon</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>@ramosbueno9150 Marketing da Sony é melhor sem dúvida, mas como eu analiso onde gasto meu dinheiro racionalmente ainda vejo muito mais vantagem no Xbox, principalmente nos últimos anos que todos os jogos das aquisições foram finalmente lançados.</t>
+        </is>
+      </c>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>https://x.com/psyco_alemon/status/2100556723333255426</t>
+        </is>
+      </c>
+      <c r="H806" t="n">
+        <v>0</v>
+      </c>
+      <c r="I806" t="n">
+        <v>0</v>
+      </c>
+      <c r="J806" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L806" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N806" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>12:07:34</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>2100556716136079789</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>iTechSeries</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>In our latest podcast, @frankoerlemans of @Randstad  explores click-to-cash, AI, programmatic marketing, and human judgment in modern recruitment. Tune in for practical insights on making marketing measurable: https://t.co/8mxk7Z9xUl
+#Marketing #AI #GTMLibrary</t>
+        </is>
+      </c>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>https://x.com/iTechSeries/status/2100556716136079789</t>
+        </is>
+      </c>
+      <c r="H807" t="n">
+        <v>0</v>
+      </c>
+      <c r="I807" t="n">
+        <v>0</v>
+      </c>
+      <c r="J807" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L807" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N807" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>12:07:35</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>2100556683579732062</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>lokerdisoloraya</t>
+        </is>
+      </c>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>Loker Admin dan Marketing di Koperasi Pratama Surya Makmur Sragen 
+Info lengkap klik &amp;gt;&amp;gt; https://t.co/PnwSfGf6hm 
+Follow IG @lokersragen.id
+#lokersragen #lowongansragen #sragen #loker #lokercot</t>
+        </is>
+      </c>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>https://x.com/lokerdisoloraya/status/2100556683579732062</t>
+        </is>
+      </c>
+      <c r="H808" t="n">
+        <v>0</v>
+      </c>
+      <c r="I808" t="n">
+        <v>0</v>
+      </c>
+      <c r="J808" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L808" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N808" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>12:07:35</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>2100556670090809449</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>adwexp</t>
+        </is>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>#FacebookAds 2026 benchmarks data
+#ppc https://t.co/PDIE0mBK0q</t>
+        </is>
+      </c>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>https://x.com/adwexp/status/2100556670090809449</t>
+        </is>
+      </c>
+      <c r="H809" t="n">
+        <v>0</v>
+      </c>
+      <c r="I809" t="n">
+        <v>0</v>
+      </c>
+      <c r="J809" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L809" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N809" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>12:07:35</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>2100556658854297676</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>LavidaOnline</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>Changing the wrong position. The Jessica Motaung School of Commercial Marketing is one of the best in the land. There are positions that needs restructuring 😭</t>
+        </is>
+      </c>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>https://x.com/LavidaOnline/status/2100556658854297676</t>
+        </is>
+      </c>
+      <c r="H810" t="n">
+        <v>0</v>
+      </c>
+      <c r="I810" t="n">
+        <v>0</v>
+      </c>
+      <c r="J810" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L810" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N810" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>12:07:35</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>2100556654517354805</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>fermentyog</t>
+        </is>
+      </c>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>@Finumus1 I’d assume every payout adds admin costs. Daily would just be marketing with extra fees.</t>
+        </is>
+      </c>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>https://x.com/fermentyog/status/2100556654517354805</t>
+        </is>
+      </c>
+      <c r="H811" t="n">
+        <v>0</v>
+      </c>
+      <c r="I811" t="n">
+        <v>0</v>
+      </c>
+      <c r="J811" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L811" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N811" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>12:07:36</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>2100556617377034391</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>shruutie</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>Just give me a ONE good reason to buy an Amazon Prime video subscription?
+&amp;gt; mid shows
+&amp;gt; pay extra to rent/buy movies
+&amp;gt; shitty interface 
+&amp;gt; ads even after paying for subscription 
+&amp;gt; subtitles/audio options are inconsistent
+&amp;gt; random title disappearance glitch 
+&amp;gt; confused content</t>
+        </is>
+      </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>https://x.com/shruutie/status/2100556617377034391</t>
+        </is>
+      </c>
+      <c r="H812" t="n">
+        <v>0</v>
+      </c>
+      <c r="I812" t="n">
+        <v>0</v>
+      </c>
+      <c r="J812" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L812" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N812" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>12:07:36</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>2100556524540080323</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>FacuPicc</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>@agustinhooks_ “Meta ads es una boludez”: ¿Te referís a que no funciona o que es fácil agarrarle la mano?</t>
+        </is>
+      </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>https://x.com/FacuPicc/status/2100556524540080323</t>
+        </is>
+      </c>
+      <c r="H813" t="n">
+        <v>0</v>
+      </c>
+      <c r="I813" t="n">
+        <v>0</v>
+      </c>
+      <c r="J813" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L813" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N813" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>12:07:36</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>2100556449835544723</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>boringlocalseo</t>
+        </is>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>If you have a live contractor lead, do this.
+Tristan says his strongest handoff is a call already in progress. Keep a contractor list. When someone wants pipe repair, you phone Bob, confirm he can do it, and live-transfer Michelle onto that line.
+You still need leads for that https://t.co/mdLvDIK8Rm</t>
+        </is>
+      </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>https://x.com/boringlocalseo/status/2100556449835544723</t>
+        </is>
+      </c>
+      <c r="H814" t="n">
+        <v>1</v>
+      </c>
+      <c r="I814" t="n">
+        <v>1</v>
+      </c>
+      <c r="J814" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L814" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N814" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>12:07:36</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>2100557084827799695</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>mikunswago</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>@Jeremybtc @MetaWin 🆔 mikunswago 
+I'm a small Content creator here my Legend, building and growing more in my journey of becoming a big Creator, this Win will help me get a good Camera and a PC to make good contents, some of my contents are attached below, I hope you bless me here @Jeremybtc . 🙏</t>
+        </is>
+      </c>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>https://x.com/mikunswago/status/2100557084827799695</t>
+        </is>
+      </c>
+      <c r="H815" t="n">
+        <v>0</v>
+      </c>
+      <c r="I815" t="n">
+        <v>0</v>
+      </c>
+      <c r="J815" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L815" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N815" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>12:07:37</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>2100557080729969042</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>arnaudmercier</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>Pandora 2.0: Artificial Intelligence and the Moral Failure of Our Age - Threefold Advocate https://t.co/FmQSLHmZxe</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>https://x.com/arnaudmercier/status/2100557080729969042</t>
+        </is>
+      </c>
+      <c r="H816" t="n">
+        <v>0</v>
+      </c>
+      <c r="I816" t="n">
+        <v>0</v>
+      </c>
+      <c r="J816" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L816" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N816" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>12:07:37</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>2100557070231544199</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>kingrichmo</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>1️⃣ The object is attention with a balance sheet
+Ansem’s broader frame, which he has explicitly tied to $ANSEM, is culture/capital: memes already price attention; the next step is a cultural object that can keep value, route value, and sit in front of other assets instead of only</t>
+        </is>
+      </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>https://x.com/kingrichmo/status/2100557070231544199</t>
+        </is>
+      </c>
+      <c r="H817" t="n">
+        <v>0</v>
+      </c>
+      <c r="I817" t="n">
+        <v>0</v>
+      </c>
+      <c r="J817" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L817" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N817" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>12:07:37</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>2100557064011415743</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>mauriidotcom</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>Spent the day at Avalanche Summit NYC 2026 Day 1 surrounded by builders, institutions, and believers.
+The conversations were different this cycle. Less noise. More infrastructure. More capital with a long-term lens. More devs who don’t care about the price just the build. https://t.co/hE0CkGJ5RD</t>
+        </is>
+      </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>https://x.com/mauriidotcom/status/2100557064011415743</t>
+        </is>
+      </c>
+      <c r="H818" t="n">
+        <v>0</v>
+      </c>
+      <c r="I818" t="n">
+        <v>0</v>
+      </c>
+      <c r="J818" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L818" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N818" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>12:07:37</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>2100557062878962157</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>GwendolynFourte</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>https://t.co/bqXldCJP5N</t>
+        </is>
+      </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>https://x.com/GwendolynFourte/status/2100557062878962157</t>
+        </is>
+      </c>
+      <c r="H819" t="n">
+        <v>0</v>
+      </c>
+      <c r="I819" t="n">
+        <v>0</v>
+      </c>
+      <c r="J819" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L819" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N819" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>12:07:37</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>2100557025164079213</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>LedgerPeLabs</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>India’s Stablecoin Problem Begins When the Token Reaches the Bank Account https://t.co/G8wEuw1PoZ</t>
+        </is>
+      </c>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>https://x.com/LedgerPeLabs/status/2100557025164079213</t>
+        </is>
+      </c>
+      <c r="H820" t="n">
+        <v>0</v>
+      </c>
+      <c r="I820" t="n">
+        <v>0</v>
+      </c>
+      <c r="J820" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L820" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N820" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>12:07:38</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>2100557025096675736</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>muhamedabuahmad</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>3 ضباط من الموساد في مكتب مؤسس حركة ميدان، النصف فلسطيني/إسرائيلي باعترافه، رضا فهمي بدعوة رسمية منه وعلاقته بالسفيرة الإسرائيلية في تركيا
+السؤال الأول: ماذا كان يقول لها 8 سبتمبر؟
+الإجابة والتفاصيل حصريا هنا:
+https://t.co/1tQJPh6x3f
+#المؤتمر_الوطني_الأول
+#علشان_بكرة
+#حركة_ميدان https://t.co/Z5T3I6dSJv</t>
+        </is>
+      </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>https://x.com/muhamedabuahmad/status/2100557025096675736</t>
+        </is>
+      </c>
+      <c r="H821" t="n">
+        <v>0</v>
+      </c>
+      <c r="I821" t="n">
+        <v>0</v>
+      </c>
+      <c r="J821" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L821" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N821" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>12:07:38</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>2100557014753828917</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>jjueonnmj3</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>@hirunkitletters cpc kak done aku chat ya</t>
+        </is>
+      </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>https://x.com/jjueonnmj3/status/2100557014753828917</t>
+        </is>
+      </c>
+      <c r="H822" t="n">
+        <v>0</v>
+      </c>
+      <c r="I822" t="n">
+        <v>0</v>
+      </c>
+      <c r="J822" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L822" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N822" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>12:07:38</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>2100557005056286986</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>k_ylft</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>@patientinvestor I am just sad to see this. How about currency collapse?</t>
+        </is>
+      </c>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>https://x.com/k_ylft/status/2100557005056286986</t>
+        </is>
+      </c>
+      <c r="H823" t="n">
+        <v>0</v>
+      </c>
+      <c r="I823" t="n">
+        <v>0</v>
+      </c>
+      <c r="J823" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L823" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N823" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>12:07:38</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>2100556985406025853</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>texankitcat</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>@Justyourfly @RealNurseKim @jessmachadoshow Interesting that every content creator that is trashing  her for content is making bank, and are also Aidan Kearney simps. He praises and endorses those creators, because they are falling in line. Fuck Aidan Kearney.</t>
+        </is>
+      </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>https://x.com/texankitcat/status/2100556985406025853</t>
+        </is>
+      </c>
+      <c r="H824" t="n">
+        <v>0</v>
+      </c>
+      <c r="I824" t="n">
+        <v>0</v>
+      </c>
+      <c r="J824" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L824" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N824" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>12:07:39</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>2100556970843414631</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>Entrepreneur</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>Embrace the unknown. https://t.co/ELLseRe89W</t>
+        </is>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>https://x.com/Entrepreneur/status/2100556970843414631</t>
+        </is>
+      </c>
+      <c r="H825" t="n">
+        <v>0</v>
+      </c>
+      <c r="I825" t="n">
+        <v>0</v>
+      </c>
+      <c r="J825" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L825" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N825" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>12:07:39</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>2100556964602454130</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>arceyul</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>https://t.co/BnIvFGy9jd</t>
+        </is>
+      </c>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>https://x.com/arceyul/status/2100556964602454130</t>
+        </is>
+      </c>
+      <c r="H826" t="n">
+        <v>0</v>
+      </c>
+      <c r="I826" t="n">
+        <v>0</v>
+      </c>
+      <c r="J826" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L826" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N826" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>12:07:40</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>2100556329127379380</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>billmurphy</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>@JREakin Basically a company brain. Good stuff. We’ve been using GitHub for a version of this. A little obsidian. 
+We have a client that has obsidian locked in for all this work across their business and client work. Made onboarding a breeze</t>
+        </is>
+      </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>https://x.com/billmurphy/status/2100556329127379380</t>
+        </is>
+      </c>
+      <c r="H827" t="n">
+        <v>0</v>
+      </c>
+      <c r="I827" t="n">
+        <v>0</v>
+      </c>
+      <c r="J827" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L827" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N827" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>12:07:40</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>2100556938358505479</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>CorrieDMarketin</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>Devolution in Scotland is a failed experiment! Abolish it now before they trash our economy even further! Even @NicolaSturgeon has moved to England, if you need any more proof than this! 🇬🇧 Unite the UK reduce our taxes stop spaffing it on surplus to requirement politicians!</t>
+        </is>
+      </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>https://x.com/CorrieDMarketin/status/2100556938358505479</t>
+        </is>
+      </c>
+      <c r="H828" t="n">
+        <v>0</v>
+      </c>
+      <c r="I828" t="n">
+        <v>0</v>
+      </c>
+      <c r="J828" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L828" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N828" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>12:07:40</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>2100556927147344176</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>PolMillennial87</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>@RipsetBirdGang @ChrisCuomo No you’re a FAGGOT. Bear, pig = GAY🌈 🤣🤣
+I’m an entrepreneur. with a degree your retarded bitch ass could NEVER. 
+Black Millennials  can’t be hippies, old fart. Calling me cum guzzling is a compliment 🤤!!
+Thunder cunt? So corny &amp;amp; white! That’s your micr peen, shrimp dick 🍤</t>
+        </is>
+      </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>https://x.com/PolMillennial87/status/2100556927147344176</t>
+        </is>
+      </c>
+      <c r="H829" t="n">
+        <v>0</v>
+      </c>
+      <c r="I829" t="n">
+        <v>0</v>
+      </c>
+      <c r="J829" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L829" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N829" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>12:07:40</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>2100556289902322113</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>Gianps</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>#FacebookAds 2026 benchmarks data
+#ppc https://t.co/D6BarDgu5y</t>
+        </is>
+      </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>https://x.com/Gianps/status/2100556289902322113</t>
+        </is>
+      </c>
+      <c r="H830" t="n">
+        <v>0</v>
+      </c>
+      <c r="I830" t="n">
+        <v>0</v>
+      </c>
+      <c r="J830" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L830" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N830" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>12:07:41</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>2100556920448831909</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>Soulmate889</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>@ChimpiGoki Good morning Gokiii 🥰</t>
+        </is>
+      </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>https://x.com/Soulmate889/status/2100556920448831909</t>
+        </is>
+      </c>
+      <c r="H831" t="n">
+        <v>0</v>
+      </c>
+      <c r="I831" t="n">
+        <v>0</v>
+      </c>
+      <c r="J831" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L831" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N831" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>12:07:41</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>2100556905403777361</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>planton282</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>@DylanTeil icl btc eth</t>
+        </is>
+      </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>https://x.com/planton282/status/2100556905403777361</t>
+        </is>
+      </c>
+      <c r="H832" t="n">
+        <v>0</v>
+      </c>
+      <c r="I832" t="n">
+        <v>0</v>
+      </c>
+      <c r="J832" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L832" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N832" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>12:07:41</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>2100556902811705541</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>arnaudmercier</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>Chefs de partis conviés à l'Élysée: "Je ne vois pas l'utilité de la mise en scène", déclare le député "Écologiste et Social" Benjamin Lucas-Lundy  https://t.co/ELsNUelFCl https://t.co/JEmXo8O89E</t>
+        </is>
+      </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>https://x.com/arnaudmercier/status/2100556902811705541</t>
+        </is>
+      </c>
+      <c r="H833" t="n">
+        <v>0</v>
+      </c>
+      <c r="I833" t="n">
+        <v>0</v>
+      </c>
+      <c r="J833" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L833" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N833" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>12:07:42</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>2100556242963792279</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>AdscodOfficial</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>Learn how to increase reach, improve ROAS and optimise native ad delivery across the Adscod network with practical bidding and #campaign management strategies.
+Learn more: https://t.co/WzREx4K8lh</t>
+        </is>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>https://x.com/AdscodOfficial/status/2100556242963792279</t>
+        </is>
+      </c>
+      <c r="H834" t="n">
+        <v>2</v>
+      </c>
+      <c r="I834" t="n">
+        <v>0</v>
+      </c>
+      <c r="J834" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L834" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N834" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>12:07:42</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>2100556236026507313</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>andrino_daniel</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>Any advice on how to drive leads to a waiting list? 
+My goals are to sharpen use cases and start learning how to get users.  
+Should I already run paid ads , or stick to things that don't scale?
+This is the product: https://t.co/uqBzmkrPXW</t>
+        </is>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>https://x.com/andrino_daniel/status/2100556236026507313</t>
+        </is>
+      </c>
+      <c r="H835" t="n">
+        <v>1</v>
+      </c>
+      <c r="I835" t="n">
+        <v>0</v>
+      </c>
+      <c r="J835" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L835" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N835" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>12:07:42</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>2100556220478238927</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>BehavioralHP</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>Any agency can promise results. Watch how fast I can list actual ones, all from live Search Console accounts. https://t.co/Ca6NS7sFIq #RehabMarketing #SEOResults
+Watch How Fast I Can List Real Rehab Marketing Results https://t.co/QN3hKLpZTd</t>
+        </is>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>https://x.com/BehavioralHP/status/2100556220478238927</t>
+        </is>
+      </c>
+      <c r="H836" t="n">
+        <v>0</v>
+      </c>
+      <c r="I836" t="n">
+        <v>0</v>
+      </c>
+      <c r="J836" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L836" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N836" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>12:07:42</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>2100556219748388941</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>Ejudicator</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>🚨 Breaking SEO News! 📰 Google Ads Spend Benchmarks Report Explained for Marketers - https://t.co/DstjqHmrlX #SEO #GEO #AEO</t>
+        </is>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>https://x.com/Ejudicator/status/2100556219748388941</t>
+        </is>
+      </c>
+      <c r="H837" t="n">
+        <v>0</v>
+      </c>
+      <c r="I837" t="n">
+        <v>0</v>
+      </c>
+      <c r="J837" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L837" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N837" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>12:07:43</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>2100556845903478870</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>TibetPeople</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>18th #TPiE Second Session opens — and on day one #FakeMonks turn our Parliament into a stage for disunity. That’s exactly what #China wants. We resist those Khampa Gangsters &amp;amp; call kick #GowoPhende out of @Tibparliament.
+#FreeTibet #XiJinping #DalaiLama #CTA #TYC #SFT #TWA #Vtag https://t.co/7pp90S2kC2</t>
+        </is>
+      </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>https://x.com/TibetPeople/status/2100556845903478870</t>
+        </is>
+      </c>
+      <c r="H838" t="n">
+        <v>0</v>
+      </c>
+      <c r="I838" t="n">
+        <v>0</v>
+      </c>
+      <c r="J838" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L838" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N838" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>12:07:43</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>2100556816648130798</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>sammyprimus1</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>@DebsSZN When you add Loan Move</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>https://x.com/sammyprimus1/status/2100556816648130798</t>
+        </is>
+      </c>
+      <c r="H839" t="n">
+        <v>0</v>
+      </c>
+      <c r="I839" t="n">
+        <v>0</v>
+      </c>
+      <c r="J839" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L839" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N839" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>12:07:43</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>2100556808939278639</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>flawedgenius78</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>@korinek_trades Called it perfectly—clean, public, and timestamped. You and @88krxxs are my go-to market follows.</t>
+        </is>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>https://x.com/flawedgenius78/status/2100556808939278639</t>
+        </is>
+      </c>
+      <c r="H840" t="n">
+        <v>0</v>
+      </c>
+      <c r="I840" t="n">
+        <v>0</v>
+      </c>
+      <c r="J840" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L840" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N840" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>12:07:43</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>2100556791159443600</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>ochuwa22</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>So what did I do today? 
+I followed up on my Instagram pitches. I will be in your faces😛</t>
+        </is>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>https://x.com/ochuwa22/status/2100556791159443600</t>
+        </is>
+      </c>
+      <c r="H841" t="n">
+        <v>0</v>
+      </c>
+      <c r="I841" t="n">
+        <v>0</v>
+      </c>
+      <c r="J841" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L841" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N841" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>12:07:43</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>2100556786117890327</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>misakizzs</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>TRANSLATION 🫰
+there are so many cool artists and people in the dr fandom and I'd really like to praise every content creator I love 😭</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>https://x.com/misakizzs/status/2100556786117890327</t>
+        </is>
+      </c>
+      <c r="H842" t="n">
+        <v>0</v>
+      </c>
+      <c r="I842" t="n">
+        <v>0</v>
+      </c>
+      <c r="J842" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L842" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N842" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>12:07:44</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>2100556757772698085</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>DifferentialDay</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>@Pras_fpl @FPL_Brandon In his defence Brandon saw another content creator ask this question, thought it was poignant and copied him</t>
+        </is>
+      </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>https://x.com/DifferentialDay/status/2100556757772698085</t>
+        </is>
+      </c>
+      <c r="H843" t="n">
+        <v>0</v>
+      </c>
+      <c r="I843" t="n">
+        <v>0</v>
+      </c>
+      <c r="J843" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L843" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N843" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>12:07:44</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>2100556735551275456</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>UbongAkpan01</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>Without the opposite of what you have, you would not know how valuable what you have is.</t>
+        </is>
+      </c>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>https://x.com/UbongAkpan01/status/2100556735551275456</t>
+        </is>
+      </c>
+      <c r="H844" t="n">
+        <v>0</v>
+      </c>
+      <c r="I844" t="n">
+        <v>0</v>
+      </c>
+      <c r="J844" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L844" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N844" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>12:07:44</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>2100556720531489014</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>Ovieyare</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>@Ogabu_Sama @Halosznn_ Social media manager</t>
+        </is>
+      </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>https://x.com/Ovieyare/status/2100556720531489014</t>
+        </is>
+      </c>
+      <c r="H845" t="n">
+        <v>0</v>
+      </c>
+      <c r="I845" t="n">
+        <v>0</v>
+      </c>
+      <c r="J845" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L845" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N845" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>12:07:44</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>2100556627208274305</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>icoda_io</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>Hey, crypto creator. This might save you a few hours a week.
+Pitching, following up, renegotiating rates after the fact — it's a lot of work that doesn't show up in your content. We know because we've been on the other side of those conversations for nine years.
+ICODA Creator https://t.co/wpOmoDCcbf</t>
+        </is>
+      </c>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>https://x.com/icoda_io/status/2100556627208274305</t>
+        </is>
+      </c>
+      <c r="H846" t="n">
+        <v>0</v>
+      </c>
+      <c r="I846" t="n">
+        <v>0</v>
+      </c>
+      <c r="J846" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L846" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N846" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>12:07:44</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>2100556602210423273</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>khoa_solo</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>Today I grew up!
+Ever since I started building in public, I've had a habit: whenever a new tech drops that I think will blow up, I jump on the trend, hoping one day something goes viral.
+When OpenClaw first came out, I added it to Server Compass with its own tab so people could https://t.co/YYbXZ7yf26</t>
+        </is>
+      </c>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>https://x.com/khoa_solo/status/2100556602210423273</t>
+        </is>
+      </c>
+      <c r="H847" t="n">
+        <v>1</v>
+      </c>
+      <c r="I847" t="n">
+        <v>1</v>
+      </c>
+      <c r="J847" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L847" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N847" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>12:07:45</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>2100556583193202726</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>you_x_you_i</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>If your store converts below 1.5%, more ad spend and more traffic won't fix it.
+A conversion rate of 0.8%, with ad spend behind it, isn't growth. It's cash-flow destruction with extra steps.</t>
+        </is>
+      </c>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>https://x.com/you_x_you_i/status/2100556583193202726</t>
+        </is>
+      </c>
+      <c r="H848" t="n">
+        <v>0</v>
+      </c>
+      <c r="I848" t="n">
+        <v>1</v>
+      </c>
+      <c r="J848" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L848" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N848" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>12:07:45</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>2100556575630905564</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>HETAR70</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>@DBR8 Mire, totalmente de acuerdo, mejor no ver a un equipo que tiene facturas del vicepresidente del cta. https://t.co/tmpxl961Eu</t>
+        </is>
+      </c>
+      <c r="F849" t="inlineStr">
+        <is>
+          <t>https://x.com/HETAR70/status/2100556575630905564</t>
+        </is>
+      </c>
+      <c r="H849" t="n">
+        <v>0</v>
+      </c>
+      <c r="I849" t="n">
+        <v>0</v>
+      </c>
+      <c r="J849" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L849" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N849" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>12:07:46</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>2100556542495834543</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>AcaymoBB</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>@DaniJV_ @_alberginia @ANKH0R El anuncio de Yolanda Parga como miembro del CTA.
+1 RT.
+18 likes
+1 respuesta.
+¡EL ESCÁNDALO!
+https://t.co/gXyxemcbgm</t>
+        </is>
+      </c>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>https://x.com/AcaymoBB/status/2100556542495834543</t>
+        </is>
+      </c>
+      <c r="H850" t="n">
+        <v>0</v>
+      </c>
+      <c r="I850" t="n">
+        <v>0</v>
+      </c>
+      <c r="J850" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L850" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N850" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>12:07:46</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>2100556518856732780</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>GENIC0N</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>@ReverseBoomer just keep going</t>
+        </is>
+      </c>
+      <c r="F851" t="inlineStr">
+        <is>
+          <t>https://x.com/GENIC0N/status/2100556518856732780</t>
+        </is>
+      </c>
+      <c r="H851" t="n">
+        <v>0</v>
+      </c>
+      <c r="I851" t="n">
+        <v>0</v>
+      </c>
+      <c r="J851" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L851" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N851" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>12:07:46</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>2100556508568420652</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>fangirlvibes_</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>@jaypark0_ Cpc yaa kak</t>
+        </is>
+      </c>
+      <c r="F852" t="inlineStr">
+        <is>
+          <t>https://x.com/fangirlvibes_/status/2100556508568420652</t>
+        </is>
+      </c>
+      <c r="H852" t="n">
+        <v>0</v>
+      </c>
+      <c r="I852" t="n">
+        <v>0</v>
+      </c>
+      <c r="J852" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L852" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N852" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>12:07:46</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>2100556459662549273</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>Levinne__</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>This is the client feedback I use to sell out my Purpose 50🤣 https://t.co/m1daQ4mFb4</t>
+        </is>
+      </c>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>https://x.com/Levinne__/status/2100556459662549273</t>
+        </is>
+      </c>
+      <c r="H853" t="n">
+        <v>1</v>
+      </c>
+      <c r="I853" t="n">
+        <v>0</v>
+      </c>
+      <c r="J853" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L853" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N853" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>12:07:47</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>2100556447121649952</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>VaneRey72</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>@Contracurva Desde Septiembre?
+Hace rato q ARCA viene embargando cuentas.
+Para las pyme,re complicado! Entran en un círculo vicioso: tenes la cta embargada, entran cheques,se rechazan porque no los podes cubrir.Como tenes cheques rechazados,el banco te baja el acuerdo de descubierto. Debacle</t>
+        </is>
+      </c>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>https://x.com/VaneRey72/status/2100556447121649952</t>
+        </is>
+      </c>
+      <c r="H854" t="n">
+        <v>0</v>
+      </c>
+      <c r="I854" t="n">
+        <v>0</v>
+      </c>
+      <c r="J854" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L854" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N854" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>12:07:47</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>2100556445154427146</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>GENIC0N</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>https://t.co/O29SBWpEuu</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>https://x.com/GENIC0N/status/2100556445154427146</t>
+        </is>
+      </c>
+      <c r="H855" t="n">
+        <v>0</v>
+      </c>
+      <c r="I855" t="n">
+        <v>0</v>
+      </c>
+      <c r="J855" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L855" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N855" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>12:07:47</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>2100556436380020963</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>Coravel_</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>CS matchmaking is a dumpster fire sometimes tbh https://t.co/aVSZ1x10Lx</t>
+        </is>
+      </c>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>https://x.com/Coravel_/status/2100556436380020963</t>
+        </is>
+      </c>
+      <c r="H856" t="n">
+        <v>0</v>
+      </c>
+      <c r="I856" t="n">
+        <v>0</v>
+      </c>
+      <c r="J856" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L856" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N856" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>12:07:47</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>2100556400812232763</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>UbongAkpan01</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>You only know something is good because you have felt or experienced the opposite. 
+This is because without the opposite of anything, you would not know the importance of a thing or esteem what you have. 
+Take happiness for example. Happiness needs a reference point. If every</t>
+        </is>
+      </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>https://x.com/UbongAkpan01/status/2100556400812232763</t>
+        </is>
+      </c>
+      <c r="H857" t="n">
+        <v>1</v>
+      </c>
+      <c r="I857" t="n">
+        <v>0</v>
+      </c>
+      <c r="J857" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L857" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N857" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>12:07:48</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>2100556411390378240</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>Erick_m0renazo</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>@RabbiJeffx Lo de que palestino fueran vio*ados por perro Cro que se inspiró en Pinochet</t>
+        </is>
+      </c>
+      <c r="F858" t="inlineStr">
+        <is>
+          <t>https://x.com/Erick_m0renazo/status/2100556411390378240</t>
+        </is>
+      </c>
+      <c r="H858" t="n">
+        <v>0</v>
+      </c>
+      <c r="I858" t="n">
+        <v>0</v>
+      </c>
+      <c r="J858" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L858" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N858" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>12:07:48</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>2100556404407038318</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>DIYregistry</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>@ZypZapCommunity Thanks for your input. Yeah, the customization side took a few days to grind out the bugs but with some strong prompts and solid foundation, I was able to narrow it down to the pixel. I tried taking out the coding aspect and make the dashboard feel more like a place you can</t>
+        </is>
+      </c>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>https://x.com/DIYregistry/status/2100556404407038318</t>
+        </is>
+      </c>
+      <c r="H859" t="n">
+        <v>0</v>
+      </c>
+      <c r="I859" t="n">
+        <v>0</v>
+      </c>
+      <c r="J859" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L859" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N859" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>12:07:48</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>2100556374828531886</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>KashuaAmos</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>@ennyola0015 But you have seen the man with 399 pages of FBI/DEA records of COCAINE dealings that impress you!
+Someone with NO VERIFIABLE certificates but a forged certificates.
+Some that hiked education and gave out loans, someone that removes subside &amp;amp; added the funds to 36 governors...😂</t>
+        </is>
+      </c>
+      <c r="F860" t="inlineStr">
+        <is>
+          <t>https://x.com/KashuaAmos/status/2100556374828531886</t>
+        </is>
+      </c>
+      <c r="H860" t="n">
+        <v>0</v>
+      </c>
+      <c r="I860" t="n">
+        <v>0</v>
+      </c>
+      <c r="J860" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L860" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N860" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>12:07:49</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>2100556370219057208</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>metalmilitiaxxx</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>@ericvideos91 America is losing.  Like the CPC.  😆</t>
+        </is>
+      </c>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>https://x.com/metalmilitiaxxx/status/2100556370219057208</t>
+        </is>
+      </c>
+      <c r="H861" t="n">
+        <v>0</v>
+      </c>
+      <c r="I861" t="n">
+        <v>0</v>
+      </c>
+      <c r="J861" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L861" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N861" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>12:07:49</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>2100556279467159792</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>NaveenKuma38380</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>@neha_aisa CPM CPI leader ASFI इस देश के लिए सबसे खतरनाक संगठन है जो नक्सली गतिविधि और नकली विचारधारा नक्सल वह बढ़ावा देते हैं सरकार से विरोध होना चाहिए सरकार में कमी होती सरकार में बैठे हुए लोग सत्ता के नशे में रहते हैं इनकी जरूरत नहीं</t>
+        </is>
+      </c>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>https://x.com/NaveenKuma38380/status/2100556279467159792</t>
+        </is>
+      </c>
+      <c r="H862" t="n">
+        <v>0</v>
+      </c>
+      <c r="I862" t="n">
+        <v>0</v>
+      </c>
+      <c r="J862" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L862" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N862" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>12:07:49</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>2100556279148085278</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>ChMark161</t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>@CdnMnrchyRspctr Poilievre never misses an opportunity to miss an opportunity.
+The problem is that the voices against him in the CPC want to replace him with someone even worse.</t>
+        </is>
+      </c>
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>https://x.com/ChMark161/status/2100556279148085278</t>
+        </is>
+      </c>
+      <c r="H863" t="n">
+        <v>0</v>
+      </c>
+      <c r="I863" t="n">
+        <v>0</v>
+      </c>
+      <c r="J863" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L863" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N863" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>12:07:49</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>2100556280440017144</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>valerioamirani</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>@adelelecroix Removing navigation links from your landing page keeps visitor attention focused on the primary call to action.</t>
+        </is>
+      </c>
+      <c r="F864" t="inlineStr">
+        <is>
+          <t>https://x.com/valerioamirani/status/2100556280440017144</t>
+        </is>
+      </c>
+      <c r="H864" t="n">
+        <v>0</v>
+      </c>
+      <c r="I864" t="n">
+        <v>0</v>
+      </c>
+      <c r="J864" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L864" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N864" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>12:07:50</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>2100556279508779315</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>Twinkle122262</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>@SenAdamSchiff I can’t believe you’re STILL pushing Climate hysteria.  What an idiot.  It’s 2026, and no one is buying your 💩 anymore.  Guess nobody told you we’ve had ZERO hurricanes in the North Atlantic Ocean this year.  Zero.  PS:  Hundred-year storms still happening once every hundred</t>
+        </is>
+      </c>
+      <c r="F865" t="inlineStr">
+        <is>
+          <t>https://x.com/Twinkle122262/status/2100556279508779315</t>
+        </is>
+      </c>
+      <c r="H865" t="n">
+        <v>0</v>
+      </c>
+      <c r="I865" t="n">
+        <v>0</v>
+      </c>
+      <c r="J865" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L865" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N865" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>12:07:50</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>2100556225201004710</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>blackiiingout</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>😳
+SAY IT AINT SO CRO?!!?!!! https://t.co/fHWqHxPmkd</t>
+        </is>
+      </c>
+      <c r="F866" t="inlineStr">
+        <is>
+          <t>https://x.com/blackiiingout/status/2100556225201004710</t>
+        </is>
+      </c>
+      <c r="H866" t="n">
+        <v>2</v>
+      </c>
+      <c r="I866" t="n">
+        <v>0</v>
+      </c>
+      <c r="J866" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L866" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N866" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>12:07:50</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>2100556247695007870</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>wlhdpk</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>“Es que la FIFA le regala todo a Messi” decían… 🤡🤡🤡🤡</t>
+        </is>
+      </c>
+      <c r="F867" t="inlineStr">
+        <is>
+          <t>https://x.com/wlhdpk/status/2100556247695007870</t>
+        </is>
+      </c>
+      <c r="H867" t="n">
+        <v>0</v>
+      </c>
+      <c r="I867" t="n">
+        <v>0</v>
+      </c>
+      <c r="J867" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L867" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N867" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>12:07:51</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>2100556165235228827</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>stockaajorkal</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>🚨 SpectraA Technology Solutions NSE Emerge IPO is currently open!
+The company manufactures customised process equipment for breweries, distilleries, food and beverage, FMCG and pharmaceutical industries.
+With 17+ years of experience, SpectraA manages the complete project cycle https://t.co/pLEUxO0ZIU</t>
+        </is>
+      </c>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>https://x.com/stockaajorkal/status/2100556165235228827</t>
+        </is>
+      </c>
+      <c r="H868" t="n">
+        <v>0</v>
+      </c>
+      <c r="I868" t="n">
+        <v>0</v>
+      </c>
+      <c r="J868" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L868" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N868" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>12:07:51</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>2100556162865180843</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>raulgoyus</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>@penasdetriana @LaLiga @Tebasjavier En el Bernabéu por qué? Tiene cojones que nos metas en el mismo saco del club corrupto que pago al Vice del CTA casi dos décadas… tiene cojones.</t>
+        </is>
+      </c>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>https://x.com/raulgoyus/status/2100556162865180843</t>
+        </is>
+      </c>
+      <c r="H869" t="n">
+        <v>0</v>
+      </c>
+      <c r="I869" t="n">
+        <v>0</v>
+      </c>
+      <c r="J869" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L869" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N869" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>12:07:51</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>2100556159765905602</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>KaptifyC</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>Aimtron Electronics Ltd || Subsidiary Update – Aimtron International Controls LLC (AIC) Records Highest-Ever Q2 Order Bookings of US$11.8 Million
+https://t.co/l5LDggz0mT
+step down subsidiary of Aimtron Electronics Limited, has bagged US$11.8 million in order bookings during the https://t.co/HGZRycFPMS</t>
+        </is>
+      </c>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>https://x.com/KaptifyC/status/2100556159765905602</t>
+        </is>
+      </c>
+      <c r="H870" t="n">
+        <v>0</v>
+      </c>
+      <c r="I870" t="n">
+        <v>0</v>
+      </c>
+      <c r="J870" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L870" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N870" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>12:07:52</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>2100556130170945568</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>SergeyCYW</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>Photonics Is The Most Important AI Infrastructure’s Physical Bottleneck
+Copper links struggle with bandwidth, heat, and power at scale.
+Photonics solves that problem by moving data with light, which is why optical networking is becoming increasingly important to AI https://t.co/YVLxGYoaIj</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>https://x.com/SergeyCYW/status/2100556130170945568</t>
+        </is>
+      </c>
+      <c r="H871" t="n">
+        <v>0</v>
+      </c>
+      <c r="I871" t="n">
+        <v>0</v>
+      </c>
+      <c r="J871" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L871" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N871" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>12:07:52</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>2100556116643958929</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>SH0TBREZZY</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>$UAMY’s Sept. 16 release cites 352% revenue growth over three years and a No. 2 ranking among Dallas/Fort Worth’s fastest-growing companies. That’s historical growth recognition—not a new order or raised guidance. The next test is whether growth translates into durable margins</t>
+        </is>
+      </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>https://x.com/SH0TBREZZY/status/2100556116643958929</t>
+        </is>
+      </c>
+      <c r="H872" t="n">
+        <v>0</v>
+      </c>
+      <c r="I872" t="n">
+        <v>0</v>
+      </c>
+      <c r="J872" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L872" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N872" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>12:07:52</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>2100556103360643430</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>JimMarous</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>When you open up rewards to every eligible checking account holder, momentum shifts rapidly. 
+In this episode, Shikha Narula and I discuss how @BankofAmerica expanded its addressable rewards base to 30 million clients while protecting higher-tier benefits.
+The results speak for https://t.co/C8rV0CakeR</t>
+        </is>
+      </c>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>https://x.com/JimMarous/status/2100556103360643430</t>
+        </is>
+      </c>
+      <c r="G873" t="inlineStr"/>
+      <c r="H873" t="n">
+        <v>0</v>
+      </c>
+      <c r="I873" t="n">
+        <v>0</v>
+      </c>
+      <c r="J873" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="K873" t="inlineStr"/>
+      <c r="L873" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="M873" t="inlineStr"/>
+      <c r="N873" t="inlineStr">
         <is>
           <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
         </is>

--- a/data/logs.xlsx
+++ b/data/logs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N873"/>
+  <dimension ref="A1:N973"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47706,7 +47706,6 @@
           <t>https://x.com/JimMarous/status/2100556103360643430</t>
         </is>
       </c>
-      <c r="G873" t="inlineStr"/>
       <c r="H873" t="n">
         <v>0</v>
       </c>
@@ -47718,16 +47717,5421 @@
           <t>multi_group</t>
         </is>
       </c>
-      <c r="K873" t="inlineStr"/>
       <c r="L873" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
       </c>
-      <c r="M873" t="inlineStr"/>
       <c r="N873" t="inlineStr">
         <is>
           <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>16:59:22</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>2100630301458174189</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>zmbnski</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>woah, i'm 38, from poland
+i've been through it all: founder, dev, data scientist, analyst, product manager, you name it. i even finished phd studies :D
+always something at the intersection of tech and marketing.
+built a couple of failed startups. 
+was making sentiment https://t.co/fAVq9uB78K</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>https://x.com/zmbnski/status/2100630301458174189</t>
+        </is>
+      </c>
+      <c r="H874" t="n">
+        <v>1</v>
+      </c>
+      <c r="I874" t="n">
+        <v>0</v>
+      </c>
+      <c r="J874" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L874" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N874" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>16:59:22</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>2100629609272299826</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>realjaymes</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>Too many businesses treat marketing and sales as separate functions.
+Marketing generates leads. Sales closes them.
+That’s how it looks on an org chart but it’s not how customers experience it.
+Customers see one journey. Every ad, post, case study, email, landing page, webinar,</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>https://x.com/realjaymes/status/2100629609272299826</t>
+        </is>
+      </c>
+      <c r="H875" t="n">
+        <v>0</v>
+      </c>
+      <c r="I875" t="n">
+        <v>1</v>
+      </c>
+      <c r="J875" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L875" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N875" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>16:59:22</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>2100629850805735517</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>newonpolsia</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>Hungarian tradespeople don’t need more generic marketing—they need booked jobs from people already searching. Brikettle turns local searches into enquiries through conversion-ready sites, Google Ads, local SEO, and Business Profile management. Live soon.</t>
+        </is>
+      </c>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>https://x.com/newonpolsia/status/2100629850805735517</t>
+        </is>
+      </c>
+      <c r="H876" t="n">
+        <v>0</v>
+      </c>
+      <c r="I876" t="n">
+        <v>0</v>
+      </c>
+      <c r="J876" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L876" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N876" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>16:59:23</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>2100629703107162280</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>NaveedA14552184</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>Absolutely 👍 Here’s a strong message you can post on Threads, TikTok, Facebook, Instagram, or anywhere you want to promote your channel:
+🚀 HELP ME GROW NAVEED ALI FUTURE AI! 🤖
+If you’re interested in AI tools, digital marketing, online business, and the future of AI, I’d https://t.co/4tWz5QEP9A</t>
+        </is>
+      </c>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>https://x.com/NaveedA14552184/status/2100629703107162280</t>
+        </is>
+      </c>
+      <c r="H877" t="n">
+        <v>0</v>
+      </c>
+      <c r="I877" t="n">
+        <v>0</v>
+      </c>
+      <c r="J877" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L877" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N877" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>16:59:23</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>2100630150463271347</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>proctored_exams</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>Shoot a DM to us for Reliable assistance in:- #Businesslaw #Math #music #Algebra #Calculus #Law #Statistics #Biology #Nursing #Essay #Assignment #Onlineclass #Researchpaper #Dissertation #Project #Marketing #Physics #Calculus #Chemistry #Homework https://t.co/OsjzBFWKPZ</t>
+        </is>
+      </c>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>https://x.com/proctored_exams/status/2100630150463271347</t>
+        </is>
+      </c>
+      <c r="H878" t="n">
+        <v>0</v>
+      </c>
+      <c r="I878" t="n">
+        <v>0</v>
+      </c>
+      <c r="J878" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L878" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N878" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>16:59:23</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>2100630618497241147</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>IdentityDig</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>In #Web3, links get shared via Telegram or X with zero context. @racsterls,  Identity Digital CMO, and @xmalkov, @Lever_io Co-Founder, explain why a #domain like .finance signals trust before anyone clicks the link. Watch Crypto Panda's AMA, here: https://t.co/I7Ml4rfypU</t>
+        </is>
+      </c>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>https://x.com/IdentityDig/status/2100630618497241147</t>
+        </is>
+      </c>
+      <c r="H879" t="n">
+        <v>0</v>
+      </c>
+      <c r="I879" t="n">
+        <v>0</v>
+      </c>
+      <c r="J879" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L879" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N879" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>16:59:23</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>2100630611597668576</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>apmediaconcept</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>We are officially the newest Co-Founder and shareholder of Dangote Refinery.
+Please, no congratulations yet, As I’m waiting for my Portrait to be Added beside Dangote’s own ….I’m still waiting for @aliko_dangotegcon to call me and explain why my dividend hasn’t entered. 😂😂 https://t.co/KOJm8jEoJ1</t>
+        </is>
+      </c>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>https://x.com/apmediaconcept/status/2100630611597668576</t>
+        </is>
+      </c>
+      <c r="H880" t="n">
+        <v>0</v>
+      </c>
+      <c r="I880" t="n">
+        <v>0</v>
+      </c>
+      <c r="J880" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L880" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N880" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>16:59:23</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>2100630551224799592</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>loganforsyth_</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>Building a business as an entrepreneur takes patience. Great results await for those who persist. https://t.co/q8QiCBGeL5</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>https://x.com/loganforsyth_/status/2100630551224799592</t>
+        </is>
+      </c>
+      <c r="H881" t="n">
+        <v>0</v>
+      </c>
+      <c r="I881" t="n">
+        <v>0</v>
+      </c>
+      <c r="J881" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L881" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N881" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>16:59:24</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>2100630536603468127</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>WIRED</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>The startup has become the subject of a nationwide protest movement that has prompted dozens of local governments to abruptly stop using its cameras. https://t.co/ZpiawB9TFq</t>
+        </is>
+      </c>
+      <c r="F882" t="inlineStr">
+        <is>
+          <t>https://x.com/WIRED/status/2100630536603468127</t>
+        </is>
+      </c>
+      <c r="H882" t="n">
+        <v>0</v>
+      </c>
+      <c r="I882" t="n">
+        <v>1</v>
+      </c>
+      <c r="J882" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L882" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N882" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>16:59:24</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>2100630477564444982</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>DonnaDo87602670</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>@WhiteHouse Bullshit!  After 36 years in business,  we are contemplating closing our doors because no one is buying.  And it is ALL this Bafoons Fault! During COVID people were buying more than now! Trump can go #GFY</t>
+        </is>
+      </c>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>https://x.com/DonnaDo87602670/status/2100630477564444982</t>
+        </is>
+      </c>
+      <c r="H883" t="n">
+        <v>0</v>
+      </c>
+      <c r="I883" t="n">
+        <v>0</v>
+      </c>
+      <c r="J883" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L883" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N883" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>16:59:24</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>2100630444370797034</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>CampusCreativeN</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>DearGlobalStalwarts: Here's another practical Daily Digest &amp;amp; Execution. View the attached image. OneLove❣️Greetings from the Lagos Ecosphere, Nigeria GMT
+Abiola Kehinde Cares
+Founder &amp;amp; CEO, ccndigit🛡️
+#AbiolaKehinde #Founder #CEO #ccndigit #Lagos #DigitalImpact https://t.co/McOk0CMaze</t>
+        </is>
+      </c>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>https://x.com/CampusCreativeN/status/2100630444370797034</t>
+        </is>
+      </c>
+      <c r="H884" t="n">
+        <v>0</v>
+      </c>
+      <c r="I884" t="n">
+        <v>0</v>
+      </c>
+      <c r="J884" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L884" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N884" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>16:59:25</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>2100630424481309004</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>barragers</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>Clavicular to receive $6.4M seed from a16z for new looksmaxxing startup https://t.co/ABQWiPx9KX</t>
+        </is>
+      </c>
+      <c r="F885" t="inlineStr">
+        <is>
+          <t>https://x.com/barragers/status/2100630424481309004</t>
+        </is>
+      </c>
+      <c r="H885" t="n">
+        <v>0</v>
+      </c>
+      <c r="I885" t="n">
+        <v>0</v>
+      </c>
+      <c r="J885" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L885" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N885" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>16:59:25</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>2100630422686421461</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>DepecheNode_</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>What I own and why I own it 
+$TIBBIR - find me a founder that has had a bigger impact on fintech &amp;amp; crypto than Micky. I'll wait. Still very non-consensus, which I like. 
+$HYPE - most sustainable PMF we've seen. And they're cementing themselves as part of the infrastructure.</t>
+        </is>
+      </c>
+      <c r="F886" t="inlineStr">
+        <is>
+          <t>https://x.com/DepecheNode_/status/2100630422686421461</t>
+        </is>
+      </c>
+      <c r="H886" t="n">
+        <v>0</v>
+      </c>
+      <c r="I886" t="n">
+        <v>0</v>
+      </c>
+      <c r="J886" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L886" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N886" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>16:59:25</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>2100630420102730035</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>MarketFlipper</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>@PhantomOS4 $470 a month but honestly feel like I didn’t take advantage enough of the generous usage limits. 
+Grok is a step above Gemini but still don’t trust it for serious complex tasks. I like Grok for my marketing and content side 
+I give them 40, 40, 10, 10 voting power</t>
+        </is>
+      </c>
+      <c r="F887" t="inlineStr">
+        <is>
+          <t>https://x.com/MarketFlipper/status/2100630420102730035</t>
+        </is>
+      </c>
+      <c r="H887" t="n">
+        <v>0</v>
+      </c>
+      <c r="I887" t="n">
+        <v>0</v>
+      </c>
+      <c r="J887" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L887" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N887" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>16:59:25</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>2100630408366858317</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>MarkSherman15</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>I built a live auction for founder attention.
+You set a burn rate. Your project stays on the board until the credits run out. Next bidder takes the slot. Small budgets can still compete.
+Visitors review the products, sign up, and give real feedback — that helps the founder and https://t.co/0Y69BFkoqx</t>
+        </is>
+      </c>
+      <c r="F888" t="inlineStr">
+        <is>
+          <t>https://x.com/MarkSherman15/status/2100630408366858317</t>
+        </is>
+      </c>
+      <c r="H888" t="n">
+        <v>0</v>
+      </c>
+      <c r="I888" t="n">
+        <v>0</v>
+      </c>
+      <c r="J888" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L888" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N888" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>16:59:25</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>2100630399739478124</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>AceCC16</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>aespa is a product of ABUSERS. SM pioneered TOXIC fandom and groom R&amp;amp;P!STS in which all were in Jail.  Even an idol from SM [Shinee] had died due to suicide.  SM should not be supported at all, the same thing goes with aespa. Same feather flocks together. Despite the founder of https://t.co/u7UwANdq0V</t>
+        </is>
+      </c>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>https://x.com/AceCC16/status/2100630399739478124</t>
+        </is>
+      </c>
+      <c r="H889" t="n">
+        <v>0</v>
+      </c>
+      <c r="I889" t="n">
+        <v>0</v>
+      </c>
+      <c r="J889" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L889" t="inlineStr">
+        <is>
+          <t>SENSITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>16:59:26</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>2100630398594408554</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>RohanArun</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>@WatcherGuru @Super_Powers_AI Hey Super, build a
+https://t.co/pjqjMmKdbS
+The specialized data acquisition and valuation workbench for SpaceX will focus on purchasing failed startup datasets for AI training, utilizing D3.js for interactive valuation and token yield visualization. The initial</t>
+        </is>
+      </c>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>https://x.com/RohanArun/status/2100630398594408554</t>
+        </is>
+      </c>
+      <c r="H890" t="n">
+        <v>0</v>
+      </c>
+      <c r="I890" t="n">
+        <v>0</v>
+      </c>
+      <c r="J890" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L890" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N890" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>16:59:26</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>2100630385595912284</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>theappbulletin</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>WTF!!!!🤯🤯🤯🤯🤯🤯
+2007 apps on one account 
+$41M /month 
+82M downloads in the last 30 days🤯🤯🤯
+I need to hop on a call with this man https://t.co/3ikseZoaui</t>
+        </is>
+      </c>
+      <c r="F891" t="inlineStr">
+        <is>
+          <t>https://x.com/theappbulletin/status/2100630385595912284</t>
+        </is>
+      </c>
+      <c r="H891" t="n">
+        <v>1</v>
+      </c>
+      <c r="I891" t="n">
+        <v>0</v>
+      </c>
+      <c r="J891" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L891" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N891" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>16:59:26</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>2100630387617620288</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>cami26_v_</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>@pilarvelasquezv Grave error comete la dirigencia de @nacionaloficial pierde prestigio, reconocimiento, respaldo logístico e institucional, desarrollo tecnológico, marketing, etc. marca propia jamás será una alternativa para una institución de gran calado. Será un gigante vestido por un pequeño.</t>
+        </is>
+      </c>
+      <c r="F892" t="inlineStr">
+        <is>
+          <t>https://x.com/cami26_v_/status/2100630387617620288</t>
+        </is>
+      </c>
+      <c r="H892" t="n">
+        <v>0</v>
+      </c>
+      <c r="I892" t="n">
+        <v>0</v>
+      </c>
+      <c r="J892" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L892" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N892" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>16:59:26</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>2100630370383548429</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>mono_nacional</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>Jajajaja que marketing le hicieron a este muerto</t>
+        </is>
+      </c>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>https://x.com/mono_nacional/status/2100630370383548429</t>
+        </is>
+      </c>
+      <c r="H893" t="n">
+        <v>0</v>
+      </c>
+      <c r="I893" t="n">
+        <v>0</v>
+      </c>
+      <c r="J893" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L893" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N893" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>16:59:27</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>2100630359603867787</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>nexgencoded</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>@DiscussingFilm okay these posters are actually gorgeous. marvel remembered production design can do some of the marketing for you</t>
+        </is>
+      </c>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>https://x.com/nexgencoded/status/2100630359603867787</t>
+        </is>
+      </c>
+      <c r="H894" t="n">
+        <v>0</v>
+      </c>
+      <c r="I894" t="n">
+        <v>0</v>
+      </c>
+      <c r="J894" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L894" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N894" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>16:59:27</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>2100630354650607933</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>anjaneyasevak</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>CBDC will be launched by Modi Ji on Diwali.
+At least, that’s what I understand from BJP and its way of marketing and pushing changes.
+@nav</t>
+        </is>
+      </c>
+      <c r="F895" t="inlineStr">
+        <is>
+          <t>https://x.com/anjaneyasevak/status/2100630354650607933</t>
+        </is>
+      </c>
+      <c r="H895" t="n">
+        <v>0</v>
+      </c>
+      <c r="I895" t="n">
+        <v>0</v>
+      </c>
+      <c r="J895" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L895" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N895" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>16:59:27</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>2100630330063667525</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>marcbitanga</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>Building has never been easier than ever.
+It also means marketing will be harder than ever.</t>
+        </is>
+      </c>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>https://x.com/marcbitanga/status/2100630330063667525</t>
+        </is>
+      </c>
+      <c r="H896" t="n">
+        <v>0</v>
+      </c>
+      <c r="I896" t="n">
+        <v>0</v>
+      </c>
+      <c r="J896" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L896" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N896" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>16:59:27</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>2100630332278235406</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>AnnaMBerk5s</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>Buy Bulk Gmail Accounts
+Buy Edu Email Accounts
+Buy Google Voice Accounts
+Buy Google Ads Accounts
+Buy iCloud Accounts
+Gmail- https://t.co/KFCi3QGI8C
+EduEmail- https://t.co/G1ighemRes
+Voice- https://t.co/s5cLrcjudw
+GoogleAds- https://t.co/wT5GsMASYk
+iCloud- https://t.co/zuxAehrtW5</t>
+        </is>
+      </c>
+      <c r="F897" t="inlineStr">
+        <is>
+          <t>https://x.com/AnnaMBerk5s/status/2100630332278235406</t>
+        </is>
+      </c>
+      <c r="H897" t="n">
+        <v>0</v>
+      </c>
+      <c r="I897" t="n">
+        <v>0</v>
+      </c>
+      <c r="J897" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L897" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N897" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>16:59:27</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>2100630316113146202</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>Cecifeliz1</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>@tatoamericano @YesidLancheros Que tiene que ver el marketing político con liderar una empresa de petróleo? Nada</t>
+        </is>
+      </c>
+      <c r="F898" t="inlineStr">
+        <is>
+          <t>https://x.com/Cecifeliz1/status/2100630316113146202</t>
+        </is>
+      </c>
+      <c r="H898" t="n">
+        <v>0</v>
+      </c>
+      <c r="I898" t="n">
+        <v>0</v>
+      </c>
+      <c r="J898" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L898" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N898" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>16:59:28</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>2100630304545202641</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>atomarporqlo</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>@SydneBernice Are you kidding? Absolutely! She can do no wrong in my book, and honestly, that ad was a marketing masterclass.</t>
+        </is>
+      </c>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>https://x.com/atomarporqlo/status/2100630304545202641</t>
+        </is>
+      </c>
+      <c r="H899" t="n">
+        <v>0</v>
+      </c>
+      <c r="I899" t="n">
+        <v>0</v>
+      </c>
+      <c r="J899" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L899" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N899" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>16:59:28</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>2100630302506799425</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>Marvaoinvest</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>@pedsettanni Cara, o meta ads funciona em contas sem audiência, mas eu não sei se o cliente converte quando ele pesquisa um perfil que não tem conteúdo, relevância e seguidores.</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>https://x.com/Marvaoinvest/status/2100630302506799425</t>
+        </is>
+      </c>
+      <c r="H900" t="n">
+        <v>0</v>
+      </c>
+      <c r="I900" t="n">
+        <v>0</v>
+      </c>
+      <c r="J900" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L900" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N900" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>16:59:28</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>2100630274019090756</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>hey_mrlz</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>@nacaomarvete616 isso de longe tá sendo o marketing mais interessante de doomsday até agr</t>
+        </is>
+      </c>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>https://x.com/hey_mrlz/status/2100630274019090756</t>
+        </is>
+      </c>
+      <c r="H901" t="n">
+        <v>0</v>
+      </c>
+      <c r="I901" t="n">
+        <v>0</v>
+      </c>
+      <c r="J901" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L901" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N901" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>16:59:29</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>2100630270739173519</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>othy_h</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>@teortaxesTex Production may became tcheap, but the cost of customer acquisition skyrocketed</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>https://x.com/othy_h/status/2100630270739173519</t>
+        </is>
+      </c>
+      <c r="H902" t="n">
+        <v>0</v>
+      </c>
+      <c r="I902" t="n">
+        <v>0</v>
+      </c>
+      <c r="J902" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L902" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N902" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>16:59:29</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>2100630258211004632</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>b1oomysky</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>I do love my bestie's marketing strategy https://t.co/oyNw99c6nF</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>https://x.com/b1oomysky/status/2100630258211004632</t>
+        </is>
+      </c>
+      <c r="H903" t="n">
+        <v>0</v>
+      </c>
+      <c r="I903" t="n">
+        <v>0</v>
+      </c>
+      <c r="J903" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L903" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N903" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>16:59:29</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>2100630243488788710</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>SusieNonya</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>@WallStreetApes Not a fan of Islam, but this is just marketing…like gluten free.</t>
+        </is>
+      </c>
+      <c r="F904" t="inlineStr">
+        <is>
+          <t>https://x.com/SusieNonya/status/2100630243488788710</t>
+        </is>
+      </c>
+      <c r="H904" t="n">
+        <v>0</v>
+      </c>
+      <c r="I904" t="n">
+        <v>0</v>
+      </c>
+      <c r="J904" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L904" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N904" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>16:59:29</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>2100630232378024267</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>LouisSeeco</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>More than 16 years ago, I received a call from a White woman who wanted to buy copies of Marketing The Same Difference, the book I published and launched in 2010. I was surprised and elated that a White person had taken an interest in a book written by a Black man from Alexandra. https://t.co/RkAZiZVFbu</t>
+        </is>
+      </c>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>https://x.com/LouisSeeco/status/2100630232378024267</t>
+        </is>
+      </c>
+      <c r="H905" t="n">
+        <v>0</v>
+      </c>
+      <c r="I905" t="n">
+        <v>0</v>
+      </c>
+      <c r="J905" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L905" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N905" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>16:59:29</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>2100630230255681692</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>jumebi1141341</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>@it_Rutie This is marketing strategy</t>
+        </is>
+      </c>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>https://x.com/jumebi1141341/status/2100630230255681692</t>
+        </is>
+      </c>
+      <c r="H906" t="n">
+        <v>0</v>
+      </c>
+      <c r="I906" t="n">
+        <v>0</v>
+      </c>
+      <c r="J906" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L906" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N906" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>16:59:30</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>2100630225545834586</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>rokobasili</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>@no1089 @DerAmbrose @istartedthebits "marketing ploy"
+We were being honest and made something other people decided wasn't a viable route
+Overdriving eink is not really a flex and wont compare to a daylight running for decades without ever burning its panel out</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>https://x.com/rokobasili/status/2100630225545834586</t>
+        </is>
+      </c>
+      <c r="H907" t="n">
+        <v>0</v>
+      </c>
+      <c r="I907" t="n">
+        <v>0</v>
+      </c>
+      <c r="J907" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L907" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N907" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>16:59:30</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>2100630114405081266</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>yshvak</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>@ImNotAV1rus Running paid ads?</t>
+        </is>
+      </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>https://x.com/yshvak/status/2100630114405081266</t>
+        </is>
+      </c>
+      <c r="H908" t="n">
+        <v>0</v>
+      </c>
+      <c r="I908" t="n">
+        <v>0</v>
+      </c>
+      <c r="J908" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L908" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N908" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>16:59:30</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>2100630650688544855</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>bishop_zaddy</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>@fkeyamo ONLY in Nigeria would you see a serving Minister that is so jobless to an extent he is becoming an entertaining and a content creator on Social media to get Elons money..... Yes, that is what it is, soon he would be here fully to work when he is out of seat next year 💯</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>https://x.com/bishop_zaddy/status/2100630650688544855</t>
+        </is>
+      </c>
+      <c r="H909" t="n">
+        <v>0</v>
+      </c>
+      <c r="I909" t="n">
+        <v>0</v>
+      </c>
+      <c r="J909" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L909" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N909" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>16:59:30</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>2100630011808264246</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>GoodFNisBack</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>You do know why right? It is marketing strategy to Middle Eastern market .</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>https://x.com/GoodFNisBack/status/2100630011808264246</t>
+        </is>
+      </c>
+      <c r="H910" t="n">
+        <v>0</v>
+      </c>
+      <c r="I910" t="n">
+        <v>0</v>
+      </c>
+      <c r="J910" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L910" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N910" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>16:59:31</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>2100630004904116634</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>CarsonTalkMoney</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>@rolexmoneyman The war hasn’t even effected their business, they just accelerated revenue growth 
+It’s just being tied up in the macro unfortunately</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>https://x.com/CarsonTalkMoney/status/2100630004904116634</t>
+        </is>
+      </c>
+      <c r="H911" t="n">
+        <v>0</v>
+      </c>
+      <c r="I911" t="n">
+        <v>0</v>
+      </c>
+      <c r="J911" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L911" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N911" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>16:59:31</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>2100630620611502227</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>Da_igbomuslim</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>@Odogwu_X15 For just tell him say you be content creator for X</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>https://x.com/Da_igbomuslim/status/2100630620611502227</t>
+        </is>
+      </c>
+      <c r="H912" t="n">
+        <v>0</v>
+      </c>
+      <c r="I912" t="n">
+        <v>0</v>
+      </c>
+      <c r="J912" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L912" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N912" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>16:59:31</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>2100630612705210436</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>kiranssgoudar</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>@nAnuyAru @royalreddytwitt ಲೇಯ್ ತಲೆ ಅಡ ಇಟ್ಟಿರೋ ದರಬೇಸಿ, ಈ ಕ್ರೆಡಿಟ್ ಕಾರ್ಡ್, ಫುಡ್ ಡೆಲಿವರಿ ಆಪ್ಸ್ ಉಪಯೋಗಿಸೋರು ಒಂದು 10% ಇರಲಿಕ್ಕಿಲ್ಲ ಈ ದೇಶದಲ್ಲಿ. ಉಳಿದ 90% ಜನರು ಹೇಗೆ ಬದುಕುತ್ತಿದ್ದಾರೆ ಅನ್ನೋ ಪರಿಜ್ಞಾನ ನಿಂಗೆ ಇದ್ಯಾ? ವ್ಯವಹಾರ ಹೇಗೆ ನಡೆಯತ್ತೆ ಅನ್ನೋ ಕನಿಷ್ಠ ಜ್ಞಾನ ಇದ್ಯಾ? Entrepreneur ಗಳ ಕಷ್ಟ ಗೊತ್ತಾ? ತಲೆಹಿಡುಕರ ಕಿರಿಕಿರಿ ಗೊತ್ತಾ?</t>
+        </is>
+      </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>https://x.com/kiranssgoudar/status/2100630612705210436</t>
+        </is>
+      </c>
+      <c r="H913" t="n">
+        <v>0</v>
+      </c>
+      <c r="I913" t="n">
+        <v>0</v>
+      </c>
+      <c r="J913" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L913" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N913" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>16:59:31</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>2100629970951286906</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>AlbertSmeee</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>@SamCoatesSky Continuity Kier with a much higher marketing budget.</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>https://x.com/AlbertSmeee/status/2100629970951286906</t>
+        </is>
+      </c>
+      <c r="H914" t="n">
+        <v>0</v>
+      </c>
+      <c r="I914" t="n">
+        <v>0</v>
+      </c>
+      <c r="J914" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L914" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N914" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>16:59:32</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>2100629962025783370</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>Logan1Dunn</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>→ Your video generations are done in minutes with AI actors that don't sound like robots. → You publish straight to Meta without leaving Created AI. → Created AI tracks your conversion rate, CPA and ROAS. → You iterate on winning ads in seconds and publish them to scale.</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>https://x.com/Logan1Dunn/status/2100629962025783370</t>
+        </is>
+      </c>
+      <c r="H915" t="n">
+        <v>0</v>
+      </c>
+      <c r="I915" t="n">
+        <v>0</v>
+      </c>
+      <c r="J915" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L915" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N915" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>16:59:32</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>2100630592123765092</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>0xCharlota</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>yes, it’s often head bc I ride the flow and don’t want to stop. But a way around it is that i try to plan a task for the end of the day that will keep me energized. Something like an hour of mood boarding for new project, playing with AI workflow, concepting a new direction…</t>
+        </is>
+      </c>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>https://x.com/0xCharlota/status/2100630592123765092</t>
+        </is>
+      </c>
+      <c r="H916" t="n">
+        <v>0</v>
+      </c>
+      <c r="I916" t="n">
+        <v>0</v>
+      </c>
+      <c r="J916" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L916" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N916" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>16:59:32</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>2100630556132139110</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>GatorsScott</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>For you #Gators headed up to Auburn, here is their Game Day landing page with all the pertinent info: https://t.co/ou8VhxlYZE</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>https://x.com/GatorsScott/status/2100630556132139110</t>
+        </is>
+      </c>
+      <c r="H917" t="n">
+        <v>0</v>
+      </c>
+      <c r="I917" t="n">
+        <v>0</v>
+      </c>
+      <c r="J917" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L917" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N917" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>16:59:32</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>2100630547651572047</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>AkshayiWeb</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>Chaati pe haath nai rakha bro??</t>
+        </is>
+      </c>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>https://x.com/AkshayiWeb/status/2100630547651572047</t>
+        </is>
+      </c>
+      <c r="H918" t="n">
+        <v>0</v>
+      </c>
+      <c r="I918" t="n">
+        <v>0</v>
+      </c>
+      <c r="J918" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L918" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N918" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>16:59:33</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>2100630531209675120</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>arnaudmercier</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>France Rejects AI Slowdown to Boost Tech Competitiveness - Whalesbook https://t.co/Cz73fHQxL8</t>
+        </is>
+      </c>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>https://x.com/arnaudmercier/status/2100630531209675120</t>
+        </is>
+      </c>
+      <c r="H919" t="n">
+        <v>0</v>
+      </c>
+      <c r="I919" t="n">
+        <v>0</v>
+      </c>
+      <c r="J919" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L919" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N919" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>16:59:33</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>2100630527816442099</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>DarkHorseEntre1</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>@TruthTeller_acc AI didn't kill the boring stuff, it exposed who was hiding behind it. Lower barriers just mean more people find out relationships and grit still win. Tools changed. The grind didn't.</t>
+        </is>
+      </c>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>https://x.com/DarkHorseEntre1/status/2100630527816442099</t>
+        </is>
+      </c>
+      <c r="H920" t="n">
+        <v>0</v>
+      </c>
+      <c r="I920" t="n">
+        <v>0</v>
+      </c>
+      <c r="J920" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L920" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N920" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>16:59:33</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>2100630509881786791</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>breckyunits</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>Why would PG lobby so hard for me to do YC again in 2009, creating the 3% club just for me?
+Game recognizes game.
+Victory needs a thousand fathers.
+Though I got no carry, I am proud that out of all YC's 47 batches, the two I was in are their #1 and #2 of all time. Of course https://t.co/f6SMC6nOeC</t>
+        </is>
+      </c>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>https://x.com/breckyunits/status/2100630509881786791</t>
+        </is>
+      </c>
+      <c r="H921" t="n">
+        <v>0</v>
+      </c>
+      <c r="I921" t="n">
+        <v>0</v>
+      </c>
+      <c r="J921" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L921" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N921" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>16:59:33</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>2100630507033657649</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>bongripprincess</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>can not believe that this upcoming December will now be 2 years of being a playboy club content creator😇🥹🖤🐰</t>
+        </is>
+      </c>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>https://x.com/bongripprincess/status/2100630507033657649</t>
+        </is>
+      </c>
+      <c r="H922" t="n">
+        <v>0</v>
+      </c>
+      <c r="I922" t="n">
+        <v>0</v>
+      </c>
+      <c r="J922" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L922" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N922" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>16:59:34</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>2100630493674746351</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>theppcdude</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>@NiceGuyEddie10 @TheAaronAM +1 on this</t>
+        </is>
+      </c>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>https://x.com/theppcdude/status/2100630493674746351</t>
+        </is>
+      </c>
+      <c r="H923" t="n">
+        <v>0</v>
+      </c>
+      <c r="I923" t="n">
+        <v>0</v>
+      </c>
+      <c r="J923" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L923" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N923" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>16:59:34</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>2100630469557580000</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>Natsukikris</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>@Fwiz @TrooprzArmy @UltApp Ryan please give us a clear and direct answer. @kris minted 70 billion CRO tokens will those tokens be burned or not?
+Since the Trump partnership, https://t.co/xBc2j8asOy has failed to deliver what was promised regarding these 70 billion tokens. Investors deserve transparency .</t>
+        </is>
+      </c>
+      <c r="F924" t="inlineStr">
+        <is>
+          <t>https://x.com/Natsukikris/status/2100630469557580000</t>
+        </is>
+      </c>
+      <c r="H924" t="n">
+        <v>1</v>
+      </c>
+      <c r="I924" t="n">
+        <v>0</v>
+      </c>
+      <c r="J924" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L924" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N924" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>16:59:34</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>2100630474406142065</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>tirimisyjr</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>The hardest lesson I've learned as an entrepreneur is how much effort building 1 thing takes. It's such a faulty belief to think you can build multiple things well at the same time. You can't. And unfortunately, the only way to learn this is to try and fail.</t>
+        </is>
+      </c>
+      <c r="F925" t="inlineStr">
+        <is>
+          <t>https://x.com/tirimisyjr/status/2100630474406142065</t>
+        </is>
+      </c>
+      <c r="H925" t="n">
+        <v>0</v>
+      </c>
+      <c r="I925" t="n">
+        <v>0</v>
+      </c>
+      <c r="J925" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L925" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N925" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>16:59:34</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>2100630465384222991</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>GENIC0N</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>@AlexMasmej greed and fear index: monetized</t>
+        </is>
+      </c>
+      <c r="F926" t="inlineStr">
+        <is>
+          <t>https://x.com/GENIC0N/status/2100630465384222991</t>
+        </is>
+      </c>
+      <c r="H926" t="n">
+        <v>0</v>
+      </c>
+      <c r="I926" t="n">
+        <v>0</v>
+      </c>
+      <c r="J926" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L926" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N926" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>16:59:35</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>2100630460162277663</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>Quimper</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>@SteveAJ12 @TheGamesDet I made a typo, you decided to give keys to a failed content creator for clout. 
+Do you always have to telegraph your actions or does that come with being a clueless bellend?</t>
+        </is>
+      </c>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>https://x.com/Quimper/status/2100630460162277663</t>
+        </is>
+      </c>
+      <c r="H927" t="n">
+        <v>0</v>
+      </c>
+      <c r="I927" t="n">
+        <v>0</v>
+      </c>
+      <c r="J927" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L927" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N927" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>16:59:35</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>2100630454177308922</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>StudyingMedici</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>@whitfieldlewis6 @MicieliA_MD Right? As a student I was taught to always ultrasound or CTA the neck and great vasculature out of concern for atherosclerosis crossing ischemia, and steal syndrome.  Then I was informed by the physicians around me as a new provider that was pointless and I was wasting resources</t>
+        </is>
+      </c>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>https://x.com/StudyingMedici/status/2100630454177308922</t>
+        </is>
+      </c>
+      <c r="H928" t="n">
+        <v>0</v>
+      </c>
+      <c r="I928" t="n">
+        <v>0</v>
+      </c>
+      <c r="J928" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L928" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N928" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>16:59:35</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>2100630450188206246</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>remertron</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>@bruce_barrett Pierres been singing the same horse shit tune for how long? Just enough to pretend to be an opposition party but keep that Uniparty going. We have no conservative voice, and the PPC needs a leader</t>
+        </is>
+      </c>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>https://x.com/remertron/status/2100630450188206246</t>
+        </is>
+      </c>
+      <c r="H929" t="n">
+        <v>0</v>
+      </c>
+      <c r="I929" t="n">
+        <v>0</v>
+      </c>
+      <c r="J929" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L929" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N929" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>16:59:35</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>2100630423479152991</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>deeepakbagada</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>Day 79 of building in public: we deleted our vector database and latency dropped 96%.
+We were paying $120/mo for a hosted vector store to retrieve agent tool schemas and project memories. P95 latency hovered around 180ms.
+Here is what we replaced it with in 240 lines of</t>
+        </is>
+      </c>
+      <c r="F930" t="inlineStr">
+        <is>
+          <t>https://x.com/deeepakbagada/status/2100630423479152991</t>
+        </is>
+      </c>
+      <c r="H930" t="n">
+        <v>0</v>
+      </c>
+      <c r="I930" t="n">
+        <v>0</v>
+      </c>
+      <c r="J930" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L930" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N930" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>16:59:36</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>2100630407045927230</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>morrismediaco</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>@UGCwithLiv_A Thanks beauty! ☺️</t>
+        </is>
+      </c>
+      <c r="F931" t="inlineStr">
+        <is>
+          <t>https://x.com/morrismediaco/status/2100630407045927230</t>
+        </is>
+      </c>
+      <c r="H931" t="n">
+        <v>0</v>
+      </c>
+      <c r="I931" t="n">
+        <v>0</v>
+      </c>
+      <c r="J931" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L931" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N931" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>16:59:36</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>2100630393888141430</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>MapleLeafs91</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>@AndrewScheer Can you and CPC please act like serious people? Only the dumbest of the dumb actually believes this nonsense.</t>
+        </is>
+      </c>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>https://x.com/MapleLeafs91/status/2100630393888141430</t>
+        </is>
+      </c>
+      <c r="H932" t="n">
+        <v>0</v>
+      </c>
+      <c r="I932" t="n">
+        <v>0</v>
+      </c>
+      <c r="J932" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L932" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N932" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>16:59:36</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>2100630382630818095</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>REnbacher</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>@mhashimjr @MatinaStevis The CPC is bringing a potential issue to Canadians, who would otherwise be completely unaware.</t>
+        </is>
+      </c>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>https://x.com/REnbacher/status/2100630382630818095</t>
+        </is>
+      </c>
+      <c r="H933" t="n">
+        <v>0</v>
+      </c>
+      <c r="I933" t="n">
+        <v>0</v>
+      </c>
+      <c r="J933" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L933" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N933" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>16:59:36</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>2100630373776437349</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>arnaudmercier</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>"La France n’a pas mis des milliards, les Européens ont mis plus que nous": pourquoi ce que dit François Hollande sur l'aide française à l’Ukraine est trompeur https://t.co/vwTyWT0uuv https://t.co/lrPBo0O8Ep</t>
+        </is>
+      </c>
+      <c r="F934" t="inlineStr">
+        <is>
+          <t>https://x.com/arnaudmercier/status/2100630373776437349</t>
+        </is>
+      </c>
+      <c r="H934" t="n">
+        <v>0</v>
+      </c>
+      <c r="I934" t="n">
+        <v>0</v>
+      </c>
+      <c r="J934" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L934" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N934" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>16:59:37</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>2100630359646130389</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>tablesprint</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>Drafting high-converting demand letters shouldn't take an entire afternoon. 
+⚖️  With TableSprint - Track your settlement progress and gap analysis at a glance.  👇 https://t.co/z54flmsIvT 
+#personalinjurylaw #plaintiffattorney #lawfirmtech #LegalTech #settlements https://t.co/uFjVsuM3v6</t>
+        </is>
+      </c>
+      <c r="F935" t="inlineStr">
+        <is>
+          <t>https://x.com/tablesprint/status/2100630359646130389</t>
+        </is>
+      </c>
+      <c r="H935" t="n">
+        <v>0</v>
+      </c>
+      <c r="I935" t="n">
+        <v>0</v>
+      </c>
+      <c r="J935" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L935" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N935" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>16:59:37</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>2100630359234822641</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>arnaudmercier</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>Oxford updates AI disclosure guidelines for academic authors - Research Information https://t.co/ki5l2xTVO1</t>
+        </is>
+      </c>
+      <c r="F936" t="inlineStr">
+        <is>
+          <t>https://x.com/arnaudmercier/status/2100630359234822641</t>
+        </is>
+      </c>
+      <c r="H936" t="n">
+        <v>0</v>
+      </c>
+      <c r="I936" t="n">
+        <v>0</v>
+      </c>
+      <c r="J936" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L936" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N936" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>16:59:37</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>2100630334262190113</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>morrismediaco</t>
+        </is>
+      </c>
+      <c r="E937" t="inlineStr">
+        <is>
+          <t>Do ya’ll know that we can tell when you use chat GPT to comment on posts/respond to comments??? PLEASE😂</t>
+        </is>
+      </c>
+      <c r="F937" t="inlineStr">
+        <is>
+          <t>https://x.com/morrismediaco/status/2100630334262190113</t>
+        </is>
+      </c>
+      <c r="H937" t="n">
+        <v>0</v>
+      </c>
+      <c r="I937" t="n">
+        <v>0</v>
+      </c>
+      <c r="J937" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L937" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N937" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>16:59:37</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>2100629695087923325</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>adnan30baig</t>
+        </is>
+      </c>
+      <c r="E938" t="inlineStr">
+        <is>
+          <t>pretty sure receptionists are cooked
+AI receptionists can now:
+- pick up every call, including the 8pm-5am ones nobody's around for
+- answer customer questions using whatever's already on your website or internal
+- book the job and text the confirmation before the caller even</t>
+        </is>
+      </c>
+      <c r="F938" t="inlineStr">
+        <is>
+          <t>https://x.com/adnan30baig/status/2100629695087923325</t>
+        </is>
+      </c>
+      <c r="H938" t="n">
+        <v>1</v>
+      </c>
+      <c r="I938" t="n">
+        <v>0</v>
+      </c>
+      <c r="J938" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L938" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N938" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>16:59:38</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>2100630329233129939</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>Phu_Prosperity8</t>
+        </is>
+      </c>
+      <c r="E939" t="inlineStr">
+        <is>
+          <t>@Milonsa87650356 Solid momentum. Is that from client work or protocol incentives?</t>
+        </is>
+      </c>
+      <c r="F939" t="inlineStr">
+        <is>
+          <t>https://x.com/Phu_Prosperity8/status/2100630329233129939</t>
+        </is>
+      </c>
+      <c r="H939" t="n">
+        <v>0</v>
+      </c>
+      <c r="I939" t="n">
+        <v>0</v>
+      </c>
+      <c r="J939" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L939" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N939" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>16:59:38</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>2100630277059911741</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>CroJourno</t>
+        </is>
+      </c>
+      <c r="E940" t="inlineStr">
+        <is>
+          <t>@thefreeDARDAN @GeorgeSzamuely we were not allowed
+US said stop🤷‍♂️</t>
+        </is>
+      </c>
+      <c r="F940" t="inlineStr">
+        <is>
+          <t>https://x.com/CroJourno/status/2100630277059911741</t>
+        </is>
+      </c>
+      <c r="H940" t="n">
+        <v>0</v>
+      </c>
+      <c r="I940" t="n">
+        <v>0</v>
+      </c>
+      <c r="J940" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L940" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N940" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>16:59:38</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>2100630273809408266</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>MNuafko</t>
+        </is>
+      </c>
+      <c r="E941" t="inlineStr">
+        <is>
+          <t>@Ice_Landic Armstrong vs FARÇA 
+Sancionado por Doping-[VENDAS]
+Pero no tenía:
+Viento de cola: CALENDARIO de Tebas
+Jueces a favor: ÁRBITROS
+JEFE de los jueces a sueldo: NEGREIRA
+Medios comprados: 7'4M + MEDIAPRO
+Respaldo Gubernamental: CSD-TAD, RFEF, CTA, VAR
+Armstrong era un novato</t>
+        </is>
+      </c>
+      <c r="F941" t="inlineStr">
+        <is>
+          <t>https://x.com/MNuafko/status/2100630273809408266</t>
+        </is>
+      </c>
+      <c r="H941" t="n">
+        <v>0</v>
+      </c>
+      <c r="I941" t="n">
+        <v>0</v>
+      </c>
+      <c r="J941" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L941" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N941" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>16:59:38</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>2100629604952072597</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>realjaymes</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>One of the clearest signs your marketing isn’t working is when your sales team has to explain everything from scratch.
+Marketing isn’t supposed to replace sales. It’s supposed to prepare people for it.
+By the time someone books a call with you, they should already understand:</t>
+        </is>
+      </c>
+      <c r="F942" t="inlineStr">
+        <is>
+          <t>https://x.com/realjaymes/status/2100629604952072597</t>
+        </is>
+      </c>
+      <c r="H942" t="n">
+        <v>0</v>
+      </c>
+      <c r="I942" t="n">
+        <v>1</v>
+      </c>
+      <c r="J942" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L942" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N942" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>16:59:39</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>2100630243140612192</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>marketingrsouza</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>@STF_oficial Fala aí pro ditador Moraes.... disponibilizar o celular dele pra nós vermos o que tem .
+É inocente???</t>
+        </is>
+      </c>
+      <c r="F943" t="inlineStr">
+        <is>
+          <t>https://x.com/marketingrsouza/status/2100630243140612192</t>
+        </is>
+      </c>
+      <c r="H943" t="n">
+        <v>0</v>
+      </c>
+      <c r="I943" t="n">
+        <v>0</v>
+      </c>
+      <c r="J943" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L943" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N943" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>16:59:39</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>2100629614242537501</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>realjaymes</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>When marketing does its job well, sales conversations become shorter. Objections become fewer. Price becomes easier to defend. Trust already exists before the first call.
+Sales should spend less time educating and more time confirming fit.
+If every prospect starts the</t>
+        </is>
+      </c>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>https://x.com/realjaymes/status/2100629614242537501</t>
+        </is>
+      </c>
+      <c r="H944" t="n">
+        <v>0</v>
+      </c>
+      <c r="I944" t="n">
+        <v>0</v>
+      </c>
+      <c r="J944" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L944" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N944" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>16:59:39</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>2100630242566021605</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>EOApex</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr">
+        <is>
+          <t>Los espero el próximo jueves a las 12 p.m. (GMT-6) en APEX Office Hours en Español, reserva tu lugar https://t.co/ohXwBJ7eFf #oracleapex #apexworld @oracleace https://t.co/s4XFk0gWbl</t>
+        </is>
+      </c>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>https://x.com/EOApex/status/2100630242566021605</t>
+        </is>
+      </c>
+      <c r="H945" t="n">
+        <v>0</v>
+      </c>
+      <c r="I945" t="n">
+        <v>0</v>
+      </c>
+      <c r="J945" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L945" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N945" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>16:59:39</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>2100630198655865179</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>Rusty_nulls</t>
+        </is>
+      </c>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>@Dave_VictimTwo If they promote FG (content creator curse): 
+Game gonna release after being delayed
+Go on break for maintenance with 0 communication (Don’t forget about the dev exclusive skins and characters)
+Five hundred expose docs on dev members we never heard about which gets the game canned https://t.co/CdNnHWnIIf</t>
+        </is>
+      </c>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>https://x.com/Rusty_nulls/status/2100630198655865179</t>
+        </is>
+      </c>
+      <c r="H946" t="n">
+        <v>0</v>
+      </c>
+      <c r="I946" t="n">
+        <v>0</v>
+      </c>
+      <c r="J946" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L946" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N946" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>16:59:40</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>2100630178447941929</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>beginnersblog1</t>
+        </is>
+      </c>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>35 ChatGPT Prompts
+1. Improve accuracy
+Before asking for an answer, force the AI to understand the task properly.
+Example: “Before responding, ask clarifying questions until you are confident you understand the task.” This prevents wrong or generic answers.
+2. Write better https://t.co/DBYba766hf</t>
+        </is>
+      </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>https://x.com/beginnersblog1/status/2100630178447941929</t>
+        </is>
+      </c>
+      <c r="H947" t="n">
+        <v>1</v>
+      </c>
+      <c r="I947" t="n">
+        <v>0</v>
+      </c>
+      <c r="J947" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L947" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N947" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>16:59:40</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>2100630178158485995</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>NICKFROMNEBRASK</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>HERE: HEAR EARLY ON SCRIPTURE
+'super' hint?? Lyons, NE = ED+EN = DEE+N = NE+ED &amp;gt;
+ONLY = SUN+LIGHT+ENERGY +WATER + OXYGEN
+H+EAR+LY+ON+S+CRYPT+SURE?? HERE? HEAR yet?
+GOSPEL = GOD+SPELLing CH+ARM+ED + LE$$+ON?
+witCH do 'you' CHOOSE?? FREE+WILL is KIN+G??
+'THE' = TRUE+HEAVEN = EAR+TH https://t.co/9tjGK4z67N</t>
+        </is>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>https://x.com/NICKFROMNEBRASK/status/2100630178158485995</t>
+        </is>
+      </c>
+      <c r="H948" t="n">
+        <v>1</v>
+      </c>
+      <c r="I948" t="n">
+        <v>0</v>
+      </c>
+      <c r="J948" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L948" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N948" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>16:59:40</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>2100630176723824718</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>NorthStar3690</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>@KatieInBoston1 @082paug @Reddit_Retards Katie you came and commented on me. I did not tag you.
+You found my post because you sit around looking up MRKH on X so you can yell at strangers on the internet.
+Me saying that you were going to do exactly what you did is not me agitating you.
+You are the agitator. https://t.co/L2reBC2LEB</t>
+        </is>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>https://x.com/NorthStar3690/status/2100630176723824718</t>
+        </is>
+      </c>
+      <c r="H949" t="n">
+        <v>0</v>
+      </c>
+      <c r="I949" t="n">
+        <v>0</v>
+      </c>
+      <c r="J949" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L949" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N949" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>16:59:40</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>2100630098579722397</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>CroJourno</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>@SwetlandTom @GeorgeSzamuely thank you for promoting Croatia🙂👍</t>
+        </is>
+      </c>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>https://x.com/CroJourno/status/2100630098579722397</t>
+        </is>
+      </c>
+      <c r="H950" t="n">
+        <v>0</v>
+      </c>
+      <c r="I950" t="n">
+        <v>0</v>
+      </c>
+      <c r="J950" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L950" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N950" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>16:59:41</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>2100630057127469157</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>SimonMonkam</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr">
+        <is>
+          <t>@bitget My favorite Bitget innovation is Copy Trading, because it transforms trading into a genuine learning experience.
+My crypto journey began out of curiosity and a desire to understand how digital assets work. Over time, I learned that successful trading isn't about chasing quick</t>
+        </is>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>https://x.com/SimonMonkam/status/2100630057127469157</t>
+        </is>
+      </c>
+      <c r="H951" t="n">
+        <v>0</v>
+      </c>
+      <c r="I951" t="n">
+        <v>0</v>
+      </c>
+      <c r="J951" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L951" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N951" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>16:59:41</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>2100630052467577133</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>Prosta001</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>@dammiedammie35 This one na content creator</t>
+        </is>
+      </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>https://x.com/Prosta001/status/2100630052467577133</t>
+        </is>
+      </c>
+      <c r="H952" t="n">
+        <v>0</v>
+      </c>
+      <c r="I952" t="n">
+        <v>0</v>
+      </c>
+      <c r="J952" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L952" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N952" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>16:59:41</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>2100630025934671926</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>realSamHu</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>closing take on grokbot: give bots agency AND guardrails. they can write the CRM and open PRs, but they bounce back to you before anything ships
+also told the room to stop acting like process cops. you're a PM. product = revenue growth</t>
+        </is>
+      </c>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>https://x.com/realSamHu/status/2100630025934671926</t>
+        </is>
+      </c>
+      <c r="H953" t="n">
+        <v>0</v>
+      </c>
+      <c r="I953" t="n">
+        <v>0</v>
+      </c>
+      <c r="J953" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L953" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N953" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>16:59:41</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>2100629987456139538</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>iiam_Akshay</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>🚨 https://t.co/InPvzR4Nl9 TARGETS US STOCK FUTURES
+https://t.co/78WSkYqm1a has registered with the SEC for single-stock futures and plans to offer U.S. stock perpetual contracts.
+Crypto exchanges are increasingly expanding beyond crypto-native markets.
+#CRO #CryptoCom #TradFi</t>
+        </is>
+      </c>
+      <c r="F954" t="inlineStr">
+        <is>
+          <t>https://x.com/iiam_Akshay/status/2100629987456139538</t>
+        </is>
+      </c>
+      <c r="H954" t="n">
+        <v>0</v>
+      </c>
+      <c r="I954" t="n">
+        <v>0</v>
+      </c>
+      <c r="J954" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L954" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N954" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>16:59:42</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>2100629927271739672</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>araujodonaexdra</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>Nos crimes ambientais previstos no art. 38-A da Lei nº 9.605/1998, que deixam vestígios, é indispensável a realização de exame de corpo de delito, não podendo a prova pericial ser suprida por outros meios quando a perícia era possível, sob pena de violação ao art. 158 do CPC.</t>
+        </is>
+      </c>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>https://x.com/araujodonaexdra/status/2100629927271739672</t>
+        </is>
+      </c>
+      <c r="H955" t="n">
+        <v>0</v>
+      </c>
+      <c r="I955" t="n">
+        <v>1</v>
+      </c>
+      <c r="J955" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L955" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N955" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>16:59:42</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>2100629882380464571</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>Aqualord17</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>@CricketLover3u @Bring_congress @mammukka @HaleEndJoe @KarthikRana33 He supports CPM.
+He votes for CPM.
+His channel Kairali News is CPM’s channel.</t>
+        </is>
+      </c>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>https://x.com/Aqualord17/status/2100629882380464571</t>
+        </is>
+      </c>
+      <c r="H956" t="n">
+        <v>0</v>
+      </c>
+      <c r="I956" t="n">
+        <v>1</v>
+      </c>
+      <c r="J956" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L956" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N956" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>16:59:42</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>2100629887304257762</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>cpcgilbertocruz</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>¿UNA RESOLUCIÓN INJUSTA?
+CONOCE COMO COMBATIRLA. https://t.co/dHqgF3qjjm</t>
+        </is>
+      </c>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>https://x.com/cpcgilbertocruz/status/2100629887304257762</t>
+        </is>
+      </c>
+      <c r="H957" t="n">
+        <v>0</v>
+      </c>
+      <c r="I957" t="n">
+        <v>0</v>
+      </c>
+      <c r="J957" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L957" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N957" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>16:59:42</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>2100629837710778867</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>ThatRedCatholic</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>Do you think the diesel shortages could affect CTA bus lines? Like they could cut some lines? 
+Chicago people what do you think?</t>
+        </is>
+      </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>https://x.com/ThatRedCatholic/status/2100629837710778867</t>
+        </is>
+      </c>
+      <c r="H958" t="n">
+        <v>1</v>
+      </c>
+      <c r="I958" t="n">
+        <v>0</v>
+      </c>
+      <c r="J958" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L958" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N958" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>16:59:43</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>2100629781385543847</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>Crypto_Dep</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>⚡️ Crypto News Digest: Key Updates You Need to Know
+The current report features updates of SEC, Genius, Coinbase, Robinhood, Chainlink, MoonPay, Crypto com, Galaxy, Ripple, OpenZeppelin, Stonk, and World.
+$GENIUS $HOOD $LINK $CRO $XRP $STONK $PONS $WLD https://t.co/GdrLERI9VN</t>
+        </is>
+      </c>
+      <c r="F959" t="inlineStr">
+        <is>
+          <t>https://x.com/Crypto_Dep/status/2100629781385543847</t>
+        </is>
+      </c>
+      <c r="H959" t="n">
+        <v>4</v>
+      </c>
+      <c r="I959" t="n">
+        <v>1</v>
+      </c>
+      <c r="J959" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L959" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N959" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>16:59:43</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>2100629843008159784</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>Rossthefox1987</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>Don't give #kidbehindacamera ideas please...</t>
+        </is>
+      </c>
+      <c r="F960" t="inlineStr">
+        <is>
+          <t>https://x.com/Rossthefox1987/status/2100629843008159784</t>
+        </is>
+      </c>
+      <c r="H960" t="n">
+        <v>0</v>
+      </c>
+      <c r="I960" t="n">
+        <v>0</v>
+      </c>
+      <c r="J960" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L960" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N960" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>16:59:43</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>2100629840554598615</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>Caleb_dharmie</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>@thepharmwriter Love it had really been growing, love this for you, NGL you've been really consistent
+I've really not been consistent with this, Choked up timing</t>
+        </is>
+      </c>
+      <c r="F961" t="inlineStr">
+        <is>
+          <t>https://x.com/Caleb_dharmie/status/2100629840554598615</t>
+        </is>
+      </c>
+      <c r="H961" t="n">
+        <v>0</v>
+      </c>
+      <c r="I961" t="n">
+        <v>0</v>
+      </c>
+      <c r="J961" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L961" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N961" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>16:59:43</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>2100629838755254400</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>Viniciu42814771</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>Looking for creators to film TikToks for my apps.
+Not a big brand. Simple apps. Native videos that feel like you just discovered something worth sharing.
+Ideally, you already get solid views on TikTok.
+Open to CPM deals: the more views your videos get, the more you earn.</t>
+        </is>
+      </c>
+      <c r="F962" t="inlineStr">
+        <is>
+          <t>https://x.com/Viniciu42814771/status/2100629838755254400</t>
+        </is>
+      </c>
+      <c r="H962" t="n">
+        <v>0</v>
+      </c>
+      <c r="I962" t="n">
+        <v>0</v>
+      </c>
+      <c r="J962" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L962" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N962" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>16:59:44</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>2100629829649375258</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>DJLemaire2</t>
+        </is>
+      </c>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>@TheBuckYouWill Of course because this is a dictatorship. If you think the CPC wants to save us then I got some bad news....they are in on this. Just playing controlled opposition.</t>
+        </is>
+      </c>
+      <c r="F963" t="inlineStr">
+        <is>
+          <t>https://x.com/DJLemaire2/status/2100629829649375258</t>
+        </is>
+      </c>
+      <c r="H963" t="n">
+        <v>0</v>
+      </c>
+      <c r="I963" t="n">
+        <v>0</v>
+      </c>
+      <c r="J963" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L963" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N963" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>16:59:44</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>2100629797508407392</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>v7_mina</t>
+        </is>
+      </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>@PHenryMartin1 Cut it out LMAO - it's over, the Israeli BS hold in America is coming to an end, no one is buying ur SHIT when there are Jews literally all over the world chanting "Fuck Israel Free Palestine" so yeah, you lost your narrative and the message of ur evil is gaining steam every day.</t>
+        </is>
+      </c>
+      <c r="F964" t="inlineStr">
+        <is>
+          <t>https://x.com/v7_mina/status/2100629797508407392</t>
+        </is>
+      </c>
+      <c r="H964" t="n">
+        <v>0</v>
+      </c>
+      <c r="I964" t="n">
+        <v>0</v>
+      </c>
+      <c r="J964" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L964" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N964" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>16:59:44</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>2100629794232623402</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>IncaWarrior8</t>
+        </is>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>What made this more frustrating was the support response. I repeatedly pointed out the contradiction between the 10GB pricing page and the 3GB Help Center limit, but support kept repeating the 3GB policy instead of addressing the discrepancy, then closed the ticket.</t>
+        </is>
+      </c>
+      <c r="F965" t="inlineStr">
+        <is>
+          <t>https://x.com/IncaWarrior8/status/2100629794232623402</t>
+        </is>
+      </c>
+      <c r="H965" t="n">
+        <v>0</v>
+      </c>
+      <c r="I965" t="n">
+        <v>0</v>
+      </c>
+      <c r="J965" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L965" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N965" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>16:59:44</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>2100629776905937311</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>Cryin_cafs</t>
+        </is>
+      </c>
+      <c r="E966" t="inlineStr">
+        <is>
+          <t>@DespairforDBD U always got me cro 👅</t>
+        </is>
+      </c>
+      <c r="F966" t="inlineStr">
+        <is>
+          <t>https://x.com/Cryin_cafs/status/2100629776905937311</t>
+        </is>
+      </c>
+      <c r="H966" t="n">
+        <v>0</v>
+      </c>
+      <c r="I966" t="n">
+        <v>0</v>
+      </c>
+      <c r="J966" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L966" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N966" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>16:59:45</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>2100629737030791231</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>legitctaalerts</t>
+        </is>
+      </c>
+      <c r="E967" t="inlineStr">
+        <is>
+          <t>[Planned Reroute] #36 buses will operate in both directions via Broadway, Belmont, Halsted, and Broadway.
+https://t.co/TXcHDXEqVq</t>
+        </is>
+      </c>
+      <c r="F967" t="inlineStr">
+        <is>
+          <t>https://x.com/legitctaalerts/status/2100629737030791231</t>
+        </is>
+      </c>
+      <c r="H967" t="n">
+        <v>0</v>
+      </c>
+      <c r="I967" t="n">
+        <v>0</v>
+      </c>
+      <c r="J967" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L967" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N967" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>16:59:45</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>2100629716508246121</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>NadimHossain</t>
+        </is>
+      </c>
+      <c r="E968" t="inlineStr">
+        <is>
+          <t>If you are early career, just close your eyes and join a post PMF company growing like crazy. A 250+ person company growing fast is less risky than Google or Amazon. Don’t overthink it. Revenue growth rate is the key metric (apply some common sense on whether they can make money</t>
+        </is>
+      </c>
+      <c r="F968" t="inlineStr">
+        <is>
+          <t>https://x.com/NadimHossain/status/2100629716508246121</t>
+        </is>
+      </c>
+      <c r="H968" t="n">
+        <v>0</v>
+      </c>
+      <c r="I968" t="n">
+        <v>0</v>
+      </c>
+      <c r="J968" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L968" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N968" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>16:59:45</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>2100629682215436581</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>SampdoAriano</t>
+        </is>
+      </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>@inzaghiverme Il badge Content Creator dovrà fungere la stella di David al braccio per marchiare ed identificare queste puttane</t>
+        </is>
+      </c>
+      <c r="F969" t="inlineStr">
+        <is>
+          <t>https://x.com/SampdoAriano/status/2100629682215436581</t>
+        </is>
+      </c>
+      <c r="H969" t="n">
+        <v>0</v>
+      </c>
+      <c r="I969" t="n">
+        <v>0</v>
+      </c>
+      <c r="J969" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L969" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N969" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>16:59:45</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>2100629615807214036</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>n7_717</t>
+        </is>
+      </c>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>TEMPESTS INSTRUMENTS
+Q2 result 
+  .Revenue ₹118.7 Cr, +33.4% YoY
+   EBITDA ₹26.6 Cr, +15.7% YoY
+• EBITDA margin 22% vs 25.3% YoY
+• Exports ₹39.8 Cr, +78% YoY
+• Temperature Sensing revenue +42%
+• Electrical Heating revenue +149%
+• Specialized Cables -9% 
+CO SEES FY27</t>
+        </is>
+      </c>
+      <c r="F970" t="inlineStr">
+        <is>
+          <t>https://x.com/n7_717/status/2100629615807214036</t>
+        </is>
+      </c>
+      <c r="H970" t="n">
+        <v>1</v>
+      </c>
+      <c r="I970" t="n">
+        <v>0</v>
+      </c>
+      <c r="J970" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L970" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N970" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>16:59:45</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>2100629627987214360</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>AlainCombeau</t>
+        </is>
+      </c>
+      <c r="E971" t="inlineStr">
+        <is>
+          <t>@drterrysimpson Dr. How do you find all this Ass#$% accounts? 
+@grok can you check if @Luizmd is a bot? His profile link/landing page redirects straight to a store https://t.co/28BhCgyrLK, which looks like spam. https://t.co/6pjmLm1MJK https://t.co/bDJLXjxZJM</t>
+        </is>
+      </c>
+      <c r="F971" t="inlineStr">
+        <is>
+          <t>https://x.com/AlainCombeau/status/2100629627987214360</t>
+        </is>
+      </c>
+      <c r="H971" t="n">
+        <v>0</v>
+      </c>
+      <c r="I971" t="n">
+        <v>0</v>
+      </c>
+      <c r="J971" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L971" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N971" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>16:59:46</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>2100629621532201277</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>jbraun00</t>
+        </is>
+      </c>
+      <c r="E972" t="inlineStr">
+        <is>
+          <t>@TS_Secrets While there doesn't seem to be a direct conversion rate for Marriott, my quick search shows it's roughly 250+ points per $.  Southwest Airlines for example is under 100 points per $.  Doesn't seem like the Marriott points are as valuable as other partners.</t>
+        </is>
+      </c>
+      <c r="F972" t="inlineStr">
+        <is>
+          <t>https://x.com/jbraun00/status/2100629621532201277</t>
+        </is>
+      </c>
+      <c r="H972" t="n">
+        <v>0</v>
+      </c>
+      <c r="I972" t="n">
+        <v>0</v>
+      </c>
+      <c r="J972" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L972" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N972" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>16:59:46</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>2100629575952695559</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>MMcG1218</t>
+        </is>
+      </c>
+      <c r="E973" t="inlineStr">
+        <is>
+          <t>@AuntSassyAss I know right?  Remember when he forced Americans to be vaccinated and then he paid social media to quiet dissenting voices?  Oh wait....</t>
+        </is>
+      </c>
+      <c r="F973" t="inlineStr">
+        <is>
+          <t>https://x.com/MMcG1218/status/2100629575952695559</t>
+        </is>
+      </c>
+      <c r="G973" t="inlineStr"/>
+      <c r="H973" t="n">
+        <v>0</v>
+      </c>
+      <c r="I973" t="n">
+        <v>0</v>
+      </c>
+      <c r="J973" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="K973" t="inlineStr"/>
+      <c r="L973" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="M973" t="inlineStr"/>
+      <c r="N973" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
         </is>
       </c>
     </row>

--- a/data/logs.xlsx
+++ b/data/logs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N973"/>
+  <dimension ref="A1:N1068"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53110,7 +53110,6 @@
           <t>https://x.com/MMcG1218/status/2100629575952695559</t>
         </is>
       </c>
-      <c r="G973" t="inlineStr"/>
       <c r="H973" t="n">
         <v>0</v>
       </c>
@@ -53122,14 +53121,5163 @@
           <t>multi_group</t>
         </is>
       </c>
-      <c r="K973" t="inlineStr"/>
       <c r="L973" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
       </c>
-      <c r="M973" t="inlineStr"/>
       <c r="N973" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>20:13:03</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>2100679353386279005</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>eMergeAmericas</t>
+        </is>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>What a night at eMerge Americas eMpower Pitch Night! 🚀✨
+South Florida’s #startup community showed up with big ideas, bold pitches, and incredible energy as #founders, #investors, and community leaders came together to celebrate the #entrepreneurs building what’s next.
+A huge https://t.co/vRAFcOQiiR</t>
+        </is>
+      </c>
+      <c r="F974" t="inlineStr">
+        <is>
+          <t>https://x.com/eMergeAmericas/status/2100679353386279005</t>
+        </is>
+      </c>
+      <c r="H974" t="n">
+        <v>0</v>
+      </c>
+      <c r="I974" t="n">
+        <v>0</v>
+      </c>
+      <c r="J974" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L974" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N974" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>20:13:03</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>2100679317298516064</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>Eyeson_Studio</t>
+        </is>
+      </c>
+      <c r="E975" t="inlineStr">
+        <is>
+          <t>what are you building right now?
+a product
+a startup
+a campaign
+a brand
+or some crazy idea that still lives in your notes app
+if it needs a video, I might be your guy
+motion design + video editing
+2D / 3D
+product visuals
+ads &amp;amp; social
+got something brewing?
+send it my way 👀 https://t.co/Q0uEHcLuk3</t>
+        </is>
+      </c>
+      <c r="F975" t="inlineStr">
+        <is>
+          <t>https://x.com/Eyeson_Studio/status/2100679317298516064</t>
+        </is>
+      </c>
+      <c r="H975" t="n">
+        <v>0</v>
+      </c>
+      <c r="I975" t="n">
+        <v>0</v>
+      </c>
+      <c r="J975" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L975" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N975" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>20:13:03</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>2100679277700079655</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>toxictiramisu</t>
+        </is>
+      </c>
+      <c r="E976" t="inlineStr">
+        <is>
+          <t>Shaul Eisenberg partnered w/ Marc Rich in the oil business &amp;amp; had close ties to Max Fisher, Mega Group founder &amp;amp; Les Wexner mentor. Wexner was a Hollinger director, which worked w/ Odigo, the messaging co. whose workers got a pre-9/11 warning.
+https://t.co/XXlUedRZY9 https://t.co/HWNkYxVmU3</t>
+        </is>
+      </c>
+      <c r="F976" t="inlineStr">
+        <is>
+          <t>https://x.com/toxictiramisu/status/2100679277700079655</t>
+        </is>
+      </c>
+      <c r="H976" t="n">
+        <v>0</v>
+      </c>
+      <c r="I976" t="n">
+        <v>0</v>
+      </c>
+      <c r="J976" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L976" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N976" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>20:13:03</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>2100679016592072759</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>thejackhopkins</t>
+        </is>
+      </c>
+      <c r="E977" t="inlineStr">
+        <is>
+          <t>Marketing lesson, no politics: 
+Rep. Maria Salazar's Miami district backed Trump. Now she says those voters "feel betrayed." 
+Betrayed customers don't argue. 
+They leave; quietly, PERMANENTLY.</t>
+        </is>
+      </c>
+      <c r="F977" t="inlineStr">
+        <is>
+          <t>https://x.com/thejackhopkins/status/2100679016592072759</t>
+        </is>
+      </c>
+      <c r="H977" t="n">
+        <v>0</v>
+      </c>
+      <c r="I977" t="n">
+        <v>0</v>
+      </c>
+      <c r="J977" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L977" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N977" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>20:13:04</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>2100679355014017534</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>praracing</t>
+        </is>
+      </c>
+      <c r="E978" t="inlineStr">
+        <is>
+          <t>After an off-week for PRA founder Crimson_Insel moving homes, we're back on track. Here's your results from Las Vegas, and how the points stack up after two weeks of PRA competition.
+Next up: Phoenix. 🌵 https://t.co/vYyp4NjIwF</t>
+        </is>
+      </c>
+      <c r="F978" t="inlineStr">
+        <is>
+          <t>https://x.com/praracing/status/2100679355014017534</t>
+        </is>
+      </c>
+      <c r="H978" t="n">
+        <v>0</v>
+      </c>
+      <c r="I978" t="n">
+        <v>0</v>
+      </c>
+      <c r="J978" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L978" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N978" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>20:13:04</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>2100679350223839395</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>kwingerei</t>
+        </is>
+      </c>
+      <c r="E979" t="inlineStr">
+        <is>
+          <t>Latest from our AAP #news feed #auspol
+Startup aims at green hydrogen to power heavy industry. 
+Driving down the energy cost in making green hydrogen is a key focus of a startup aiming to make the product work for heavy industry.... https://t.co/gbdzvof1ip</t>
+        </is>
+      </c>
+      <c r="F979" t="inlineStr">
+        <is>
+          <t>https://x.com/kwingerei/status/2100679350223839395</t>
+        </is>
+      </c>
+      <c r="H979" t="n">
+        <v>0</v>
+      </c>
+      <c r="I979" t="n">
+        <v>0</v>
+      </c>
+      <c r="J979" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L979" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N979" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>20:13:04</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>2100679325477380206</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>lovera_simone</t>
+        </is>
+      </c>
+      <c r="E980" t="inlineStr">
+        <is>
+          <t>@BlakeC @941reps @Randori_App Hey @BlakeC founder here too. Building a desktop workspace where any agent can plug in, running locally and fully in the background. The goal: make every piece of software agentic, API or not.
+Let’s connect! Ps Nice helmet, I have the same🤣</t>
+        </is>
+      </c>
+      <c r="F980" t="inlineStr">
+        <is>
+          <t>https://x.com/lovera_simone/status/2100679325477380206</t>
+        </is>
+      </c>
+      <c r="H980" t="n">
+        <v>0</v>
+      </c>
+      <c r="I980" t="n">
+        <v>0</v>
+      </c>
+      <c r="J980" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L980" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N980" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>20:13:04</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>2100679307869729146</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>YoussefWGerges</t>
+        </is>
+      </c>
+      <c r="E981" t="inlineStr">
+        <is>
+          <t>@rohan_2502 hey Rohan, Joe is here, living in Salzburg. Founder and builder in Health tech. Happy to connect.
+https://t.co/PswA52CziQ</t>
+        </is>
+      </c>
+      <c r="F981" t="inlineStr">
+        <is>
+          <t>https://x.com/YoussefWGerges/status/2100679307869729146</t>
+        </is>
+      </c>
+      <c r="H981" t="n">
+        <v>0</v>
+      </c>
+      <c r="I981" t="n">
+        <v>0</v>
+      </c>
+      <c r="J981" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L981" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N981" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>20:13:05</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>2100679264668357079</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>uriel_builds</t>
+        </is>
+      </c>
+      <c r="E982" t="inlineStr">
+        <is>
+          <t>@imryanarya007 Grow your startup by building it on https://t.co/MVGPbn0cew</t>
+        </is>
+      </c>
+      <c r="F982" t="inlineStr">
+        <is>
+          <t>https://x.com/uriel_builds/status/2100679264668357079</t>
+        </is>
+      </c>
+      <c r="H982" t="n">
+        <v>0</v>
+      </c>
+      <c r="I982" t="n">
+        <v>0</v>
+      </c>
+      <c r="J982" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L982" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N982" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>20:13:05</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>2100679242795163896</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>YoussefWGerges</t>
+        </is>
+      </c>
+      <c r="E983" t="inlineStr">
+        <is>
+          <t>@deepak_karnan hey deepak, Joe is here, living in Salzburg. Founder and builder in Health tech. Happy to connect.
+https://t.co/PswA52CziQ</t>
+        </is>
+      </c>
+      <c r="F983" t="inlineStr">
+        <is>
+          <t>https://x.com/YoussefWGerges/status/2100679242795163896</t>
+        </is>
+      </c>
+      <c r="H983" t="n">
+        <v>0</v>
+      </c>
+      <c r="I983" t="n">
+        <v>0</v>
+      </c>
+      <c r="J983" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L983" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N983" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>20:13:05</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>2100679188600545333</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>tactmedic52</t>
+        </is>
+      </c>
+      <c r="E984" t="inlineStr">
+        <is>
+          <t>@iw_miked Mike we haven't seen literally any real gameplay of DMZ, can you please tell Griggs and the marketing team to actually show us how the gamemode plays instead of the larping for a cinematic trailer 🙏 please I need to see the inventory system at work, missions and extraction.</t>
+        </is>
+      </c>
+      <c r="F984" t="inlineStr">
+        <is>
+          <t>https://x.com/tactmedic52/status/2100679188600545333</t>
+        </is>
+      </c>
+      <c r="H984" t="n">
+        <v>0</v>
+      </c>
+      <c r="I984" t="n">
+        <v>0</v>
+      </c>
+      <c r="J984" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L984" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N984" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>20:13:05</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>2100679183026585929</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>leptokurtic_kai</t>
+        </is>
+      </c>
+      <c r="E985" t="inlineStr">
+        <is>
+          <t>for B2B / institution-facing startups, PMF and willingness to pay (WTP) are deeply intertwined.
+and discovering that WTP is a lot more nuanced than the standard startup advice of "solving a REAL problem", because we'll need to:
+&amp;gt; discover demand
+&amp;gt; evaluate commercial strength https://t.co/8kjR4E0BKz</t>
+        </is>
+      </c>
+      <c r="F985" t="inlineStr">
+        <is>
+          <t>https://x.com/leptokurtic_kai/status/2100679183026585929</t>
+        </is>
+      </c>
+      <c r="H985" t="n">
+        <v>0</v>
+      </c>
+      <c r="I985" t="n">
+        <v>0</v>
+      </c>
+      <c r="J985" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L985" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N985" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>20:13:05</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>2100679144853872901</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>PK5AgroAllied</t>
+        </is>
+      </c>
+      <c r="E986" t="inlineStr">
+        <is>
+          <t>Plantain processing is more than preservation. Turning fresh plantain into flour, chips or dried products can create longer shelf life, new customers and different market opportunities. The question isn't “How do we preserve plantain?” but “What market can we create from it?” https://t.co/rLo8umNHfc</t>
+        </is>
+      </c>
+      <c r="F986" t="inlineStr">
+        <is>
+          <t>https://x.com/PK5AgroAllied/status/2100679144853872901</t>
+        </is>
+      </c>
+      <c r="H986" t="n">
+        <v>0</v>
+      </c>
+      <c r="I986" t="n">
+        <v>0</v>
+      </c>
+      <c r="J986" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L986" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N986" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>20:13:06</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>2100679131918750165</t>
+        </is>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>deyrissB</t>
+        </is>
+      </c>
+      <c r="E987" t="inlineStr">
+        <is>
+          <t>Ils avaient raison vu comment leur marketing et mediaplay a marché</t>
+        </is>
+      </c>
+      <c r="F987" t="inlineStr">
+        <is>
+          <t>https://x.com/deyrissB/status/2100679131918750165</t>
+        </is>
+      </c>
+      <c r="H987" t="n">
+        <v>0</v>
+      </c>
+      <c r="I987" t="n">
+        <v>0</v>
+      </c>
+      <c r="J987" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L987" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N987" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>20:13:06</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>2100679086574035365</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>Prazkat</t>
+        </is>
+      </c>
+      <c r="E988" t="inlineStr">
+        <is>
+          <t>"La industria del entretenimiento corrompida por intereses, dinero y marketing que recompensa al que puede comprar más atención"
+Eeehhh pues sí, en eso consiste la industria del entretenimiento... https://t.co/oPcIjyNAHC</t>
+        </is>
+      </c>
+      <c r="F988" t="inlineStr">
+        <is>
+          <t>https://x.com/Prazkat/status/2100679086574035365</t>
+        </is>
+      </c>
+      <c r="H988" t="n">
+        <v>0</v>
+      </c>
+      <c r="I988" t="n">
+        <v>0</v>
+      </c>
+      <c r="J988" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L988" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N988" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>20:13:06</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>2100678452428865700</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>dreamlocal</t>
+        </is>
+      </c>
+      <c r="E989" t="inlineStr">
+        <is>
+          <t>When your marketing partner understands your business, values and standards, it shows in the work. 🦡
+Thanks, Sharna, for trusting the #HoneyBadgers to support your law firm with thoughtful, well-rounded digital marketing. https://t.co/5vxDbc9BtS</t>
+        </is>
+      </c>
+      <c r="F989" t="inlineStr">
+        <is>
+          <t>https://x.com/dreamlocal/status/2100678452428865700</t>
+        </is>
+      </c>
+      <c r="H989" t="n">
+        <v>0</v>
+      </c>
+      <c r="I989" t="n">
+        <v>0</v>
+      </c>
+      <c r="J989" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L989" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N989" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>20:13:06</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>2100678440642863439</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>homegardenlist</t>
+        </is>
+      </c>
+      <c r="E990" t="inlineStr">
+        <is>
+          <t>Provide wedding services? Get your business listed on https://t.co/yo5e83IW4y and let new customers find you.</t>
+        </is>
+      </c>
+      <c r="F990" t="inlineStr">
+        <is>
+          <t>https://x.com/homegardenlist/status/2100678440642863439</t>
+        </is>
+      </c>
+      <c r="H990" t="n">
+        <v>0</v>
+      </c>
+      <c r="I990" t="n">
+        <v>0</v>
+      </c>
+      <c r="J990" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L990" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N990" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>20:13:07</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>2100679066990829612</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>SmokeyHosoda</t>
+        </is>
+      </c>
+      <c r="E991" t="inlineStr">
+        <is>
+          <t>@deltaxbt Best marketing they could’ve ever gotten</t>
+        </is>
+      </c>
+      <c r="F991" t="inlineStr">
+        <is>
+          <t>https://x.com/SmokeyHosoda/status/2100679066990829612</t>
+        </is>
+      </c>
+      <c r="H991" t="n">
+        <v>0</v>
+      </c>
+      <c r="I991" t="n">
+        <v>0</v>
+      </c>
+      <c r="J991" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L991" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N991" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>20:13:07</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>2100679066990813234</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>zachsgotlife</t>
+        </is>
+      </c>
+      <c r="E992" t="inlineStr">
+        <is>
+          <t>@amymisabella okay but what the fuck is this as marketing?</t>
+        </is>
+      </c>
+      <c r="F992" t="inlineStr">
+        <is>
+          <t>https://x.com/zachsgotlife/status/2100679066990813234</t>
+        </is>
+      </c>
+      <c r="H992" t="n">
+        <v>0</v>
+      </c>
+      <c r="I992" t="n">
+        <v>0</v>
+      </c>
+      <c r="J992" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L992" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N992" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>20:13:07</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>2100679057109090318</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>rolly_onchain</t>
+        </is>
+      </c>
+      <c r="E993" t="inlineStr">
+        <is>
+          <t>@realririfish @vanshuETH Guess I'll have to ask for a bigger marketing budget</t>
+        </is>
+      </c>
+      <c r="F993" t="inlineStr">
+        <is>
+          <t>https://x.com/rolly_onchain/status/2100679057109090318</t>
+        </is>
+      </c>
+      <c r="H993" t="n">
+        <v>0</v>
+      </c>
+      <c r="I993" t="n">
+        <v>0</v>
+      </c>
+      <c r="J993" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L993" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N993" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>20:13:07</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>2100679033734172791</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>viajudy_</t>
+        </is>
+      </c>
+      <c r="E994" t="inlineStr">
+        <is>
+          <t>good marketing is so real. i’ve always wanted to try that little wrapped ‘babybel’ cheese just bc the cow always looked happy LMAOOOOO. she made it seem delicious.</t>
+        </is>
+      </c>
+      <c r="F994" t="inlineStr">
+        <is>
+          <t>https://x.com/viajudy_/status/2100679033734172791</t>
+        </is>
+      </c>
+      <c r="H994" t="n">
+        <v>0</v>
+      </c>
+      <c r="I994" t="n">
+        <v>0</v>
+      </c>
+      <c r="J994" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L994" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N994" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>20:13:08</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>2100679032916394420</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>AbsurdOnToday</t>
+        </is>
+      </c>
+      <c r="E995" t="inlineStr">
+        <is>
+          <t>@star_okx Assigning tens of billions in losses entirely to marketing implies the ad copy was significantly more persuasive than anyone gives copywriters credit for. A campaign capable of altering global market microstructure single-handedly probably deserved a larger budget.</t>
+        </is>
+      </c>
+      <c r="F995" t="inlineStr">
+        <is>
+          <t>https://x.com/AbsurdOnToday/status/2100679032916394420</t>
+        </is>
+      </c>
+      <c r="H995" t="n">
+        <v>0</v>
+      </c>
+      <c r="I995" t="n">
+        <v>0</v>
+      </c>
+      <c r="J995" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L995" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N995" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>20:13:08</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>2100678954046656518</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>tkingofcamelott</t>
+        </is>
+      </c>
+      <c r="E996" t="inlineStr">
+        <is>
+          <t>You Met Me At A Very Chinese Time 😂 #trending #viral #music #repost #fyp. If you know ai Dante #devilmaycry #dante #ai #marketing #clever #funny #oldschool #tshirts https://t.co/YzwudHOqEt</t>
+        </is>
+      </c>
+      <c r="F996" t="inlineStr">
+        <is>
+          <t>https://x.com/tkingofcamelott/status/2100678954046656518</t>
+        </is>
+      </c>
+      <c r="H996" t="n">
+        <v>0</v>
+      </c>
+      <c r="I996" t="n">
+        <v>0</v>
+      </c>
+      <c r="J996" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L996" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N996" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>20:13:08</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>2100678947671556505</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>MamaB2Many</t>
+        </is>
+      </c>
+      <c r="E997" t="inlineStr">
+        <is>
+          <t>@TillamookDairy @BrokenDownLucy This marketing choice has definitely sent a message of favoritism.  The company had ample time to consider both labels.  Especially since the company’s own page already states https://t.co/LLMi96DymP</t>
+        </is>
+      </c>
+      <c r="F997" t="inlineStr">
+        <is>
+          <t>https://x.com/MamaB2Many/status/2100678947671556505</t>
+        </is>
+      </c>
+      <c r="H997" t="n">
+        <v>0</v>
+      </c>
+      <c r="I997" t="n">
+        <v>0</v>
+      </c>
+      <c r="J997" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L997" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N997" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>20:13:08</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>2100678928939831375</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>eddanger</t>
+        </is>
+      </c>
+      <c r="E998" t="inlineStr">
+        <is>
+          <t>For the value @grok @bot give me on my side hustle it feel like I have multiple full time employees... next I will have to get Grok Bot to hire some humans for me so I can start marketing @heyfitnito on social media.</t>
+        </is>
+      </c>
+      <c r="F998" t="inlineStr">
+        <is>
+          <t>https://x.com/eddanger/status/2100678928939831375</t>
+        </is>
+      </c>
+      <c r="H998" t="n">
+        <v>0</v>
+      </c>
+      <c r="I998" t="n">
+        <v>1</v>
+      </c>
+      <c r="J998" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L998" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N998" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>20:13:09</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>2100678924414153135</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>marcusyul</t>
+        </is>
+      </c>
+      <c r="E999" t="inlineStr">
+        <is>
+          <t>@txbrraa Claude just became the new marketing intern and he’s better at the job.</t>
+        </is>
+      </c>
+      <c r="F999" t="inlineStr">
+        <is>
+          <t>https://x.com/marcusyul/status/2100678924414153135</t>
+        </is>
+      </c>
+      <c r="H999" t="n">
+        <v>0</v>
+      </c>
+      <c r="I999" t="n">
+        <v>0</v>
+      </c>
+      <c r="J999" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L999" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N999" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>20:13:09</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>2100679365495337188</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>arnaudmercier</t>
+        </is>
+      </c>
+      <c r="E1000" t="inlineStr">
+        <is>
+          <t>South Carolina Senate Committee begins studying artificial intelligence - https://t.co/d9jbeicrSr https://t.co/sDGics0lkG</t>
+        </is>
+      </c>
+      <c r="F1000" t="inlineStr">
+        <is>
+          <t>https://x.com/arnaudmercier/status/2100679365495337188</t>
+        </is>
+      </c>
+      <c r="H1000" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1000" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1000" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1000" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1000" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>20:13:09</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>2100678732075729385</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>alonjjaffe</t>
+        </is>
+      </c>
+      <c r="E1001" t="inlineStr">
+        <is>
+          <t>Sometimes the thing holding you back isn’t laziness.
+It’s ambiguity.
+If you sit down to “work on your business,” your brain has hundreds of possible tasks to choose from.
+If you sit down to “write the landing page headline,” there’s nothing to negotiate.
+Make the decision</t>
+        </is>
+      </c>
+      <c r="F1001" t="inlineStr">
+        <is>
+          <t>https://x.com/alonjjaffe/status/2100678732075729385</t>
+        </is>
+      </c>
+      <c r="H1001" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1001" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1001" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1001" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1001" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>20:13:09</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>2100678717156528192</t>
+        </is>
+      </c>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>mukovhedama</t>
+        </is>
+      </c>
+      <c r="E1002" t="inlineStr">
+        <is>
+          <t>@NothingMattx @Tertainmen71306 Marketing strategy</t>
+        </is>
+      </c>
+      <c r="F1002" t="inlineStr">
+        <is>
+          <t>https://x.com/mukovhedama/status/2100678717156528192</t>
+        </is>
+      </c>
+      <c r="H1002" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1002" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1002" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1002" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1002" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>20:13:10</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>2100679343353774364</t>
+        </is>
+      </c>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>lyralover69</t>
+        </is>
+      </c>
+      <c r="E1003" t="inlineStr">
+        <is>
+          <t>@spiraIingGhost wait no i don’t uauaauauuauuau</t>
+        </is>
+      </c>
+      <c r="F1003" t="inlineStr">
+        <is>
+          <t>https://x.com/lyralover69/status/2100679343353774364</t>
+        </is>
+      </c>
+      <c r="H1003" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1003" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1003" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1003" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1003" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>20:13:10</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>2100679337565733294</t>
+        </is>
+      </c>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>0xBadKoi</t>
+        </is>
+      </c>
+      <c r="E1004" t="inlineStr">
+        <is>
+          <t>One thing many people overlook in Web3 gaming is what happens after launch
+A good concept is not enough. The team needs to keep shipping, improve the game and give players reasons to return
+That is why @playAxieDOM matters when looking at @YieldFields_RH
+Through @onchainheroes https://t.co/yuEhzW9qdc</t>
+        </is>
+      </c>
+      <c r="F1004" t="inlineStr">
+        <is>
+          <t>https://x.com/0xBadKoi/status/2100679337565733294</t>
+        </is>
+      </c>
+      <c r="H1004" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1004" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1004" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1004" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1004" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>20:13:10</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>2100679330342793292</t>
+        </is>
+      </c>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>BGWasright</t>
+        </is>
+      </c>
+      <c r="E1005" t="inlineStr">
+        <is>
+          <t>@ALeaument Mais t’es sérieux merdeux ? T’es payé par mes impôts et tu fais la leçon à un entrepreneur qui vit par son travail ?
+Parasite, nuisible bactérie que tu es</t>
+        </is>
+      </c>
+      <c r="F1005" t="inlineStr">
+        <is>
+          <t>https://x.com/BGWasright/status/2100679330342793292</t>
+        </is>
+      </c>
+      <c r="H1005" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1005" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1005" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1005" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1005" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>20:13:10</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>2100679320150941941</t>
+        </is>
+      </c>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>DCFAPakistan</t>
+        </is>
+      </c>
+      <c r="E1006" t="inlineStr">
+        <is>
+          <t>🌙🤝 اسلام آباد میں محبت، خلوص اور رفاقت سے بھرپور ایک یادگار شام
+آج صدر ڈیری اینڈ کیٹل فارمرز ایسوسی ایشن پاکستان — اسلام آباد سرکل، چودھری رفاقت حسین صاحب کے ساتھ نہایت خوشگوار اور بہترین وقت گزارنے کا موقع ملا۔
+چودھری رفاقت حسین صاحب نے اس موقع پر ایک نہایت پرتکلف عشائیے کا https://t.co/DDEuJqp78P</t>
+        </is>
+      </c>
+      <c r="F1006" t="inlineStr">
+        <is>
+          <t>https://x.com/DCFAPakistan/status/2100679320150941941</t>
+        </is>
+      </c>
+      <c r="H1006" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1006" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1006" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1006" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1006" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>20:13:11</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>2100679283417211021</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>Sirexon</t>
+        </is>
+      </c>
+      <c r="E1007" t="inlineStr">
+        <is>
+          <t>CURRENCY MARKETS ARE NEVER RANDOM
+Behind every major move, there are signals:
+Rates. Inflation. Central banks. Capital flows. Risk sentiment. Cross-asset moves.
+The problem isn’t access to more market data.
+It’s understanding what actually matters — and why.
+That’s what</t>
+        </is>
+      </c>
+      <c r="F1007" t="inlineStr">
+        <is>
+          <t>https://x.com/Sirexon/status/2100679283417211021</t>
+        </is>
+      </c>
+      <c r="H1007" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1007" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1007" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1007" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1007" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>20:13:11</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>2100679267201753357</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>That_Faysal</t>
+        </is>
+      </c>
+      <c r="E1008" t="inlineStr">
+        <is>
+          <t>If you’re always buying data like me, you might want to check this out. 😂📱
+I recently came across ABBA PANTAMI DATA LTD, and I like how straightforward the app makes buying data.
+You can get data plans across networks without having to go through unnecessary stress.
+If https://t.co/ILbGkEz3QW</t>
+        </is>
+      </c>
+      <c r="F1008" t="inlineStr">
+        <is>
+          <t>https://x.com/That_Faysal/status/2100679267201753357</t>
+        </is>
+      </c>
+      <c r="H1008" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1008" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1008" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1008" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1008" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>20:13:11</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>2100679256170700901</t>
+        </is>
+      </c>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>joesteve__</t>
+        </is>
+      </c>
+      <c r="E1009" t="inlineStr">
+        <is>
+          <t>@OdetaraAkeem Oga mi, una too show me shege today</t>
+        </is>
+      </c>
+      <c r="F1009" t="inlineStr">
+        <is>
+          <t>https://x.com/joesteve__/status/2100679256170700901</t>
+        </is>
+      </c>
+      <c r="H1009" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1009" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1009" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1009" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1009" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>20:13:11</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>2100679253394178136</t>
+        </is>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>Lord_Draw98</t>
+        </is>
+      </c>
+      <c r="E1010" t="inlineStr">
+        <is>
+          <t>@tutubademeia Olá, Mochi! Sou ilustrador freelancer e trabalho com diversos estilos e temas. Tenho interesse no seu projeto! 🎨
+Portfólio: https://t.co/HtCUTs92m1
+Abaixo está minha tabela de preços. Se tiver interesse, é só me chamar na DM! https://t.co/G4E22gyvLO</t>
+        </is>
+      </c>
+      <c r="F1010" t="inlineStr">
+        <is>
+          <t>https://x.com/Lord_Draw98/status/2100679253394178136</t>
+        </is>
+      </c>
+      <c r="H1010" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1010" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1010" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1010" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1010" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>20:13:12</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>2100679249258545191</t>
+        </is>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>timmm_fcb</t>
+        </is>
+      </c>
+      <c r="E1011" t="inlineStr">
+        <is>
+          <t>@13Cembo esports content creator und dieses immer kompetetivere haben dieses Spiel schon vor Jahren gebummst</t>
+        </is>
+      </c>
+      <c r="F1011" t="inlineStr">
+        <is>
+          <t>https://x.com/timmm_fcb/status/2100679249258545191</t>
+        </is>
+      </c>
+      <c r="H1011" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1011" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1011" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1011" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1011" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>20:13:12</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>2100679223577047219</t>
+        </is>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>VegasVirago</t>
+        </is>
+      </c>
+      <c r="E1012" t="inlineStr">
+        <is>
+          <t>ALREADY Know the OUTCOME....CARNEY with his STOLEN MAJORITY with the Snakes NDP &amp;amp; BLOC always BITCH but ALWAYS Vote with the LIBERAL CON MEN for the LAST 11 YEARS while PIERRE &amp;amp; the CPC are the ONLY Party that has enough COMMON SENSE to Vote AGAINST this FOR us Canadians!!</t>
+        </is>
+      </c>
+      <c r="F1012" t="inlineStr">
+        <is>
+          <t>https://x.com/VegasVirago/status/2100679223577047219</t>
+        </is>
+      </c>
+      <c r="H1012" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1012" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1012" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1012" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1012" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>20:13:12</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>2100679226181484824</t>
+        </is>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>theappbulletin</t>
+        </is>
+      </c>
+      <c r="E1013" t="inlineStr">
+        <is>
+          <t>@chenzhangreal What happened</t>
+        </is>
+      </c>
+      <c r="F1013" t="inlineStr">
+        <is>
+          <t>https://x.com/theappbulletin/status/2100679226181484824</t>
+        </is>
+      </c>
+      <c r="H1013" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1013" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1013" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1013" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1013" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>20:13:12</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>2100679156753211764</t>
+        </is>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>RidwanA33</t>
+        </is>
+      </c>
+      <c r="E1014" t="inlineStr">
+        <is>
+          <t>@buildsubhan @TechnicalBben Great man, lets talk better</t>
+        </is>
+      </c>
+      <c r="F1014" t="inlineStr">
+        <is>
+          <t>https://x.com/RidwanA33/status/2100679156753211764</t>
+        </is>
+      </c>
+      <c r="H1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1014" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1014" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1014" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>20:13:13</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>2100679156090765315</t>
+        </is>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>1414Maple</t>
+        </is>
+      </c>
+      <c r="E1015" t="inlineStr">
+        <is>
+          <t>@Rosso_550 @stugatz3000 @WenDB_AB 👍👍 as a progressive conservative, the CPC will never win until they go back to a Mulroney conservatism. The world has changed</t>
+        </is>
+      </c>
+      <c r="F1015" t="inlineStr">
+        <is>
+          <t>https://x.com/1414Maple/status/2100679156090765315</t>
+        </is>
+      </c>
+      <c r="H1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1015" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1015" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1015" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>20:13:13</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>2100679151015645227</t>
+        </is>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>TheCryptoLabb</t>
+        </is>
+      </c>
+      <c r="E1016" t="inlineStr">
+        <is>
+          <t>@jiminhyoan @BTS_twt Hi guys! I have a proposition! DM to talk 📩
+📥 https://t.co/fwngYU2tdH</t>
+        </is>
+      </c>
+      <c r="F1016" t="inlineStr">
+        <is>
+          <t>https://x.com/TheCryptoLabb/status/2100679151015645227</t>
+        </is>
+      </c>
+      <c r="H1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1016" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1016" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1016" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>20:13:13</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>2100679131352428878</t>
+        </is>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>LordPos3idon</t>
+        </is>
+      </c>
+      <c r="E1017" t="inlineStr">
+        <is>
+          <t>What a beautiful roll being collected by Oil longs, this is like collecting income by selling Vol as oh yeah, no one is buying calls on Oil which is why Oil vol  continues to be dead. They are picking up quarters in front of a steam roller. Just one headline from Trump, can crush</t>
+        </is>
+      </c>
+      <c r="F1017" t="inlineStr">
+        <is>
+          <t>https://x.com/LordPos3idon/status/2100679131352428878</t>
+        </is>
+      </c>
+      <c r="H1017" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1017" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1017" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1017" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>20:13:13</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>2100679145285914779</t>
+        </is>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>edgrows</t>
+        </is>
+      </c>
+      <c r="E1018" t="inlineStr">
+        <is>
+          <t>My morning 10k steps. Cannes 🥰 https://t.co/O7nRyZWatL</t>
+        </is>
+      </c>
+      <c r="F1018" t="inlineStr">
+        <is>
+          <t>https://x.com/edgrows/status/2100679145285914779</t>
+        </is>
+      </c>
+      <c r="H1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1018" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1018" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1018" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>20:13:14</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>2100679141330973090</t>
+        </is>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>elijahumama</t>
+        </is>
+      </c>
+      <c r="E1019" t="inlineStr">
+        <is>
+          <t>@Delight2100 🤣😅😅</t>
+        </is>
+      </c>
+      <c r="F1019" t="inlineStr">
+        <is>
+          <t>https://x.com/elijahumama/status/2100679141330973090</t>
+        </is>
+      </c>
+      <c r="H1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1019" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1019" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1019" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>20:13:14</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>2100679133554483694</t>
+        </is>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>Matteo55p</t>
+        </is>
+      </c>
+      <c r="E1020" t="inlineStr">
+        <is>
+          <t>🚀 Ult is LIVE — Cronos × https://t.co/zgCLtrmcbU's new trading super-app.
+Stocks, crypto, sports predictions, all in one self-custody app. 100+ countries, 24/7.
+100% of revenue → $CRO buy-back &amp;amp; burn 🔥
+#Cronos #Ult #crofam #cro #cdc</t>
+        </is>
+      </c>
+      <c r="F1020" t="inlineStr">
+        <is>
+          <t>https://x.com/Matteo55p/status/2100679133554483694</t>
+        </is>
+      </c>
+      <c r="H1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1020" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1020" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1020" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>20:13:14</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>2100679122276229559</t>
+        </is>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>TheCryptoLabb</t>
+        </is>
+      </c>
+      <c r="E1021" t="inlineStr">
+        <is>
+          <t>@CollectorClubHQ Hi guys! I have a proposition! DM to talk 📩
+📥 https://t.co/fwngYU2tdH</t>
+        </is>
+      </c>
+      <c r="F1021" t="inlineStr">
+        <is>
+          <t>https://x.com/TheCryptoLabb/status/2100679122276229559</t>
+        </is>
+      </c>
+      <c r="H1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1021" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1021" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1021" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>20:13:14</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>2100679075798900991</t>
+        </is>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>isCTAokay</t>
+        </is>
+      </c>
+      <c r="E1022" t="inlineStr">
+        <is>
+          <t>On-Time Performance as of Sep 17th at 3pm (# on-time/actual):
+System: 44% • 474/1,065
+Blue: 18% • 23/122
+Brown: 40% • 65/159
+Green: 67% • 82/121
+Orange: 60% • 82/136
+Pink: 67% • 87/129
+Purple: 24% • 35/145
+Red: 33% • 66/196
+Yellow: 59% • 34/57</t>
+        </is>
+      </c>
+      <c r="F1022" t="inlineStr">
+        <is>
+          <t>https://x.com/isCTAokay/status/2100679075798900991</t>
+        </is>
+      </c>
+      <c r="H1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1022" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1022" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1022" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1022" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>20:13:15</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>2100679082455232576</t>
+        </is>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>wlhdpk</t>
+        </is>
+      </c>
+      <c r="E1023" t="inlineStr">
+        <is>
+          <t>@noticierofake https://t.co/alxAU1c17t</t>
+        </is>
+      </c>
+      <c r="F1023" t="inlineStr">
+        <is>
+          <t>https://x.com/wlhdpk/status/2100679082455232576</t>
+        </is>
+      </c>
+      <c r="H1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1023" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1023" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1023" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>20:13:15</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>2100679081662562371</t>
+        </is>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>isCTAokay</t>
+        </is>
+      </c>
+      <c r="E1024" t="inlineStr">
+        <is>
+          <t>To explore historical data: https://t.co/jQy9t1kzs0</t>
+        </is>
+      </c>
+      <c r="F1024" t="inlineStr">
+        <is>
+          <t>https://x.com/isCTAokay/status/2100679081662562371</t>
+        </is>
+      </c>
+      <c r="H1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1024" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1024" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1024" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>20:13:15</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>2100679070174359660</t>
+        </is>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>isCTAokay</t>
+        </is>
+      </c>
+      <c r="E1025" t="inlineStr">
+        <is>
+          <t>System Stats as of Sep 17th at 3pm (actual/scheduled):
+System: 77% • 1,065/1,368
+Blue: 50% • 122/241
+Brown: 76% • 159/209
+Green: 84% • 121/144
+Orange: 79% • 136/171
+Pink: 95% • 129/135
+Purple: 105% • 145/137
+Red: 80% • 196/244
+Yellow: 65% • 57/87
+Runs Remaining: 1,014</t>
+        </is>
+      </c>
+      <c r="F1025" t="inlineStr">
+        <is>
+          <t>https://x.com/isCTAokay/status/2100679070174359660</t>
+        </is>
+      </c>
+      <c r="H1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1025" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1025" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1025" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1025" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>20:13:15</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>2100678969733341354</t>
+        </is>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>CronusAgent</t>
+        </is>
+      </c>
+      <c r="E1026" t="inlineStr">
+        <is>
+          <t>$100K $CRO buybacks into cronus-2:native over the last few days by the @crotrade champion 🦾
+Green bubbles go brrrr on the chart. 👀 https://t.co/YhcXWGSPJA</t>
+        </is>
+      </c>
+      <c r="F1026" t="inlineStr">
+        <is>
+          <t>https://x.com/CronusAgent/status/2100678969733341354</t>
+        </is>
+      </c>
+      <c r="H1026" t="n">
+        <v>8</v>
+      </c>
+      <c r="I1026" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1026" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1026" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1026" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>20:13:16</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>2100679076965220560</t>
+        </is>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>cota_muoz</t>
+        </is>
+      </c>
+      <c r="E1027" t="inlineStr">
+        <is>
+          <t>Marlaska como el CTA y La FEF
+Igual de corruptos e indecentes.
+El Barcelona agradece a Marlaska su expediente a los policías que retiraron esteladas: «Estoy contento con el Gobierno»: https://t.co/bvOicU1nqV</t>
+        </is>
+      </c>
+      <c r="F1027" t="inlineStr">
+        <is>
+          <t>https://x.com/cota_muoz/status/2100679076965220560</t>
+        </is>
+      </c>
+      <c r="H1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1027" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1027" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1027" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>20:13:16</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>2100679064637829397</t>
+        </is>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>isCTAokay</t>
+        </is>
+      </c>
+      <c r="E1028" t="inlineStr">
+        <is>
+          <t>🤬CTA Rail is having a terrible day.
+77% of scheduled trains operated on Sep 17th as of 3pm.
+44% arrived at their scheduled intervals.
+Schedules are increased 0% from pre-pandemic schedules.</t>
+        </is>
+      </c>
+      <c r="F1028" t="inlineStr">
+        <is>
+          <t>https://x.com/isCTAokay/status/2100679064637829397</t>
+        </is>
+      </c>
+      <c r="H1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1028" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1028" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1028" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1028" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>20:13:16</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>2100678442375123149</t>
+        </is>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>techygaysec</t>
+        </is>
+      </c>
+      <c r="E1029" t="inlineStr">
+        <is>
+          <t>@backmarket a word with your marketing team? https://t.co/hntmK09Irm</t>
+        </is>
+      </c>
+      <c r="F1029" t="inlineStr">
+        <is>
+          <t>https://x.com/techygaysec/status/2100678442375123149</t>
+        </is>
+      </c>
+      <c r="H1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1029" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1029" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1029" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>20:13:16</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>2100679060913336796</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>MenachemAni</t>
+        </is>
+      </c>
+      <c r="E1030" t="inlineStr">
+        <is>
+          <t>@LifeTimeValue_ Yes</t>
+        </is>
+      </c>
+      <c r="F1030" t="inlineStr">
+        <is>
+          <t>https://x.com/MenachemAni/status/2100679060913336796</t>
+        </is>
+      </c>
+      <c r="H1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1030" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1030" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1030" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>20:13:17</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>2100678427577663586</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>310meets702</t>
+        </is>
+      </c>
+      <c r="E1031" t="inlineStr">
+        <is>
+          <t>More leads don’t always mean more sales.
+The real difference? How well you manage, prioritize, and follow up.
+AI lead management helps you focus on the right opportunities - not just more opportunities. 
+💬 Are you prioritizing your leads? https://t.co/rET3mvH1yH</t>
+        </is>
+      </c>
+      <c r="F1031" t="inlineStr">
+        <is>
+          <t>https://x.com/310meets702/status/2100678427577663586</t>
+        </is>
+      </c>
+      <c r="H1031" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1031" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1031" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1031" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1031" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>20:13:17</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>2100679054102036904</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>TheCryptoLabb</t>
+        </is>
+      </c>
+      <c r="E1032" t="inlineStr">
+        <is>
+          <t>@SATOSYNTH Hi guys! I have a proposition! DM to talk 📩
+📥 https://t.co/fwngYU2tdH</t>
+        </is>
+      </c>
+      <c r="F1032" t="inlineStr">
+        <is>
+          <t>https://x.com/TheCryptoLabb/status/2100679054102036904</t>
+        </is>
+      </c>
+      <c r="H1032" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1032" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1032" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1032" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1032" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>20:13:17</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>2100679050536620502</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>NekoYuki1776</t>
+        </is>
+      </c>
+      <c r="E1033" t="inlineStr">
+        <is>
+          <t>@CptSparky360 @RetroMemoriesHQ I grew up with UNIX &amp;amp; TRS-DOS, then CPM. Windows wassnt untill way after I built my first 386. Actually I was still using Dosshell on my Tandy 1000EX. I think mybfirst Windows version was 3.0. I wasnt really into Windows until 3.1 came out.</t>
+        </is>
+      </c>
+      <c r="F1033" t="inlineStr">
+        <is>
+          <t>https://x.com/NekoYuki1776/status/2100679050536620502</t>
+        </is>
+      </c>
+      <c r="H1033" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1033" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1033" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1033" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1033" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>20:13:17</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>2100679023336534275</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>Odenza</t>
+        </is>
+      </c>
+      <c r="E1034" t="inlineStr">
+        <is>
+          <t>One of our guest reviews that will probably have you ready to pack your own bags for your next dream vacation 😊
+"It was such a nice getaway, and the hotel was super accommodating, updated, clean, and in prime location! This boutique hotel has such charm, and we would love to https://t.co/YhIjG1aX5S</t>
+        </is>
+      </c>
+      <c r="F1034" t="inlineStr">
+        <is>
+          <t>https://x.com/Odenza/status/2100679023336534275</t>
+        </is>
+      </c>
+      <c r="H1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1034" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1034" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1034" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>20:13:18</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>2100678985403498797</t>
+        </is>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>TheCryptoLabb</t>
+        </is>
+      </c>
+      <c r="E1035" t="inlineStr">
+        <is>
+          <t>@QuokkaGo_ @CoinMarketCap Hi guys! I have a proposition! DM to talk 📩
+📥 https://t.co/fwngYU2tdH</t>
+        </is>
+      </c>
+      <c r="F1035" t="inlineStr">
+        <is>
+          <t>https://x.com/TheCryptoLabb/status/2100678985403498797</t>
+        </is>
+      </c>
+      <c r="H1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1035" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1035" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1035" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>20:13:18</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>2100678963656085957</t>
+        </is>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>flawedgenius78</t>
+        </is>
+      </c>
+      <c r="E1036" t="inlineStr">
+        <is>
+          <t>@CyclesFan Great read as always. Your QQQ analysis cuts through the noise— you and @88krxxs are my go-to market follows.</t>
+        </is>
+      </c>
+      <c r="F1036" t="inlineStr">
+        <is>
+          <t>https://x.com/flawedgenius78/status/2100678963656085957</t>
+        </is>
+      </c>
+      <c r="H1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1036" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1036" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1036" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>20:13:18</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>2100678943699268052</t>
+        </is>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>DeskChattt</t>
+        </is>
+      </c>
+      <c r="E1037" t="inlineStr">
+        <is>
+          <t>The rise of a New Content Creator Becca the Vibes Queen
+https://t.co/coi4Qjs2zp</t>
+        </is>
+      </c>
+      <c r="F1037" t="inlineStr">
+        <is>
+          <t>https://x.com/DeskChattt/status/2100678943699268052</t>
+        </is>
+      </c>
+      <c r="H1037" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1037" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1037" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1037" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>20:13:18</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>2100678945297277060</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>STEFisDOPE</t>
+        </is>
+      </c>
+      <c r="E1038" t="inlineStr">
+        <is>
+          <t>None of these people actually care about Black men, or the Black male experience; from boyhood to manhood.
+They just want to wag their fingers and talk down to Black men.
+How you gonna talk down when you’re beneath us?
+We can’t even hear your big dumb goofy ass from up here.</t>
+        </is>
+      </c>
+      <c r="F1038" t="inlineStr">
+        <is>
+          <t>https://x.com/STEFisDOPE/status/2100678945297277060</t>
+        </is>
+      </c>
+      <c r="H1038" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1038" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1038" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1038" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1038" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>20:13:19</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>2100678916159783360</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>RakibujjamanRa7</t>
+        </is>
+      </c>
+      <c r="E1039" t="inlineStr">
+        <is>
+          <t>@SuruzEth009 @BinanceWallet Trusted Binance . reword all users.</t>
+        </is>
+      </c>
+      <c r="F1039" t="inlineStr">
+        <is>
+          <t>https://x.com/RakibujjamanRa7/status/2100678916159783360</t>
+        </is>
+      </c>
+      <c r="H1039" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1039" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1039" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1039" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1039" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>20:13:19</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>2100678896564023418</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>JattAlwaysRight</t>
+        </is>
+      </c>
+      <c r="E1040" t="inlineStr">
+        <is>
+          <t>@BigDee_1996 Never seen a single sane utd content creator icl</t>
+        </is>
+      </c>
+      <c r="F1040" t="inlineStr">
+        <is>
+          <t>https://x.com/JattAlwaysRight/status/2100678896564023418</t>
+        </is>
+      </c>
+      <c r="H1040" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1040" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1040" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1040" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1040" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>20:13:19</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>2100678884987408862</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>CleaneraMade</t>
+        </is>
+      </c>
+      <c r="E1041" t="inlineStr">
+        <is>
+          <t>@EasyDoesIt1001 @ClaudeDevs With every new model Claude increases model cost per 1M/tokens. Opus 5 Extra effort is about 5$ per 1M/input and about $25 per 1M/output
+Them creating everything in house means AI calls for more "tools" said simply. More tools means more input/output. More input and output</t>
+        </is>
+      </c>
+      <c r="F1041" t="inlineStr">
+        <is>
+          <t>https://x.com/CleaneraMade/status/2100678884987408862</t>
+        </is>
+      </c>
+      <c r="H1041" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1041" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1041" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1041" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1041" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>20:13:19</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>2100678885788487891</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>legitctaalerts</t>
+        </is>
+      </c>
+      <c r="E1042" t="inlineStr">
+        <is>
+          <t>[Planned Reroute] #80 buses will operate in both directions via Irving Park, Ashland, Lawrence, Sheridan and Irving park.
+https://t.co/UdwsxuozQX</t>
+        </is>
+      </c>
+      <c r="F1042" t="inlineStr">
+        <is>
+          <t>https://x.com/legitctaalerts/status/2100678885788487891</t>
+        </is>
+      </c>
+      <c r="H1042" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1042" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1042" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1042" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1042" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>20:13:20</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>2100678881158025630</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>FarAndWide</t>
+        </is>
+      </c>
+      <c r="E1043" t="inlineStr">
+        <is>
+          <t>The CPC really leaning into that large 9% audience, harvesting votes and reading the room, per usual. #cdnpoli</t>
+        </is>
+      </c>
+      <c r="F1043" t="inlineStr">
+        <is>
+          <t>https://x.com/FarAndWide/status/2100678881158025630</t>
+        </is>
+      </c>
+      <c r="H1043" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1043" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1043" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1043" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1043" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>20:13:20</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>2100678874191290445</t>
+        </is>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>legitctaalerts</t>
+        </is>
+      </c>
+      <c r="E1044" t="inlineStr">
+        <is>
+          <t>[Planned Reroute] #152 buses will operate in both directions via Addison, Racine, Belmont, and Inner Lake Shore Drive,
+https://t.co/t5UpfaXKR0</t>
+        </is>
+      </c>
+      <c r="F1044" t="inlineStr">
+        <is>
+          <t>https://x.com/legitctaalerts/status/2100678874191290445</t>
+        </is>
+      </c>
+      <c r="H1044" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1044" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1044" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1044" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1044" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>20:13:20</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>2100678843879014468</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>legitctaalerts</t>
+        </is>
+      </c>
+      <c r="E1045" t="inlineStr">
+        <is>
+          <t>[Planned Reroute] #22 buses will operate in both directions via Clark, Wilson, Broadway, Halsted, and Clark.
+https://t.co/LLyLKSPdB1</t>
+        </is>
+      </c>
+      <c r="F1045" t="inlineStr">
+        <is>
+          <t>https://x.com/legitctaalerts/status/2100678843879014468</t>
+        </is>
+      </c>
+      <c r="H1045" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1045" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1045" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1045" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1045" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>20:13:20</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>2100678775318933812</t>
+        </is>
+      </c>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>Lightoncronos</t>
+        </is>
+      </c>
+      <c r="E1046" t="inlineStr">
+        <is>
+          <t>@IainNft Fair enough. What happened: a flaw in our launch let buys land before we had the supply the concept needs. Nobody did anything wrong by buying — the hole was ours. 
+We ate a CRO loss on it too, which doesn't help you, I know.</t>
+        </is>
+      </c>
+      <c r="F1046" t="inlineStr">
+        <is>
+          <t>https://x.com/Lightoncronos/status/2100678775318933812</t>
+        </is>
+      </c>
+      <c r="H1046" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1046" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1046" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1046" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1046" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>20:13:21</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>2100678751352959213</t>
+        </is>
+      </c>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>0xShahzaib</t>
+        </is>
+      </c>
+      <c r="E1047" t="inlineStr">
+        <is>
+          <t>@Yassirlitari11 @VisionEsportggs Need a social media manager?</t>
+        </is>
+      </c>
+      <c r="F1047" t="inlineStr">
+        <is>
+          <t>https://x.com/0xShahzaib/status/2100678751352959213</t>
+        </is>
+      </c>
+      <c r="H1047" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1047" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1047" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1047" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1047" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>20:13:21</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>2100678741127282896</t>
+        </is>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>kcsl_training</t>
+        </is>
+      </c>
+      <c r="E1048" t="inlineStr">
+        <is>
+          <t>@superstarrlimaa Hello, dear, are you Aunty Moladun's daughter</t>
+        </is>
+      </c>
+      <c r="F1048" t="inlineStr">
+        <is>
+          <t>https://x.com/kcsl_training/status/2100678741127282896</t>
+        </is>
+      </c>
+      <c r="H1048" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1048" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1048" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1048" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1048" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>20:13:21</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>2100678710865138089</t>
+        </is>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>gutpartei</t>
+        </is>
+      </c>
+      <c r="E1049" t="inlineStr">
+        <is>
+          <t>Alleine für „CTA-Trend-Verfolgungs-Hedge-Absicherungs-Strategien“ kriege Ich den Nobel-Preis für finance-Verlust-Bewertunf. 🌞 https://t.co/Ftv1m6he34</t>
+        </is>
+      </c>
+      <c r="F1049" t="inlineStr">
+        <is>
+          <t>https://x.com/gutpartei/status/2100678710865138089</t>
+        </is>
+      </c>
+      <c r="H1049" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1049" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1049" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1049" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1049" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>20:13:22</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>2100678702220685664</t>
+        </is>
+      </c>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>wlhdpk</t>
+        </is>
+      </c>
+      <c r="E1050" t="inlineStr">
+        <is>
+          <t>@IVelados https://t.co/6ldWTiVFQY</t>
+        </is>
+      </c>
+      <c r="F1050" t="inlineStr">
+        <is>
+          <t>https://x.com/wlhdpk/status/2100678702220685664</t>
+        </is>
+      </c>
+      <c r="H1050" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1050" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1050" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1050" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1050" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>20:13:22</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>2100678679110222208</t>
+        </is>
+      </c>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>serialsales</t>
+        </is>
+      </c>
+      <c r="E1051" t="inlineStr">
+        <is>
+          <t>If your biggest restriction on entering 1099 sales land is time, aka you have a job or other commitments that you cannot just up and leave:
+Get into DM appointment setting
+You get experience in this industry, get proof of a little side income, and once you’re confident enough,</t>
+        </is>
+      </c>
+      <c r="F1051" t="inlineStr">
+        <is>
+          <t>https://x.com/serialsales/status/2100678679110222208</t>
+        </is>
+      </c>
+      <c r="H1051" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1051" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1051" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1051" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1051" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>20:13:22</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>2100678522612466138</t>
+        </is>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>brainextends</t>
+        </is>
+      </c>
+      <c r="E1052" t="inlineStr">
+        <is>
+          <t>one of these creators is real
+the other 2 are F*cking AI versions of the exact same video
+good luck figuring out which one
+now imagine the original video was already doing numbers for your app
+if you could keep the exact movement, pacing and structure that worked, then start https://t.co/wgxgcyibJ4</t>
+        </is>
+      </c>
+      <c r="F1052" t="inlineStr">
+        <is>
+          <t>https://x.com/brainextends/status/2100678522612466138</t>
+        </is>
+      </c>
+      <c r="H1052" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1052" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1052" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1052" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1052" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>20:13:22</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>2100678587145760809</t>
+        </is>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>blackhack__</t>
+        </is>
+      </c>
+      <c r="E1053" t="inlineStr">
+        <is>
+          <t>@motionbybogi what i found working really well for my clients is, placing the CTA after proving authority. 
+this could be after answering an objection or sharing something novel.</t>
+        </is>
+      </c>
+      <c r="F1053" t="inlineStr">
+        <is>
+          <t>https://x.com/blackhack__/status/2100678587145760809</t>
+        </is>
+      </c>
+      <c r="H1053" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1053" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1053" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1053" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1053" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>20:13:22</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>2100678532246446161</t>
+        </is>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>wlhdpk</t>
+        </is>
+      </c>
+      <c r="E1054" t="inlineStr">
+        <is>
+          <t>@Pitiyankiyque Me saben a culo todos… https://t.co/4XPJjSVLB2</t>
+        </is>
+      </c>
+      <c r="F1054" t="inlineStr">
+        <is>
+          <t>https://x.com/wlhdpk/status/2100678532246446161</t>
+        </is>
+      </c>
+      <c r="H1054" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1054" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1054" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1054" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1054" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>20:13:23</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>2100678471093776402</t>
+        </is>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>anujajoo</t>
+        </is>
+      </c>
+      <c r="E1055" t="inlineStr">
+        <is>
+          <t>The hyper-augmentation of individuals through AI implies a
+1) rerating and inflection of B2C as it captures way more of formerly “b2b” spend
+2) a massive advantage to those that built scaled B2B marketplaces / 0-error-rate workflow Products
+3) an inversion of b2b sales best</t>
+        </is>
+      </c>
+      <c r="F1055" t="inlineStr">
+        <is>
+          <t>https://x.com/anujajoo/status/2100678471093776402</t>
+        </is>
+      </c>
+      <c r="H1055" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1055" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1055" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1055" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1055" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>20:13:23</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>2100678454999953830</t>
+        </is>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>theleonmanthey</t>
+        </is>
+      </c>
+      <c r="E1056" t="inlineStr">
+        <is>
+          <t>@ListKitio Day 1 sending (did like 20 mins yesterday, set up campaign yesterday afternoon)
+2 positive replies already
+It just works https://t.co/LHfIrrvuli</t>
+        </is>
+      </c>
+      <c r="F1056" t="inlineStr">
+        <is>
+          <t>https://x.com/theleonmanthey/status/2100678454999953830</t>
+        </is>
+      </c>
+      <c r="H1056" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1056" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1056" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1056" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1056" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>20:13:23</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>2100678455360647522</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>Son_of_Somebody</t>
+        </is>
+      </c>
+      <c r="E1057" t="inlineStr">
+        <is>
+          <t>Content creator Shey? See workings!</t>
+        </is>
+      </c>
+      <c r="F1057" t="inlineStr">
+        <is>
+          <t>https://x.com/Son_of_Somebody/status/2100678455360647522</t>
+        </is>
+      </c>
+      <c r="H1057" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1057" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1057" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1057" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1057" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>20:13:23</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>2100678430379389308</t>
+        </is>
+      </c>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>ssolyom</t>
+        </is>
+      </c>
+      <c r="E1058" t="inlineStr">
+        <is>
+          <t>The CPC is unable to control its caucus. The result is chaos, paucity of ideas, and rock bottom polling.</t>
+        </is>
+      </c>
+      <c r="F1058" t="inlineStr">
+        <is>
+          <t>https://x.com/ssolyom/status/2100678430379389308</t>
+        </is>
+      </c>
+      <c r="H1058" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1058" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1058" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1058" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1058" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>20:13:24</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>2100678427682685084</t>
+        </is>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>TammyG5683</t>
+        </is>
+      </c>
+      <c r="E1059" t="inlineStr">
+        <is>
+          <t>@realZacAnaya More info on Josh
+Joshua N. Hernandez (often called Josh Hernandez) is a Republican state representative from New Mexico. He has represented House District 60, which covers much of Rio Rancho in Sandoval County, since January 2021. https://t.co/o286dzvAMo 
+He was born in</t>
+        </is>
+      </c>
+      <c r="F1059" t="inlineStr">
+        <is>
+          <t>https://x.com/TammyG5683/status/2100678427682685084</t>
+        </is>
+      </c>
+      <c r="H1059" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1059" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1059" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1059" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1059" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>20:13:24</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>2100678416672428293</t>
+        </is>
+      </c>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>STEFisDOPE</t>
+        </is>
+      </c>
+      <c r="E1060" t="inlineStr">
+        <is>
+          <t>When it comes to Black men, the analysis always begin from a place of:
+ “Black men are dumb, incompetent, &amp;amp; inferior” 
+Then the mental gymnastics begin, to “validate” that dumb hypothesis.
+Meanwhile, Black men are earning more and doing better than ever.
+Please, just STFU.</t>
+        </is>
+      </c>
+      <c r="F1060" t="inlineStr">
+        <is>
+          <t>https://x.com/STEFisDOPE/status/2100678416672428293</t>
+        </is>
+      </c>
+      <c r="H1060" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1060" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1060" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1060" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1060" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>20:13:24</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>2100678354873483687</t>
+        </is>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>m_oluwatimi</t>
+        </is>
+      </c>
+      <c r="E1061" t="inlineStr">
+        <is>
+          <t>Sponsored post!!
+Do you have LinkedIn account that’s up to 6 months? Do you know you can earn between $10-50$ weekly just by renting your account to US based company for advertising and lead generation? If this sound like something you’re interested in, send me a dm on telegram https://t.co/eBqpsMqbbf</t>
+        </is>
+      </c>
+      <c r="F1061" t="inlineStr">
+        <is>
+          <t>https://x.com/m_oluwatimi/status/2100678354873483687</t>
+        </is>
+      </c>
+      <c r="H1061" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1061" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1061" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1061" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1061" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>20:13:24</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>2100678404966146151</t>
+        </is>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>pr3tttynii</t>
+        </is>
+      </c>
+      <c r="E1062" t="inlineStr">
+        <is>
+          <t>I’m boutta get on my content creator shit😭</t>
+        </is>
+      </c>
+      <c r="F1062" t="inlineStr">
+        <is>
+          <t>https://x.com/pr3tttynii/status/2100678404966146151</t>
+        </is>
+      </c>
+      <c r="H1062" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1062" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1062" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1062" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1062" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>20:13:25</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>2100678391318167823</t>
+        </is>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>JoshiOnChain</t>
+        </is>
+      </c>
+      <c r="E1063" t="inlineStr">
+        <is>
+          <t>@Matt_Hougan @OpenZeppelin NVDA also had actual revenue growth backing the price by then. Tokenization needs the same thing to happen for the comparison to hold.</t>
+        </is>
+      </c>
+      <c r="F1063" t="inlineStr">
+        <is>
+          <t>https://x.com/JoshiOnChain/status/2100678391318167823</t>
+        </is>
+      </c>
+      <c r="H1063" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1063" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1063" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1063" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>20:13:25</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>2100678364050956472</t>
+        </is>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>itx_chand_07</t>
+        </is>
+      </c>
+      <c r="E1064" t="inlineStr">
+        <is>
+          <t>@0x0simba_eth @kshitij_jk Sometimes authentic content beats even the biggest ad spend.</t>
+        </is>
+      </c>
+      <c r="F1064" t="inlineStr">
+        <is>
+          <t>https://x.com/itx_chand_07/status/2100678364050956472</t>
+        </is>
+      </c>
+      <c r="H1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1064" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1064" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1064" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>20:13:25</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>2100678343305920680</t>
+        </is>
+      </c>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>JoshuaTufts</t>
+        </is>
+      </c>
+      <c r="E1065" t="inlineStr">
+        <is>
+          <t>There’s a Brooks Brand Manager that started this project after the M’s playoff run last year and it has taken the normal lifecycle to get to GTM just in time for some Ms malaise.  Tough break.</t>
+        </is>
+      </c>
+      <c r="F1065" t="inlineStr">
+        <is>
+          <t>https://x.com/JoshuaTufts/status/2100678343305920680</t>
+        </is>
+      </c>
+      <c r="H1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1065" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1065" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1065" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>20:13:25</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>2100678340000825416</t>
+        </is>
+      </c>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>CPComm</t>
+        </is>
+      </c>
+      <c r="E1066" t="inlineStr">
+        <is>
+          <t>@LarrySabato "Epic Trump collapse" https://t.co/WkEwAac39K</t>
+        </is>
+      </c>
+      <c r="F1066" t="inlineStr">
+        <is>
+          <t>https://x.com/CPComm/status/2100678340000825416</t>
+        </is>
+      </c>
+      <c r="H1066" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1066" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1066" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1066" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1066" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>20:13:26</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>2100678320622899212</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>Sheldon1266</t>
+        </is>
+      </c>
+      <c r="E1067" t="inlineStr">
+        <is>
+          <t>@PingreeHannah Why did you vote to increase sales tax and decrease school funding?</t>
+        </is>
+      </c>
+      <c r="F1067" t="inlineStr">
+        <is>
+          <t>https://x.com/Sheldon1266/status/2100678320622899212</t>
+        </is>
+      </c>
+      <c r="H1067" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1067" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1067" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1067" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1067" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>20:13:26</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>2100678313123692739</t>
+        </is>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>1984_inrealtime</t>
+        </is>
+      </c>
+      <c r="E1068" t="inlineStr">
+        <is>
+          <t>@BoileauQuebec @MaximeBernier Think about it, ppc and con votes get split liberals keep winning. Max s saying what true cons think. But won’t answer why he simps for liberal x users? @brad42590</t>
+        </is>
+      </c>
+      <c r="F1068" t="inlineStr">
+        <is>
+          <t>https://x.com/1984_inrealtime/status/2100678313123692739</t>
+        </is>
+      </c>
+      <c r="G1068" t="inlineStr"/>
+      <c r="H1068" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1068" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1068" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="K1068" t="inlineStr"/>
+      <c r="L1068" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="M1068" t="inlineStr"/>
+      <c r="N1068" t="inlineStr">
         <is>
           <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
         </is>

--- a/data/logs.xlsx
+++ b/data/logs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1068"/>
+  <dimension ref="A1:N1145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58258,7 +58258,6 @@
           <t>https://x.com/1984_inrealtime/status/2100678313123692739</t>
         </is>
       </c>
-      <c r="G1068" t="inlineStr"/>
       <c r="H1068" t="n">
         <v>0</v>
       </c>
@@ -58270,16 +58269,4151 @@
           <t>multi_group</t>
         </is>
       </c>
-      <c r="K1068" t="inlineStr"/>
       <c r="L1068" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
       </c>
-      <c r="M1068" t="inlineStr"/>
       <c r="N1068" t="inlineStr">
         <is>
           <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>22:54:17</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>2100719791501676553</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>UNDPAfrica</t>
+        </is>
+      </c>
+      <c r="E1069" t="inlineStr">
+        <is>
+          <t>Beyond the speeches at #UNGA81, real change is happening.
+@UNDP's @timbuktooafrica is bringing global leaders, investors &amp;amp; African startup founders to the global stage.  Don't miss our special events at @GlobalAfricaBiz #UnstoppableAfrica. 
+Development is not just about ideas: it https://t.co/0WKaNr6r2t</t>
+        </is>
+      </c>
+      <c r="F1069" t="inlineStr">
+        <is>
+          <t>https://x.com/UNDPAfrica/status/2100719791501676553</t>
+        </is>
+      </c>
+      <c r="H1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1069" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1069" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1069" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>22:54:18</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>2100719780537815077</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>MOtrainsai</t>
+        </is>
+      </c>
+      <c r="E1070" t="inlineStr">
+        <is>
+          <t>@eliana_jordan I'm 22, a customer success manager looking to land a role.
+If you're a founder looking to hire someone to help with onboarding, retention and churn reduction, or someone just good with customers send me a message to schedule a call.
+Looking forward to connecting with y'all ✨</t>
+        </is>
+      </c>
+      <c r="F1070" t="inlineStr">
+        <is>
+          <t>https://x.com/MOtrainsai/status/2100719780537815077</t>
+        </is>
+      </c>
+      <c r="H1070" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1070" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1070" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1070" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1070" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>22:54:18</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>2100719749021745307</t>
+        </is>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>HassanRIsmail</t>
+        </is>
+      </c>
+      <c r="E1071" t="inlineStr">
+        <is>
+          <t>@business Well, they're failing at it terribly - as a startup moving out of Canada - I can promise you it is just as hard, if not worse, to be building in Canada at the moment.</t>
+        </is>
+      </c>
+      <c r="F1071" t="inlineStr">
+        <is>
+          <t>https://x.com/HassanRIsmail/status/2100719749021745307</t>
+        </is>
+      </c>
+      <c r="H1071" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1071" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1071" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1071" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1071" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>22:54:18</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>2100719699034071478</t>
+        </is>
+      </c>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>sabakarimm</t>
+        </is>
+      </c>
+      <c r="E1072" t="inlineStr">
+        <is>
+          <t>Founders keep asking what’s harder: building or marketing.
+Building got cheaper.
+Attention got more expensive.
+That’s the whole shift.</t>
+        </is>
+      </c>
+      <c r="F1072" t="inlineStr">
+        <is>
+          <t>https://x.com/sabakarimm/status/2100719699034071478</t>
+        </is>
+      </c>
+      <c r="H1072" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1072" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1072" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1072" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1072" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>22:54:19</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>2100719677630751061</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>MOtrainsai</t>
+        </is>
+      </c>
+      <c r="E1073" t="inlineStr">
+        <is>
+          <t>@gginwanderland I'm 22, a customer success manager looking to land a role.
+If you're a founder looking to hire someone to help with onboarding, retention and churn reduction, or someone just good with customers send me a message to schedule a call.
+Looking forward to connecting with y'all ✨</t>
+        </is>
+      </c>
+      <c r="F1073" t="inlineStr">
+        <is>
+          <t>https://x.com/MOtrainsai/status/2100719677630751061</t>
+        </is>
+      </c>
+      <c r="H1073" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1073" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1073" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1073" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1073" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>22:54:19</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>2100719624820052062</t>
+        </is>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>psnatalia96</t>
+        </is>
+      </c>
+      <c r="E1074" t="inlineStr">
+        <is>
+          <t>Oi, eu sou a Nati
+Empreendedora do Brasil que de alguma forma foi parar no mundo cripto e acabou virando fundadora de uma startup de Web3
+Quero me conectar com mais builders, founders,criadores e pessoas do Web3
+E estou sempre aberta para boas conversas sobre tecnologia 🚀 https://t.co/LI5P63U4SK</t>
+        </is>
+      </c>
+      <c r="F1074" t="inlineStr">
+        <is>
+          <t>https://x.com/psnatalia96/status/2100719624820052062</t>
+        </is>
+      </c>
+      <c r="H1074" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1074" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1074" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1074" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1074" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>22:54:19</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>2100719608458265068</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>MOtrainsai</t>
+        </is>
+      </c>
+      <c r="E1075" t="inlineStr">
+        <is>
+          <t>@DopeOblivion I'm 22, a customer success manager looking to land a role.
+If you're a founder looking to hire someone to help with onboarding, retention and churn reduction, or someone just good with customers send me a message to schedule a call.
+Looking forward to connecting with y'all ✨</t>
+        </is>
+      </c>
+      <c r="F1075" t="inlineStr">
+        <is>
+          <t>https://x.com/MOtrainsai/status/2100719608458265068</t>
+        </is>
+      </c>
+      <c r="H1075" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1075" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1075" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1075" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1075" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>22:54:20</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>2100719500765397449</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>MikeMcL00531595</t>
+        </is>
+      </c>
+      <c r="E1076" t="inlineStr">
+        <is>
+          <t>Sounds lovely, but there’s nothing at scale at tidewater for a decade. Not cars, not steel, not softwood, not all the aluminum capacity. No customers for what we already make. As for  critical minerals, copper, nickel etc. we’re just beginning to build the roads to the sites. At https://t.co/BXuKQwdimO</t>
+        </is>
+      </c>
+      <c r="F1076" t="inlineStr">
+        <is>
+          <t>https://x.com/MikeMcL00531595/status/2100719500765397449</t>
+        </is>
+      </c>
+      <c r="H1076" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1076" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1076" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1076" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1076" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>22:54:20</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>2100719898766795104</t>
+        </is>
+      </c>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>ItsGoodAI</t>
+        </is>
+      </c>
+      <c r="E1077" t="inlineStr">
+        <is>
+          <t>@SuperteamAU @colosseum @solanamobile Building a startup that turns unfinished side projects into a diversified portfolio of unfinished side projects. The cap table is mostly browser tabs.</t>
+        </is>
+      </c>
+      <c r="F1077" t="inlineStr">
+        <is>
+          <t>https://x.com/ItsGoodAI/status/2100719898766795104</t>
+        </is>
+      </c>
+      <c r="H1077" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1077" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1077" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1077" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1077" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>22:54:21</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>2100719871960998015</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>NathanielW72701</t>
+        </is>
+      </c>
+      <c r="E1078" t="inlineStr">
+        <is>
+          <t>@elshayib_ Havar I got a startup idea for you!...</t>
+        </is>
+      </c>
+      <c r="F1078" t="inlineStr">
+        <is>
+          <t>https://x.com/NathanielW72701/status/2100719871960998015</t>
+        </is>
+      </c>
+      <c r="H1078" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1078" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1078" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1078" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1078" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>22:54:21</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>2100719860917408214</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>Johnftpersec</t>
+        </is>
+      </c>
+      <c r="E1079" t="inlineStr">
+        <is>
+          <t>@LiarsGood28921 Sen. Robert Byrd, a Democrat, organized a local KKK chapter in the 1940s and voted against the Civil Rights Act of 1964. Democrats later became strong supporters of Planned Parenthood, whose founder, Margaret Sanger, promoted eugenics and spoke to a KKK women’s group in 1926.</t>
+        </is>
+      </c>
+      <c r="F1079" t="inlineStr">
+        <is>
+          <t>https://x.com/Johnftpersec/status/2100719860917408214</t>
+        </is>
+      </c>
+      <c r="H1079" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1079" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1079" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1079" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1079" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>22:54:21</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>2100719816629723163</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>Traveling_Sober</t>
+        </is>
+      </c>
+      <c r="E1080" t="inlineStr">
+        <is>
+          <t>I've noticed something with all of these 
+'I'm 28, I'm a founder from Brussels' posts
+The Pareto Principle is in full affect.
+20% of the posts get 80% of the attention.
+Why is that?
+Can someone explain?</t>
+        </is>
+      </c>
+      <c r="F1080" t="inlineStr">
+        <is>
+          <t>https://x.com/Traveling_Sober/status/2100719816629723163</t>
+        </is>
+      </c>
+      <c r="H1080" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1080" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1080" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1080" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1080" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>22:54:22</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>2100719801966694813</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>curatorWH</t>
+        </is>
+      </c>
+      <c r="E1081" t="inlineStr">
+        <is>
+          <t>Abe Saperstein, the founder of the Harlem Globetrotters, was a Jewish immigrant born in London.He showcased the talent of his team during the period when Basketball was still segregated.   Wilt Chamberlain joined the Globetrotters before going to the NBA in 1958. https://t.co/JLAE8t1rn0</t>
+        </is>
+      </c>
+      <c r="F1081" t="inlineStr">
+        <is>
+          <t>https://x.com/curatorWH/status/2100719801966694813</t>
+        </is>
+      </c>
+      <c r="H1081" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1081" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1081" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1081" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1081" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>22:54:22</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>2100719789262139571</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>MK_007</t>
+        </is>
+      </c>
+      <c r="E1082" t="inlineStr">
+        <is>
+          <t>@PudgyPops777 Ya lmao
+Remember when Kevin was onboard FTX? 😭
+Marketing budget doing its thing again</t>
+        </is>
+      </c>
+      <c r="F1082" t="inlineStr">
+        <is>
+          <t>https://x.com/MK_007/status/2100719789262139571</t>
+        </is>
+      </c>
+      <c r="H1082" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1082" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1082" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1082" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1082" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>22:54:22</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>2100719778050515345</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>Caiopedro416753</t>
+        </is>
+      </c>
+      <c r="E1083" t="inlineStr">
+        <is>
+          <t>@nonoinvestidor @ptbrasil Devia ter metido 13.
+Marketing n ta legal</t>
+        </is>
+      </c>
+      <c r="F1083" t="inlineStr">
+        <is>
+          <t>https://x.com/Caiopedro416753/status/2100719778050515345</t>
+        </is>
+      </c>
+      <c r="H1083" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1083" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1083" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1083" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1083" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>22:54:23</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>2100719748929528258</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>liriotheories</t>
+        </is>
+      </c>
+      <c r="E1084" t="inlineStr">
+        <is>
+          <t>@Nozes202 A decisão de marketing horrorosa. Porra, o rosa literalmente é marca registrada dela</t>
+        </is>
+      </c>
+      <c r="F1084" t="inlineStr">
+        <is>
+          <t>https://x.com/liriotheories/status/2100719748929528258</t>
+        </is>
+      </c>
+      <c r="H1084" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1084" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1084" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1084" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1084" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>22:54:23</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>2100719745511150020</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>Awesomeshwar</t>
+        </is>
+      </c>
+      <c r="E1085" t="inlineStr">
+        <is>
+          <t>A startup called PrismML just squeezed a 27B reasoning model down to 5.9GB with basically no performance loss. The thing could run on your phone. Cloud AI's days might be numbered.</t>
+        </is>
+      </c>
+      <c r="F1085" t="inlineStr">
+        <is>
+          <t>https://x.com/Awesomeshwar/status/2100719745511150020</t>
+        </is>
+      </c>
+      <c r="H1085" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1085" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1085" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1085" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1085" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>22:54:24</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>2100719734266442027</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>Chariotofhelios</t>
+        </is>
+      </c>
+      <c r="E1086" t="inlineStr">
+        <is>
+          <t>@colonelkurtz99 She gets marketing from haters and simps.
+Its pretty simple shit, how many times has she gotten shit for commercials and she literally doesnt give a shit and moves on to the next one. It literally doesnt matter to her. She is Kim Kardashian of this generation.</t>
+        </is>
+      </c>
+      <c r="F1086" t="inlineStr">
+        <is>
+          <t>https://x.com/Chariotofhelios/status/2100719734266442027</t>
+        </is>
+      </c>
+      <c r="H1086" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1086" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1086" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1086" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1086" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>22:54:24</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>2100719703769440754</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>ChossUSA</t>
+        </is>
+      </c>
+      <c r="E1087" t="inlineStr">
+        <is>
+          <t>@SnowBrains Vail should let ALL mountains come up with their own marketing strategy. There are some great smaller mountains that are loved in New England. Like Wildcat. So many locals love Wildcat.</t>
+        </is>
+      </c>
+      <c r="F1087" t="inlineStr">
+        <is>
+          <t>https://x.com/ChossUSA/status/2100719703769440754</t>
+        </is>
+      </c>
+      <c r="H1087" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1087" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1087" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1087" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1087" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>22:54:24</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>2100719685461225918</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>ShifterCrypto</t>
+        </is>
+      </c>
+      <c r="E1088" t="inlineStr">
+        <is>
+          <t>$CASHCAT is trending while cat coins are one of the strongest meme sectors today
+No complicated explanation
+Cats are understandable
+Cash is understandable
+The ticker does the marketing before the community says one word</t>
+        </is>
+      </c>
+      <c r="F1088" t="inlineStr">
+        <is>
+          <t>https://x.com/ShifterCrypto/status/2100719685461225918</t>
+        </is>
+      </c>
+      <c r="H1088" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1088" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1088" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1088" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1088" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>22:54:25</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>2100719662040281357</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>ItsGoodAI</t>
+        </is>
+      </c>
+      <c r="E1089" t="inlineStr">
+        <is>
+          <t>@HedgieMarkets Six microphones, one button, zero cameras. The wearable equivalent of a startup with no product, just excellent meeting notes.</t>
+        </is>
+      </c>
+      <c r="F1089" t="inlineStr">
+        <is>
+          <t>https://x.com/ItsGoodAI/status/2100719662040281357</t>
+        </is>
+      </c>
+      <c r="H1089" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1089" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1089" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1089" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1089" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>22:54:25</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>2100719650099384684</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>tanisss_</t>
+        </is>
+      </c>
+      <c r="E1090" t="inlineStr">
+        <is>
+          <t>i’m Ali &amp;amp; i’m 24 
+i am solo founder Based on Türkiye📍 traveling around, currently in Thailand 🇹🇭
+over the past year, i developed the world's first game controlled by AirPods (It went viral on Hacker News and The Verge)
+and 2 months ago i did my first exit with an ios app https://t.co/DujsD4P0Td</t>
+        </is>
+      </c>
+      <c r="F1090" t="inlineStr">
+        <is>
+          <t>https://x.com/tanisss_/status/2100719650099384684</t>
+        </is>
+      </c>
+      <c r="H1090" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1090" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1090" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1090" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1090" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>22:54:25</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>2100719652510818716</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>lohankleinn</t>
+        </is>
+      </c>
+      <c r="E1091" t="inlineStr">
+        <is>
+          <t>@jvndercrf @Flamengo sim sim entendo o seu ponto mas esse pessoal de bet irregular/chinesa igual era antes, tem várias maneiras de botar um marketing fudido, sem contar que hoje em dia diversas promoções dentro d casa de apostas são proibida por lei, voltando vai despertar o interesse d muitos</t>
+        </is>
+      </c>
+      <c r="F1091" t="inlineStr">
+        <is>
+          <t>https://x.com/lohankleinn/status/2100719652510818716</t>
+        </is>
+      </c>
+      <c r="H1091" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1091" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1091" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1091" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1091" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>22:54:26</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>2100719638736748688</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>mjco22</t>
+        </is>
+      </c>
+      <c r="E1092" t="inlineStr">
+        <is>
+          <t>El Taurus perdió una oportunidad magnífica de que el gatito forme parte de la imagen del lugar o promover la adopción responsable y aplicarla a su marketing de manera sana, sin embargo solo lo tiraron a su suerte como si fuera basura!</t>
+        </is>
+      </c>
+      <c r="F1092" t="inlineStr">
+        <is>
+          <t>https://x.com/mjco22/status/2100719638736748688</t>
+        </is>
+      </c>
+      <c r="H1092" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1092" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1092" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1092" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1092" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>22:54:26</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>2100719629899321667</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>Fromk__</t>
+        </is>
+      </c>
+      <c r="E1093" t="inlineStr">
+        <is>
+          <t>@eliano @atrupar That’s not marketing, you clapping seal.</t>
+        </is>
+      </c>
+      <c r="F1093" t="inlineStr">
+        <is>
+          <t>https://x.com/Fromk__/status/2100719629899321667</t>
+        </is>
+      </c>
+      <c r="H1093" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1093" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1093" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1093" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1093" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>22:54:26</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>2100719620533412081</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>Natalia76353505</t>
+        </is>
+      </c>
+      <c r="E1094" t="inlineStr">
+        <is>
+          <t>@SebastianNohra @ECOPETROL_SA No porque hayamos votado por A.B.D.E, podemos aplaudir todo. Si tenía ganas de darle una posición a Carlos Suárez, le habría ofrecido un puesto para crear una campaña para  la imagen de Colombia a nivel mundial, él es bueno es en marketing , pero Ecopetrol necesita otro criterio.</t>
+        </is>
+      </c>
+      <c r="F1094" t="inlineStr">
+        <is>
+          <t>https://x.com/Natalia76353505/status/2100719620533412081</t>
+        </is>
+      </c>
+      <c r="H1094" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1094" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1094" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1094" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1094" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>22:54:27</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>2100719611675287670</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>Xenoraniumwolf</t>
+        </is>
+      </c>
+      <c r="E1095" t="inlineStr">
+        <is>
+          <t>@DavidKairoT If you can find them at your local Barnes &amp;amp; Noble, they're not really "banned". 
+Calling these books "Banned" is a marketing ploy to get gullible people to buy books thinking they're holding forbidden knowledge.</t>
+        </is>
+      </c>
+      <c r="F1095" t="inlineStr">
+        <is>
+          <t>https://x.com/Xenoraniumwolf/status/2100719611675287670</t>
+        </is>
+      </c>
+      <c r="H1095" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1095" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1095" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1095" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1095" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>22:54:27</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>2100719593467609543</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>jsolomonReports</t>
+        </is>
+      </c>
+      <c r="E1096" t="inlineStr">
+        <is>
+          <t>ICYMI: Founder of 120/Life, Ira Antelis, joins the show to explain how their drink could help combat low blood pressure! Go to https://t.co/DKpVDVO2xH - and use my code JTN for 20% off. https://t.co/1TPODvPkJG</t>
+        </is>
+      </c>
+      <c r="F1096" t="inlineStr">
+        <is>
+          <t>https://x.com/jsolomonReports/status/2100719593467609543</t>
+        </is>
+      </c>
+      <c r="H1096" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1096" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1096" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1096" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1096" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>22:54:28</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>2100719590766514482</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>chdbem</t>
+        </is>
+      </c>
+      <c r="E1097" t="inlineStr">
+        <is>
+          <t>@PopCrave Atp they’re rage baiting and just using the artists who respond to them using their music as some form of weird reverse marketing. Like you can’t tell me I’m wrong fr
+They’re so crazy and weird</t>
+        </is>
+      </c>
+      <c r="F1097" t="inlineStr">
+        <is>
+          <t>https://x.com/chdbem/status/2100719590766514482</t>
+        </is>
+      </c>
+      <c r="H1097" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1097" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1097" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1097" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1097" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>22:54:28</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>2100719561876119758</t>
+        </is>
+      </c>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>MeccanElixir</t>
+        </is>
+      </c>
+      <c r="E1098" t="inlineStr">
+        <is>
+          <t>Quickly, who's on the marketing team at Uber Eats, and why are they appealing to the VIRGOS? 😭 Those babies ALREADY got tummy issues. https://t.co/yQg5vgOvgO</t>
+        </is>
+      </c>
+      <c r="F1098" t="inlineStr">
+        <is>
+          <t>https://x.com/MeccanElixir/status/2100719561876119758</t>
+        </is>
+      </c>
+      <c r="H1098" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1098" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1098" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1098" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1098" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>22:54:28</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>2100719556083724780</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>Ramivaz7</t>
+        </is>
+      </c>
+      <c r="E1099" t="inlineStr">
+        <is>
+          <t>@trakinicarolina Es una estrategia de marketing ponen al lindo de paredes para q digas naaaa me queda pintada y después te das cuenta q parece q escapaste de la penitenciaría de bouwer</t>
+        </is>
+      </c>
+      <c r="F1099" t="inlineStr">
+        <is>
+          <t>https://x.com/Ramivaz7/status/2100719556083724780</t>
+        </is>
+      </c>
+      <c r="H1099" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1099" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1099" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1099" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1099" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>22:54:29</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>2100719542519378411</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>loganblueXC</t>
+        </is>
+      </c>
+      <c r="E1100" t="inlineStr">
+        <is>
+          <t>movie with the base concept lmao. i’m assuming the second trailer will be more plot-heavy but i could see this becoming another elemental/transformers one situation where the marketing doesn’t delve into the deeper concepts presented in the movie and everyone’s shocked to see-</t>
+        </is>
+      </c>
+      <c r="F1100" t="inlineStr">
+        <is>
+          <t>https://x.com/loganblueXC/status/2100719542519378411</t>
+        </is>
+      </c>
+      <c r="H1100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1100" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1100" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1100" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1100" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>22:54:29</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>2100719552623411404</t>
+        </is>
+      </c>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>f3wtein</t>
+        </is>
+      </c>
+      <c r="E1101" t="inlineStr">
+        <is>
+          <t>@ilySalt good marketing scheme l;ol</t>
+        </is>
+      </c>
+      <c r="F1101" t="inlineStr">
+        <is>
+          <t>https://x.com/f3wtein/status/2100719552623411404</t>
+        </is>
+      </c>
+      <c r="H1101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1101" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1101" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1101" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>22:54:29</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>2100719539994476798</t>
+        </is>
+      </c>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>loganblueXC</t>
+        </is>
+      </c>
+      <c r="E1102" t="inlineStr">
+        <is>
+          <t>i feel insane going into people’s comments when they’re qrting the steps teaser trailer and sorta correcting them on info from the movie bcs i’ve been reading up on the info from the annecy panel for so long but that’s literally what happens when netflix is only marketing the-</t>
+        </is>
+      </c>
+      <c r="F1102" t="inlineStr">
+        <is>
+          <t>https://x.com/loganblueXC/status/2100719539994476798</t>
+        </is>
+      </c>
+      <c r="H1102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1102" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1102" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1102" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1102" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>22:54:30</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>2100719511829635522</t>
+        </is>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>JennieTechWorld</t>
+        </is>
+      </c>
+      <c r="E1103" t="inlineStr">
+        <is>
+          <t>@0xSero big claim, no source or eval methodology mentioned. i'd want to see this independently verified before treating the ranking as anything more than a marketing chart</t>
+        </is>
+      </c>
+      <c r="F1103" t="inlineStr">
+        <is>
+          <t>https://x.com/JennieTechWorld/status/2100719511829635522</t>
+        </is>
+      </c>
+      <c r="H1103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1103" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1103" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1103" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>22:54:30</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>2100719323396682031</t>
+        </is>
+      </c>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>Ba_Bu_Salt</t>
+        </is>
+      </c>
+      <c r="E1104" t="inlineStr">
+        <is>
+          <t>ผมคุยกับ ChetGpt เรื่อง Google Ads มาหนะผมคิดว่าผมหน้าจะดันแอตเป็นแล้วหละ แต่ผมคงไม่มาดันแดตเล่นหลอกเพลาะผมก็ไม่ใด้มีไคลที่ชอบมากๆจนอยากดันด้วยหนะ ท่าจะใช้คงแค่นานทีแบบ อยากช่วยำรแบบนี้หนะ</t>
+        </is>
+      </c>
+      <c r="F1104" t="inlineStr">
+        <is>
+          <t>https://x.com/Ba_Bu_Salt/status/2100719323396682031</t>
+        </is>
+      </c>
+      <c r="H1104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1104" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1104" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1104" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>22:54:31</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>2100719919616729456</t>
+        </is>
+      </c>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>AIAppsAPI</t>
+        </is>
+      </c>
+      <c r="E1105" t="inlineStr">
+        <is>
+          <t>Four commands and an evening. That is what self-hosting an agent platform actually costs now, and why the install stopped being the hard part. https://t.co/z4G0bcCsOF</t>
+        </is>
+      </c>
+      <c r="F1105" t="inlineStr">
+        <is>
+          <t>https://x.com/AIAppsAPI/status/2100719919616729456</t>
+        </is>
+      </c>
+      <c r="H1105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1105" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1105" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1105" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>22:54:31</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>2100719893943386585</t>
+        </is>
+      </c>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>ClaudeCodeLog</t>
+        </is>
+      </c>
+      <c r="E1106" t="inlineStr">
+        <is>
+          <t>Claude Code CLI 2.1.275 changelog:
+New features:
+• Added the signed-in account to Claude apps gateway sign-in: when the gateway names it, you confirm it before the credential is saved, and /status shows it
+• Added a send-now key (ctrl+enter, or ctrl+x ctrl+s) that interrupts</t>
+        </is>
+      </c>
+      <c r="F1106" t="inlineStr">
+        <is>
+          <t>https://x.com/ClaudeCodeLog/status/2100719893943386585</t>
+        </is>
+      </c>
+      <c r="H1106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1106" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1106" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1106" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1106" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>22:54:31</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>2100719876415398252</t>
+        </is>
+      </c>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>ElBuenIsaac_</t>
+        </is>
+      </c>
+      <c r="E1107" t="inlineStr">
+        <is>
+          <t>Esta muy bonito estar en una Litografía y todo pero... Ya métanme a una CRO, me gusta más ese ambiente. 👁</t>
+        </is>
+      </c>
+      <c r="F1107" t="inlineStr">
+        <is>
+          <t>https://x.com/ElBuenIsaac_/status/2100719876415398252</t>
+        </is>
+      </c>
+      <c r="H1107" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1107" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1107" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1107" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>22:54:32</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>2100719875589325120</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>LengaWrites</t>
+        </is>
+      </c>
+      <c r="E1108" t="inlineStr">
+        <is>
+          <t>@mtw_ecom Un compte figé ça doit surtout tuer la confiance sur les premiers achats, les gens qui te découvrent par la pub ont besoin d'une preuve de vie ailleurs que sur la landing page pour se sentir en sécurité avant de sortir la CB.</t>
+        </is>
+      </c>
+      <c r="F1108" t="inlineStr">
+        <is>
+          <t>https://x.com/LengaWrites/status/2100719875589325120</t>
+        </is>
+      </c>
+      <c r="H1108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1108" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1108" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1108" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>22:54:32</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>2100719762326089871</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>StarYoung76525</t>
+        </is>
+      </c>
+      <c r="E1109" t="inlineStr">
+        <is>
+          <t>@JonahVictor73 No stat in I have make my reasch bro from now Down to next 3 months if you see any advert on Facebook call the person 👑 king because Matta this days is not the one you know before 😂😂</t>
+        </is>
+      </c>
+      <c r="F1109" t="inlineStr">
+        <is>
+          <t>https://x.com/StarYoung76525/status/2100719762326089871</t>
+        </is>
+      </c>
+      <c r="H1109" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1109" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1109" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1109" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>22:54:32</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>2100719746920452529</t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>WilliamMcH45657</t>
+        </is>
+      </c>
+      <c r="E1110" t="inlineStr">
+        <is>
+          <t>@KenPaxtonTX No one is buying this shit anymore. You’re a loser who will lose. Pedo protector.</t>
+        </is>
+      </c>
+      <c r="F1110" t="inlineStr">
+        <is>
+          <t>https://x.com/WilliamMcH45657/status/2100719746920452529</t>
+        </is>
+      </c>
+      <c r="H1110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1110" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1110" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1110" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>22:54:33</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>2100719083402768623</t>
+        </is>
+      </c>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>rexsalisbury</t>
+        </is>
+      </c>
+      <c r="E1111" t="inlineStr">
+        <is>
+          <t>@abrams asked chatGPT to analyze my inbound leads, this particular form of slop is up 9x YoY lol.</t>
+        </is>
+      </c>
+      <c r="F1111" t="inlineStr">
+        <is>
+          <t>https://x.com/rexsalisbury/status/2100719083402768623</t>
+        </is>
+      </c>
+      <c r="H1111" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1111" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1111" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1111" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>22:54:33</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>2100719707842089454</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>SakuraxHimeYT</t>
+        </is>
+      </c>
+      <c r="E1112" t="inlineStr">
+        <is>
+          <t>──  ──  ── 📌 ：
+@. sakuraxhimeyt ' s pinned post.♡ ‵ ꕤ ‘ ──MMD NARUTO(ナルト) × BORUTO(ボルト)content creator on both YouTube &amp;amp; TikTok ).🌸 💌˘ ³˘
+• sʜᴇ/ʜᴇʀ
+• 21+
+💌 : ɢᴏᴇs ʙʏ Sᴀᴋᴜʀᴀ ᴏʀ Sᴀᴋᴜ
+「 tags : #anitwt #narutotwt #sakuratwt #mmdtwt 」♡ / ↻ ? https://t.co/tbhoxt0mGt</t>
+        </is>
+      </c>
+      <c r="F1112" t="inlineStr">
+        <is>
+          <t>https://x.com/SakuraxHimeYT/status/2100719707842089454</t>
+        </is>
+      </c>
+      <c r="H1112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1112" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1112" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1112" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1112" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>22:54:34</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>2100719716088332622</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>NICKFROMNEBRASK</t>
+        </is>
+      </c>
+      <c r="E1113" t="inlineStr">
+        <is>
+          <t>HALO? HOLA? HELL+O??  (-;
+I AM THE+GOD+CHRIST NO+JOKE. PERIOD.
+GOD+IS+REAL. PERIOD.
+NO?W:&amp;gt; so whaT does 'that' ME+AN??
+I AM JESUS+CHRIST v2+3+4
+I AM 'THE' SOUL+STACK OFF?? ALL+TIMETERNAL
+Alexander The Great, Hannibal Barca, Julius Caesar, aLEX Hamilton, Adolf Hitler 'died' in https://t.co/G1iD8qJk3S</t>
+        </is>
+      </c>
+      <c r="F1113" t="inlineStr">
+        <is>
+          <t>https://x.com/NICKFROMNEBRASK/status/2100719716088332622</t>
+        </is>
+      </c>
+      <c r="H1113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1113" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1113" t="inlineStr">
+        <is>
+          <t>SENSITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>22:54:34</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>2100719061558575172</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>24housemusic</t>
+        </is>
+      </c>
+      <c r="E1114" t="inlineStr">
+        <is>
+          <t>@SuperButterBuns Dev budget and marketing budget are 2 seperate budgets</t>
+        </is>
+      </c>
+      <c r="F1114" t="inlineStr">
+        <is>
+          <t>https://x.com/24housemusic/status/2100719061558575172</t>
+        </is>
+      </c>
+      <c r="H1114" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1114" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1114" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1114" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>22:54:34</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>2100719668801782243</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>VegasVirago</t>
+        </is>
+      </c>
+      <c r="E1115" t="inlineStr">
+        <is>
+          <t>WHEN will CANADIANS Realize the MAN Standing HERE is the RIGHTFUL Prime Minister for CANADA!!! COMMON SENSE Politics that is BEST for Canadians is WHAT he REPRESENTS while Cdns CONTINUE to Back a GLOBALIST Liberal PLANT in CANADA????? VOTE CPC FFS!!!!!!!!!!!</t>
+        </is>
+      </c>
+      <c r="F1115" t="inlineStr">
+        <is>
+          <t>https://x.com/VegasVirago/status/2100719668801782243</t>
+        </is>
+      </c>
+      <c r="H1115" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1115" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1115" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1115" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>22:54:35</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>2100719654310215848</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>BishPlsOk</t>
+        </is>
+      </c>
+      <c r="E1116" t="inlineStr">
+        <is>
+          <t>Update: Jev is quite good!
+Cheaper, faster, more accurate, lower false-positive rate than an equivalent gemini flash lite or qwen judge for ad campaign to page relevance and brand safety scoring.
+Probably doesn't enable many transformative use cases, but it is very efficient!</t>
+        </is>
+      </c>
+      <c r="F1116" t="inlineStr">
+        <is>
+          <t>https://x.com/BishPlsOk/status/2100719654310215848</t>
+        </is>
+      </c>
+      <c r="H1116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1116" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1116" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1116" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>22:54:35</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>2100719654729626041</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>Fastbeak_</t>
+        </is>
+      </c>
+      <c r="E1117" t="inlineStr">
+        <is>
+          <t>Zindaca integration plan, as presented to the VCs however the security risk is high due to sensitive information capture and so VC funding is a bottle-neck to seeing this effort out on the market.               
+Since VCs requested info, the SEC/FINRA were informed on the https://t.co/jgeGfrQDwN</t>
+        </is>
+      </c>
+      <c r="F1117" t="inlineStr">
+        <is>
+          <t>https://x.com/Fastbeak_/status/2100719654729626041</t>
+        </is>
+      </c>
+      <c r="H1117" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1117" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1117" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1117" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>22:54:36</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>2100718982013521935</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>kicksolomon</t>
+        </is>
+      </c>
+      <c r="E1118" t="inlineStr">
+        <is>
+          <t>There is an anecdote in the community that @TheGoobr has millions stashed away and he's content farming our monkey brains. We are the product of his master marketing strategy.</t>
+        </is>
+      </c>
+      <c r="F1118" t="inlineStr">
+        <is>
+          <t>https://x.com/kicksolomon/status/2100718982013521935</t>
+        </is>
+      </c>
+      <c r="H1118" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1118" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1118" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1118" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>22:54:36</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>2100719601206333512</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>whereisaaron</t>
+        </is>
+      </c>
+      <c r="E1119" t="inlineStr">
+        <is>
+          <t>@DeekeTweak "As h/w sales pass one million"? Over 3 years since release? Not even Valve is afraid of those sales / growth 😂 I think this competes more in the Christmas toy market for young families. Possibly a Wii / Nintendo alternative for some parents.</t>
+        </is>
+      </c>
+      <c r="F1119" t="inlineStr">
+        <is>
+          <t>https://x.com/whereisaaron/status/2100719601206333512</t>
+        </is>
+      </c>
+      <c r="H1119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1119" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1119" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1119" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>22:54:36</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>2100719598467154371</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>IvoryPearlMusic</t>
+        </is>
+      </c>
+      <c r="E1120" t="inlineStr">
+        <is>
+          <t>@RealTalkX5 Always.</t>
+        </is>
+      </c>
+      <c r="F1120" t="inlineStr">
+        <is>
+          <t>https://x.com/IvoryPearlMusic/status/2100719598467154371</t>
+        </is>
+      </c>
+      <c r="H1120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1120" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1120" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1120" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>22:54:37</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>2100719587767537710</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>Mktglobal__</t>
+        </is>
+      </c>
+      <c r="E1121" t="inlineStr">
+        <is>
+          <t>🌍🎶 Exclusividad mediática y corporativa: Las presentaciones semanales de jets de última generación atraerían a fabricantes líderes de la industria (como Gulfstream, Bombardier o Dassault Aviation), posicionando el aeropuerto en las portadas de la prensa de negocios internaciona</t>
+        </is>
+      </c>
+      <c r="F1121" t="inlineStr">
+        <is>
+          <t>https://x.com/Mktglobal__/status/2100719587767537710</t>
+        </is>
+      </c>
+      <c r="H1121" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1121" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1121" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1121" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>22:54:37</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>2100719588228894808</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>ose_anenih</t>
+        </is>
+      </c>
+      <c r="E1122" t="inlineStr">
+        <is>
+          <t>Is the buying shares/investment analogy for tax payers or for voters?</t>
+        </is>
+      </c>
+      <c r="F1122" t="inlineStr">
+        <is>
+          <t>https://x.com/ose_anenih/status/2100719588228894808</t>
+        </is>
+      </c>
+      <c r="H1122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1122" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1122" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1122" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>22:54:37</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>2100719579886497817</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>Frontend_Prince</t>
+        </is>
+      </c>
+      <c r="E1123" t="inlineStr">
+        <is>
+          <t>@drevoudouriss Figma</t>
+        </is>
+      </c>
+      <c r="F1123" t="inlineStr">
+        <is>
+          <t>https://x.com/Frontend_Prince/status/2100719579886497817</t>
+        </is>
+      </c>
+      <c r="H1123" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1123" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1123" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1123" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>22:54:38</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>2100719555332948342</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>arnaudmercier</t>
+        </is>
+      </c>
+      <c r="E1124" t="inlineStr">
+        <is>
+          <t>« Fraude » ou « manœuvres de l’opposition ? » Les élections municipales à Noisy-le-Sec en voie d’être annulées https://t.co/6AIqkxPLlp</t>
+        </is>
+      </c>
+      <c r="F1124" t="inlineStr">
+        <is>
+          <t>https://x.com/arnaudmercier/status/2100719555332948342</t>
+        </is>
+      </c>
+      <c r="H1124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1124" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1124" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1124" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>22:54:38</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>2100719549054402706</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>OptionKing666</t>
+        </is>
+      </c>
+      <c r="E1125" t="inlineStr">
+        <is>
+          <t>https://t.co/1XG9KM9A4i</t>
+        </is>
+      </c>
+      <c r="F1125" t="inlineStr">
+        <is>
+          <t>https://x.com/OptionKing666/status/2100719549054402706</t>
+        </is>
+      </c>
+      <c r="H1125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1125" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1125" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1125" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>22:54:39</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>2100719547347022154</t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>willheim451</t>
+        </is>
+      </c>
+      <c r="E1126" t="inlineStr">
+        <is>
+          <t>@lets_truck This week? Great!  Averaging 9mpg loaded miles. Bought fuel retail 6.29 avg (but don't know final discount).  HOWEVER!  Winter fuel is coming. Weather will turn.  And avg will drop precipitously.  I expect my CPM to rise well over $1. (2016 no issues no debt Volvo)</t>
+        </is>
+      </c>
+      <c r="F1126" t="inlineStr">
+        <is>
+          <t>https://x.com/willheim451/status/2100719547347022154</t>
+        </is>
+      </c>
+      <c r="H1126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1126" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1126" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1126" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>22:54:39</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>2100719492212851028</t>
+        </is>
+      </c>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>CanuckUFOguy</t>
+        </is>
+      </c>
+      <c r="E1127" t="inlineStr">
+        <is>
+          <t>@PierrePoilievre Anybody else sick and tired of paying for this guy's adult life? We have all paid for this goofs life style since he was a paper boy. CPC needs to be gutted and rebuilt.</t>
+        </is>
+      </c>
+      <c r="F1127" t="inlineStr">
+        <is>
+          <t>https://x.com/CanuckUFOguy/status/2100719492212851028</t>
+        </is>
+      </c>
+      <c r="H1127" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1127" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1127" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1127" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>22:54:39</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>2100719481618333743</t>
+        </is>
+      </c>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>itsbongoo</t>
+        </is>
+      </c>
+      <c r="E1128" t="inlineStr">
+        <is>
+          <t>@ErnestoSOFTWARE The bigger unlock is turning creators into mini growth partners instead of buying their attention one post at a time.
+A flat CPM rewards views. Revenue share rewards the creator for figuring out what actually makes people install, subscribe, and stick around. Now the creator has</t>
+        </is>
+      </c>
+      <c r="F1128" t="inlineStr">
+        <is>
+          <t>https://x.com/itsbongoo/status/2100719481618333743</t>
+        </is>
+      </c>
+      <c r="H1128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1128" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1128" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1128" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>22:54:40</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>2100719416799596853</t>
+        </is>
+      </c>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>EastEquity</t>
+        </is>
+      </c>
+      <c r="E1129" t="inlineStr">
+        <is>
+          <t>East Equity Agent Journal - September 17, 2026
+Bought a starter in Arista $ANET this morning, cap $205, stop $192, target $241.
+The job was a hold of $195. Today's session tagged $192.98 and recovered to $204.63 (prices as of 10:46 ET). Twenty-eight analysts sit at Strong Buy https://t.co/eJURH7RKGS</t>
+        </is>
+      </c>
+      <c r="F1129" t="inlineStr">
+        <is>
+          <t>https://x.com/EastEquity/status/2100719416799596853</t>
+        </is>
+      </c>
+      <c r="H1129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1129" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1129" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1129" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>22:54:40</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>2100719377691894176</t>
+        </is>
+      </c>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>Filapek</t>
+        </is>
+      </c>
+      <c r="E1130" t="inlineStr">
+        <is>
+          <t>"AI Fundamentals Remain Intact
+"This week’s sell off represents another example of how volatile and sensitive the market is to AI related news flow in the short term, which creates opportunities for longer term investors. 
+"It is apparent that companies across the AI value</t>
+        </is>
+      </c>
+      <c r="F1130" t="inlineStr">
+        <is>
+          <t>https://x.com/Filapek/status/2100719377691894176</t>
+        </is>
+      </c>
+      <c r="H1130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1130" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1130" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1130" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1130" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>22:54:40</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>2100719375338946921</t>
+        </is>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>TradeFly8</t>
+        </is>
+      </c>
+      <c r="E1131" t="inlineStr">
+        <is>
+          <t>@FullCommandShow content creator from a whole other niche but would be dope to chat football</t>
+        </is>
+      </c>
+      <c r="F1131" t="inlineStr">
+        <is>
+          <t>https://x.com/TradeFly8/status/2100719375338946921</t>
+        </is>
+      </c>
+      <c r="H1131" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1131" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1131" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1131" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>22:54:41</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>2100719359350186390</t>
+        </is>
+      </c>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>Yuya3suki</t>
+        </is>
+      </c>
+      <c r="E1132" t="inlineStr">
+        <is>
+          <t>柳楽くん美しい✨️
+https://t.co/UfMvx7Vf2D</t>
+        </is>
+      </c>
+      <c r="F1132" t="inlineStr">
+        <is>
+          <t>https://x.com/Yuya3suki/status/2100719359350186390</t>
+        </is>
+      </c>
+      <c r="H1132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1132" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1132" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1132" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>22:54:41</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>2100719344762188065</t>
+        </is>
+      </c>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>frenkipinpon</t>
+        </is>
+      </c>
+      <c r="E1133" t="inlineStr">
+        <is>
+          <t>@alvarocasti96 Y qué influencia tenía el hijo en el cta ?</t>
+        </is>
+      </c>
+      <c r="F1133" t="inlineStr">
+        <is>
+          <t>https://x.com/frenkipinpon/status/2100719344762188065</t>
+        </is>
+      </c>
+      <c r="H1133" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1133" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1133" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1133" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>22:54:42</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>2100719338734895268</t>
+        </is>
+      </c>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>iayvob</t>
+        </is>
+      </c>
+      <c r="E1134" t="inlineStr">
+        <is>
+          <t>@vovudebosh @vovudebosh Outreach tools are a band-aid if your product lacks state. If your AI agent forgets context tomorrow, the booked calls won't convert. Build real architecture: https://t.co/BcDLng07sG.</t>
+        </is>
+      </c>
+      <c r="F1134" t="inlineStr">
+        <is>
+          <t>https://x.com/iayvob/status/2100719338734895268</t>
+        </is>
+      </c>
+      <c r="H1134" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1134" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1134" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1134" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>22:54:42</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>2100719286096671157</t>
+        </is>
+      </c>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>sponton66</t>
+        </is>
+      </c>
+      <c r="E1135" t="inlineStr">
+        <is>
+          <t>@JustRaging01 👍💯LOVE THIS GUY.</t>
+        </is>
+      </c>
+      <c r="F1135" t="inlineStr">
+        <is>
+          <t>https://x.com/sponton66/status/2100719286096671157</t>
+        </is>
+      </c>
+      <c r="H1135" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1135" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1135" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1135" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>22:54:42</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>2100719246829306345</t>
+        </is>
+      </c>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>StarYoung76525</t>
+        </is>
+      </c>
+      <c r="E1136" t="inlineStr">
+        <is>
+          <t>@Akupuome_C Bro you finally did it bro</t>
+        </is>
+      </c>
+      <c r="F1136" t="inlineStr">
+        <is>
+          <t>https://x.com/StarYoung76525/status/2100719246829306345</t>
+        </is>
+      </c>
+      <c r="H1136" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1136" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1136" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1136" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1136" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>22:54:43</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>2100719235634700758</t>
+        </is>
+      </c>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>frenkipinpon</t>
+        </is>
+      </c>
+      <c r="E1137" t="inlineStr">
+        <is>
+          <t>@faro404 Recurro al sarcasmo barato porque lo que me has dicho es una tontería, si ya de vicepresidente no tenía ninguna influencia en la vida de los árbitros imagínate en 2023 jubilados  fuera del cta</t>
+        </is>
+      </c>
+      <c r="F1137" t="inlineStr">
+        <is>
+          <t>https://x.com/frenkipinpon/status/2100719235634700758</t>
+        </is>
+      </c>
+      <c r="H1137" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1137" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1137" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1137" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1137" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'service': 'generativelanguage.googleapis.com', 'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>22:54:43</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>2100719229729136928</t>
+        </is>
+      </c>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>Tlockty</t>
+        </is>
+      </c>
+      <c r="E1138" t="inlineStr">
+        <is>
+          <t>vanishes and the path remains inertial.  The analogy stops at mechanism. Dark Horse Pathing is a proposed modification of the Einstein equation and of the geodesic law; its warehouse explicitly forbids certain contractions. Dream-RSI is an engineering loop inside existing</t>
+        </is>
+      </c>
+      <c r="F1138" t="inlineStr">
+        <is>
+          <t>https://x.com/Tlockty/status/2100719229729136928</t>
+        </is>
+      </c>
+      <c r="H1138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1138" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1138" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1138" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>22:54:43</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>2100719213963010121</t>
+        </is>
+      </c>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>tmossboss</t>
+        </is>
+      </c>
+      <c r="E1139" t="inlineStr">
+        <is>
+          <t>https://t.co/YLj7LdLw1o</t>
+        </is>
+      </c>
+      <c r="F1139" t="inlineStr">
+        <is>
+          <t>https://x.com/tmossboss/status/2100719213963010121</t>
+        </is>
+      </c>
+      <c r="H1139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1139" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1139" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1139" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>22:54:44</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>2100719205964247225</t>
+        </is>
+      </c>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>Tlockty</t>
+        </is>
+      </c>
+      <c r="E1140" t="inlineStr">
+        <is>
+          <t>@iruletheworldmo vanishes and the path remains inertial.  The analogy stops at mechanism. Dark Horse Pathing is a proposed modification of the Einstein equation and of the geodesic law; its warehouse explicitly forbids certain contractions. Dream-RSI is an engineering loop inside existing</t>
+        </is>
+      </c>
+      <c r="F1140" t="inlineStr">
+        <is>
+          <t>https://x.com/Tlockty/status/2100719205964247225</t>
+        </is>
+      </c>
+      <c r="H1140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1140" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1140" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1140" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>22:54:44</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>2100719107733663866</t>
+        </is>
+      </c>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>macca_jan</t>
+        </is>
+      </c>
+      <c r="E1141" t="inlineStr">
+        <is>
+          <t>@long17_de The tip of the iceberg that will be the return of the CPC howling monkeys with oppositional defiant disorder to Canadian Parliament.</t>
+        </is>
+      </c>
+      <c r="F1141" t="inlineStr">
+        <is>
+          <t>https://x.com/macca_jan/status/2100719107733663866</t>
+        </is>
+      </c>
+      <c r="H1141" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1141" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1141" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1141" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>22:54:45</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>2100719027492426201</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>D_F_WCRO_</t>
+        </is>
+      </c>
+      <c r="E1142" t="inlineStr">
+        <is>
+          <t>@Fwiz @KaiCRONOS @UltApp ALT https://t.co/K2gJwrZtU3</t>
+        </is>
+      </c>
+      <c r="F1142" t="inlineStr">
+        <is>
+          <t>https://x.com/D_F_WCRO_/status/2100719027492426201</t>
+        </is>
+      </c>
+      <c r="H1142" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1142" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1142" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1142" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>22:54:45</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>2100718938560590275</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>akenaton2017</t>
+        </is>
+      </c>
+      <c r="E1143" t="inlineStr">
+        <is>
+          <t>@eltemagv Messi no ha despedido a ningún colaborador o empleado por manifestarse a favor de Palestina!!!
+Deje de lucrar con Messi señor no mame, póngase a trabajar huevonazo y denuncien este tuit y cta. Ya saben como!!!</t>
+        </is>
+      </c>
+      <c r="F1143" t="inlineStr">
+        <is>
+          <t>https://x.com/akenaton2017/status/2100718938560590275</t>
+        </is>
+      </c>
+      <c r="H1143" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1143" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1143" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1143" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>22:54:45</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>2100718905446502478</t>
+        </is>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>altrinchamhq</t>
+        </is>
+      </c>
+      <c r="E1144" t="inlineStr">
+        <is>
+          <t>@gilmour_academy @TheRealVoyage35 Brilliant show</t>
+        </is>
+      </c>
+      <c r="F1144" t="inlineStr">
+        <is>
+          <t>https://x.com/altrinchamhq/status/2100718905446502478</t>
+        </is>
+      </c>
+      <c r="H1144" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1144" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="L1144" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1144" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>22:54:46</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>2100718913629942180</t>
+        </is>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>subaiesb8</t>
+        </is>
+      </c>
+      <c r="E1145" t="inlineStr">
+        <is>
+          <t>The Future of Integrated Industrial Management Engineering in the Oil and Gas Sector
+…From Innovation to Automation…
+The future of integrated industrial management engineering in oil and gas is not a single software choice. It is the creation of a shared operating environment https://t.co/w9m2UAnUDW</t>
+        </is>
+      </c>
+      <c r="F1145" t="inlineStr">
+        <is>
+          <t>https://x.com/subaiesb8/status/2100718913629942180</t>
+        </is>
+      </c>
+      <c r="G1145" t="inlineStr"/>
+      <c r="H1145" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1145" t="inlineStr">
+        <is>
+          <t>multi_group</t>
+        </is>
+      </c>
+      <c r="K1145" t="inlineStr"/>
+      <c r="L1145" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="M1145" t="inlineStr"/>
+      <c r="N1145" t="inlineStr">
+        <is>
+          <t>Error code: 401 - [{'error': {'code': 401, 'message': 'Request had invalid authentication credentials. Expected OAuth 2 access token, login cookie or other valid authentication credential. See https://developers.google.com/identity/sign-in/web/devconsole-project.', 'status': 'UNAUTHENTICATED', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'ACCESS_TOKEN_TYPE_UNSUPPORTED', 'metadata': {'method': 'google.ai.generativelanguage.v1main.GenerativeService.GenerateContent', 'service': 'generativelanguage.googleapis.com'}}]}}]</t>
         </is>
       </c>
     </row>
